--- a/docs/美術清單.xlsx
+++ b/docs/美術清單.xlsx
@@ -36,7 +36,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'F 介面圖示'!$A$4:$H$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'G 插圖與上架'!$A$4:$F$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'H 地圖'!$A$4:$F$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'現有素材'!$A$4:$E$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'現有素材'!$A$4:$E$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'交件檢查'!$A$4:$C$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2827,7 +2827,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="56" customWidth="1" min="1" max="1"/>
@@ -2891,11 +2891,11 @@
       </c>
       <c r="C5" s="22" t="inlineStr">
         <is>
-          <t>512×512</t>
+          <t>160×160</t>
         </is>
       </c>
       <c r="D5" s="24" t="n">
-        <v>37.9</v>
+        <v>8</v>
       </c>
       <c r="E5" s="22" t="inlineStr">
         <is>
@@ -2916,11 +2916,11 @@
       </c>
       <c r="C6" s="23" t="inlineStr">
         <is>
-          <t>512×512</t>
+          <t>160×160</t>
         </is>
       </c>
       <c r="D6" s="27" t="n">
-        <v>28.2</v>
+        <v>6</v>
       </c>
       <c r="E6" s="23" t="inlineStr">
         <is>
@@ -3031,71 +3031,71 @@
     <row r="11">
       <c r="A11" s="22" t="inlineStr">
         <is>
-          <t>src/assets/scenes/focus-night.webp</t>
+          <t>src/assets/scenes/forest.webp</t>
         </is>
       </c>
       <c r="B11" s="22" t="inlineStr">
         <is>
-          <t>原本的專注畫面夜景</t>
+          <t>我的小島：森林</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
         <is>
-          <t>853×1844</t>
+          <t>1167×1347</t>
         </is>
       </c>
       <c r="D11" s="24" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="E11" s="22" t="inlineStr">
         <is>
-          <t>停用（專注畫面改成望遠鏡）</t>
+          <t>使用中（暫代）</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="23" t="inlineStr">
         <is>
-          <t>src/assets/scenes/forest.webp</t>
+          <t>src/assets/scenes/world-map.webp</t>
         </is>
       </c>
       <c r="B12" s="23" t="inlineStr">
         <is>
-          <t>我的小島：森林</t>
+          <t>區域切換的世界地圖</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
         <is>
-          <t>1167×1347</t>
+          <t>1200×572</t>
         </is>
       </c>
       <c r="D12" s="27" t="n">
-        <v>105</v>
+        <v>89.5</v>
       </c>
       <c r="E12" s="23" t="inlineStr">
         <is>
-          <t>使用中（暫代）</t>
+          <t>使用中</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="22" t="inlineStr">
         <is>
-          <t>src/assets/scenes/world-map.webp</t>
+          <t>src/assets/scenes/map-tw.webp</t>
         </is>
       </c>
       <c r="B13" s="22" t="inlineStr">
         <is>
-          <t>區域切換的世界地圖</t>
+          <t>台灣 3D 地圖貼圖</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
         <is>
-          <t>1816×866</t>
+          <t>1024×1536</t>
         </is>
       </c>
       <c r="D13" s="24" t="n">
-        <v>214.4</v>
+        <v>101.4</v>
       </c>
       <c r="E13" s="22" t="inlineStr">
         <is>
@@ -3106,21 +3106,21 @@
     <row r="14">
       <c r="A14" s="23" t="inlineStr">
         <is>
-          <t>src/assets/scenes/map-tw.webp</t>
+          <t>src/assets/scenes/map-jp.webp</t>
         </is>
       </c>
       <c r="B14" s="23" t="inlineStr">
         <is>
-          <t>台灣 3D 地圖貼圖</t>
+          <t>日本 3D 地圖貼圖</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
         <is>
-          <t>1024×1536</t>
+          <t>1254×1254</t>
         </is>
       </c>
       <c r="D14" s="27" t="n">
-        <v>101.4</v>
+        <v>57</v>
       </c>
       <c r="E14" s="23" t="inlineStr">
         <is>
@@ -3131,21 +3131,21 @@
     <row r="15">
       <c r="A15" s="22" t="inlineStr">
         <is>
-          <t>src/assets/scenes/map-jp.webp</t>
+          <t>src/assets/animals/leopard_cat.webp</t>
         </is>
       </c>
       <c r="B15" s="22" t="inlineStr">
         <is>
-          <t>日本 3D 地圖貼圖</t>
+          <t>石虎成年主圖（靜態）</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
         <is>
-          <t>1254×1254</t>
+          <t>512×512</t>
         </is>
       </c>
       <c r="D15" s="24" t="n">
-        <v>57</v>
+        <v>29.5</v>
       </c>
       <c r="E15" s="22" t="inlineStr">
         <is>
@@ -3156,12 +3156,12 @@
     <row r="16">
       <c r="A16" s="23" t="inlineStr">
         <is>
-          <t>src/assets/animals/leopard_cat.webp</t>
+          <t>public/icon-512.png</t>
         </is>
       </c>
       <c r="B16" s="23" t="inlineStr">
         <is>
-          <t>石虎成年主圖（靜態）</t>
+          <t>App 圖示（舊）</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
@@ -3170,18 +3170,18 @@
         </is>
       </c>
       <c r="D16" s="27" t="n">
-        <v>29.5</v>
+        <v>11.3</v>
       </c>
       <c r="E16" s="23" t="inlineStr">
         <is>
-          <t>使用中</t>
+          <t>暫代</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="22" t="inlineStr">
         <is>
-          <t>public/icon-512.png</t>
+          <t>public/icon-192.png</t>
         </is>
       </c>
       <c r="B17" s="22" t="inlineStr">
@@ -3191,11 +3191,11 @@
       </c>
       <c r="C17" s="22" t="inlineStr">
         <is>
-          <t>512×512</t>
+          <t>192×192</t>
         </is>
       </c>
       <c r="D17" s="24" t="n">
-        <v>11.3</v>
+        <v>3.9</v>
       </c>
       <c r="E17" s="22" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
     <row r="18">
       <c r="A18" s="23" t="inlineStr">
         <is>
-          <t>public/icon-192.png</t>
+          <t>public/apple-touch-icon.png</t>
         </is>
       </c>
       <c r="B18" s="23" t="inlineStr">
@@ -3216,11 +3216,11 @@
       </c>
       <c r="C18" s="23" t="inlineStr">
         <is>
-          <t>192×192</t>
+          <t>180×180</t>
         </is>
       </c>
       <c r="D18" s="27" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="E18" s="23" t="inlineStr">
         <is>
@@ -3231,55 +3231,30 @@
     <row r="19">
       <c r="A19" s="22" t="inlineStr">
         <is>
-          <t>public/apple-touch-icon.png</t>
+          <t>src/assets/animals/mesh/leopard_cat/（12 個圖層）</t>
         </is>
       </c>
       <c r="B19" s="22" t="inlineStr">
         <is>
-          <t>App 圖示（舊）</t>
+          <t>石虎網格動態的圖層</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
         <is>
-          <t>180×180</t>
+          <t>半尺寸</t>
         </is>
       </c>
       <c r="D19" s="24" t="n">
-        <v>3.4</v>
+        <v>67.5</v>
       </c>
       <c r="E19" s="22" t="inlineStr">
         <is>
-          <t>暫代</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="23" t="inlineStr">
-        <is>
-          <t>src/assets/animals/mesh/leopard_cat/（12 個圖層）</t>
-        </is>
-      </c>
-      <c r="B20" s="23" t="inlineStr">
-        <is>
-          <t>石虎網格動態的圖層</t>
-        </is>
-      </c>
-      <c r="C20" s="23" t="inlineStr">
-        <is>
-          <t>半尺寸</t>
-        </is>
-      </c>
-      <c r="D20" s="27" t="n">
-        <v>67.5</v>
-      </c>
-      <c r="E20" s="23" t="inlineStr">
-        <is>
           <t>製作中（另一個對話接入中）</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:E20"/>
+  <autoFilter ref="A4:E19"/>
   <mergeCells count="1">
     <mergeCell ref="A2:E2"/>
   </mergeCells>

--- a/docs/美術清單.xlsx
+++ b/docs/美術清單.xlsx
@@ -8618,7 +8618,7 @@
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>專注時上方圓形鏡片在橫向全景上左右搜尋、推近拉遠，動物中段才在遠方出現、越來越近。全景照「棲地」共用，不照國家分。晨昏先用白天版調色（選配列）。規格見 C-1。</t>
+          <t>專注時上方圓形鏡片在橫向全景上左右搜尋、推近拉遠，動物專注一小段時間後在遠方出現、越來越近。全景照「棲地」共用，不照國家分。晨昏先用白天版調色（選配列）。規格見 C-1。</t>
         </is>
       </c>
     </row>

--- a/docs/美術清單.xlsx
+++ b/docs/美術清單.xlsx
@@ -9,35 +9,37 @@
   <sheets>
     <sheet name="總覽" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="共通規格" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="A 動物主圖" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="B 動物動態" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="B-1 體型模板" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="C 望遠鏡全景" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="C-1 全景規格" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="D 小島場景" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="D-1 場景規格" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="E 小道具" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="F 介面圖示" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="G 插圖與上架" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="H 地圖" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="現有素材" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="交件檢查" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="動物尺寸" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="A 動物主圖" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="B 動物動態" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="B-1 體型模板" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="C 望遠鏡全景" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="C-1 全景規格" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="D 小島場景" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="D-1 場景規格" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="E 小道具" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="F 介面圖示" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="G 插圖與上架" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="H 地圖" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="現有素材" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="交件檢查" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'共通規格'!$A$4:$C$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'A 動物主圖'!$A$4:$R$33</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'B 動物動態'!$A$4:$M$33</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'B-1 體型模板'!$A$4:$H$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'C 望遠鏡全景'!$A$4:$J$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'C-1 全景規格'!$A$4:$C$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'D 小島場景'!$A$4:$J$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'D-1 場景規格'!$A$4:$C$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'E 小道具'!$A$4:$G$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'F 介面圖示'!$A$4:$H$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'G 插圖與上架'!$A$4:$F$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'H 地圖'!$A$4:$F$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'現有素材'!$A$4:$E$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'交件檢查'!$A$4:$C$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'共通規格'!$A$4:$C$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'動物尺寸'!$A$4:$E$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'A 動物主圖'!$A$4:$R$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'B 動物動態'!$A$4:$M$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'B-1 體型模板'!$A$4:$H$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'C 望遠鏡全景'!$A$4:$J$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'C-1 全景規格'!$A$4:$C$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'D 小島場景'!$A$4:$J$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'D-1 場景規格'!$A$4:$C$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'E 小道具'!$A$4:$G$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'F 介面圖示'!$A$4:$H$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'G 插圖與上架'!$A$4:$F$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'H 地圖'!$A$4:$F$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'現有素材'!$A$4:$E$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'交件檢查'!$A$4:$C$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -46,7 +48,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -74,6 +76,12 @@
     <font>
       <name val="Microsoft JhengHei"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft JhengHei"/>
+      <b val="1"/>
+      <color rgb="004A6A42"/>
+      <sz val="12"/>
     </font>
     <font>
       <name val="Microsoft JhengHei"/>
@@ -192,34 +200,34 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -227,13 +235,18 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1159,6 +1172,176 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="56" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="21" t="inlineStr">
+        <is>
+          <t>D-1. 小島場景規格</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="2" t="inlineStr"/>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>規格</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>說明</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="22" t="inlineStr">
+        <is>
+          <t>方向</t>
+        </is>
+      </c>
+      <c r="B5" s="22" t="inlineStr">
+        <is>
+          <t>2D 分層插畫（不做 3D 模型）</t>
+        </is>
+      </c>
+      <c r="C5" s="22" t="inlineStr">
+        <is>
+          <t>最省電、最適合直式手機、也最容易用 AI 輔助。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="23" t="inlineStr">
+        <is>
+          <t>畫布</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>底圖與每張疊圖同一個畫布大小、完全對齊</t>
+        </is>
+      </c>
+      <c r="C6" s="23" t="inlineStr">
+        <is>
+          <t>目前底圖 1167×1347；正式版建議 1440×1664。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="22" t="inlineStr">
+        <is>
+          <t>疊圖</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>每個工程一張去背圖，裡面拆成 2～4 個物件圖層</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>投入 25／50／75／100% 時依序出現（例如小屋：地板 → 牆 → 屋頂 → 亮燈）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="23" t="inlineStr">
+        <is>
+          <t>動物位置</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>前景留 6 個站位不被樹擋住</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="inlineStr">
+        <is>
+          <t>程式座標見 src/pages/Island.tsx 的 SPOTS。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="22" t="inlineStr">
+        <is>
+          <t>地面</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>從枯黃慢慢轉綠：可給 3 張地面色層（荒廢、一半、完成）</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>程式依修復進度交叉淡入。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="23" t="inlineStr">
+        <is>
+          <t>放棄專注</t>
+        </is>
+      </c>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>不用另外畫</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="inlineStr">
+        <is>
+          <t>程式把畫面調灰。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="22" t="inlineStr">
+        <is>
+          <t>完成演出</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>全部工程完成後的夜晚與螢火蟲</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>螢火蟲由程式畫；需要一張夜晚色調版（或由程式調色）。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:C11"/>
+  <mergeCells count="1">
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1248,12 +1431,12 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="F5" s="29" t="inlineStr">
+      <c r="F5" s="32" t="inlineStr">
         <is>
           <t>暫代</t>
         </is>
       </c>
-      <c r="G5" s="26" t="inlineStr">
+      <c r="G5" s="29" t="inlineStr">
         <is>
           <t>目前程式畫</t>
         </is>
@@ -1285,12 +1468,12 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="F6" s="30" t="inlineStr">
+      <c r="F6" s="33" t="inlineStr">
         <is>
           <t>選配</t>
         </is>
       </c>
-      <c r="G6" s="26" t="inlineStr"/>
+      <c r="G6" s="29" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="22" t="inlineStr">
@@ -1318,12 +1501,12 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="F7" s="30" t="inlineStr">
+      <c r="F7" s="33" t="inlineStr">
         <is>
           <t>選配</t>
         </is>
       </c>
-      <c r="G7" s="26" t="inlineStr">
+      <c r="G7" s="29" t="inlineStr">
         <is>
           <t>目前沒有用到</t>
         </is>
@@ -1355,12 +1538,12 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="F8" s="30" t="inlineStr">
+      <c r="F8" s="33" t="inlineStr">
         <is>
           <t>選配</t>
         </is>
       </c>
-      <c r="G8" s="26" t="inlineStr">
+      <c r="G8" s="29" t="inlineStr">
         <is>
           <t>每個地區 1 張</t>
         </is>
@@ -1392,12 +1575,12 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="F9" s="25" t="inlineStr">
+      <c r="F9" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="G9" s="26" t="inlineStr"/>
+      <c r="G9" s="29" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="23" t="inlineStr">
@@ -1425,12 +1608,12 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="F10" s="25" t="inlineStr">
+      <c r="F10" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="G10" s="26" t="inlineStr"/>
+      <c r="G10" s="29" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:G10"/>
@@ -1447,7 +1630,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1553,12 +1736,12 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="G5" s="31" t="inlineStr">
+      <c r="G5" s="34" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
       </c>
-      <c r="H5" s="26" t="inlineStr">
+      <c r="H5" s="29" t="inlineStr">
         <is>
           <t>src/assets/icons/coin.webp</t>
         </is>
@@ -1595,12 +1778,12 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="G6" s="31" t="inlineStr">
+      <c r="G6" s="34" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
       </c>
-      <c r="H6" s="26" t="inlineStr">
+      <c r="H6" s="29" t="inlineStr">
         <is>
           <t>src/assets/icons/gem.webp</t>
         </is>
@@ -1637,12 +1820,12 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="G7" s="31" t="inlineStr">
+      <c r="G7" s="34" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
       </c>
-      <c r="H7" s="26" t="inlineStr"/>
+      <c r="H7" s="29" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="23" t="inlineStr">
@@ -1675,12 +1858,12 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="G8" s="31" t="inlineStr">
+      <c r="G8" s="34" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
       </c>
-      <c r="H8" s="26" t="inlineStr"/>
+      <c r="H8" s="29" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="22" t="inlineStr">
@@ -1713,12 +1896,12 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="G9" s="31" t="inlineStr">
+      <c r="G9" s="34" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
       </c>
-      <c r="H9" s="26" t="inlineStr"/>
+      <c r="H9" s="29" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="23" t="inlineStr">
@@ -1751,12 +1934,12 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="G10" s="25" t="inlineStr">
+      <c r="G10" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="H10" s="26" t="inlineStr">
+      <c r="H10" s="29" t="inlineStr">
         <is>
           <t>使用者有提供圖，但檔案沒有傳成功，要再傳一次</t>
         </is>
@@ -1793,12 +1976,12 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="G11" s="25" t="inlineStr">
+      <c r="G11" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="H11" s="26" t="inlineStr">
+      <c r="H11" s="29" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
@@ -1835,12 +2018,12 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="G12" s="25" t="inlineStr">
+      <c r="G12" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="H12" s="26" t="inlineStr">
+      <c r="H12" s="29" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
@@ -1877,12 +2060,12 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="G13" s="25" t="inlineStr">
+      <c r="G13" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="H13" s="26" t="inlineStr">
+      <c r="H13" s="29" t="inlineStr">
         <is>
           <t>目前用文字</t>
         </is>
@@ -1919,12 +2102,12 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="G14" s="25" t="inlineStr">
+      <c r="G14" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="H14" s="26" t="inlineStr">
+      <c r="H14" s="29" t="inlineStr">
         <is>
           <t>目前用 emoji</t>
         </is>
@@ -1961,12 +2144,12 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="G15" s="25" t="inlineStr">
+      <c r="G15" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="H15" s="26" t="inlineStr">
+      <c r="H15" s="29" t="inlineStr">
         <is>
           <t>目前用 emoji</t>
         </is>
@@ -2003,12 +2186,12 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="G16" s="29" t="inlineStr">
+      <c r="G16" s="32" t="inlineStr">
         <is>
           <t>暫代</t>
         </is>
       </c>
-      <c r="H16" s="26" t="inlineStr">
+      <c r="H16" s="29" t="inlineStr">
         <is>
           <t>目前用 lucide 線條圖示，可以沿用</t>
         </is>
@@ -2045,12 +2228,12 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="G17" s="29" t="inlineStr">
+      <c r="G17" s="32" t="inlineStr">
         <is>
           <t>暫代</t>
         </is>
       </c>
-      <c r="H17" s="26" t="inlineStr">
+      <c r="H17" s="29" t="inlineStr">
         <is>
           <t>目前用 lucide 線條圖示，可以沿用</t>
         </is>
@@ -2087,12 +2270,12 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G18" s="31" t="inlineStr">
+      <c r="G18" s="34" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
       </c>
-      <c r="H18" s="26" t="inlineStr">
+      <c r="H18" s="29" t="inlineStr">
         <is>
           <t>不用畫</t>
         </is>
@@ -2113,7 +2296,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2193,12 +2376,12 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="E5" s="29" t="inlineStr">
+      <c r="E5" s="32" t="inlineStr">
         <is>
           <t>暫代</t>
         </is>
       </c>
-      <c r="F5" s="26" t="inlineStr">
+      <c r="F5" s="29" t="inlineStr">
         <is>
           <t>目前是舊的溫室主題小島</t>
         </is>
@@ -2225,12 +2408,12 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="E6" s="29" t="inlineStr">
+      <c r="E6" s="32" t="inlineStr">
         <is>
           <t>暫代</t>
         </is>
       </c>
-      <c r="F6" s="26" t="inlineStr"/>
+      <c r="F6" s="29" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="22" t="inlineStr">
@@ -2253,12 +2436,12 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="E7" s="29" t="inlineStr">
+      <c r="E7" s="32" t="inlineStr">
         <is>
           <t>暫代</t>
         </is>
       </c>
-      <c r="F7" s="26" t="inlineStr">
+      <c r="F7" s="29" t="inlineStr">
         <is>
           <t>目前是程式畫的望遠鏡，可以沿用</t>
         </is>
@@ -2285,12 +2468,12 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="E8" s="25" t="inlineStr">
+      <c r="E8" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="F8" s="26" t="inlineStr">
+      <c r="F8" s="29" t="inlineStr">
         <is>
           <t>上架必填</t>
         </is>
@@ -2317,12 +2500,12 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="E9" s="25" t="inlineStr">
+      <c r="E9" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="F9" s="26" t="inlineStr">
+      <c r="F9" s="29" t="inlineStr">
         <is>
           <t>建議：大廳、望遠鏡專注、遇見動物、我的小島、觀察圖鑑地圖、專注紀錄、上週回顧、時間守護</t>
         </is>
@@ -2349,12 +2532,12 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="E10" s="25" t="inlineStr">
+      <c r="E10" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="F10" s="26" t="inlineStr">
+      <c r="F10" s="29" t="inlineStr">
         <is>
           <t>可用 App 圖示</t>
         </is>
@@ -2381,12 +2564,12 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E11" s="29" t="inlineStr">
+      <c r="E11" s="32" t="inlineStr">
         <is>
           <t>暫代</t>
         </is>
       </c>
-      <c r="F11" s="26" t="inlineStr">
+      <c r="F11" s="29" t="inlineStr">
         <is>
           <t>目前用動物圖拼湊</t>
         </is>
@@ -2413,12 +2596,12 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E12" s="29" t="inlineStr">
+      <c r="E12" s="32" t="inlineStr">
         <is>
           <t>暫代</t>
         </is>
       </c>
-      <c r="F12" s="26" t="inlineStr">
+      <c r="F12" s="29" t="inlineStr">
         <is>
           <t>目前用程式畫，可以沿用</t>
         </is>
@@ -2445,12 +2628,12 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E13" s="29" t="inlineStr">
+      <c r="E13" s="32" t="inlineStr">
         <is>
           <t>暫代</t>
         </is>
       </c>
-      <c r="F13" s="26" t="inlineStr">
+      <c r="F13" s="29" t="inlineStr">
         <is>
           <t>目前用守護動物</t>
         </is>
@@ -2477,12 +2660,12 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E14" s="25" t="inlineStr">
+      <c r="E14" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="F14" s="26" t="inlineStr"/>
+      <c r="F14" s="29" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="22" t="inlineStr">
@@ -2505,12 +2688,12 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E15" s="25" t="inlineStr">
+      <c r="E15" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="F15" s="26" t="inlineStr">
+      <c r="F15" s="29" t="inlineStr">
         <is>
           <t>總時數、專注天數、最佳日、陪你最久、和前一週比、排名、總結卡</t>
         </is>
@@ -2537,12 +2720,12 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E16" s="25" t="inlineStr">
+      <c r="E16" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="F16" s="26" t="inlineStr"/>
+      <c r="F16" s="29" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="22" t="inlineStr">
@@ -2565,12 +2748,12 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E17" s="25" t="inlineStr">
+      <c r="E17" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="F17" s="26" t="inlineStr">
+      <c r="F17" s="29" t="inlineStr">
         <is>
           <t>要和金幣動物有區別</t>
         </is>
@@ -2597,217 +2780,15 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E18" s="25" t="inlineStr">
+      <c r="E18" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="F18" s="26" t="inlineStr"/>
+      <c r="F18" s="29" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:F18"/>
-  <mergeCells count="1">
-    <mergeCell ref="A2:F2"/>
-  </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="E5:E304" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="狀態" error="請從清單選一個狀態" type="list">
-      <formula1>"未開始,製作中,待驗收,已完成,暫代,選配"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="7" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="21" t="inlineStr">
-        <is>
-          <t>H. 地圖</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="2" t="inlineStr"/>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>檔案</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>尺寸</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>優先度</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>狀態</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>備註</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="22" t="inlineStr">
-        <is>
-          <t>區域切換的世界地圖</t>
-        </is>
-      </c>
-      <c r="B5" s="22" t="inlineStr">
-        <is>
-          <t>src/assets/scenes/world-map.webp</t>
-        </is>
-      </c>
-      <c r="C5" s="22" t="inlineStr">
-        <is>
-          <t>1816×866</t>
-        </is>
-      </c>
-      <c r="D5" s="22" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="E5" s="31" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="F5" s="26" t="inlineStr">
-        <is>
-          <t>新增區域時要補標記位置</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="23" t="inlineStr">
-        <is>
-          <t>觀察圖鑑：台灣 3D 地圖貼圖</t>
-        </is>
-      </c>
-      <c r="B6" s="23" t="inlineStr">
-        <is>
-          <t>src/assets/scenes/map-tw.webp</t>
-        </is>
-      </c>
-      <c r="C6" s="23" t="inlineStr">
-        <is>
-          <t>1024×1536</t>
-        </is>
-      </c>
-      <c r="D6" s="23" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E6" s="31" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="F6" s="26" t="inlineStr">
-        <is>
-          <t>GPT 畫，已簡化 30%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="22" t="inlineStr">
-        <is>
-          <t>觀察圖鑑：日本 3D 地圖貼圖</t>
-        </is>
-      </c>
-      <c r="B7" s="22" t="inlineStr">
-        <is>
-          <t>src/assets/scenes/map-jp.webp</t>
-        </is>
-      </c>
-      <c r="C7" s="22" t="inlineStr">
-        <is>
-          <t>1254×1254</t>
-        </is>
-      </c>
-      <c r="D7" s="22" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E7" s="31" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="F7" s="26" t="inlineStr">
-        <is>
-          <t>中間只有富士山與立山連峰</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="23" t="inlineStr">
-        <is>
-          <t>之後新地區的 3D 地圖貼圖</t>
-        </is>
-      </c>
-      <c r="B8" s="23" t="inlineStr">
-        <is>
-          <t>src/assets/scenes/map-{地區}.webp</t>
-        </is>
-      </c>
-      <c r="C8" s="23" t="inlineStr">
-        <is>
-          <t>依地形</t>
-        </is>
-      </c>
-      <c r="D8" s="23" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="E8" s="25" t="inlineStr">
-        <is>
-          <t>未開始</t>
-        </is>
-      </c>
-      <c r="F8" s="26" t="inlineStr">
-        <is>
-          <t>用地形資料畫配置圖給 GPT 對位</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A4:F8"/>
   <mergeCells count="1">
     <mergeCell ref="A2:F2"/>
   </mergeCells>
@@ -2827,6 +2808,208 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="21" t="inlineStr">
+        <is>
+          <t>H. 地圖</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="2" t="inlineStr"/>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>檔案</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>尺寸</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>優先度</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>狀態</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>備註</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="22" t="inlineStr">
+        <is>
+          <t>區域切換的世界地圖</t>
+        </is>
+      </c>
+      <c r="B5" s="22" t="inlineStr">
+        <is>
+          <t>src/assets/scenes/world-map.webp</t>
+        </is>
+      </c>
+      <c r="C5" s="22" t="inlineStr">
+        <is>
+          <t>1816×866</t>
+        </is>
+      </c>
+      <c r="D5" s="22" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E5" s="34" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="F5" s="29" t="inlineStr">
+        <is>
+          <t>新增區域時要補標記位置</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="23" t="inlineStr">
+        <is>
+          <t>觀察圖鑑：台灣 3D 地圖貼圖</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>src/assets/scenes/map-tw.webp</t>
+        </is>
+      </c>
+      <c r="C6" s="23" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E6" s="34" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="F6" s="29" t="inlineStr">
+        <is>
+          <t>GPT 畫，已簡化 30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="22" t="inlineStr">
+        <is>
+          <t>觀察圖鑑：日本 3D 地圖貼圖</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>src/assets/scenes/map-jp.webp</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>1254×1254</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E7" s="34" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="F7" s="29" t="inlineStr">
+        <is>
+          <t>中間只有富士山與立山連峰</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="23" t="inlineStr">
+        <is>
+          <t>之後新地區的 3D 地圖貼圖</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>src/assets/scenes/map-{地區}.webp</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="inlineStr">
+        <is>
+          <t>依地形</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="E8" s="28" t="inlineStr">
+        <is>
+          <t>未開始</t>
+        </is>
+      </c>
+      <c r="F8" s="29" t="inlineStr">
+        <is>
+          <t>用地形資料畫配置圖給 GPT 對位</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:F8"/>
+  <mergeCells count="1">
+    <mergeCell ref="A2:F2"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="E5:E304" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="狀態" error="請從清單選一個狀態" type="list">
+      <formula1>"未開始,製作中,待驗收,已完成,暫代,選配"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2894,7 +3077,7 @@
           <t>160×160</t>
         </is>
       </c>
-      <c r="D5" s="24" t="n">
+      <c r="D5" s="27" t="n">
         <v>8</v>
       </c>
       <c r="E5" s="22" t="inlineStr">
@@ -2919,7 +3102,7 @@
           <t>160×160</t>
         </is>
       </c>
-      <c r="D6" s="27" t="n">
+      <c r="D6" s="30" t="n">
         <v>6</v>
       </c>
       <c r="E6" s="23" t="inlineStr">
@@ -2944,7 +3127,7 @@
           <t>512×512</t>
         </is>
       </c>
-      <c r="D7" s="24" t="n">
+      <c r="D7" s="27" t="n">
         <v>33.5</v>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -2969,7 +3152,7 @@
           <t>512×512</t>
         </is>
       </c>
-      <c r="D8" s="27" t="n">
+      <c r="D8" s="30" t="n">
         <v>38.2</v>
       </c>
       <c r="E8" s="23" t="inlineStr">
@@ -2994,7 +3177,7 @@
           <t>512×512</t>
         </is>
       </c>
-      <c r="D9" s="24" t="n">
+      <c r="D9" s="27" t="n">
         <v>49.2</v>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -3019,7 +3202,7 @@
           <t>1697×927</t>
         </is>
       </c>
-      <c r="D10" s="27" t="n">
+      <c r="D10" s="30" t="n">
         <v>145.6</v>
       </c>
       <c r="E10" s="23" t="inlineStr">
@@ -3044,7 +3227,7 @@
           <t>1167×1347</t>
         </is>
       </c>
-      <c r="D11" s="24" t="n">
+      <c r="D11" s="27" t="n">
         <v>105</v>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -3069,7 +3252,7 @@
           <t>1200×572</t>
         </is>
       </c>
-      <c r="D12" s="27" t="n">
+      <c r="D12" s="30" t="n">
         <v>89.5</v>
       </c>
       <c r="E12" s="23" t="inlineStr">
@@ -3094,7 +3277,7 @@
           <t>1024×1536</t>
         </is>
       </c>
-      <c r="D13" s="24" t="n">
+      <c r="D13" s="27" t="n">
         <v>101.4</v>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -3119,7 +3302,7 @@
           <t>1254×1254</t>
         </is>
       </c>
-      <c r="D14" s="27" t="n">
+      <c r="D14" s="30" t="n">
         <v>57</v>
       </c>
       <c r="E14" s="23" t="inlineStr">
@@ -3144,7 +3327,7 @@
           <t>512×512</t>
         </is>
       </c>
-      <c r="D15" s="24" t="n">
+      <c r="D15" s="27" t="n">
         <v>29.5</v>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -3169,7 +3352,7 @@
           <t>512×512</t>
         </is>
       </c>
-      <c r="D16" s="27" t="n">
+      <c r="D16" s="30" t="n">
         <v>11.3</v>
       </c>
       <c r="E16" s="23" t="inlineStr">
@@ -3194,7 +3377,7 @@
           <t>192×192</t>
         </is>
       </c>
-      <c r="D17" s="24" t="n">
+      <c r="D17" s="27" t="n">
         <v>3.9</v>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -3219,7 +3402,7 @@
           <t>180×180</t>
         </is>
       </c>
-      <c r="D18" s="27" t="n">
+      <c r="D18" s="30" t="n">
         <v>3.4</v>
       </c>
       <c r="E18" s="23" t="inlineStr">
@@ -3244,7 +3427,7 @@
           <t>半尺寸</t>
         </is>
       </c>
-      <c r="D19" s="24" t="n">
+      <c r="D19" s="27" t="n">
         <v>67.5</v>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -3263,7 +3446,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3319,7 +3502,7 @@
           <t>檔名照規則（英文小寫、底線、階段編號）</t>
         </is>
       </c>
-      <c r="C5" s="26" t="inlineStr"/>
+      <c r="C5" s="29" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="23" t="inlineStr">
@@ -3332,7 +3515,7 @@
           <t>透明背景、sRGB；深色與淺色背景上都沒有白邊、殘留色塊</t>
         </is>
       </c>
-      <c r="C6" s="26" t="inlineStr"/>
+      <c r="C6" s="29" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="22" t="inlineStr">
@@ -3345,7 +3528,7 @@
           <t>沒有文字、浮水印、地面陰影、背景物件</t>
         </is>
       </c>
-      <c r="C7" s="26" t="inlineStr"/>
+      <c r="C7" s="29" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="23" t="inlineStr">
@@ -3358,7 +3541,7 @@
           <t>用手機實際顯示的大小檢查一次（縮小後線條、斷層最容易出現）</t>
         </is>
       </c>
-      <c r="C8" s="26" t="inlineStr"/>
+      <c r="C8" s="29" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="22" t="inlineStr">
@@ -3371,7 +3554,7 @@
           <t>正側面、頭朝右；腳底貼齊 y＝472（512 畫布，離下緣 40 px），水平置中</t>
         </is>
       </c>
-      <c r="C9" s="26" t="inlineStr"/>
+      <c r="C9" s="29" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="23" t="inlineStr">
@@ -3384,7 +3567,7 @@
           <t>三個成長階段畫布一樣大，幼年約成年的 60%、亞成年約 80%，腳底在同一條線</t>
         </is>
       </c>
-      <c r="C10" s="26" t="inlineStr"/>
+      <c r="C10" s="29" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="22" t="inlineStr">
@@ -3397,7 +3580,7 @@
           <t>三個階段看得出是同一種（毛色、斑紋、臉型一致）；縮到 30 px 仍認得出</t>
         </is>
       </c>
-      <c r="C11" s="26" t="inlineStr"/>
+      <c r="C11" s="29" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="23" t="inlineStr">
@@ -3410,7 +3593,7 @@
           <t>靜止時網格圖層合成跟主圖比：平均差 ≤ 1.5、p99 ≤ 10</t>
         </is>
       </c>
-      <c r="C12" s="26" t="inlineStr"/>
+      <c r="C12" s="29" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="22" t="inlineStr">
@@ -3423,7 +3606,7 @@
           <t>走路四個時間點、張望、低頭、張嘴、眨眼、甩尾兩端、耳朵最大角度，都用半尺寸貼圖放大檢查</t>
         </is>
       </c>
-      <c r="C13" s="26" t="inlineStr"/>
+      <c r="C13" s="29" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="23" t="inlineStr">
@@ -3436,7 +3619,7 @@
           <t>在 Galaxy A8s 實機確認；每隻壓縮後 ≤ 120 KB</t>
         </is>
       </c>
-      <c r="C14" s="26" t="inlineStr"/>
+      <c r="C14" s="29" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="22" t="inlineStr">
@@ -3449,7 +3632,7 @@
           <t>3000×1150 左右；動物停下的位置（62%, 59～70%）乾淨；夜晚版與白天版構圖完全一致</t>
         </is>
       </c>
-      <c r="C15" s="26" t="inlineStr"/>
+      <c r="C15" s="29" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="23" t="inlineStr">
@@ -3462,7 +3645,7 @@
           <t>與底圖同畫布、完全對齊；6 個動物站位不被擋住</t>
         </is>
       </c>
-      <c r="C16" s="26" t="inlineStr"/>
+      <c r="C16" s="29" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="22" t="inlineStr">
@@ -3475,7 +3658,7 @@
           <t>512 px 置中、去背；縮到 24 px 仍清楚</t>
         </is>
       </c>
-      <c r="C17" s="26" t="inlineStr"/>
+      <c r="C17" s="29" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:C17"/>
@@ -3493,7 +3676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3637,175 +3820,192 @@
     <row r="11">
       <c r="A11" s="22" t="inlineStr">
         <is>
-          <t>小尺寸辨識</t>
+          <t>動物解析度</t>
         </is>
       </c>
       <c r="B11" s="22" t="inlineStr">
         <is>
-          <t>縮到 30～50 px 仍要一眼分辨種類</t>
+          <t>製作主圖 1024×1024（動物本體寬約 850～950 px）；App 用 512 px（之後可改 768）</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
         <is>
-          <t>專注紀錄的格子在月／年檢視只有 6～50 px。</t>
+          <t>畫面上最大的是望遠鏡最後推近：A8s 約需 550 px、旗艦機約 770 px。詳細見「動物尺寸」分頁。</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="23" t="inlineStr">
         <is>
-          <t>禁止</t>
+          <t>小尺寸辨識</t>
         </is>
       </c>
       <c r="B12" s="23" t="inlineStr">
         <is>
-          <t>文字、浮水印、背景物件、地面陰影、玩具式關節</t>
+          <t>縮到 30～50 px 仍要一眼分辨種類</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
         <is>
-          <t>地面陰影由程式加；讓 GPT 分開畫部件會把關節畫成插銷（見 B 動物動態）。</t>
+          <t>專注紀錄的格子在月／年檢視只有 6～50 px。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="22" t="inlineStr">
         <is>
-          <t>交件格式</t>
+          <t>禁止</t>
         </is>
       </c>
       <c r="B13" s="22" t="inlineStr">
         <is>
-          <t>透明 PNG（sRGB），程式轉成 WebP</t>
+          <t>文字、浮水印、背景物件、地面陰影、玩具式關節</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
         <is>
-          <t>尺寸用 2 的倍數；向量圖示可以給 SVG。</t>
+          <t>地面陰影由程式加；讓 GPT 分開畫部件會把關節畫成插銷（見 B 動物動態）。</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="23" t="inlineStr">
         <is>
-          <t>去背</t>
+          <t>交件格式</t>
         </is>
       </c>
       <c r="B14" s="23" t="inlineStr">
         <is>
-          <t>深色、淺色背景各檢查一次，不能有白邊</t>
+          <t>透明 PNG（sRGB），程式轉成 WebP</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
         <is>
-          <t>白底去背：遮罩先往內縮 2 px 再柔化 0.8 px。</t>
+          <t>尺寸用 2 的倍數；向量圖示可以給 SVG。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="22" t="inlineStr">
         <is>
-          <t>縮圖</t>
+          <t>去背</t>
         </is>
       </c>
       <c r="B15" s="22" t="inlineStr">
         <is>
-          <t>縮小一律用 BOX（區域平均），不用 Lanczos</t>
+          <t>深色、淺色背景各檢查一次，不能有白邊</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
         <is>
-          <t>Lanczos 在硬邊會產生一圈亮線（振鈴）。</t>
+          <t>白底去背：遮罩先往內縮 2 px 再柔化 0.8 px。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="23" t="inlineStr">
         <is>
-          <t>命名</t>
+          <t>縮圖</t>
         </is>
       </c>
       <c r="B16" s="23" t="inlineStr">
         <is>
-          <t>英文小寫加底線，例如 blue_magpie-2.png</t>
+          <t>縮小一律用 BOX（區域平均），不用 Lanczos</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
         <is>
-          <t>代號見各分頁的「代號」欄。</t>
+          <t>Lanczos 在硬邊會產生一圈亮線（振鈴）。</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="22" t="inlineStr">
         <is>
-          <t>AI 輔助</t>
+          <t>命名</t>
         </is>
       </c>
       <c r="B17" s="22" t="inlineStr">
         <is>
-          <t>先定一張主圖，之後只做「只改一處」的編輯</t>
+          <t>英文小寫加底線，例如 blue_magpie-2.png</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
         <is>
-          <t>用同一張風格參考（石虎主圖），整系列才像同一款遊戲。</t>
+          <t>代號見各分頁的「代號」欄。</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="23" t="inlineStr">
         <is>
-          <t>減少動態</t>
+          <t>AI 輔助</t>
         </is>
       </c>
       <c r="B18" s="23" t="inlineStr">
         <is>
-          <t>每個會動的東西都要有一張靜態畫面</t>
+          <t>先定一張主圖，之後只做「只改一處」的編輯</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
         <is>
-          <t>系統「減少動態效果」、App「平靜模式」時改用靜態。</t>
+          <t>用同一張風格參考（石虎主圖），整系列才像同一款遊戲。</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="22" t="inlineStr">
         <is>
-          <t>容量</t>
+          <t>減少動態</t>
         </is>
       </c>
       <c r="B19" s="22" t="inlineStr">
         <is>
-          <t>動物網格每隻 ≤120 KB；全景每張 200～400 KB；圖示 ≤40 KB</t>
+          <t>每個會動的東西都要有一張靜態畫面</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
         <is>
-          <t>手機 App 安裝檔要小，載入要快。</t>
+          <t>系統「減少動態效果」、App「平靜模式」時改用靜態。</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="23" t="inlineStr">
         <is>
+          <t>容量</t>
+        </is>
+      </c>
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>動物網格每隻 ≤120 KB；全景每張 200～400 KB；圖示 ≤40 KB</t>
+        </is>
+      </c>
+      <c r="C20" s="23" t="inlineStr">
+        <is>
+          <t>手機 App 安裝檔要小，載入要快。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="22" t="inlineStr">
+        <is>
           <t>驗收</t>
         </is>
       </c>
-      <c r="B20" s="23" t="inlineStr">
+      <c r="B21" s="22" t="inlineStr">
         <is>
           <t>一律用手機實際顯示的大小檢查（半尺寸貼圖），並在 Galaxy A8s 實機確認</t>
         </is>
       </c>
-      <c r="C20" s="23" t="inlineStr">
+      <c r="C21" s="22" t="inlineStr">
         <is>
           <t>原尺寸看起來正常、縮小後才出現的白線和斷層最常被漏掉。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:C20"/>
+  <autoFilter ref="A4:C21"/>
   <mergeCells count="1">
     <mergeCell ref="A2:C2"/>
   </mergeCells>
@@ -3815,6 +4015,338 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="21" t="inlineStr">
+        <is>
+          <t>動物尺寸：各畫面實際需要的像素</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>手機實際像素＝畫面大小（CSS px）× 螢幕密度（Galaxy A8s 約 2.6 倍，旗艦機約 3～3.5 倍）。結論：製作主圖 1024，App 用 512（之後可改 768）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>出現的地方</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>畫面上的大小（CSS px）</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>A8s 實際需要（px）</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>旗艦機實際需要（px）</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>備註</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="22" t="inlineStr">
+        <is>
+          <t>望遠鏡最後鎖定、推近（最大）</t>
+        </is>
+      </c>
+      <c r="B5" s="22" t="inlineStr">
+        <is>
+          <t>約 200～220</t>
+        </is>
+      </c>
+      <c r="C5" s="22" t="inlineStr">
+        <is>
+          <t>約 550</t>
+        </is>
+      </c>
+      <c r="D5" s="22" t="inlineStr">
+        <is>
+          <t>約 700～770</t>
+        </is>
+      </c>
+      <c r="E5" s="22" t="inlineStr">
+        <is>
+          <t>專注結束那一刻；決定主圖要多大</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="23" t="inlineStr">
+        <is>
+          <t>遇見動物的揭曉畫面</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="C6" s="23" t="inlineStr">
+        <is>
+          <t>約 440</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="inlineStr">
+        <is>
+          <t>約 600</t>
+        </is>
+      </c>
+      <c r="E6" s="23" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="22" t="inlineStr">
+        <is>
+          <t>動物卡</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>約 365</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>約 490</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="23" t="inlineStr">
+        <is>
+          <t>結算卡片</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>約 120</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="inlineStr">
+        <is>
+          <t>約 315</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t>約 420</t>
+        </is>
+      </c>
+      <c r="E8" s="23" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="22" t="inlineStr">
+        <is>
+          <t>分享圖（輸出 1080 寬）</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>固定</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>440</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>440</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>和手機無關</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="23" t="inlineStr">
+        <is>
+          <t>我的小島</t>
+        </is>
+      </c>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>52～96</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="inlineStr">
+        <is>
+          <t>約 250</t>
+        </is>
+      </c>
+      <c r="D10" s="23" t="inlineStr">
+        <is>
+          <t>約 340</t>
+        </is>
+      </c>
+      <c r="E10" s="23" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="22" t="inlineStr">
+        <is>
+          <t>專注紀錄的格子</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>6～50</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>很小</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>很小</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
+        <is>
+          <t>要能一眼認出種類</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="24" t="inlineStr">
+        <is>
+          <t>建議規格</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="25" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B14" s="25" t="inlineStr">
+        <is>
+          <t>規格</t>
+        </is>
+      </c>
+      <c r="C14" s="25" t="inlineStr">
+        <is>
+          <t>說明</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="26" t="inlineStr">
+        <is>
+          <t>製作主圖</t>
+        </is>
+      </c>
+      <c r="B15" s="26" t="inlineStr">
+        <is>
+          <t>1024×1024，動物本體寬約 850～950 px</t>
+        </is>
+      </c>
+      <c r="C15" s="26" t="inlineStr">
+        <is>
+          <t>所有部件、網格動態的唯一來源；之後裁切、局部重畫都要留解析度。GPT 一次畫 1024 剛好。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="26" t="inlineStr">
+        <is>
+          <t>App 貼圖（建議）</t>
+        </is>
+      </c>
+      <c r="B16" s="26" t="inlineStr">
+        <is>
+          <t>512 px</t>
+        </is>
+      </c>
+      <c r="C16" s="26" t="inlineStr">
+        <is>
+          <t>A8s 幾乎看不出差別、容量最省（每隻網格 ≤120 KB）；旗艦機在望遠鏡推近那一刻稍微軟一點。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="26" t="inlineStr">
+        <is>
+          <t>App 貼圖（之後可選）</t>
+        </is>
+      </c>
+      <c r="B17" s="26" t="inlineStr">
+        <is>
+          <t>768 px</t>
+        </is>
+      </c>
+      <c r="C17" s="26" t="inlineStr">
+        <is>
+          <t>旗艦機推近也清楚；每隻容量約多 1.5～2 倍，29 隻約多 3～4 MB。主圖是 1024，可以直接重新輸出，不用重畫。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="26" t="inlineStr">
+        <is>
+          <t>幼年、亞成年</t>
+        </is>
+      </c>
+      <c r="B18" s="26" t="inlineStr">
+        <is>
+          <t>同一張畫布，本體約成年的 60%、80%</t>
+        </is>
+      </c>
+      <c r="C18" s="26" t="inlineStr">
+        <is>
+          <t>畫面上本來就比較小，不用另外畫大。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:E11"/>
+  <mergeCells count="1">
+    <mergeCell ref="A2:E2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3950,7 +4482,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="24" t="n">
+      <c r="A5" s="27" t="n">
         <v>1</v>
       </c>
       <c r="B5" s="22" t="inlineStr">
@@ -3973,7 +4505,7 @@
           <t>鳥</t>
         </is>
       </c>
-      <c r="F5" s="24" t="n">
+      <c r="F5" s="27" t="n">
         <v>3</v>
       </c>
       <c r="G5" s="22" t="inlineStr">
@@ -4011,7 +4543,7 @@
           <t>一開始就能找</t>
         </is>
       </c>
-      <c r="N5" s="24" t="n">
+      <c r="N5" s="27" t="n">
         <v>1</v>
       </c>
       <c r="O5" s="22" t="inlineStr">
@@ -4024,15 +4556,15 @@
           <t>blue_magpie-0/1/2.png</t>
         </is>
       </c>
-      <c r="Q5" s="25" t="inlineStr">
+      <c r="Q5" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="R5" s="26" t="inlineStr"/>
+      <c r="R5" s="29" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="27" t="n">
+      <c r="A6" s="30" t="n">
         <v>2</v>
       </c>
       <c r="B6" s="23" t="inlineStr">
@@ -4055,7 +4587,7 @@
           <t>貓頭鷹</t>
         </is>
       </c>
-      <c r="F6" s="27" t="n">
+      <c r="F6" s="30" t="n">
         <v>3</v>
       </c>
       <c r="G6" s="23" t="inlineStr">
@@ -4093,7 +4625,7 @@
           <t>一開始就能找</t>
         </is>
       </c>
-      <c r="N6" s="27" t="n">
+      <c r="N6" s="30" t="n">
         <v>1</v>
       </c>
       <c r="O6" s="23" t="inlineStr">
@@ -4106,15 +4638,15 @@
           <t>scops_owl-0/1/2.png</t>
         </is>
       </c>
-      <c r="Q6" s="25" t="inlineStr">
+      <c r="Q6" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="R6" s="26" t="inlineStr"/>
+      <c r="R6" s="29" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="24" t="n">
+      <c r="A7" s="27" t="n">
         <v>3</v>
       </c>
       <c r="B7" s="22" t="inlineStr">
@@ -4137,7 +4669,7 @@
           <t>穿山甲</t>
         </is>
       </c>
-      <c r="F7" s="24" t="n">
+      <c r="F7" s="27" t="n">
         <v>3</v>
       </c>
       <c r="G7" s="22" t="inlineStr">
@@ -4175,7 +4707,7 @@
           <t>修好「清出林間步道」</t>
         </is>
       </c>
-      <c r="N7" s="24" t="n">
+      <c r="N7" s="27" t="n">
         <v>1</v>
       </c>
       <c r="O7" s="22" t="inlineStr">
@@ -4188,15 +4720,15 @@
           <t>pangolin-0/1/2.png</t>
         </is>
       </c>
-      <c r="Q7" s="25" t="inlineStr">
+      <c r="Q7" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="R7" s="26" t="inlineStr"/>
+      <c r="R7" s="29" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="27" t="n">
+      <c r="A8" s="30" t="n">
         <v>4</v>
       </c>
       <c r="B8" s="23" t="inlineStr">
@@ -4219,7 +4751,7 @@
           <t>鳥</t>
         </is>
       </c>
-      <c r="F8" s="27" t="n">
+      <c r="F8" s="30" t="n">
         <v>3</v>
       </c>
       <c r="G8" s="23" t="inlineStr">
@@ -4257,7 +4789,7 @@
           <t>修好「種回原生樹苗」</t>
         </is>
       </c>
-      <c r="N8" s="27" t="n">
+      <c r="N8" s="30" t="n">
         <v>1</v>
       </c>
       <c r="O8" s="23" t="inlineStr">
@@ -4270,15 +4802,15 @@
           <t>pitta-0/1/2.png</t>
         </is>
       </c>
-      <c r="Q8" s="25" t="inlineStr">
+      <c r="Q8" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="R8" s="26" t="inlineStr"/>
+      <c r="R8" s="29" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="24" t="n">
+      <c r="A9" s="27" t="n">
         <v>5</v>
       </c>
       <c r="B9" s="22" t="inlineStr">
@@ -4301,7 +4833,7 @@
           <t>貓科</t>
         </is>
       </c>
-      <c r="F9" s="24" t="n">
+      <c r="F9" s="27" t="n">
         <v>3</v>
       </c>
       <c r="G9" s="22" t="inlineStr">
@@ -4339,7 +4871,7 @@
           <t>修好「修好森林觀察小屋」</t>
         </is>
       </c>
-      <c r="N9" s="24" t="n">
+      <c r="N9" s="27" t="n">
         <v>1</v>
       </c>
       <c r="O9" s="22" t="inlineStr">
@@ -4352,19 +4884,19 @@
           <t>leopard_cat-0/1/2.png</t>
         </is>
       </c>
-      <c r="Q9" s="28" t="inlineStr">
+      <c r="Q9" s="31" t="inlineStr">
         <is>
           <t>製作中</t>
         </is>
       </c>
-      <c r="R9" s="26" t="inlineStr">
+      <c r="R9" s="29" t="inlineStr">
         <is>
           <t>成年主圖、網格已完成（全系列的風格與規格參考）；幼年、亞成年未做</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="27" t="n">
+      <c r="A10" s="30" t="n">
         <v>6</v>
       </c>
       <c r="B10" s="23" t="inlineStr">
@@ -4387,7 +4919,7 @@
           <t>雉雞</t>
         </is>
       </c>
-      <c r="F10" s="27" t="n">
+      <c r="F10" s="30" t="n">
         <v>3</v>
       </c>
       <c r="G10" s="23" t="inlineStr">
@@ -4425,7 +4957,7 @@
           <t>修好「恢復林下草叢」</t>
         </is>
       </c>
-      <c r="N10" s="27" t="n">
+      <c r="N10" s="30" t="n">
         <v>2</v>
       </c>
       <c r="O10" s="23" t="inlineStr">
@@ -4438,15 +4970,15 @@
           <t>swinhoe_pheasant-0/1/2.png</t>
         </is>
       </c>
-      <c r="Q10" s="25" t="inlineStr">
+      <c r="Q10" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="R10" s="26" t="inlineStr"/>
+      <c r="R10" s="29" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="24" t="n">
+      <c r="A11" s="27" t="n">
         <v>7</v>
       </c>
       <c r="B11" s="22" t="inlineStr">
@@ -4469,7 +5001,7 @@
           <t>貂、獴</t>
         </is>
       </c>
-      <c r="F11" s="24" t="n">
+      <c r="F11" s="27" t="n">
         <v>3</v>
       </c>
       <c r="G11" s="22" t="inlineStr">
@@ -4507,7 +5039,7 @@
           <t>修好「架設生態廊道」</t>
         </is>
       </c>
-      <c r="N11" s="24" t="n">
+      <c r="N11" s="27" t="n">
         <v>2</v>
       </c>
       <c r="O11" s="22" t="inlineStr">
@@ -4520,15 +5052,15 @@
           <t>crab_mongoose-0/1/2.png</t>
         </is>
       </c>
-      <c r="Q11" s="25" t="inlineStr">
+      <c r="Q11" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="R11" s="26" t="inlineStr"/>
+      <c r="R11" s="29" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="27" t="n">
+      <c r="A12" s="30" t="n">
         <v>8</v>
       </c>
       <c r="B12" s="23" t="inlineStr">
@@ -4551,7 +5083,7 @@
           <t>貂、獴</t>
         </is>
       </c>
-      <c r="F12" s="27" t="n">
+      <c r="F12" s="30" t="n">
         <v>3</v>
       </c>
       <c r="G12" s="23" t="inlineStr">
@@ -4589,7 +5121,7 @@
           <t>修好「整理森林水源地」</t>
         </is>
       </c>
-      <c r="N12" s="27" t="n">
+      <c r="N12" s="30" t="n">
         <v>2</v>
       </c>
       <c r="O12" s="23" t="inlineStr">
@@ -4602,15 +5134,15 @@
           <t>marten-0/1/2.png</t>
         </is>
       </c>
-      <c r="Q12" s="25" t="inlineStr">
+      <c r="Q12" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="R12" s="26" t="inlineStr"/>
+      <c r="R12" s="29" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="24" t="n">
+      <c r="A13" s="27" t="n">
         <v>9</v>
       </c>
       <c r="B13" s="22" t="inlineStr">
@@ -4633,7 +5165,7 @@
           <t>猛禽</t>
         </is>
       </c>
-      <c r="F13" s="24" t="n">
+      <c r="F13" s="27" t="n">
         <v>3</v>
       </c>
       <c r="G13" s="22" t="inlineStr">
@@ -4671,7 +5203,7 @@
           <t>修好「搭建樹冠步道」</t>
         </is>
       </c>
-      <c r="N13" s="24" t="n">
+      <c r="N13" s="27" t="n">
         <v>2</v>
       </c>
       <c r="O13" s="22" t="inlineStr">
@@ -4684,15 +5216,15 @@
           <t>hawk_eagle-0/1/2.png</t>
         </is>
       </c>
-      <c r="Q13" s="25" t="inlineStr">
+      <c r="Q13" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="R13" s="26" t="inlineStr"/>
+      <c r="R13" s="29" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="27" t="n">
+      <c r="A14" s="30" t="n">
         <v>10</v>
       </c>
       <c r="B14" s="23" t="inlineStr">
@@ -4715,7 +5247,7 @@
           <t>熊</t>
         </is>
       </c>
-      <c r="F14" s="27" t="n">
+      <c r="F14" s="30" t="n">
         <v>3</v>
       </c>
       <c r="G14" s="23" t="inlineStr">
@@ -4753,7 +5285,7 @@
           <t>修好「設立保育救傷站」</t>
         </is>
       </c>
-      <c r="N14" s="27" t="n">
+      <c r="N14" s="30" t="n">
         <v>2</v>
       </c>
       <c r="O14" s="23" t="inlineStr">
@@ -4766,15 +5298,15 @@
           <t>black_bear-0/1/2.png</t>
         </is>
       </c>
-      <c r="Q14" s="25" t="inlineStr">
+      <c r="Q14" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="R14" s="26" t="inlineStr"/>
+      <c r="R14" s="29" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="24" t="n">
+      <c r="A15" s="27" t="n">
         <v>11</v>
       </c>
       <c r="B15" s="22" t="inlineStr">
@@ -4797,7 +5329,7 @@
           <t>貓科</t>
         </is>
       </c>
-      <c r="F15" s="24" t="n">
+      <c r="F15" s="27" t="n">
         <v>1</v>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -4835,7 +5367,7 @@
           <t>商店 800 金幣</t>
         </is>
       </c>
-      <c r="N15" s="24" t="n">
+      <c r="N15" s="27" t="n">
         <v>4</v>
       </c>
       <c r="O15" s="22" t="inlineStr">
@@ -4848,15 +5380,15 @@
           <t>civet-2.png</t>
         </is>
       </c>
-      <c r="Q15" s="25" t="inlineStr">
+      <c r="Q15" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="R15" s="26" t="inlineStr"/>
+      <c r="R15" s="29" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="27" t="n">
+      <c r="A16" s="30" t="n">
         <v>12</v>
       </c>
       <c r="B16" s="23" t="inlineStr">
@@ -4879,7 +5411,7 @@
           <t>雉雞</t>
         </is>
       </c>
-      <c r="F16" s="27" t="n">
+      <c r="F16" s="30" t="n">
         <v>1</v>
       </c>
       <c r="G16" s="23" t="inlineStr">
@@ -4917,7 +5449,7 @@
           <t>商店 1,200 金幣</t>
         </is>
       </c>
-      <c r="N16" s="27" t="n">
+      <c r="N16" s="30" t="n">
         <v>4</v>
       </c>
       <c r="O16" s="23" t="inlineStr">
@@ -4930,15 +5462,15 @@
           <t>mikado_pheasant-2.png</t>
         </is>
       </c>
-      <c r="Q16" s="25" t="inlineStr">
+      <c r="Q16" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="R16" s="26" t="inlineStr"/>
+      <c r="R16" s="29" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="24" t="n">
+      <c r="A17" s="27" t="n">
         <v>13</v>
       </c>
       <c r="B17" s="22" t="inlineStr">
@@ -4961,7 +5493,7 @@
           <t>山羊</t>
         </is>
       </c>
-      <c r="F17" s="24" t="n">
+      <c r="F17" s="27" t="n">
         <v>1</v>
       </c>
       <c r="G17" s="22" t="inlineStr">
@@ -4999,7 +5531,7 @@
           <t>商店 1,600 金幣</t>
         </is>
       </c>
-      <c r="N17" s="24" t="n">
+      <c r="N17" s="27" t="n">
         <v>4</v>
       </c>
       <c r="O17" s="22" t="inlineStr">
@@ -5012,15 +5544,15 @@
           <t>serow-2.png</t>
         </is>
       </c>
-      <c r="Q17" s="25" t="inlineStr">
+      <c r="Q17" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="R17" s="26" t="inlineStr"/>
+      <c r="R17" s="29" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="27" t="n">
+      <c r="A18" s="30" t="n">
         <v>14</v>
       </c>
       <c r="B18" s="23" t="inlineStr">
@@ -5043,7 +5575,7 @@
           <t>猛禽</t>
         </is>
       </c>
-      <c r="F18" s="27" t="n">
+      <c r="F18" s="30" t="n">
         <v>1</v>
       </c>
       <c r="G18" s="23" t="inlineStr">
@@ -5081,7 +5613,7 @@
           <t>商店 1,400 金幣</t>
         </is>
       </c>
-      <c r="N18" s="27" t="n">
+      <c r="N18" s="30" t="n">
         <v>4</v>
       </c>
       <c r="O18" s="23" t="inlineStr">
@@ -5094,15 +5626,15 @@
           <t>crested_serpent_eagle-2.png</t>
         </is>
       </c>
-      <c r="Q18" s="25" t="inlineStr">
+      <c r="Q18" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="R18" s="26" t="inlineStr"/>
+      <c r="R18" s="29" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="24" t="n">
+      <c r="A19" s="27" t="n">
         <v>15</v>
       </c>
       <c r="B19" s="22" t="inlineStr">
@@ -5125,7 +5657,7 @@
           <t>鳥</t>
         </is>
       </c>
-      <c r="F19" s="24" t="n">
+      <c r="F19" s="27" t="n">
         <v>1</v>
       </c>
       <c r="G19" s="22" t="inlineStr">
@@ -5163,7 +5695,7 @@
           <t>商店 1,800 金幣</t>
         </is>
       </c>
-      <c r="N19" s="24" t="n">
+      <c r="N19" s="27" t="n">
         <v>4</v>
       </c>
       <c r="O19" s="22" t="inlineStr">
@@ -5176,15 +5708,15 @@
           <t>maroon_oriole-2.png</t>
         </is>
       </c>
-      <c r="Q19" s="25" t="inlineStr">
+      <c r="Q19" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="R19" s="26" t="inlineStr"/>
+      <c r="R19" s="29" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="27" t="n">
+      <c r="A20" s="30" t="n">
         <v>16</v>
       </c>
       <c r="B20" s="23" t="inlineStr">
@@ -5207,7 +5739,7 @@
           <t>鳥</t>
         </is>
       </c>
-      <c r="F20" s="27" t="n">
+      <c r="F20" s="30" t="n">
         <v>1</v>
       </c>
       <c r="G20" s="23" t="inlineStr">
@@ -5245,7 +5777,7 @@
           <t>商店 70 寶石</t>
         </is>
       </c>
-      <c r="N20" s="27" t="n">
+      <c r="N20" s="30" t="n">
         <v>4</v>
       </c>
       <c r="O20" s="23" t="inlineStr">
@@ -5258,15 +5790,15 @@
           <t>yellow_tit-2.png</t>
         </is>
       </c>
-      <c r="Q20" s="25" t="inlineStr">
+      <c r="Q20" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="R20" s="26" t="inlineStr"/>
+      <c r="R20" s="29" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="24" t="n">
+      <c r="A21" s="27" t="n">
         <v>17</v>
       </c>
       <c r="B21" s="22" t="inlineStr">
@@ -5289,7 +5821,7 @@
           <t>貓頭鷹</t>
         </is>
       </c>
-      <c r="F21" s="24" t="n">
+      <c r="F21" s="27" t="n">
         <v>1</v>
       </c>
       <c r="G21" s="22" t="inlineStr">
@@ -5327,7 +5859,7 @@
           <t>商店 90 寶石</t>
         </is>
       </c>
-      <c r="N21" s="24" t="n">
+      <c r="N21" s="27" t="n">
         <v>4</v>
       </c>
       <c r="O21" s="22" t="inlineStr">
@@ -5340,15 +5872,15 @@
           <t>fish_owl-2.png</t>
         </is>
       </c>
-      <c r="Q21" s="25" t="inlineStr">
+      <c r="Q21" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="R21" s="26" t="inlineStr"/>
+      <c r="R21" s="29" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="27" t="n">
+      <c r="A22" s="30" t="n">
         <v>18</v>
       </c>
       <c r="B22" s="23" t="inlineStr">
@@ -5371,7 +5903,7 @@
           <t>貓科</t>
         </is>
       </c>
-      <c r="F22" s="27" t="n">
+      <c r="F22" s="30" t="n">
         <v>3</v>
       </c>
       <c r="G22" s="23" t="inlineStr">
@@ -5409,7 +5941,7 @@
           <t>一開始就能找</t>
         </is>
       </c>
-      <c r="N22" s="27" t="n">
+      <c r="N22" s="30" t="n">
         <v>3</v>
       </c>
       <c r="O22" s="23" t="inlineStr">
@@ -5422,15 +5954,15 @@
           <t>iriomote_cat-0/1/2.png</t>
         </is>
       </c>
-      <c r="Q22" s="25" t="inlineStr">
+      <c r="Q22" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="R22" s="26" t="inlineStr"/>
+      <c r="R22" s="29" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="24" t="n">
+      <c r="A23" s="27" t="n">
         <v>19</v>
       </c>
       <c r="B23" s="22" t="inlineStr">
@@ -5453,7 +5985,7 @@
           <t>鳥</t>
         </is>
       </c>
-      <c r="F23" s="24" t="n">
+      <c r="F23" s="27" t="n">
         <v>3</v>
       </c>
       <c r="G23" s="22" t="inlineStr">
@@ -5491,7 +6023,7 @@
           <t>一開始就能找</t>
         </is>
       </c>
-      <c r="N23" s="24" t="n">
+      <c r="N23" s="27" t="n">
         <v>3</v>
       </c>
       <c r="O23" s="22" t="inlineStr">
@@ -5504,15 +6036,15 @@
           <t>okinawa_woodpecker-0/1/2.png</t>
         </is>
       </c>
-      <c r="Q23" s="25" t="inlineStr">
+      <c r="Q23" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="R23" s="26" t="inlineStr"/>
+      <c r="R23" s="29" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="27" t="n">
+      <c r="A24" s="30" t="n">
         <v>20</v>
       </c>
       <c r="B24" s="23" t="inlineStr">
@@ -5535,7 +6067,7 @@
           <t>山羊</t>
         </is>
       </c>
-      <c r="F24" s="27" t="n">
+      <c r="F24" s="30" t="n">
         <v>3</v>
       </c>
       <c r="G24" s="23" t="inlineStr">
@@ -5573,7 +6105,7 @@
           <t>修好「清出杉林小徑」</t>
         </is>
       </c>
-      <c r="N24" s="27" t="n">
+      <c r="N24" s="30" t="n">
         <v>3</v>
       </c>
       <c r="O24" s="23" t="inlineStr">
@@ -5586,15 +6118,15 @@
           <t>japanese_serow-0/1/2.png</t>
         </is>
       </c>
-      <c r="Q24" s="25" t="inlineStr">
+      <c r="Q24" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="R24" s="26" t="inlineStr"/>
+      <c r="R24" s="29" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="24" t="n">
+      <c r="A25" s="27" t="n">
         <v>21</v>
       </c>
       <c r="B25" s="22" t="inlineStr">
@@ -5617,7 +6149,7 @@
           <t>雉雞</t>
         </is>
       </c>
-      <c r="F25" s="24" t="n">
+      <c r="F25" s="27" t="n">
         <v>3</v>
       </c>
       <c r="G25" s="22" t="inlineStr">
@@ -5655,7 +6187,7 @@
           <t>修好「復原里山梯田」</t>
         </is>
       </c>
-      <c r="N25" s="24" t="n">
+      <c r="N25" s="27" t="n">
         <v>3</v>
       </c>
       <c r="O25" s="22" t="inlineStr">
@@ -5668,15 +6200,15 @@
           <t>ptarmigan-0/1/2.png</t>
         </is>
       </c>
-      <c r="Q25" s="25" t="inlineStr">
+      <c r="Q25" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="R25" s="26" t="inlineStr"/>
+      <c r="R25" s="29" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="27" t="n">
+      <c r="A26" s="30" t="n">
         <v>22</v>
       </c>
       <c r="B26" s="23" t="inlineStr">
@@ -5699,7 +6231,7 @@
           <t>貓頭鷹</t>
         </is>
       </c>
-      <c r="F26" s="27" t="n">
+      <c r="F26" s="30" t="n">
         <v>3</v>
       </c>
       <c r="G26" s="23" t="inlineStr">
@@ -5737,7 +6269,7 @@
           <t>修好「修好山中小屋」</t>
         </is>
       </c>
-      <c r="N26" s="27" t="n">
+      <c r="N26" s="30" t="n">
         <v>3</v>
       </c>
       <c r="O26" s="23" t="inlineStr">
@@ -5750,15 +6282,15 @@
           <t>blakiston_owl-0/1/2.png</t>
         </is>
       </c>
-      <c r="Q26" s="25" t="inlineStr">
+      <c r="Q26" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="R26" s="26" t="inlineStr"/>
+      <c r="R26" s="29" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="24" t="n">
+      <c r="A27" s="27" t="n">
         <v>23</v>
       </c>
       <c r="B27" s="22" t="inlineStr">
@@ -5781,7 +6313,7 @@
           <t>貓科</t>
         </is>
       </c>
-      <c r="F27" s="24" t="n">
+      <c r="F27" s="27" t="n">
         <v>3</v>
       </c>
       <c r="G27" s="22" t="inlineStr">
@@ -5819,7 +6351,7 @@
           <t>修好「疏伐過密的竹林」</t>
         </is>
       </c>
-      <c r="N27" s="24" t="n">
+      <c r="N27" s="27" t="n">
         <v>3</v>
       </c>
       <c r="O27" s="22" t="inlineStr">
@@ -5832,15 +6364,15 @@
           <t>tsushima_cat-0/1/2.png</t>
         </is>
       </c>
-      <c r="Q27" s="25" t="inlineStr">
+      <c r="Q27" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="R27" s="26" t="inlineStr"/>
+      <c r="R27" s="29" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="27" t="n">
+      <c r="A28" s="30" t="n">
         <v>24</v>
       </c>
       <c r="B28" s="23" t="inlineStr">
@@ -5863,7 +6395,7 @@
           <t>猛禽</t>
         </is>
       </c>
-      <c r="F28" s="27" t="n">
+      <c r="F28" s="30" t="n">
         <v>3</v>
       </c>
       <c r="G28" s="23" t="inlineStr">
@@ -5901,7 +6433,7 @@
           <t>修好「恢復清澈溪流」</t>
         </is>
       </c>
-      <c r="N28" s="27" t="n">
+      <c r="N28" s="30" t="n">
         <v>3</v>
       </c>
       <c r="O28" s="23" t="inlineStr">
@@ -5914,15 +6446,15 @@
           <t>steller_eagle-0/1/2.png</t>
         </is>
       </c>
-      <c r="Q28" s="25" t="inlineStr">
+      <c r="Q28" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="R28" s="26" t="inlineStr"/>
+      <c r="R28" s="29" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="24" t="n">
+      <c r="A29" s="27" t="n">
         <v>25</v>
       </c>
       <c r="B29" s="22" t="inlineStr">
@@ -5945,7 +6477,7 @@
           <t>熊</t>
         </is>
       </c>
-      <c r="F29" s="24" t="n">
+      <c r="F29" s="27" t="n">
         <v>3</v>
       </c>
       <c r="G29" s="22" t="inlineStr">
@@ -5983,7 +6515,7 @@
           <t>修好「設立野生動物保護站」</t>
         </is>
       </c>
-      <c r="N29" s="24" t="n">
+      <c r="N29" s="27" t="n">
         <v>3</v>
       </c>
       <c r="O29" s="22" t="inlineStr">
@@ -5996,15 +6528,15 @@
           <t>moon_bear-0/1/2.png</t>
         </is>
       </c>
-      <c r="Q29" s="25" t="inlineStr">
+      <c r="Q29" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="R29" s="26" t="inlineStr"/>
+      <c r="R29" s="29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="27" t="n">
+      <c r="A30" s="30" t="n">
         <v>26</v>
       </c>
       <c r="B30" s="23" t="inlineStr">
@@ -6027,7 +6559,7 @@
           <t>貓科</t>
         </is>
       </c>
-      <c r="F30" s="27" t="n">
+      <c r="F30" s="30" t="n">
         <v>1</v>
       </c>
       <c r="G30" s="23" t="inlineStr">
@@ -6065,7 +6597,7 @@
           <t>Plus 會員</t>
         </is>
       </c>
-      <c r="N30" s="27" t="n">
+      <c r="N30" s="30" t="n">
         <v>5</v>
       </c>
       <c r="O30" s="23" t="inlineStr">
@@ -6078,15 +6610,15 @@
           <t>clouded_leopard-2.png</t>
         </is>
       </c>
-      <c r="Q30" s="25" t="inlineStr">
+      <c r="Q30" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="R30" s="26" t="inlineStr"/>
+      <c r="R30" s="29" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="24" t="n">
+      <c r="A31" s="27" t="n">
         <v>27</v>
       </c>
       <c r="B31" s="22" t="inlineStr">
@@ -6109,7 +6641,7 @@
           <t>猛禽</t>
         </is>
       </c>
-      <c r="F31" s="24" t="n">
+      <c r="F31" s="27" t="n">
         <v>1</v>
       </c>
       <c r="G31" s="22" t="inlineStr">
@@ -6147,7 +6679,7 @@
           <t>Plus 會員</t>
         </is>
       </c>
-      <c r="N31" s="24" t="n">
+      <c r="N31" s="27" t="n">
         <v>5</v>
       </c>
       <c r="O31" s="22" t="inlineStr">
@@ -6160,15 +6692,15 @@
           <t>black_eagle-2.png</t>
         </is>
       </c>
-      <c r="Q31" s="25" t="inlineStr">
+      <c r="Q31" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="R31" s="26" t="inlineStr"/>
+      <c r="R31" s="29" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="27" t="n">
+      <c r="A32" s="30" t="n">
         <v>28</v>
       </c>
       <c r="B32" s="23" t="inlineStr">
@@ -6191,7 +6723,7 @@
           <t>貓頭鷹</t>
         </is>
       </c>
-      <c r="F32" s="27" t="n">
+      <c r="F32" s="30" t="n">
         <v>1</v>
       </c>
       <c r="G32" s="23" t="inlineStr">
@@ -6229,7 +6761,7 @@
           <t>Plus 會員</t>
         </is>
       </c>
-      <c r="N32" s="27" t="n">
+      <c r="N32" s="30" t="n">
         <v>5</v>
       </c>
       <c r="O32" s="23" t="inlineStr">
@@ -6242,15 +6774,15 @@
           <t>lanyu_scops_owl-2.png</t>
         </is>
       </c>
-      <c r="Q32" s="25" t="inlineStr">
+      <c r="Q32" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="R32" s="26" t="inlineStr"/>
+      <c r="R32" s="29" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="24" t="n">
+      <c r="A33" s="27" t="n">
         <v>29</v>
       </c>
       <c r="B33" s="22" t="inlineStr">
@@ -6273,7 +6805,7 @@
           <t>雉雞</t>
         </is>
       </c>
-      <c r="F33" s="24" t="n">
+      <c r="F33" s="27" t="n">
         <v>1</v>
       </c>
       <c r="G33" s="22" t="inlineStr">
@@ -6311,7 +6843,7 @@
           <t>Plus 會員</t>
         </is>
       </c>
-      <c r="N33" s="24" t="n">
+      <c r="N33" s="27" t="n">
         <v>5</v>
       </c>
       <c r="O33" s="22" t="inlineStr">
@@ -6324,12 +6856,12 @@
           <t>hill_partridge-2.png</t>
         </is>
       </c>
-      <c r="Q33" s="25" t="inlineStr">
+      <c r="Q33" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="R33" s="26" t="inlineStr"/>
+      <c r="R33" s="29" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:R33"/>
@@ -6347,7 +6879,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6453,7 +6985,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="24" t="n">
+      <c r="A5" s="27" t="n">
         <v>1</v>
       </c>
       <c r="B5" s="22" t="inlineStr">
@@ -6471,7 +7003,7 @@
           <t>鳥</t>
         </is>
       </c>
-      <c r="E5" s="24" t="n">
+      <c r="E5" s="27" t="n">
         <v>3</v>
       </c>
       <c r="F5" s="22" t="inlineStr">
@@ -6494,7 +7026,7 @@
           <t>≤ 120 KB</t>
         </is>
       </c>
-      <c r="J5" s="24" t="n">
+      <c r="J5" s="27" t="n">
         <v>1</v>
       </c>
       <c r="K5" s="22" t="inlineStr">
@@ -6502,15 +7034,15 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="L5" s="25" t="inlineStr">
+      <c r="L5" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="M5" s="26" t="inlineStr"/>
+      <c r="M5" s="29" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="27" t="n">
+      <c r="A6" s="30" t="n">
         <v>2</v>
       </c>
       <c r="B6" s="23" t="inlineStr">
@@ -6528,7 +7060,7 @@
           <t>貓頭鷹</t>
         </is>
       </c>
-      <c r="E6" s="27" t="n">
+      <c r="E6" s="30" t="n">
         <v>3</v>
       </c>
       <c r="F6" s="23" t="inlineStr">
@@ -6551,7 +7083,7 @@
           <t>≤ 120 KB</t>
         </is>
       </c>
-      <c r="J6" s="27" t="n">
+      <c r="J6" s="30" t="n">
         <v>1</v>
       </c>
       <c r="K6" s="23" t="inlineStr">
@@ -6559,15 +7091,15 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="L6" s="25" t="inlineStr">
+      <c r="L6" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="M6" s="26" t="inlineStr"/>
+      <c r="M6" s="29" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="24" t="n">
+      <c r="A7" s="27" t="n">
         <v>3</v>
       </c>
       <c r="B7" s="22" t="inlineStr">
@@ -6585,7 +7117,7 @@
           <t>穿山甲</t>
         </is>
       </c>
-      <c r="E7" s="24" t="n">
+      <c r="E7" s="27" t="n">
         <v>3</v>
       </c>
       <c r="F7" s="22" t="inlineStr">
@@ -6608,7 +7140,7 @@
           <t>≤ 120 KB</t>
         </is>
       </c>
-      <c r="J7" s="24" t="n">
+      <c r="J7" s="27" t="n">
         <v>1</v>
       </c>
       <c r="K7" s="22" t="inlineStr">
@@ -6616,15 +7148,15 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="L7" s="25" t="inlineStr">
+      <c r="L7" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="M7" s="26" t="inlineStr"/>
+      <c r="M7" s="29" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="27" t="n">
+      <c r="A8" s="30" t="n">
         <v>4</v>
       </c>
       <c r="B8" s="23" t="inlineStr">
@@ -6642,7 +7174,7 @@
           <t>鳥</t>
         </is>
       </c>
-      <c r="E8" s="27" t="n">
+      <c r="E8" s="30" t="n">
         <v>3</v>
       </c>
       <c r="F8" s="23" t="inlineStr">
@@ -6665,7 +7197,7 @@
           <t>≤ 120 KB</t>
         </is>
       </c>
-      <c r="J8" s="27" t="n">
+      <c r="J8" s="30" t="n">
         <v>1</v>
       </c>
       <c r="K8" s="23" t="inlineStr">
@@ -6673,15 +7205,15 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="L8" s="25" t="inlineStr">
+      <c r="L8" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="M8" s="26" t="inlineStr"/>
+      <c r="M8" s="29" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="24" t="n">
+      <c r="A9" s="27" t="n">
         <v>5</v>
       </c>
       <c r="B9" s="22" t="inlineStr">
@@ -6699,7 +7231,7 @@
           <t>貓科</t>
         </is>
       </c>
-      <c r="E9" s="24" t="n">
+      <c r="E9" s="27" t="n">
         <v>3</v>
       </c>
       <c r="F9" s="22" t="inlineStr">
@@ -6722,7 +7254,7 @@
           <t>≤ 120 KB</t>
         </is>
       </c>
-      <c r="J9" s="24" t="n">
+      <c r="J9" s="27" t="n">
         <v>1</v>
       </c>
       <c r="K9" s="22" t="inlineStr">
@@ -6730,19 +7262,19 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="L9" s="28" t="inlineStr">
+      <c r="L9" s="31" t="inlineStr">
         <is>
           <t>製作中</t>
         </is>
       </c>
-      <c r="M9" s="26" t="inlineStr">
+      <c r="M9" s="29" t="inlineStr">
         <is>
           <t>成年完成；目前未壓縮 460 KB 要壓到 ≤120 KB；後腿之間一小撮淺色未解；幼年、亞成年未做</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="27" t="n">
+      <c r="A10" s="30" t="n">
         <v>6</v>
       </c>
       <c r="B10" s="23" t="inlineStr">
@@ -6760,7 +7292,7 @@
           <t>雉雞</t>
         </is>
       </c>
-      <c r="E10" s="27" t="n">
+      <c r="E10" s="30" t="n">
         <v>3</v>
       </c>
       <c r="F10" s="23" t="inlineStr">
@@ -6783,7 +7315,7 @@
           <t>≤ 120 KB</t>
         </is>
       </c>
-      <c r="J10" s="27" t="n">
+      <c r="J10" s="30" t="n">
         <v>2</v>
       </c>
       <c r="K10" s="23" t="inlineStr">
@@ -6791,15 +7323,15 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="L10" s="25" t="inlineStr">
+      <c r="L10" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="M10" s="26" t="inlineStr"/>
+      <c r="M10" s="29" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="24" t="n">
+      <c r="A11" s="27" t="n">
         <v>7</v>
       </c>
       <c r="B11" s="22" t="inlineStr">
@@ -6817,7 +7349,7 @@
           <t>貂、獴</t>
         </is>
       </c>
-      <c r="E11" s="24" t="n">
+      <c r="E11" s="27" t="n">
         <v>3</v>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -6840,7 +7372,7 @@
           <t>≤ 120 KB</t>
         </is>
       </c>
-      <c r="J11" s="24" t="n">
+      <c r="J11" s="27" t="n">
         <v>2</v>
       </c>
       <c r="K11" s="22" t="inlineStr">
@@ -6848,15 +7380,15 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="L11" s="25" t="inlineStr">
+      <c r="L11" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="M11" s="26" t="inlineStr"/>
+      <c r="M11" s="29" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="27" t="n">
+      <c r="A12" s="30" t="n">
         <v>8</v>
       </c>
       <c r="B12" s="23" t="inlineStr">
@@ -6874,7 +7406,7 @@
           <t>貂、獴</t>
         </is>
       </c>
-      <c r="E12" s="27" t="n">
+      <c r="E12" s="30" t="n">
         <v>3</v>
       </c>
       <c r="F12" s="23" t="inlineStr">
@@ -6897,7 +7429,7 @@
           <t>≤ 120 KB</t>
         </is>
       </c>
-      <c r="J12" s="27" t="n">
+      <c r="J12" s="30" t="n">
         <v>2</v>
       </c>
       <c r="K12" s="23" t="inlineStr">
@@ -6905,15 +7437,15 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="L12" s="25" t="inlineStr">
+      <c r="L12" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="M12" s="26" t="inlineStr"/>
+      <c r="M12" s="29" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="24" t="n">
+      <c r="A13" s="27" t="n">
         <v>9</v>
       </c>
       <c r="B13" s="22" t="inlineStr">
@@ -6931,7 +7463,7 @@
           <t>猛禽</t>
         </is>
       </c>
-      <c r="E13" s="24" t="n">
+      <c r="E13" s="27" t="n">
         <v>3</v>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -6954,7 +7486,7 @@
           <t>≤ 120 KB</t>
         </is>
       </c>
-      <c r="J13" s="24" t="n">
+      <c r="J13" s="27" t="n">
         <v>2</v>
       </c>
       <c r="K13" s="22" t="inlineStr">
@@ -6962,15 +7494,15 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="L13" s="25" t="inlineStr">
+      <c r="L13" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="M13" s="26" t="inlineStr"/>
+      <c r="M13" s="29" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="27" t="n">
+      <c r="A14" s="30" t="n">
         <v>10</v>
       </c>
       <c r="B14" s="23" t="inlineStr">
@@ -6988,7 +7520,7 @@
           <t>熊</t>
         </is>
       </c>
-      <c r="E14" s="27" t="n">
+      <c r="E14" s="30" t="n">
         <v>3</v>
       </c>
       <c r="F14" s="23" t="inlineStr">
@@ -7011,7 +7543,7 @@
           <t>≤ 120 KB</t>
         </is>
       </c>
-      <c r="J14" s="27" t="n">
+      <c r="J14" s="30" t="n">
         <v>2</v>
       </c>
       <c r="K14" s="23" t="inlineStr">
@@ -7019,15 +7551,15 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="L14" s="25" t="inlineStr">
+      <c r="L14" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="M14" s="26" t="inlineStr"/>
+      <c r="M14" s="29" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="24" t="n">
+      <c r="A15" s="27" t="n">
         <v>11</v>
       </c>
       <c r="B15" s="22" t="inlineStr">
@@ -7045,7 +7577,7 @@
           <t>貓科</t>
         </is>
       </c>
-      <c r="E15" s="24" t="n">
+      <c r="E15" s="27" t="n">
         <v>1</v>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -7068,7 +7600,7 @@
           <t>≤ 120 KB</t>
         </is>
       </c>
-      <c r="J15" s="24" t="n">
+      <c r="J15" s="27" t="n">
         <v>4</v>
       </c>
       <c r="K15" s="22" t="inlineStr">
@@ -7076,15 +7608,15 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="L15" s="25" t="inlineStr">
+      <c r="L15" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="M15" s="26" t="inlineStr"/>
+      <c r="M15" s="29" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="27" t="n">
+      <c r="A16" s="30" t="n">
         <v>12</v>
       </c>
       <c r="B16" s="23" t="inlineStr">
@@ -7102,7 +7634,7 @@
           <t>雉雞</t>
         </is>
       </c>
-      <c r="E16" s="27" t="n">
+      <c r="E16" s="30" t="n">
         <v>1</v>
       </c>
       <c r="F16" s="23" t="inlineStr">
@@ -7125,7 +7657,7 @@
           <t>≤ 120 KB</t>
         </is>
       </c>
-      <c r="J16" s="27" t="n">
+      <c r="J16" s="30" t="n">
         <v>4</v>
       </c>
       <c r="K16" s="23" t="inlineStr">
@@ -7133,15 +7665,15 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="L16" s="25" t="inlineStr">
+      <c r="L16" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="M16" s="26" t="inlineStr"/>
+      <c r="M16" s="29" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="24" t="n">
+      <c r="A17" s="27" t="n">
         <v>13</v>
       </c>
       <c r="B17" s="22" t="inlineStr">
@@ -7159,7 +7691,7 @@
           <t>山羊</t>
         </is>
       </c>
-      <c r="E17" s="24" t="n">
+      <c r="E17" s="27" t="n">
         <v>1</v>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -7182,7 +7714,7 @@
           <t>≤ 120 KB</t>
         </is>
       </c>
-      <c r="J17" s="24" t="n">
+      <c r="J17" s="27" t="n">
         <v>4</v>
       </c>
       <c r="K17" s="22" t="inlineStr">
@@ -7190,15 +7722,15 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="L17" s="25" t="inlineStr">
+      <c r="L17" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="M17" s="26" t="inlineStr"/>
+      <c r="M17" s="29" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="27" t="n">
+      <c r="A18" s="30" t="n">
         <v>14</v>
       </c>
       <c r="B18" s="23" t="inlineStr">
@@ -7216,7 +7748,7 @@
           <t>猛禽</t>
         </is>
       </c>
-      <c r="E18" s="27" t="n">
+      <c r="E18" s="30" t="n">
         <v>1</v>
       </c>
       <c r="F18" s="23" t="inlineStr">
@@ -7239,7 +7771,7 @@
           <t>≤ 120 KB</t>
         </is>
       </c>
-      <c r="J18" s="27" t="n">
+      <c r="J18" s="30" t="n">
         <v>4</v>
       </c>
       <c r="K18" s="23" t="inlineStr">
@@ -7247,15 +7779,15 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="L18" s="25" t="inlineStr">
+      <c r="L18" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="M18" s="26" t="inlineStr"/>
+      <c r="M18" s="29" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="24" t="n">
+      <c r="A19" s="27" t="n">
         <v>15</v>
       </c>
       <c r="B19" s="22" t="inlineStr">
@@ -7273,7 +7805,7 @@
           <t>鳥</t>
         </is>
       </c>
-      <c r="E19" s="24" t="n">
+      <c r="E19" s="27" t="n">
         <v>1</v>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -7296,7 +7828,7 @@
           <t>≤ 120 KB</t>
         </is>
       </c>
-      <c r="J19" s="24" t="n">
+      <c r="J19" s="27" t="n">
         <v>4</v>
       </c>
       <c r="K19" s="22" t="inlineStr">
@@ -7304,15 +7836,15 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="L19" s="25" t="inlineStr">
+      <c r="L19" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="M19" s="26" t="inlineStr"/>
+      <c r="M19" s="29" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="27" t="n">
+      <c r="A20" s="30" t="n">
         <v>16</v>
       </c>
       <c r="B20" s="23" t="inlineStr">
@@ -7330,7 +7862,7 @@
           <t>鳥</t>
         </is>
       </c>
-      <c r="E20" s="27" t="n">
+      <c r="E20" s="30" t="n">
         <v>1</v>
       </c>
       <c r="F20" s="23" t="inlineStr">
@@ -7353,7 +7885,7 @@
           <t>≤ 120 KB</t>
         </is>
       </c>
-      <c r="J20" s="27" t="n">
+      <c r="J20" s="30" t="n">
         <v>4</v>
       </c>
       <c r="K20" s="23" t="inlineStr">
@@ -7361,15 +7893,15 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="L20" s="25" t="inlineStr">
+      <c r="L20" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="M20" s="26" t="inlineStr"/>
+      <c r="M20" s="29" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="24" t="n">
+      <c r="A21" s="27" t="n">
         <v>17</v>
       </c>
       <c r="B21" s="22" t="inlineStr">
@@ -7387,7 +7919,7 @@
           <t>貓頭鷹</t>
         </is>
       </c>
-      <c r="E21" s="24" t="n">
+      <c r="E21" s="27" t="n">
         <v>1</v>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -7410,7 +7942,7 @@
           <t>≤ 120 KB</t>
         </is>
       </c>
-      <c r="J21" s="24" t="n">
+      <c r="J21" s="27" t="n">
         <v>4</v>
       </c>
       <c r="K21" s="22" t="inlineStr">
@@ -7418,15 +7950,15 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="L21" s="25" t="inlineStr">
+      <c r="L21" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="M21" s="26" t="inlineStr"/>
+      <c r="M21" s="29" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="27" t="n">
+      <c r="A22" s="30" t="n">
         <v>18</v>
       </c>
       <c r="B22" s="23" t="inlineStr">
@@ -7444,7 +7976,7 @@
           <t>貓科</t>
         </is>
       </c>
-      <c r="E22" s="27" t="n">
+      <c r="E22" s="30" t="n">
         <v>3</v>
       </c>
       <c r="F22" s="23" t="inlineStr">
@@ -7467,7 +7999,7 @@
           <t>≤ 120 KB</t>
         </is>
       </c>
-      <c r="J22" s="27" t="n">
+      <c r="J22" s="30" t="n">
         <v>3</v>
       </c>
       <c r="K22" s="23" t="inlineStr">
@@ -7475,15 +8007,15 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="L22" s="25" t="inlineStr">
+      <c r="L22" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="M22" s="26" t="inlineStr"/>
+      <c r="M22" s="29" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="24" t="n">
+      <c r="A23" s="27" t="n">
         <v>19</v>
       </c>
       <c r="B23" s="22" t="inlineStr">
@@ -7501,7 +8033,7 @@
           <t>鳥</t>
         </is>
       </c>
-      <c r="E23" s="24" t="n">
+      <c r="E23" s="27" t="n">
         <v>3</v>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -7524,7 +8056,7 @@
           <t>≤ 120 KB</t>
         </is>
       </c>
-      <c r="J23" s="24" t="n">
+      <c r="J23" s="27" t="n">
         <v>3</v>
       </c>
       <c r="K23" s="22" t="inlineStr">
@@ -7532,15 +8064,15 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="L23" s="25" t="inlineStr">
+      <c r="L23" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="M23" s="26" t="inlineStr"/>
+      <c r="M23" s="29" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="27" t="n">
+      <c r="A24" s="30" t="n">
         <v>20</v>
       </c>
       <c r="B24" s="23" t="inlineStr">
@@ -7558,7 +8090,7 @@
           <t>山羊</t>
         </is>
       </c>
-      <c r="E24" s="27" t="n">
+      <c r="E24" s="30" t="n">
         <v>3</v>
       </c>
       <c r="F24" s="23" t="inlineStr">
@@ -7581,7 +8113,7 @@
           <t>≤ 120 KB</t>
         </is>
       </c>
-      <c r="J24" s="27" t="n">
+      <c r="J24" s="30" t="n">
         <v>3</v>
       </c>
       <c r="K24" s="23" t="inlineStr">
@@ -7589,15 +8121,15 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="L24" s="25" t="inlineStr">
+      <c r="L24" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="M24" s="26" t="inlineStr"/>
+      <c r="M24" s="29" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="24" t="n">
+      <c r="A25" s="27" t="n">
         <v>21</v>
       </c>
       <c r="B25" s="22" t="inlineStr">
@@ -7615,7 +8147,7 @@
           <t>雉雞</t>
         </is>
       </c>
-      <c r="E25" s="24" t="n">
+      <c r="E25" s="27" t="n">
         <v>3</v>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -7638,7 +8170,7 @@
           <t>≤ 120 KB</t>
         </is>
       </c>
-      <c r="J25" s="24" t="n">
+      <c r="J25" s="27" t="n">
         <v>3</v>
       </c>
       <c r="K25" s="22" t="inlineStr">
@@ -7646,15 +8178,15 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="L25" s="25" t="inlineStr">
+      <c r="L25" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="M25" s="26" t="inlineStr"/>
+      <c r="M25" s="29" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="27" t="n">
+      <c r="A26" s="30" t="n">
         <v>22</v>
       </c>
       <c r="B26" s="23" t="inlineStr">
@@ -7672,7 +8204,7 @@
           <t>貓頭鷹</t>
         </is>
       </c>
-      <c r="E26" s="27" t="n">
+      <c r="E26" s="30" t="n">
         <v>3</v>
       </c>
       <c r="F26" s="23" t="inlineStr">
@@ -7695,7 +8227,7 @@
           <t>≤ 120 KB</t>
         </is>
       </c>
-      <c r="J26" s="27" t="n">
+      <c r="J26" s="30" t="n">
         <v>3</v>
       </c>
       <c r="K26" s="23" t="inlineStr">
@@ -7703,15 +8235,15 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="L26" s="25" t="inlineStr">
+      <c r="L26" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="M26" s="26" t="inlineStr"/>
+      <c r="M26" s="29" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="24" t="n">
+      <c r="A27" s="27" t="n">
         <v>23</v>
       </c>
       <c r="B27" s="22" t="inlineStr">
@@ -7729,7 +8261,7 @@
           <t>貓科</t>
         </is>
       </c>
-      <c r="E27" s="24" t="n">
+      <c r="E27" s="27" t="n">
         <v>3</v>
       </c>
       <c r="F27" s="22" t="inlineStr">
@@ -7752,7 +8284,7 @@
           <t>≤ 120 KB</t>
         </is>
       </c>
-      <c r="J27" s="24" t="n">
+      <c r="J27" s="27" t="n">
         <v>3</v>
       </c>
       <c r="K27" s="22" t="inlineStr">
@@ -7760,15 +8292,15 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="L27" s="25" t="inlineStr">
+      <c r="L27" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="M27" s="26" t="inlineStr"/>
+      <c r="M27" s="29" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="27" t="n">
+      <c r="A28" s="30" t="n">
         <v>24</v>
       </c>
       <c r="B28" s="23" t="inlineStr">
@@ -7786,7 +8318,7 @@
           <t>猛禽</t>
         </is>
       </c>
-      <c r="E28" s="27" t="n">
+      <c r="E28" s="30" t="n">
         <v>3</v>
       </c>
       <c r="F28" s="23" t="inlineStr">
@@ -7809,7 +8341,7 @@
           <t>≤ 120 KB</t>
         </is>
       </c>
-      <c r="J28" s="27" t="n">
+      <c r="J28" s="30" t="n">
         <v>3</v>
       </c>
       <c r="K28" s="23" t="inlineStr">
@@ -7817,15 +8349,15 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="L28" s="25" t="inlineStr">
+      <c r="L28" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="M28" s="26" t="inlineStr"/>
+      <c r="M28" s="29" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="24" t="n">
+      <c r="A29" s="27" t="n">
         <v>25</v>
       </c>
       <c r="B29" s="22" t="inlineStr">
@@ -7843,7 +8375,7 @@
           <t>熊</t>
         </is>
       </c>
-      <c r="E29" s="24" t="n">
+      <c r="E29" s="27" t="n">
         <v>3</v>
       </c>
       <c r="F29" s="22" t="inlineStr">
@@ -7866,7 +8398,7 @@
           <t>≤ 120 KB</t>
         </is>
       </c>
-      <c r="J29" s="24" t="n">
+      <c r="J29" s="27" t="n">
         <v>3</v>
       </c>
       <c r="K29" s="22" t="inlineStr">
@@ -7874,15 +8406,15 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="L29" s="25" t="inlineStr">
+      <c r="L29" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="M29" s="26" t="inlineStr"/>
+      <c r="M29" s="29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="27" t="n">
+      <c r="A30" s="30" t="n">
         <v>26</v>
       </c>
       <c r="B30" s="23" t="inlineStr">
@@ -7900,7 +8432,7 @@
           <t>貓科</t>
         </is>
       </c>
-      <c r="E30" s="27" t="n">
+      <c r="E30" s="30" t="n">
         <v>1</v>
       </c>
       <c r="F30" s="23" t="inlineStr">
@@ -7923,7 +8455,7 @@
           <t>≤ 120 KB</t>
         </is>
       </c>
-      <c r="J30" s="27" t="n">
+      <c r="J30" s="30" t="n">
         <v>5</v>
       </c>
       <c r="K30" s="23" t="inlineStr">
@@ -7931,15 +8463,15 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="L30" s="25" t="inlineStr">
+      <c r="L30" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="M30" s="26" t="inlineStr"/>
+      <c r="M30" s="29" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="24" t="n">
+      <c r="A31" s="27" t="n">
         <v>27</v>
       </c>
       <c r="B31" s="22" t="inlineStr">
@@ -7957,7 +8489,7 @@
           <t>猛禽</t>
         </is>
       </c>
-      <c r="E31" s="24" t="n">
+      <c r="E31" s="27" t="n">
         <v>1</v>
       </c>
       <c r="F31" s="22" t="inlineStr">
@@ -7980,7 +8512,7 @@
           <t>≤ 120 KB</t>
         </is>
       </c>
-      <c r="J31" s="24" t="n">
+      <c r="J31" s="27" t="n">
         <v>5</v>
       </c>
       <c r="K31" s="22" t="inlineStr">
@@ -7988,15 +8520,15 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="L31" s="25" t="inlineStr">
+      <c r="L31" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="M31" s="26" t="inlineStr"/>
+      <c r="M31" s="29" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="27" t="n">
+      <c r="A32" s="30" t="n">
         <v>28</v>
       </c>
       <c r="B32" s="23" t="inlineStr">
@@ -8014,7 +8546,7 @@
           <t>貓頭鷹</t>
         </is>
       </c>
-      <c r="E32" s="27" t="n">
+      <c r="E32" s="30" t="n">
         <v>1</v>
       </c>
       <c r="F32" s="23" t="inlineStr">
@@ -8037,7 +8569,7 @@
           <t>≤ 120 KB</t>
         </is>
       </c>
-      <c r="J32" s="27" t="n">
+      <c r="J32" s="30" t="n">
         <v>5</v>
       </c>
       <c r="K32" s="23" t="inlineStr">
@@ -8045,15 +8577,15 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="L32" s="25" t="inlineStr">
+      <c r="L32" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="M32" s="26" t="inlineStr"/>
+      <c r="M32" s="29" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="24" t="n">
+      <c r="A33" s="27" t="n">
         <v>29</v>
       </c>
       <c r="B33" s="22" t="inlineStr">
@@ -8071,7 +8603,7 @@
           <t>雉雞</t>
         </is>
       </c>
-      <c r="E33" s="24" t="n">
+      <c r="E33" s="27" t="n">
         <v>1</v>
       </c>
       <c r="F33" s="22" t="inlineStr">
@@ -8094,7 +8626,7 @@
           <t>≤ 120 KB</t>
         </is>
       </c>
-      <c r="J33" s="24" t="n">
+      <c r="J33" s="27" t="n">
         <v>5</v>
       </c>
       <c r="K33" s="22" t="inlineStr">
@@ -8102,12 +8634,12 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="L33" s="25" t="inlineStr">
+      <c r="L33" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="M33" s="26" t="inlineStr"/>
+      <c r="M33" s="29" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:M33"/>
@@ -8124,7 +8656,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8235,7 +8767,7 @@
           <t>待機呼吸、張望、低頭聞、甩尾、耳朵抖、眨眼、張嘴、走路（定格每秒 8 格）</t>
         </is>
       </c>
-      <c r="H5" s="26" t="inlineStr">
+      <c r="H5" s="29" t="inlineStr">
         <is>
           <t>已驗證（石虎）</t>
         </is>
@@ -8277,7 +8809,7 @@
           <t>待機、張望、低頭聞、坐下、走路</t>
         </is>
       </c>
-      <c r="H6" s="26" t="inlineStr">
+      <c r="H6" s="29" t="inlineStr">
         <is>
           <t>待第一隻實作確認</t>
         </is>
@@ -8319,7 +8851,7 @@
           <t>待機、張望、低頭吃草、甩耳、走路</t>
         </is>
       </c>
-      <c r="H7" s="26" t="inlineStr">
+      <c r="H7" s="29" t="inlineStr">
         <is>
           <t>待第一隻實作確認</t>
         </is>
@@ -8361,7 +8893,7 @@
           <t>待機、站起來張望、低頭聞、甩尾、走路</t>
         </is>
       </c>
-      <c r="H8" s="26" t="inlineStr">
+      <c r="H8" s="29" t="inlineStr">
         <is>
           <t>待第一隻實作確認</t>
         </is>
@@ -8403,7 +8935,7 @@
           <t>待機、低頭聞、甩尾、走路（選配：捲成球）</t>
         </is>
       </c>
-      <c r="H9" s="26" t="inlineStr">
+      <c r="H9" s="29" t="inlineStr">
         <is>
           <t>待第一隻實作確認</t>
         </is>
@@ -8445,7 +8977,7 @@
           <t>待機、跳兩步、低頭啄、理羽毛、歪頭、眨眼、拍翅；另需「飛行姿勢」1 張</t>
         </is>
       </c>
-      <c r="H10" s="26" t="inlineStr">
+      <c r="H10" s="29" t="inlineStr">
         <is>
           <t>待第一隻實作確認</t>
         </is>
@@ -8487,7 +9019,7 @@
           <t>待機、走路、低頭啄、抬頭張望、眨眼</t>
         </is>
       </c>
-      <c r="H11" s="26" t="inlineStr">
+      <c r="H11" s="29" t="inlineStr">
         <is>
           <t>待第一隻實作確認</t>
         </is>
@@ -8529,7 +9061,7 @@
           <t>待機、張望、展翅；另需「飛行姿勢（展翅盤旋）」1 張</t>
         </is>
       </c>
-      <c r="H12" s="26" t="inlineStr">
+      <c r="H12" s="29" t="inlineStr">
         <is>
           <t>待第一隻實作確認</t>
         </is>
@@ -8571,7 +9103,7 @@
           <t>待機、大角度轉頭、眨眼、縮成一團（發光眼睛由程式畫）</t>
         </is>
       </c>
-      <c r="H13" s="26" t="inlineStr">
+      <c r="H13" s="29" t="inlineStr">
         <is>
           <t>待第一隻實作確認</t>
         </is>
@@ -8587,7 +9119,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8675,7 +9207,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="24" t="n">
+      <c r="A5" s="27" t="n">
         <v>1</v>
       </c>
       <c r="B5" s="22" t="inlineStr">
@@ -8703,7 +9235,7 @@
           <t>約 3000×1150</t>
         </is>
       </c>
-      <c r="G5" s="24" t="n">
+      <c r="G5" s="27" t="n">
         <v>1</v>
       </c>
       <c r="H5" s="22" t="inlineStr">
@@ -8711,19 +9243,19 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="I5" s="29" t="inlineStr">
+      <c r="I5" s="32" t="inlineStr">
         <is>
           <t>暫代</t>
         </is>
       </c>
-      <c r="J5" s="26" t="inlineStr">
+      <c r="J5" s="29" t="inlineStr">
         <is>
           <t>原型暫時用 focus-done.webp（白天山景）</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="27" t="n">
+      <c r="A6" s="30" t="n">
         <v>2</v>
       </c>
       <c r="B6" s="23" t="inlineStr">
@@ -8751,7 +9283,7 @@
           <t>約 3000×1150</t>
         </is>
       </c>
-      <c r="G6" s="27" t="n">
+      <c r="G6" s="30" t="n">
         <v>1</v>
       </c>
       <c r="H6" s="23" t="inlineStr">
@@ -8759,19 +9291,19 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="I6" s="29" t="inlineStr">
+      <c r="I6" s="32" t="inlineStr">
         <is>
           <t>暫代</t>
         </is>
       </c>
-      <c r="J6" s="26" t="inlineStr">
+      <c r="J6" s="29" t="inlineStr">
         <is>
           <t>原型暫時把白天全景壓暗</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="24" t="n">
+      <c r="A7" s="27" t="n">
         <v>3</v>
       </c>
       <c r="B7" s="22" t="inlineStr">
@@ -8799,7 +9331,7 @@
           <t>約 3000×1150</t>
         </is>
       </c>
-      <c r="G7" s="24" t="n">
+      <c r="G7" s="27" t="n">
         <v>2</v>
       </c>
       <c r="H7" s="22" t="inlineStr">
@@ -8807,15 +9339,15 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I7" s="25" t="inlineStr">
+      <c r="I7" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="J7" s="26" t="inlineStr"/>
+      <c r="J7" s="29" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="27" t="n">
+      <c r="A8" s="30" t="n">
         <v>4</v>
       </c>
       <c r="B8" s="23" t="inlineStr">
@@ -8843,7 +9375,7 @@
           <t>約 3000×1150</t>
         </is>
       </c>
-      <c r="G8" s="27" t="n">
+      <c r="G8" s="30" t="n">
         <v>2</v>
       </c>
       <c r="H8" s="23" t="inlineStr">
@@ -8851,15 +9383,15 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I8" s="25" t="inlineStr">
+      <c r="I8" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="J8" s="26" t="inlineStr"/>
+      <c r="J8" s="29" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="24" t="n">
+      <c r="A9" s="27" t="n">
         <v>5</v>
       </c>
       <c r="B9" s="22" t="inlineStr">
@@ -8887,7 +9419,7 @@
           <t>約 3000×1150</t>
         </is>
       </c>
-      <c r="G9" s="24" t="n">
+      <c r="G9" s="27" t="n">
         <v>3</v>
       </c>
       <c r="H9" s="22" t="inlineStr">
@@ -8895,15 +9427,15 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I9" s="25" t="inlineStr">
+      <c r="I9" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="J9" s="26" t="inlineStr"/>
+      <c r="J9" s="29" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="27" t="n">
+      <c r="A10" s="30" t="n">
         <v>6</v>
       </c>
       <c r="B10" s="23" t="inlineStr">
@@ -8931,7 +9463,7 @@
           <t>約 3000×1150</t>
         </is>
       </c>
-      <c r="G10" s="27" t="n">
+      <c r="G10" s="30" t="n">
         <v>3</v>
       </c>
       <c r="H10" s="23" t="inlineStr">
@@ -8939,15 +9471,15 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I10" s="25" t="inlineStr">
+      <c r="I10" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="J10" s="26" t="inlineStr"/>
+      <c r="J10" s="29" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="24" t="n">
+      <c r="A11" s="27" t="n">
         <v>7</v>
       </c>
       <c r="B11" s="22" t="inlineStr">
@@ -8975,7 +9507,7 @@
           <t>約 3000×1150</t>
         </is>
       </c>
-      <c r="G11" s="24" t="n">
+      <c r="G11" s="27" t="n">
         <v>4</v>
       </c>
       <c r="H11" s="22" t="inlineStr">
@@ -8983,15 +9515,15 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I11" s="25" t="inlineStr">
+      <c r="I11" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="J11" s="26" t="inlineStr"/>
+      <c r="J11" s="29" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="27" t="n">
+      <c r="A12" s="30" t="n">
         <v>8</v>
       </c>
       <c r="B12" s="23" t="inlineStr">
@@ -9019,7 +9551,7 @@
           <t>約 3000×1150</t>
         </is>
       </c>
-      <c r="G12" s="27" t="n">
+      <c r="G12" s="30" t="n">
         <v>4</v>
       </c>
       <c r="H12" s="23" t="inlineStr">
@@ -9027,15 +9559,15 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I12" s="25" t="inlineStr">
+      <c r="I12" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="J12" s="26" t="inlineStr"/>
+      <c r="J12" s="29" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="24" t="n">
+      <c r="A13" s="27" t="n">
         <v>9</v>
       </c>
       <c r="B13" s="22" t="inlineStr">
@@ -9063,7 +9595,7 @@
           <t>約 3000×1150</t>
         </is>
       </c>
-      <c r="G13" s="24" t="n">
+      <c r="G13" s="27" t="n">
         <v>4</v>
       </c>
       <c r="H13" s="22" t="inlineStr">
@@ -9071,15 +9603,15 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I13" s="25" t="inlineStr">
+      <c r="I13" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="J13" s="26" t="inlineStr"/>
+      <c r="J13" s="29" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="27" t="n">
+      <c r="A14" s="30" t="n">
         <v>10</v>
       </c>
       <c r="B14" s="23" t="inlineStr">
@@ -9107,7 +9639,7 @@
           <t>約 3000×1150</t>
         </is>
       </c>
-      <c r="G14" s="27" t="n">
+      <c r="G14" s="30" t="n">
         <v>5</v>
       </c>
       <c r="H14" s="23" t="inlineStr">
@@ -9115,19 +9647,19 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="I14" s="30" t="inlineStr">
+      <c r="I14" s="33" t="inlineStr">
         <is>
           <t>選配</t>
         </is>
       </c>
-      <c r="J14" s="26" t="inlineStr">
+      <c r="J14" s="29" t="inlineStr">
         <is>
           <t>之後新增日本白天活動的動物時再畫</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="24" t="n">
+      <c r="A15" s="27" t="n">
         <v>11</v>
       </c>
       <c r="B15" s="22" t="inlineStr">
@@ -9155,7 +9687,7 @@
           <t>約 3000×1150</t>
         </is>
       </c>
-      <c r="G15" s="24" t="n">
+      <c r="G15" s="27" t="n">
         <v>5</v>
       </c>
       <c r="H15" s="22" t="inlineStr">
@@ -9163,19 +9695,19 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="I15" s="30" t="inlineStr">
+      <c r="I15" s="33" t="inlineStr">
         <is>
           <t>選配</t>
         </is>
       </c>
-      <c r="J15" s="26" t="inlineStr">
+      <c r="J15" s="29" t="inlineStr">
         <is>
           <t>先用白天版加暖色調</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="27" t="n">
+      <c r="A16" s="30" t="n">
         <v>12</v>
       </c>
       <c r="B16" s="23" t="inlineStr">
@@ -9203,7 +9735,7 @@
           <t>約 3000×1150</t>
         </is>
       </c>
-      <c r="G16" s="27" t="n">
+      <c r="G16" s="30" t="n">
         <v>5</v>
       </c>
       <c r="H16" s="23" t="inlineStr">
@@ -9211,19 +9743,19 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="I16" s="30" t="inlineStr">
+      <c r="I16" s="33" t="inlineStr">
         <is>
           <t>選配</t>
         </is>
       </c>
-      <c r="J16" s="26" t="inlineStr">
+      <c r="J16" s="29" t="inlineStr">
         <is>
           <t>先用白天版加暖色調</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="24" t="n">
+      <c r="A17" s="27" t="n">
         <v>13</v>
       </c>
       <c r="B17" s="22" t="inlineStr">
@@ -9251,7 +9783,7 @@
           <t>約 3000×1150</t>
         </is>
       </c>
-      <c r="G17" s="24" t="n">
+      <c r="G17" s="27" t="n">
         <v>5</v>
       </c>
       <c r="H17" s="22" t="inlineStr">
@@ -9259,12 +9791,12 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="I17" s="30" t="inlineStr">
+      <c r="I17" s="33" t="inlineStr">
         <is>
           <t>選配</t>
         </is>
       </c>
-      <c r="J17" s="26" t="inlineStr">
+      <c r="J17" s="29" t="inlineStr">
         <is>
           <t>先用白天版加暖色調</t>
         </is>
@@ -9285,7 +9817,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9489,7 +10021,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9582,7 +10114,7 @@
           <t>台灣・棲光森林</t>
         </is>
       </c>
-      <c r="B5" s="24" t="n">
+      <c r="B5" s="27" t="n">
         <v>0</v>
       </c>
       <c r="C5" s="22" t="inlineStr">
@@ -9611,12 +10143,12 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="I5" s="29" t="inlineStr">
+      <c r="I5" s="32" t="inlineStr">
         <is>
           <t>暫代</t>
         </is>
       </c>
-      <c r="J5" s="26" t="inlineStr">
+      <c r="J5" s="29" t="inlineStr">
         <is>
           <t>目前用 forest.webp（1167×1347，GPT 畫的完成狀態）</t>
         </is>
@@ -9628,7 +10160,7 @@
           <t>台灣・棲光森林</t>
         </is>
       </c>
-      <c r="B6" s="27" t="n">
+      <c r="B6" s="30" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="23" t="inlineStr">
@@ -9641,7 +10173,7 @@
           <t>清出林間步道</t>
         </is>
       </c>
-      <c r="E6" s="27" t="n">
+      <c r="E6" s="30" t="n">
         <v>10</v>
       </c>
       <c r="F6" s="23" t="inlineStr">
@@ -9659,12 +10191,12 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="I6" s="25" t="inlineStr">
+      <c r="I6" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="J6" s="26" t="inlineStr"/>
+      <c r="J6" s="29" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="22" t="inlineStr">
@@ -9672,7 +10204,7 @@
           <t>台灣・棲光森林</t>
         </is>
       </c>
-      <c r="B7" s="24" t="n">
+      <c r="B7" s="27" t="n">
         <v>2</v>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -9685,7 +10217,7 @@
           <t>種回原生樹苗</t>
         </is>
       </c>
-      <c r="E7" s="24" t="n">
+      <c r="E7" s="27" t="n">
         <v>430</v>
       </c>
       <c r="F7" s="22" t="inlineStr">
@@ -9703,12 +10235,12 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="I7" s="25" t="inlineStr">
+      <c r="I7" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="J7" s="26" t="inlineStr"/>
+      <c r="J7" s="29" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="23" t="inlineStr">
@@ -9716,7 +10248,7 @@
           <t>台灣・棲光森林</t>
         </is>
       </c>
-      <c r="B8" s="27" t="n">
+      <c r="B8" s="30" t="n">
         <v>3</v>
       </c>
       <c r="C8" s="23" t="inlineStr">
@@ -9729,7 +10261,7 @@
           <t>修好森林觀察小屋</t>
         </is>
       </c>
-      <c r="E8" s="27" t="n">
+      <c r="E8" s="30" t="n">
         <v>1300</v>
       </c>
       <c r="F8" s="23" t="inlineStr">
@@ -9747,12 +10279,12 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="I8" s="25" t="inlineStr">
+      <c r="I8" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="J8" s="26" t="inlineStr"/>
+      <c r="J8" s="29" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="22" t="inlineStr">
@@ -9760,7 +10292,7 @@
           <t>台灣・棲光森林</t>
         </is>
       </c>
-      <c r="B9" s="24" t="n">
+      <c r="B9" s="27" t="n">
         <v>4</v>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -9773,7 +10305,7 @@
           <t>恢復林下草叢</t>
         </is>
       </c>
-      <c r="E9" s="24" t="n">
+      <c r="E9" s="27" t="n">
         <v>1850</v>
       </c>
       <c r="F9" s="22" t="inlineStr">
@@ -9791,12 +10323,12 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="I9" s="25" t="inlineStr">
+      <c r="I9" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="J9" s="26" t="inlineStr"/>
+      <c r="J9" s="29" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="23" t="inlineStr">
@@ -9804,7 +10336,7 @@
           <t>台灣・棲光森林</t>
         </is>
       </c>
-      <c r="B10" s="27" t="n">
+      <c r="B10" s="30" t="n">
         <v>5</v>
       </c>
       <c r="C10" s="23" t="inlineStr">
@@ -9817,7 +10349,7 @@
           <t>架設生態廊道</t>
         </is>
       </c>
-      <c r="E10" s="27" t="n">
+      <c r="E10" s="30" t="n">
         <v>2150</v>
       </c>
       <c r="F10" s="23" t="inlineStr">
@@ -9835,12 +10367,12 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="I10" s="25" t="inlineStr">
+      <c r="I10" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="J10" s="26" t="inlineStr"/>
+      <c r="J10" s="29" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="22" t="inlineStr">
@@ -9848,7 +10380,7 @@
           <t>台灣・棲光森林</t>
         </is>
       </c>
-      <c r="B11" s="24" t="n">
+      <c r="B11" s="27" t="n">
         <v>6</v>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -9861,7 +10393,7 @@
           <t>整理森林水源地</t>
         </is>
       </c>
-      <c r="E11" s="24" t="n">
+      <c r="E11" s="27" t="n">
         <v>2450</v>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -9879,12 +10411,12 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="I11" s="25" t="inlineStr">
+      <c r="I11" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="J11" s="26" t="inlineStr"/>
+      <c r="J11" s="29" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="23" t="inlineStr">
@@ -9892,7 +10424,7 @@
           <t>台灣・棲光森林</t>
         </is>
       </c>
-      <c r="B12" s="27" t="n">
+      <c r="B12" s="30" t="n">
         <v>7</v>
       </c>
       <c r="C12" s="23" t="inlineStr">
@@ -9905,7 +10437,7 @@
           <t>搭建樹冠步道</t>
         </is>
       </c>
-      <c r="E12" s="27" t="n">
+      <c r="E12" s="30" t="n">
         <v>2600</v>
       </c>
       <c r="F12" s="23" t="inlineStr">
@@ -9923,12 +10455,12 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="I12" s="25" t="inlineStr">
+      <c r="I12" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="J12" s="26" t="inlineStr"/>
+      <c r="J12" s="29" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="22" t="inlineStr">
@@ -9936,7 +10468,7 @@
           <t>台灣・棲光森林</t>
         </is>
       </c>
-      <c r="B13" s="24" t="n">
+      <c r="B13" s="27" t="n">
         <v>8</v>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -9949,7 +10481,7 @@
           <t>設立保育救傷站</t>
         </is>
       </c>
-      <c r="E13" s="24" t="n">
+      <c r="E13" s="27" t="n">
         <v>2700</v>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -9967,12 +10499,12 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="I13" s="25" t="inlineStr">
+      <c r="I13" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="J13" s="26" t="inlineStr"/>
+      <c r="J13" s="29" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="23" t="inlineStr">
@@ -9980,7 +10512,7 @@
           <t>日本・里山</t>
         </is>
       </c>
-      <c r="B14" s="27" t="n">
+      <c r="B14" s="30" t="n">
         <v>0</v>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -10009,12 +10541,12 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I14" s="25" t="inlineStr">
+      <c r="I14" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="J14" s="26" t="inlineStr"/>
+      <c r="J14" s="29" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="22" t="inlineStr">
@@ -10022,7 +10554,7 @@
           <t>日本・里山</t>
         </is>
       </c>
-      <c r="B15" s="24" t="n">
+      <c r="B15" s="27" t="n">
         <v>1</v>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -10035,7 +10567,7 @@
           <t>清出杉林小徑</t>
         </is>
       </c>
-      <c r="E15" s="24" t="n">
+      <c r="E15" s="27" t="n">
         <v>300</v>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -10053,12 +10585,12 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I15" s="25" t="inlineStr">
+      <c r="I15" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="J15" s="26" t="inlineStr"/>
+      <c r="J15" s="29" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="23" t="inlineStr">
@@ -10066,7 +10598,7 @@
           <t>日本・里山</t>
         </is>
       </c>
-      <c r="B16" s="27" t="n">
+      <c r="B16" s="30" t="n">
         <v>2</v>
       </c>
       <c r="C16" s="23" t="inlineStr">
@@ -10079,7 +10611,7 @@
           <t>復原里山梯田</t>
         </is>
       </c>
-      <c r="E16" s="27" t="n">
+      <c r="E16" s="30" t="n">
         <v>800</v>
       </c>
       <c r="F16" s="23" t="inlineStr">
@@ -10097,12 +10629,12 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I16" s="25" t="inlineStr">
+      <c r="I16" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="J16" s="26" t="inlineStr"/>
+      <c r="J16" s="29" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="22" t="inlineStr">
@@ -10110,7 +10642,7 @@
           <t>日本・里山</t>
         </is>
       </c>
-      <c r="B17" s="24" t="n">
+      <c r="B17" s="27" t="n">
         <v>3</v>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -10123,7 +10655,7 @@
           <t>修好山中小屋</t>
         </is>
       </c>
-      <c r="E17" s="24" t="n">
+      <c r="E17" s="27" t="n">
         <v>1100</v>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -10141,12 +10673,12 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I17" s="25" t="inlineStr">
+      <c r="I17" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="J17" s="26" t="inlineStr"/>
+      <c r="J17" s="29" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="23" t="inlineStr">
@@ -10154,7 +10686,7 @@
           <t>日本・里山</t>
         </is>
       </c>
-      <c r="B18" s="27" t="n">
+      <c r="B18" s="30" t="n">
         <v>4</v>
       </c>
       <c r="C18" s="23" t="inlineStr">
@@ -10167,7 +10699,7 @@
           <t>疏伐過密的竹林</t>
         </is>
       </c>
-      <c r="E18" s="27" t="n">
+      <c r="E18" s="30" t="n">
         <v>1300</v>
       </c>
       <c r="F18" s="23" t="inlineStr">
@@ -10185,12 +10717,12 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I18" s="25" t="inlineStr">
+      <c r="I18" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="J18" s="26" t="inlineStr"/>
+      <c r="J18" s="29" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="22" t="inlineStr">
@@ -10198,7 +10730,7 @@
           <t>日本・里山</t>
         </is>
       </c>
-      <c r="B19" s="24" t="n">
+      <c r="B19" s="27" t="n">
         <v>5</v>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -10211,7 +10743,7 @@
           <t>恢復清澈溪流</t>
         </is>
       </c>
-      <c r="E19" s="24" t="n">
+      <c r="E19" s="27" t="n">
         <v>1500</v>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -10229,12 +10761,12 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I19" s="25" t="inlineStr">
+      <c r="I19" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="J19" s="26" t="inlineStr"/>
+      <c r="J19" s="29" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="23" t="inlineStr">
@@ -10242,7 +10774,7 @@
           <t>日本・里山</t>
         </is>
       </c>
-      <c r="B20" s="27" t="n">
+      <c r="B20" s="30" t="n">
         <v>6</v>
       </c>
       <c r="C20" s="23" t="inlineStr">
@@ -10255,7 +10787,7 @@
           <t>設立野生動物保護站</t>
         </is>
       </c>
-      <c r="E20" s="27" t="n">
+      <c r="E20" s="30" t="n">
         <v>1600</v>
       </c>
       <c r="F20" s="23" t="inlineStr">
@@ -10273,12 +10805,12 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I20" s="25" t="inlineStr">
+      <c r="I20" s="28" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="J20" s="26" t="inlineStr"/>
+      <c r="J20" s="29" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:J20"/>
@@ -10293,174 +10825,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:C11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="56" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="21" t="inlineStr">
-        <is>
-          <t>D-1. 小島場景規格</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="2" t="inlineStr"/>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>規格</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>說明</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="22" t="inlineStr">
-        <is>
-          <t>方向</t>
-        </is>
-      </c>
-      <c r="B5" s="22" t="inlineStr">
-        <is>
-          <t>2D 分層插畫（不做 3D 模型）</t>
-        </is>
-      </c>
-      <c r="C5" s="22" t="inlineStr">
-        <is>
-          <t>最省電、最適合直式手機、也最容易用 AI 輔助。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="23" t="inlineStr">
-        <is>
-          <t>畫布</t>
-        </is>
-      </c>
-      <c r="B6" s="23" t="inlineStr">
-        <is>
-          <t>底圖與每張疊圖同一個畫布大小、完全對齊</t>
-        </is>
-      </c>
-      <c r="C6" s="23" t="inlineStr">
-        <is>
-          <t>目前底圖 1167×1347；正式版建議 1440×1664。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="22" t="inlineStr">
-        <is>
-          <t>疊圖</t>
-        </is>
-      </c>
-      <c r="B7" s="22" t="inlineStr">
-        <is>
-          <t>每個工程一張去背圖，裡面拆成 2～4 個物件圖層</t>
-        </is>
-      </c>
-      <c r="C7" s="22" t="inlineStr">
-        <is>
-          <t>投入 25／50／75／100% 時依序出現（例如小屋：地板 → 牆 → 屋頂 → 亮燈）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="23" t="inlineStr">
-        <is>
-          <t>動物位置</t>
-        </is>
-      </c>
-      <c r="B8" s="23" t="inlineStr">
-        <is>
-          <t>前景留 6 個站位不被樹擋住</t>
-        </is>
-      </c>
-      <c r="C8" s="23" t="inlineStr">
-        <is>
-          <t>程式座標見 src/pages/Island.tsx 的 SPOTS。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="22" t="inlineStr">
-        <is>
-          <t>地面</t>
-        </is>
-      </c>
-      <c r="B9" s="22" t="inlineStr">
-        <is>
-          <t>從枯黃慢慢轉綠：可給 3 張地面色層（荒廢、一半、完成）</t>
-        </is>
-      </c>
-      <c r="C9" s="22" t="inlineStr">
-        <is>
-          <t>程式依修復進度交叉淡入。</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="23" t="inlineStr">
-        <is>
-          <t>放棄專注</t>
-        </is>
-      </c>
-      <c r="B10" s="23" t="inlineStr">
-        <is>
-          <t>不用另外畫</t>
-        </is>
-      </c>
-      <c r="C10" s="23" t="inlineStr">
-        <is>
-          <t>程式把畫面調灰。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="22" t="inlineStr">
-        <is>
-          <t>完成演出</t>
-        </is>
-      </c>
-      <c r="B11" s="22" t="inlineStr">
-        <is>
-          <t>全部工程完成後的夜晚與螢火蟲</t>
-        </is>
-      </c>
-      <c r="C11" s="22" t="inlineStr">
-        <is>
-          <t>螢火蟲由程式畫；需要一張夜晚色調版（或由程式調色）。</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A4:C11"/>
-  <mergeCells count="1">
-    <mergeCell ref="A2:C2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/docs/美術清單.xlsx
+++ b/docs/美術清單.xlsx
@@ -7008,7 +7008,7 @@
       </c>
       <c r="F5" s="22" t="inlineStr">
         <is>
-          <t>拿掉近側翅膀；拿掉頭；閉眼；拿掉近側腳</t>
+          <t>拿掉近側翅膀；拿掉頭；閉眼；拿掉近側腳；頭轉向鏡頭</t>
         </is>
       </c>
       <c r="G5" s="22" t="inlineStr">
@@ -7065,7 +7065,7 @@
       </c>
       <c r="F6" s="23" t="inlineStr">
         <is>
-          <t>拿掉頭；閉眼；拿掉耳羽</t>
+          <t>拿掉頭；閉眼；拿掉耳羽；頭轉向鏡頭</t>
         </is>
       </c>
       <c r="G6" s="23" t="inlineStr">
@@ -7179,7 +7179,7 @@
       </c>
       <c r="F8" s="23" t="inlineStr">
         <is>
-          <t>拿掉近側翅膀；拿掉頭；閉眼；拿掉近側腳</t>
+          <t>拿掉近側翅膀；拿掉頭；閉眼；拿掉近側腳；頭轉向鏡頭</t>
         </is>
       </c>
       <c r="G8" s="23" t="inlineStr">
@@ -7236,7 +7236,7 @@
       </c>
       <c r="F9" s="22" t="inlineStr">
         <is>
-          <t>E1 拿掉近側兩條腿；E3 拿掉頭；E4 拿掉兩隻耳朵；E5 閉眼</t>
+          <t>E1 拿掉近側兩條腿；E3 拿掉頭；E4 拿掉兩隻耳朵；E5 閉眼；E7 頭轉向鏡頭</t>
         </is>
       </c>
       <c r="G9" s="22" t="inlineStr">
@@ -7582,7 +7582,7 @@
       </c>
       <c r="F15" s="22" t="inlineStr">
         <is>
-          <t>E1 拿掉近側兩條腿；E3 拿掉頭；E4 拿掉兩隻耳朵；E5 閉眼</t>
+          <t>E1 拿掉近側兩條腿；E3 拿掉頭；E4 拿掉兩隻耳朵；E5 閉眼；E7 頭轉向鏡頭</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -7810,7 +7810,7 @@
       </c>
       <c r="F19" s="22" t="inlineStr">
         <is>
-          <t>拿掉近側翅膀；拿掉頭；閉眼；拿掉近側腳</t>
+          <t>拿掉近側翅膀；拿掉頭；閉眼；拿掉近側腳；頭轉向鏡頭</t>
         </is>
       </c>
       <c r="G19" s="22" t="inlineStr">
@@ -7867,7 +7867,7 @@
       </c>
       <c r="F20" s="23" t="inlineStr">
         <is>
-          <t>拿掉近側翅膀；拿掉頭；閉眼；拿掉近側腳</t>
+          <t>拿掉近側翅膀；拿掉頭；閉眼；拿掉近側腳；頭轉向鏡頭</t>
         </is>
       </c>
       <c r="G20" s="23" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="F21" s="22" t="inlineStr">
         <is>
-          <t>拿掉頭；閉眼；拿掉耳羽</t>
+          <t>拿掉頭；閉眼；拿掉耳羽；頭轉向鏡頭</t>
         </is>
       </c>
       <c r="G21" s="22" t="inlineStr">
@@ -7981,7 +7981,7 @@
       </c>
       <c r="F22" s="23" t="inlineStr">
         <is>
-          <t>E1 拿掉近側兩條腿；E3 拿掉頭；E4 拿掉兩隻耳朵；E5 閉眼</t>
+          <t>E1 拿掉近側兩條腿；E3 拿掉頭；E4 拿掉兩隻耳朵；E5 閉眼；E7 頭轉向鏡頭</t>
         </is>
       </c>
       <c r="G22" s="23" t="inlineStr">
@@ -8038,7 +8038,7 @@
       </c>
       <c r="F23" s="22" t="inlineStr">
         <is>
-          <t>拿掉近側翅膀；拿掉頭；閉眼；拿掉近側腳</t>
+          <t>拿掉近側翅膀；拿掉頭；閉眼；拿掉近側腳；頭轉向鏡頭</t>
         </is>
       </c>
       <c r="G23" s="22" t="inlineStr">
@@ -8209,7 +8209,7 @@
       </c>
       <c r="F26" s="23" t="inlineStr">
         <is>
-          <t>拿掉頭；閉眼；拿掉耳羽</t>
+          <t>拿掉頭；閉眼；拿掉耳羽；頭轉向鏡頭</t>
         </is>
       </c>
       <c r="G26" s="23" t="inlineStr">
@@ -8266,7 +8266,7 @@
       </c>
       <c r="F27" s="22" t="inlineStr">
         <is>
-          <t>E1 拿掉近側兩條腿；E3 拿掉頭；E4 拿掉兩隻耳朵；E5 閉眼</t>
+          <t>E1 拿掉近側兩條腿；E3 拿掉頭；E4 拿掉兩隻耳朵；E5 閉眼；E7 頭轉向鏡頭</t>
         </is>
       </c>
       <c r="G27" s="22" t="inlineStr">
@@ -8437,7 +8437,7 @@
       </c>
       <c r="F30" s="23" t="inlineStr">
         <is>
-          <t>E1 拿掉近側兩條腿；E3 拿掉頭；E4 拿掉兩隻耳朵；E5 閉眼</t>
+          <t>E1 拿掉近側兩條腿；E3 拿掉頭；E4 拿掉兩隻耳朵；E5 閉眼；E7 頭轉向鏡頭</t>
         </is>
       </c>
       <c r="G30" s="23" t="inlineStr">
@@ -8551,7 +8551,7 @@
       </c>
       <c r="F32" s="23" t="inlineStr">
         <is>
-          <t>拿掉頭；閉眼；拿掉耳羽</t>
+          <t>拿掉頭；閉眼；拿掉耳羽；頭轉向鏡頭</t>
         </is>
       </c>
       <c r="G32" s="23" t="inlineStr">
@@ -8754,7 +8754,7 @@
       </c>
       <c r="E5" s="22" t="inlineStr">
         <is>
-          <t>E1 拿掉近側兩條腿；E3 拿掉頭；E4 拿掉兩隻耳朵；E5 閉眼</t>
+          <t>E1 拿掉近側兩條腿；E3 拿掉頭；E4 拿掉兩隻耳朵；E5 閉眼；E7 頭轉向鏡頭</t>
         </is>
       </c>
       <c r="F5" s="22" t="inlineStr">
@@ -8964,7 +8964,7 @@
       </c>
       <c r="E10" s="23" t="inlineStr">
         <is>
-          <t>拿掉近側翅膀；拿掉頭；閉眼；拿掉近側腳</t>
+          <t>拿掉近側翅膀；拿掉頭；閉眼；拿掉近側腳；頭轉向鏡頭</t>
         </is>
       </c>
       <c r="F10" s="23" t="inlineStr">
@@ -9090,7 +9090,7 @@
       </c>
       <c r="E13" s="22" t="inlineStr">
         <is>
-          <t>拿掉頭；閉眼；拿掉耳羽</t>
+          <t>拿掉頭；閉眼；拿掉耳羽；頭轉向鏡頭</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">

--- a/docs/美術清單.xlsx
+++ b/docs/美術清單.xlsx
@@ -29,8 +29,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'動物尺寸'!$A$4:$E$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'A 動物主圖'!$A$4:$R$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'B 動物動態'!$A$4:$M$33</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'B-1 體型模板'!$A$4:$H$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'C 望遠鏡全景'!$A$4:$J$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'B-1 體型模板'!$A$4:$H$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'C 望遠鏡全景'!$A$4:$J$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'C-1 全景規格'!$A$4:$C$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'D 小島場景'!$A$4:$J$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'D-1 場景規格'!$A$4:$C$11</definedName>
@@ -376,7 +376,7 @@
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
       <text>
-        <t>1＝新玩家前兩週一定遇到；2＝台灣主線；3＝日本區；4＝商店；5＝Plus 會員。</t>
+        <t>1＝新玩家前兩週一定遇到；2＝台灣主線；3＝日本區；4＝商店；5＝Plus 會員；6＝新增物種（需要新的棲地與出現方式）。</t>
       </text>
     </comment>
   </commentList>
@@ -749,7 +749,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>29 種動物，每個成長階段 1 張（正側面）</t>
+          <t>29 種動物（台灣 21、日本 8），每個成長階段 1 張（正側面）</t>
         </is>
       </c>
       <c r="C5" s="5">
@@ -829,15 +829,15 @@
         </is>
       </c>
       <c r="C7" s="5">
-        <f>COUNTA('C 望遠鏡全景'!$B$5:$B$17)</f>
+        <f>COUNTA('C 望遠鏡全景'!$B$5:$B$20)</f>
         <v/>
       </c>
       <c r="D7" s="5">
-        <f>COUNTA('C 望遠鏡全景'!$B$5:$B$17)</f>
+        <f>COUNTA('C 望遠鏡全景'!$B$5:$B$20)</f>
         <v/>
       </c>
       <c r="E7" s="5">
-        <f>COUNTIF('C 望遠鏡全景'!$I$5:$I$17,"已完成")</f>
+        <f>COUNTIF('C 望遠鏡全景'!$I$5:$I$20,"已完成")</f>
         <v/>
       </c>
       <c r="F7" s="6">
@@ -4385,7 +4385,7 @@
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>正側面、頭朝右；製作時 1024×1024 白底主圖，App 用 512×512 透明（腳底 y＝472，離下緣 40 px）。三個成長階段畫布一樣大：幼年約成年的 60%、亞成年約 80%，腳底同一條線。這張主圖同時是 B 動物動態的唯一像素來源。黃色欄位由製作者更新。</t>
+          <t>正側面、頭朝右；製作時 1024×1024 白底主圖，App 用 512×512 透明（腳底 y＝472，離下緣 40 px）。三個成長階段畫布一樣大：幼年約成年的 60%、亞成年約 80%，腳底同一條線。這張主圖同時是 B 動物動態的唯一像素來源。黃色欄位由製作者更新。保育等級來源：維基百科「臺灣保育物種列表」（整理自農業部、海洋委員會名錄），上架前要以農業部 114/2/7 版名錄 PDF 再核對。</t>
         </is>
       </c>
     </row>
@@ -4447,7 +4447,7 @@
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>保育等級</t>
+          <t>保育等級（稀有度）</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
@@ -4487,12 +4487,12 @@
       </c>
       <c r="B5" s="22" t="inlineStr">
         <is>
-          <t>blue_magpie</t>
+          <t>black_bear</t>
         </is>
       </c>
       <c r="C5" s="22" t="inlineStr">
         <is>
-          <t>台灣藍鵲</t>
+          <t>台灣黑熊</t>
         </is>
       </c>
       <c r="D5" s="22" t="inlineStr">
@@ -4502,7 +4502,7 @@
       </c>
       <c r="E5" s="22" t="inlineStr">
         <is>
-          <t>鳥</t>
+          <t>熊</t>
         </is>
       </c>
       <c r="F5" s="27" t="n">
@@ -4510,17 +4510,17 @@
       </c>
       <c r="G5" s="22" t="inlineStr">
         <is>
-          <t>雛鳥／幼鳥／成鳥</t>
+          <t>幼年／亞成年／成年</t>
         </is>
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
-          <t>寶藍色身體、黑頭、紅嘴紅腳、非常長的白端尾羽</t>
+          <t>黑色毛、胸前白色 V 字斑、圓耳</t>
         </is>
       </c>
       <c r="I5" s="22" t="inlineStr">
         <is>
-          <t>中低海拔森林</t>
+          <t>山地森林</t>
         </is>
       </c>
       <c r="J5" s="22" t="inlineStr">
@@ -4530,21 +4530,21 @@
       </c>
       <c r="K5" s="22" t="inlineStr">
         <is>
-          <t>遠處飛 → 停到倒木上</t>
+          <t>從遠處走過來</t>
         </is>
       </c>
       <c r="L5" s="22" t="inlineStr">
         <is>
-          <t>三級・其他應予保育</t>
+          <t>第一級・瀕臨絕種</t>
         </is>
       </c>
       <c r="M5" s="22" t="inlineStr">
         <is>
-          <t>一開始就能找</t>
+          <t>修好「設立保育救傷站」</t>
         </is>
       </c>
       <c r="N5" s="27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O5" s="22" t="inlineStr">
         <is>
@@ -4553,7 +4553,7 @@
       </c>
       <c r="P5" s="22" t="inlineStr">
         <is>
-          <t>blue_magpie-0/1/2.png</t>
+          <t>black_bear-0/1/2.png</t>
         </is>
       </c>
       <c r="Q5" s="28" t="inlineStr">
@@ -4569,12 +4569,12 @@
       </c>
       <c r="B6" s="23" t="inlineStr">
         <is>
-          <t>scops_owl</t>
+          <t>leopard_cat</t>
         </is>
       </c>
       <c r="C6" s="23" t="inlineStr">
         <is>
-          <t>領角鴞</t>
+          <t>石虎</t>
         </is>
       </c>
       <c r="D6" s="23" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="E6" s="23" t="inlineStr">
         <is>
-          <t>貓頭鷹</t>
+          <t>貓科</t>
         </is>
       </c>
       <c r="F6" s="30" t="n">
@@ -4592,12 +4592,12 @@
       </c>
       <c r="G6" s="23" t="inlineStr">
         <is>
-          <t>雛鳥／幼鳥／成鳥</t>
+          <t>幼年／亞成年／成年</t>
         </is>
       </c>
       <c r="H6" s="23" t="inlineStr">
         <is>
-          <t>小型貓頭鷹、灰褐斑駁羽色、頭上一對耳羽、橘黃色眼睛</t>
+          <t>家貓大小、黃褐底色有黑斑、額頭兩條白紋、耳背白斑（已有主圖，作為全系列風格參考）</t>
         </is>
       </c>
       <c r="I6" s="23" t="inlineStr">
@@ -4607,22 +4607,22 @@
       </c>
       <c r="J6" s="23" t="inlineStr">
         <is>
-          <t>夜晚</t>
+          <t>晨昏</t>
         </is>
       </c>
       <c r="K6" s="23" t="inlineStr">
         <is>
-          <t>夜裡先亮眼睛 → 停到倒木上</t>
+          <t>從遠處走過來</t>
         </is>
       </c>
       <c r="L6" s="23" t="inlineStr">
         <is>
-          <t>二級・珍貴稀有</t>
+          <t>第一級・瀕臨絕種</t>
         </is>
       </c>
       <c r="M6" s="23" t="inlineStr">
         <is>
-          <t>一開始就能找</t>
+          <t>修好「修好森林觀察小屋」</t>
         </is>
       </c>
       <c r="N6" s="30" t="n">
@@ -4635,15 +4635,19 @@
       </c>
       <c r="P6" s="23" t="inlineStr">
         <is>
-          <t>scops_owl-0/1/2.png</t>
-        </is>
-      </c>
-      <c r="Q6" s="28" t="inlineStr">
-        <is>
-          <t>未開始</t>
-        </is>
-      </c>
-      <c r="R6" s="29" t="inlineStr"/>
+          <t>leopard_cat-0/1/2.png</t>
+        </is>
+      </c>
+      <c r="Q6" s="31" t="inlineStr">
+        <is>
+          <t>製作中</t>
+        </is>
+      </c>
+      <c r="R6" s="29" t="inlineStr">
+        <is>
+          <t>成年主圖、網格已完成（全系列的風格與規格參考）；幼年、亞成年未做</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="27" t="n">
@@ -4674,7 +4678,7 @@
       </c>
       <c r="G7" s="22" t="inlineStr">
         <is>
-          <t>幼獸／亞成獸／成獸</t>
+          <t>幼年／亞成年／成年</t>
         </is>
       </c>
       <c r="H7" s="22" t="inlineStr">
@@ -4699,7 +4703,7 @@
       </c>
       <c r="L7" s="22" t="inlineStr">
         <is>
-          <t>二級・珍貴稀有</t>
+          <t>第二級・珍貴稀有</t>
         </is>
       </c>
       <c r="M7" s="22" t="inlineStr">
@@ -4733,12 +4737,12 @@
       </c>
       <c r="B8" s="23" t="inlineStr">
         <is>
-          <t>pitta</t>
+          <t>blue_magpie</t>
         </is>
       </c>
       <c r="C8" s="23" t="inlineStr">
         <is>
-          <t>八色鳥</t>
+          <t>台灣藍鵲</t>
         </is>
       </c>
       <c r="D8" s="23" t="inlineStr">
@@ -4761,7 +4765,7 @@
       </c>
       <c r="H8" s="23" t="inlineStr">
         <is>
-          <t>綠背、藍色肩斑、黑色過眼線、橘黃腹部、紅色尾下覆羽，短尾</t>
+          <t>寶藍色身體、黑頭、紅嘴紅腳、非常長的白端尾羽</t>
         </is>
       </c>
       <c r="I8" s="23" t="inlineStr">
@@ -4781,12 +4785,12 @@
       </c>
       <c r="L8" s="23" t="inlineStr">
         <is>
-          <t>二級・珍貴稀有</t>
+          <t>第三級・其他應予保育</t>
         </is>
       </c>
       <c r="M8" s="23" t="inlineStr">
         <is>
-          <t>修好「種回原生樹苗」</t>
+          <t>一開始就能找</t>
         </is>
       </c>
       <c r="N8" s="30" t="n">
@@ -4799,7 +4803,7 @@
       </c>
       <c r="P8" s="23" t="inlineStr">
         <is>
-          <t>pitta-0/1/2.png</t>
+          <t>blue_magpie-0/1/2.png</t>
         </is>
       </c>
       <c r="Q8" s="28" t="inlineStr">
@@ -4815,12 +4819,12 @@
       </c>
       <c r="B9" s="22" t="inlineStr">
         <is>
-          <t>leopard_cat</t>
+          <t>pitta</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
         <is>
-          <t>石虎</t>
+          <t>八色鳥</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -4830,7 +4834,7 @@
       </c>
       <c r="E9" s="22" t="inlineStr">
         <is>
-          <t>貓科</t>
+          <t>鳥</t>
         </is>
       </c>
       <c r="F9" s="27" t="n">
@@ -4838,12 +4842,12 @@
       </c>
       <c r="G9" s="22" t="inlineStr">
         <is>
-          <t>幼獸／亞成獸／成獸</t>
+          <t>雛鳥／幼鳥／成鳥</t>
         </is>
       </c>
       <c r="H9" s="22" t="inlineStr">
         <is>
-          <t>家貓大小、黃褐底色有黑斑、額頭兩條白紋、耳背白斑（已有主圖，作為全系列風格參考）</t>
+          <t>綠背、藍色肩斑、黑色過眼線、橘黃腹部、紅色尾下覆羽，短尾</t>
         </is>
       </c>
       <c r="I9" s="22" t="inlineStr">
@@ -4853,22 +4857,22 @@
       </c>
       <c r="J9" s="22" t="inlineStr">
         <is>
-          <t>晨昏</t>
+          <t>白天</t>
         </is>
       </c>
       <c r="K9" s="22" t="inlineStr">
         <is>
-          <t>從遠處走過來</t>
+          <t>遠處飛 → 停到倒木上</t>
         </is>
       </c>
       <c r="L9" s="22" t="inlineStr">
         <is>
-          <t>一級・瀕臨絕種</t>
+          <t>第二級・珍貴稀有</t>
         </is>
       </c>
       <c r="M9" s="22" t="inlineStr">
         <is>
-          <t>修好「修好森林觀察小屋」</t>
+          <t>修好「種回原生樹苗」</t>
         </is>
       </c>
       <c r="N9" s="27" t="n">
@@ -4881,19 +4885,15 @@
       </c>
       <c r="P9" s="22" t="inlineStr">
         <is>
-          <t>leopard_cat-0/1/2.png</t>
-        </is>
-      </c>
-      <c r="Q9" s="31" t="inlineStr">
-        <is>
-          <t>製作中</t>
-        </is>
-      </c>
-      <c r="R9" s="29" t="inlineStr">
-        <is>
-          <t>成年主圖、網格已完成（全系列的風格與規格參考）；幼年、亞成年未做</t>
-        </is>
-      </c>
+          <t>pitta-0/1/2.png</t>
+        </is>
+      </c>
+      <c r="Q9" s="28" t="inlineStr">
+        <is>
+          <t>未開始</t>
+        </is>
+      </c>
+      <c r="R9" s="29" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="30" t="n">
@@ -4901,12 +4901,12 @@
       </c>
       <c r="B10" s="23" t="inlineStr">
         <is>
-          <t>swinhoe_pheasant</t>
+          <t>mikado_pheasant</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
         <is>
-          <t>藍腹鷴</t>
+          <t>帝雉</t>
         </is>
       </c>
       <c r="D10" s="23" t="inlineStr">
@@ -4920,21 +4920,21 @@
         </is>
       </c>
       <c r="F10" s="30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G10" s="23" t="inlineStr">
         <is>
-          <t>雛鳥／幼鳥／成鳥</t>
+          <t>只有一種樣式</t>
         </is>
       </c>
       <c r="H10" s="23" t="inlineStr">
         <is>
-          <t>雄鳥深藍身體、白色長尾羽、紅色臉部裸皮、白色冠羽</t>
+          <t>雄鳥深藍紫光澤羽毛、紅色臉、尾羽有白色橫帶</t>
         </is>
       </c>
       <c r="I10" s="23" t="inlineStr">
         <is>
-          <t>中低海拔森林</t>
+          <t>山地森林</t>
         </is>
       </c>
       <c r="J10" s="23" t="inlineStr">
@@ -4949,25 +4949,25 @@
       </c>
       <c r="L10" s="23" t="inlineStr">
         <is>
-          <t>二級・珍貴稀有</t>
+          <t>第二級・珍貴稀有</t>
         </is>
       </c>
       <c r="M10" s="23" t="inlineStr">
         <is>
-          <t>修好「恢復林下草叢」</t>
+          <t>商店 1,200 金幣</t>
         </is>
       </c>
       <c r="N10" s="30" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O10" s="23" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="P10" s="23" t="inlineStr">
         <is>
-          <t>swinhoe_pheasant-0/1/2.png</t>
+          <t>mikado_pheasant-2.png</t>
         </is>
       </c>
       <c r="Q10" s="28" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="B11" s="22" t="inlineStr">
         <is>
-          <t>crab_mongoose</t>
+          <t>swinhoe_pheasant</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
         <is>
-          <t>食蟹獴</t>
+          <t>藍腹鷴</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -4998,7 +4998,7 @@
       </c>
       <c r="E11" s="22" t="inlineStr">
         <is>
-          <t>貂、獴</t>
+          <t>雉雞</t>
         </is>
       </c>
       <c r="F11" s="27" t="n">
@@ -5006,22 +5006,22 @@
       </c>
       <c r="G11" s="22" t="inlineStr">
         <is>
-          <t>幼獸／亞成獸／成獸</t>
+          <t>雛鳥／幼鳥／成鳥</t>
         </is>
       </c>
       <c r="H11" s="22" t="inlineStr">
         <is>
-          <t>灰褐色長身體、臉頰到頸側一條白紋、蓬鬆尾巴</t>
+          <t>雄鳥深藍身體、白色長尾羽、紅色臉部裸皮、白色冠羽</t>
         </is>
       </c>
       <c r="I11" s="22" t="inlineStr">
         <is>
-          <t>溪流</t>
+          <t>中低海拔森林</t>
         </is>
       </c>
       <c r="J11" s="22" t="inlineStr">
         <is>
-          <t>白天</t>
+          <t>晨昏</t>
         </is>
       </c>
       <c r="K11" s="22" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="L11" s="22" t="inlineStr">
         <is>
-          <t>三級・其他應予保育</t>
+          <t>第二級・珍貴稀有</t>
         </is>
       </c>
       <c r="M11" s="22" t="inlineStr">
         <is>
-          <t>修好「架設生態廊道」</t>
+          <t>修好「恢復林下草叢」</t>
         </is>
       </c>
       <c r="N11" s="27" t="n">
@@ -5049,7 +5049,7 @@
       </c>
       <c r="P11" s="22" t="inlineStr">
         <is>
-          <t>crab_mongoose-0/1/2.png</t>
+          <t>swinhoe_pheasant-0/1/2.png</t>
         </is>
       </c>
       <c r="Q11" s="28" t="inlineStr">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="G12" s="23" t="inlineStr">
         <is>
-          <t>幼獸／亞成獸／成獸</t>
+          <t>幼年／亞成年／成年</t>
         </is>
       </c>
       <c r="H12" s="23" t="inlineStr">
@@ -5113,7 +5113,7 @@
       </c>
       <c r="L12" s="23" t="inlineStr">
         <is>
-          <t>三級・其他應予保育</t>
+          <t>第三級・其他應予保育</t>
         </is>
       </c>
       <c r="M12" s="23" t="inlineStr">
@@ -5195,7 +5195,7 @@
       </c>
       <c r="L13" s="22" t="inlineStr">
         <is>
-          <t>一級・瀕臨絕種</t>
+          <t>第一級・瀕臨絕種</t>
         </is>
       </c>
       <c r="M13" s="22" t="inlineStr">
@@ -5229,12 +5229,12 @@
       </c>
       <c r="B14" s="23" t="inlineStr">
         <is>
-          <t>black_bear</t>
+          <t>fish_owl</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
         <is>
-          <t>台灣黑熊</t>
+          <t>黃魚鴞</t>
         </is>
       </c>
       <c r="D14" s="23" t="inlineStr">
@@ -5244,58 +5244,58 @@
       </c>
       <c r="E14" s="23" t="inlineStr">
         <is>
-          <t>熊</t>
+          <t>貓頭鷹</t>
         </is>
       </c>
       <c r="F14" s="30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G14" s="23" t="inlineStr">
         <is>
-          <t>幼獸／亞成獸／成獸</t>
+          <t>只有一種樣式</t>
         </is>
       </c>
       <c r="H14" s="23" t="inlineStr">
         <is>
-          <t>黑色毛、胸前白色 V 字斑、圓耳</t>
+          <t>大型貓頭鷹、橘黃褐色、明顯耳羽、黃色眼睛、腳上沒有羽毛</t>
         </is>
       </c>
       <c r="I14" s="23" t="inlineStr">
         <is>
-          <t>山地森林</t>
+          <t>溪流</t>
         </is>
       </c>
       <c r="J14" s="23" t="inlineStr">
         <is>
-          <t>白天</t>
+          <t>夜晚</t>
         </is>
       </c>
       <c r="K14" s="23" t="inlineStr">
         <is>
-          <t>從遠處走過來</t>
+          <t>夜裡先亮眼睛 → 停到倒木上</t>
         </is>
       </c>
       <c r="L14" s="23" t="inlineStr">
         <is>
-          <t>一級・瀕臨絕種</t>
+          <t>第二級・珍貴稀有</t>
         </is>
       </c>
       <c r="M14" s="23" t="inlineStr">
         <is>
-          <t>修好「設立保育救傷站」</t>
+          <t>商店 90 寶石</t>
         </is>
       </c>
       <c r="N14" s="30" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O14" s="23" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="P14" s="23" t="inlineStr">
         <is>
-          <t>black_bear-0/1/2.png</t>
+          <t>fish_owl-2.png</t>
         </is>
       </c>
       <c r="Q14" s="28" t="inlineStr">
@@ -5303,7 +5303,11 @@
           <t>未開始</t>
         </is>
       </c>
-      <c r="R14" s="29" t="inlineStr"/>
+      <c r="R14" s="29" t="inlineStr">
+        <is>
+          <t>程式原本寫第一級，已改成第二級</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="27" t="n">
@@ -5311,12 +5315,12 @@
       </c>
       <c r="B15" s="22" t="inlineStr">
         <is>
-          <t>civet</t>
+          <t>black_faced_spoonbill</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
         <is>
-          <t>小麝香貓</t>
+          <t>黑面琵鷺</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -5326,7 +5330,7 @@
       </c>
       <c r="E15" s="22" t="inlineStr">
         <is>
-          <t>貓科</t>
+          <t>涉禽</t>
         </is>
       </c>
       <c r="F15" s="27" t="n">
@@ -5334,50 +5338,50 @@
       </c>
       <c r="G15" s="22" t="inlineStr">
         <is>
-          <t>成獸（只有一種樣式）</t>
+          <t>只有一種樣式</t>
         </is>
       </c>
       <c r="H15" s="22" t="inlineStr">
         <is>
-          <t>灰褐色、身上成排黑斑、尾巴有一圈一圈黑白環紋</t>
+          <t>白色羽毛、黑色的臉、黑色湯匙狀長嘴、長腳（冬候鳥，曾文溪口）</t>
         </is>
       </c>
       <c r="I15" s="22" t="inlineStr">
         <is>
-          <t>中低海拔森林</t>
+          <t>濕地河口</t>
         </is>
       </c>
       <c r="J15" s="22" t="inlineStr">
         <is>
-          <t>夜晚</t>
+          <t>白天</t>
         </is>
       </c>
       <c r="K15" s="22" t="inlineStr">
         <is>
-          <t>從遠處走過來</t>
+          <t>從遠處涉水走過來</t>
         </is>
       </c>
       <c r="L15" s="22" t="inlineStr">
         <is>
-          <t>二級・珍貴稀有</t>
+          <t>第一級・瀕臨絕種</t>
         </is>
       </c>
       <c r="M15" s="22" t="inlineStr">
         <is>
-          <t>商店 800 金幣</t>
+          <t>待定（新物種）</t>
         </is>
       </c>
       <c r="N15" s="27" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O15" s="22" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="P15" s="22" t="inlineStr">
         <is>
-          <t>civet-2.png</t>
+          <t>black_faced_spoonbill-2.png</t>
         </is>
       </c>
       <c r="Q15" s="28" t="inlineStr">
@@ -5385,7 +5389,11 @@
           <t>未開始</t>
         </is>
       </c>
-      <c r="R15" s="29" t="inlineStr"/>
+      <c r="R15" s="29" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="30" t="n">
@@ -5393,12 +5401,12 @@
       </c>
       <c r="B16" s="23" t="inlineStr">
         <is>
-          <t>mikado_pheasant</t>
+          <t>yellow_tit</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
         <is>
-          <t>帝雉</t>
+          <t>黃山雀</t>
         </is>
       </c>
       <c r="D16" s="23" t="inlineStr">
@@ -5408,7 +5416,7 @@
       </c>
       <c r="E16" s="23" t="inlineStr">
         <is>
-          <t>雉雞</t>
+          <t>鳥</t>
         </is>
       </c>
       <c r="F16" s="30" t="n">
@@ -5416,12 +5424,12 @@
       </c>
       <c r="G16" s="23" t="inlineStr">
         <is>
-          <t>成鳥（只有一種樣式）</t>
+          <t>只有一種樣式</t>
         </is>
       </c>
       <c r="H16" s="23" t="inlineStr">
         <is>
-          <t>雄鳥深藍紫光澤羽毛、紅色臉、尾羽有白色橫帶</t>
+          <t>黃色身體、黑色冠羽、黑色喉部、灰藍翅膀（台灣特有種）</t>
         </is>
       </c>
       <c r="I16" s="23" t="inlineStr">
@@ -5431,22 +5439,22 @@
       </c>
       <c r="J16" s="23" t="inlineStr">
         <is>
-          <t>晨昏</t>
+          <t>白天</t>
         </is>
       </c>
       <c r="K16" s="23" t="inlineStr">
         <is>
-          <t>從遠處走過來</t>
+          <t>遠處飛 → 停到倒木上</t>
         </is>
       </c>
       <c r="L16" s="23" t="inlineStr">
         <is>
-          <t>二級・珍貴稀有</t>
+          <t>第二級・珍貴稀有</t>
         </is>
       </c>
       <c r="M16" s="23" t="inlineStr">
         <is>
-          <t>商店 1,200 金幣</t>
+          <t>商店 70 寶石</t>
         </is>
       </c>
       <c r="N16" s="30" t="n">
@@ -5459,7 +5467,7 @@
       </c>
       <c r="P16" s="23" t="inlineStr">
         <is>
-          <t>mikado_pheasant-2.png</t>
+          <t>yellow_tit-2.png</t>
         </is>
       </c>
       <c r="Q16" s="28" t="inlineStr">
@@ -5475,12 +5483,12 @@
       </c>
       <c r="B17" s="22" t="inlineStr">
         <is>
-          <t>serow</t>
+          <t>hill_partridge</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
         <is>
-          <t>長鬃山羊</t>
+          <t>台灣山鷓鴣</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -5490,7 +5498,7 @@
       </c>
       <c r="E17" s="22" t="inlineStr">
         <is>
-          <t>山羊</t>
+          <t>雉雞</t>
         </is>
       </c>
       <c r="F17" s="27" t="n">
@@ -5498,17 +5506,17 @@
       </c>
       <c r="G17" s="22" t="inlineStr">
         <is>
-          <t>成獸（只有一種樣式）</t>
+          <t>只有一種樣式</t>
         </is>
       </c>
       <c r="H17" s="22" t="inlineStr">
         <is>
-          <t>深褐色、頸部長鬃毛、一對短角</t>
+          <t>圓胖的地棲鳥、褐色身體、白色喉部、紅色眼周（台灣特有）</t>
         </is>
       </c>
       <c r="I17" s="22" t="inlineStr">
         <is>
-          <t>高山</t>
+          <t>中低海拔森林</t>
         </is>
       </c>
       <c r="J17" s="22" t="inlineStr">
@@ -5523,25 +5531,25 @@
       </c>
       <c r="L17" s="22" t="inlineStr">
         <is>
-          <t>三級・其他應予保育</t>
+          <t>第三級・其他應予保育</t>
         </is>
       </c>
       <c r="M17" s="22" t="inlineStr">
         <is>
-          <t>商店 1,600 金幣</t>
+          <t>Plus 會員</t>
         </is>
       </c>
       <c r="N17" s="27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O17" s="22" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="P17" s="22" t="inlineStr">
         <is>
-          <t>serow-2.png</t>
+          <t>hill_partridge-2.png</t>
         </is>
       </c>
       <c r="Q17" s="28" t="inlineStr">
@@ -5557,12 +5565,12 @@
       </c>
       <c r="B18" s="23" t="inlineStr">
         <is>
-          <t>crested_serpent_eagle</t>
+          <t>clouded_leopard</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
         <is>
-          <t>大冠鷲</t>
+          <t>台灣雲豹</t>
         </is>
       </c>
       <c r="D18" s="23" t="inlineStr">
@@ -5572,7 +5580,7 @@
       </c>
       <c r="E18" s="23" t="inlineStr">
         <is>
-          <t>猛禽</t>
+          <t>貓科</t>
         </is>
       </c>
       <c r="F18" s="30" t="n">
@@ -5580,50 +5588,50 @@
       </c>
       <c r="G18" s="23" t="inlineStr">
         <is>
-          <t>成鳥（只有一種樣式）</t>
+          <t>只有一種樣式</t>
         </is>
       </c>
       <c r="H18" s="23" t="inlineStr">
         <is>
-          <t>中大型猛禽、深褐色、黃色臉部裸皮、腹部白點、頭後冠羽</t>
+          <t>雲朵狀大斑塊、長尾、傳說感（可以畫得特別一點，例如淡淡的霧）</t>
         </is>
       </c>
       <c r="I18" s="23" t="inlineStr">
         <is>
-          <t>山地森林</t>
+          <t>中低海拔森林</t>
         </is>
       </c>
       <c r="J18" s="23" t="inlineStr">
         <is>
-          <t>白天</t>
+          <t>夜晚</t>
         </is>
       </c>
       <c r="K18" s="23" t="inlineStr">
         <is>
-          <t>天空盤旋 → 降落</t>
+          <t>從遠處走過來</t>
         </is>
       </c>
       <c r="L18" s="23" t="inlineStr">
         <is>
-          <t>二級・珍貴稀有</t>
+          <t>第一級・瀕臨絕種</t>
         </is>
       </c>
       <c r="M18" s="23" t="inlineStr">
         <is>
-          <t>商店 1,400 金幣</t>
+          <t>Plus 會員</t>
         </is>
       </c>
       <c r="N18" s="30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O18" s="23" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="P18" s="23" t="inlineStr">
         <is>
-          <t>crested_serpent_eagle-2.png</t>
+          <t>clouded_leopard-2.png</t>
         </is>
       </c>
       <c r="Q18" s="28" t="inlineStr">
@@ -5631,7 +5639,11 @@
           <t>未開始</t>
         </is>
       </c>
-      <c r="R18" s="29" t="inlineStr"/>
+      <c r="R18" s="29" t="inlineStr">
+        <is>
+          <t>名錄列第一級；野外可能已滅絕（傳說）</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="27" t="n">
@@ -5639,12 +5651,12 @@
       </c>
       <c r="B19" s="22" t="inlineStr">
         <is>
-          <t>maroon_oriole</t>
+          <t>eurasian_otter</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
         <is>
-          <t>朱鸝</t>
+          <t>歐亞水獺（金門）</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -5654,7 +5666,7 @@
       </c>
       <c r="E19" s="22" t="inlineStr">
         <is>
-          <t>鳥</t>
+          <t>水獺</t>
         </is>
       </c>
       <c r="F19" s="27" t="n">
@@ -5662,50 +5674,50 @@
       </c>
       <c r="G19" s="22" t="inlineStr">
         <is>
-          <t>成鳥（只有一種樣式）</t>
+          <t>只有一種樣式</t>
         </is>
       </c>
       <c r="H19" s="22" t="inlineStr">
         <is>
-          <t>全身酒紅色、頭與翅膀黑色、淺藍灰色嘴</t>
+          <t>深褐色流線身體、扁頭、粗長的尾巴、蹼足、濕亮的毛（金門）</t>
         </is>
       </c>
       <c r="I19" s="22" t="inlineStr">
         <is>
-          <t>中低海拔森林</t>
+          <t>溪流</t>
         </is>
       </c>
       <c r="J19" s="22" t="inlineStr">
         <is>
-          <t>白天</t>
+          <t>夜晚</t>
         </is>
       </c>
       <c r="K19" s="22" t="inlineStr">
         <is>
-          <t>遠處飛 → 停到倒木上</t>
+          <t>從遠處走過來（溪邊、湖邊）</t>
         </is>
       </c>
       <c r="L19" s="22" t="inlineStr">
         <is>
-          <t>二級・珍貴稀有</t>
+          <t>第一級・瀕臨絕種</t>
         </is>
       </c>
       <c r="M19" s="22" t="inlineStr">
         <is>
-          <t>商店 1,800 金幣</t>
+          <t>待定（新物種）</t>
         </is>
       </c>
       <c r="N19" s="27" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O19" s="22" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="P19" s="22" t="inlineStr">
         <is>
-          <t>maroon_oriole-2.png</t>
+          <t>eurasian_otter-2.png</t>
         </is>
       </c>
       <c r="Q19" s="28" t="inlineStr">
@@ -5713,7 +5725,11 @@
           <t>未開始</t>
         </is>
       </c>
-      <c r="R19" s="29" t="inlineStr"/>
+      <c r="R19" s="29" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="30" t="n">
@@ -5721,12 +5737,12 @@
       </c>
       <c r="B20" s="23" t="inlineStr">
         <is>
-          <t>yellow_tit</t>
+          <t>formosan_salmon</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
         <is>
-          <t>黃山雀</t>
+          <t>櫻花鉤吻鮭</t>
         </is>
       </c>
       <c r="D20" s="23" t="inlineStr">
@@ -5736,7 +5752,7 @@
       </c>
       <c r="E20" s="23" t="inlineStr">
         <is>
-          <t>鳥</t>
+          <t>魚</t>
         </is>
       </c>
       <c r="F20" s="30" t="n">
@@ -5744,17 +5760,17 @@
       </c>
       <c r="G20" s="23" t="inlineStr">
         <is>
-          <t>成鳥（只有一種樣式）</t>
+          <t>只有一種樣式</t>
         </is>
       </c>
       <c r="H20" s="23" t="inlineStr">
         <is>
-          <t>黃色身體、黑色冠羽、黑色喉部、灰藍翅膀（台灣特有種）</t>
+          <t>銀綠色身體、體側橢圓形雲斑，繁殖期帶粉紅色（七家灣溪）</t>
         </is>
       </c>
       <c r="I20" s="23" t="inlineStr">
         <is>
-          <t>山地森林</t>
+          <t>溪流水下</t>
         </is>
       </c>
       <c r="J20" s="23" t="inlineStr">
@@ -5764,30 +5780,30 @@
       </c>
       <c r="K20" s="23" t="inlineStr">
         <is>
-          <t>遠處飛 → 停到倒木上</t>
+          <t>水裡由遠游近（新出現方式，程式待做）</t>
         </is>
       </c>
       <c r="L20" s="23" t="inlineStr">
         <is>
-          <t>二級・珍貴稀有</t>
+          <t>第一級・瀕臨絕種</t>
         </is>
       </c>
       <c r="M20" s="23" t="inlineStr">
         <is>
-          <t>商店 70 寶石</t>
+          <t>待定（新物種）</t>
         </is>
       </c>
       <c r="N20" s="30" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O20" s="23" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="P20" s="23" t="inlineStr">
         <is>
-          <t>yellow_tit-2.png</t>
+          <t>formosan_salmon-2.png</t>
         </is>
       </c>
       <c r="Q20" s="28" t="inlineStr">
@@ -5795,7 +5811,11 @@
           <t>未開始</t>
         </is>
       </c>
-      <c r="R20" s="29" t="inlineStr"/>
+      <c r="R20" s="29" t="inlineStr">
+        <is>
+          <t>新增（台灣特有亞種）</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="27" t="n">
@@ -5803,12 +5823,12 @@
       </c>
       <c r="B21" s="22" t="inlineStr">
         <is>
-          <t>fish_owl</t>
+          <t>green_turtle</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
         <is>
-          <t>黃魚鴞</t>
+          <t>綠蠵龜</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -5818,7 +5838,7 @@
       </c>
       <c r="E21" s="22" t="inlineStr">
         <is>
-          <t>貓頭鷹</t>
+          <t>海龜</t>
         </is>
       </c>
       <c r="F21" s="27" t="n">
@@ -5826,50 +5846,50 @@
       </c>
       <c r="G21" s="22" t="inlineStr">
         <is>
-          <t>成鳥（只有一種樣式）</t>
+          <t>只有一種樣式</t>
         </is>
       </c>
       <c r="H21" s="22" t="inlineStr">
         <is>
-          <t>大型貓頭鷹、橘黃褐色、明顯耳羽、黃色眼睛、腳上沒有羽毛</t>
+          <t>橢圓形背甲（橄欖綠帶褐色放射紋）、鰭狀前肢、小頭</t>
         </is>
       </c>
       <c r="I21" s="22" t="inlineStr">
         <is>
-          <t>溪流</t>
+          <t>海洋</t>
         </is>
       </c>
       <c r="J21" s="22" t="inlineStr">
         <is>
-          <t>夜晚</t>
+          <t>白天</t>
         </is>
       </c>
       <c r="K21" s="22" t="inlineStr">
         <is>
-          <t>夜裡先亮眼睛 → 停到倒木上</t>
+          <t>浮出海面換氣，越游越近（新，程式待做）</t>
         </is>
       </c>
       <c r="L21" s="22" t="inlineStr">
         <is>
-          <t>一級・瀕臨絕種</t>
+          <t>第一級・瀕臨絕種</t>
         </is>
       </c>
       <c r="M21" s="22" t="inlineStr">
         <is>
-          <t>商店 90 寶石</t>
+          <t>待定（新物種）</t>
         </is>
       </c>
       <c r="N21" s="27" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O21" s="22" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="P21" s="22" t="inlineStr">
         <is>
-          <t>fish_owl-2.png</t>
+          <t>green_turtle-2.png</t>
         </is>
       </c>
       <c r="Q21" s="28" t="inlineStr">
@@ -5877,7 +5897,11 @@
           <t>未開始</t>
         </is>
       </c>
-      <c r="R21" s="29" t="inlineStr"/>
+      <c r="R21" s="29" t="inlineStr">
+        <is>
+          <t>新增（海洋保育類）</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="30" t="n">
@@ -5885,73 +5909,73 @@
       </c>
       <c r="B22" s="23" t="inlineStr">
         <is>
-          <t>iriomote_cat</t>
+          <t>white_dolphin</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
         <is>
-          <t>西表山貓</t>
+          <t>中華白海豚</t>
         </is>
       </c>
       <c r="D22" s="23" t="inlineStr">
         <is>
-          <t>日本</t>
+          <t>台灣</t>
         </is>
       </c>
       <c r="E22" s="23" t="inlineStr">
         <is>
-          <t>貓科</t>
+          <t>海豚</t>
         </is>
       </c>
       <c r="F22" s="30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G22" s="23" t="inlineStr">
         <is>
-          <t>幼獸／亞成獸／成獸</t>
+          <t>只有一種樣式</t>
         </is>
       </c>
       <c r="H22" s="23" t="inlineStr">
         <is>
-          <t>深褐色帶斑點、耳背白斑、尾巴較粗短</t>
+          <t>粉紅帶灰白斑點的身體、細長的嘴、三角形背鰭（台灣西部沿岸）</t>
         </is>
       </c>
       <c r="I22" s="23" t="inlineStr">
         <is>
-          <t>南方島嶼</t>
+          <t>海洋</t>
         </is>
       </c>
       <c r="J22" s="23" t="inlineStr">
         <is>
-          <t>夜晚</t>
+          <t>白天</t>
         </is>
       </c>
       <c r="K22" s="23" t="inlineStr">
         <is>
-          <t>從遠處走過來</t>
+          <t>遠方躍出海面，越來越近（新，程式待做）</t>
         </is>
       </c>
       <c r="L22" s="23" t="inlineStr">
         <is>
-          <t>特別天然紀念物</t>
+          <t>第一級・瀕臨絕種</t>
         </is>
       </c>
       <c r="M22" s="23" t="inlineStr">
         <is>
-          <t>一開始就能找</t>
+          <t>待定（新物種）</t>
         </is>
       </c>
       <c r="N22" s="30" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O22" s="23" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="P22" s="23" t="inlineStr">
         <is>
-          <t>iriomote_cat-0/1/2.png</t>
+          <t>white_dolphin-2.png</t>
         </is>
       </c>
       <c r="Q22" s="28" t="inlineStr">
@@ -5959,7 +5983,11 @@
           <t>未開始</t>
         </is>
       </c>
-      <c r="R22" s="29" t="inlineStr"/>
+      <c r="R22" s="29" t="inlineStr">
+        <is>
+          <t>新增（海洋保育類，台灣亞種）</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="27" t="n">
@@ -5967,40 +5995,40 @@
       </c>
       <c r="B23" s="22" t="inlineStr">
         <is>
-          <t>okinawa_woodpecker</t>
+          <t>broad_tailed_swallowtail</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
         <is>
-          <t>野口啄木鳥</t>
+          <t>寬尾鳳蝶</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
         <is>
-          <t>日本</t>
+          <t>台灣</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
         <is>
-          <t>鳥</t>
+          <t>蝴蝶</t>
         </is>
       </c>
       <c r="F23" s="27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G23" s="22" t="inlineStr">
         <is>
-          <t>雛鳥／幼鳥／成鳥</t>
+          <t>只有一種樣式</t>
         </is>
       </c>
       <c r="H23" s="22" t="inlineStr">
         <is>
-          <t>全身深紅褐色、頭頂紅色（雄鳥）、啄木鳥姿態</t>
+          <t>黑色翅膀、後翅有寬大的尾突與紅色斑紋（台灣特有種）</t>
         </is>
       </c>
       <c r="I23" s="22" t="inlineStr">
         <is>
-          <t>南方島嶼</t>
+          <t>山地森林</t>
         </is>
       </c>
       <c r="J23" s="22" t="inlineStr">
@@ -6010,30 +6038,30 @@
       </c>
       <c r="K23" s="22" t="inlineStr">
         <is>
-          <t>遠處飛 → 停到倒木上</t>
+          <t>飛舞，最後停到花上（新，程式待做）</t>
         </is>
       </c>
       <c r="L23" s="22" t="inlineStr">
         <is>
-          <t>特別天然紀念物</t>
+          <t>第一級・瀕臨絕種</t>
         </is>
       </c>
       <c r="M23" s="22" t="inlineStr">
         <is>
-          <t>一開始就能找</t>
+          <t>待定（新物種）</t>
         </is>
       </c>
       <c r="N23" s="27" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O23" s="22" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="P23" s="22" t="inlineStr">
         <is>
-          <t>okinawa_woodpecker-0/1/2.png</t>
+          <t>broad_tailed_swallowtail-2.png</t>
         </is>
       </c>
       <c r="Q23" s="28" t="inlineStr">
@@ -6041,7 +6069,11 @@
           <t>未開始</t>
         </is>
       </c>
-      <c r="R23" s="29" t="inlineStr"/>
+      <c r="R23" s="29" t="inlineStr">
+        <is>
+          <t>新增（台灣特有種）</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="30" t="n">
@@ -6049,73 +6081,73 @@
       </c>
       <c r="B24" s="23" t="inlineStr">
         <is>
-          <t>japanese_serow</t>
+          <t>farmland_tree_frog</t>
         </is>
       </c>
       <c r="C24" s="23" t="inlineStr">
         <is>
-          <t>日本鬣羚</t>
+          <t>諸羅樹蛙</t>
         </is>
       </c>
       <c r="D24" s="23" t="inlineStr">
         <is>
-          <t>日本</t>
+          <t>台灣</t>
         </is>
       </c>
       <c r="E24" s="23" t="inlineStr">
         <is>
-          <t>山羊</t>
+          <t>蛙</t>
         </is>
       </c>
       <c r="F24" s="30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G24" s="23" t="inlineStr">
         <is>
-          <t>幼獸／亞成獸／成獸</t>
+          <t>只有一種樣式</t>
         </is>
       </c>
       <c r="H24" s="23" t="inlineStr">
         <is>
-          <t>灰黑色、頸部有鬃毛、短角、常站在岩石上</t>
+          <t>翠綠色背部、白色腹部、體側白線、指端吸盤（台灣特有種，雲嘉南平地）</t>
         </is>
       </c>
       <c r="I24" s="23" t="inlineStr">
         <is>
-          <t>山地森林</t>
+          <t>中低海拔森林</t>
         </is>
       </c>
       <c r="J24" s="23" t="inlineStr">
         <is>
-          <t>晨昏</t>
+          <t>夜晚</t>
         </is>
       </c>
       <c r="K24" s="23" t="inlineStr">
         <is>
-          <t>從遠處走過來</t>
+          <t>夜裡先聽到叫聲、看到眼睛（同貓頭鷹）</t>
         </is>
       </c>
       <c r="L24" s="23" t="inlineStr">
         <is>
-          <t>特別天然紀念物</t>
+          <t>第二級・珍貴稀有</t>
         </is>
       </c>
       <c r="M24" s="23" t="inlineStr">
         <is>
-          <t>修好「清出杉林小徑」</t>
+          <t>待定（新物種）</t>
         </is>
       </c>
       <c r="N24" s="30" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O24" s="23" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="P24" s="23" t="inlineStr">
         <is>
-          <t>japanese_serow-0/1/2.png</t>
+          <t>farmland_tree_frog-2.png</t>
         </is>
       </c>
       <c r="Q24" s="28" t="inlineStr">
@@ -6123,7 +6155,11 @@
           <t>未開始</t>
         </is>
       </c>
-      <c r="R24" s="29" t="inlineStr"/>
+      <c r="R24" s="29" t="inlineStr">
+        <is>
+          <t>新增（台灣特有種）</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="27" t="n">
@@ -6131,73 +6167,73 @@
       </c>
       <c r="B25" s="22" t="inlineStr">
         <is>
-          <t>ptarmigan</t>
+          <t>formosan_flying_fox</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
         <is>
-          <t>雷鳥</t>
+          <t>台灣狐蝠</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
         <is>
-          <t>日本</t>
+          <t>台灣</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
         <is>
-          <t>雉雞</t>
+          <t>蝙蝠</t>
         </is>
       </c>
       <c r="F25" s="27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G25" s="22" t="inlineStr">
         <is>
-          <t>雛鳥／幼鳥／成鳥</t>
+          <t>只有一種樣式</t>
         </is>
       </c>
       <c r="H25" s="22" t="inlineStr">
         <is>
-          <t>夏羽褐色斑駁、眼上紅色肉冠、腳有羽毛（冬羽全白可之後再做）</t>
+          <t>大型蝙蝠、狐狸臉、金褐色頸毛、黑色膜翼（綠島、龜山島）</t>
         </is>
       </c>
       <c r="I25" s="22" t="inlineStr">
         <is>
-          <t>高山</t>
+          <t>南方島嶼</t>
         </is>
       </c>
       <c r="J25" s="22" t="inlineStr">
         <is>
-          <t>白天</t>
+          <t>夜晚</t>
         </is>
       </c>
       <c r="K25" s="22" t="inlineStr">
         <is>
-          <t>從遠處走過來</t>
+          <t>夜空中飛，最後倒掛在樹枝上（同猛禽盤旋）</t>
         </is>
       </c>
       <c r="L25" s="22" t="inlineStr">
         <is>
-          <t>特別天然紀念物</t>
+          <t>第一級・瀕臨絕種</t>
         </is>
       </c>
       <c r="M25" s="22" t="inlineStr">
         <is>
-          <t>修好「復原里山梯田」</t>
+          <t>待定（新物種）</t>
         </is>
       </c>
       <c r="N25" s="27" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O25" s="22" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="P25" s="22" t="inlineStr">
         <is>
-          <t>ptarmigan-0/1/2.png</t>
+          <t>formosan_flying_fox-2.png</t>
         </is>
       </c>
       <c r="Q25" s="28" t="inlineStr">
@@ -6205,7 +6241,11 @@
           <t>未開始</t>
         </is>
       </c>
-      <c r="R25" s="29" t="inlineStr"/>
+      <c r="R25" s="29" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="30" t="n">
@@ -6213,12 +6253,12 @@
       </c>
       <c r="B26" s="23" t="inlineStr">
         <is>
-          <t>blakiston_owl</t>
+          <t>iriomote_cat</t>
         </is>
       </c>
       <c r="C26" s="23" t="inlineStr">
         <is>
-          <t>毛腿魚鴞</t>
+          <t>西表山貓</t>
         </is>
       </c>
       <c r="D26" s="23" t="inlineStr">
@@ -6228,7 +6268,7 @@
       </c>
       <c r="E26" s="23" t="inlineStr">
         <is>
-          <t>貓頭鷹</t>
+          <t>貓科</t>
         </is>
       </c>
       <c r="F26" s="30" t="n">
@@ -6236,17 +6276,17 @@
       </c>
       <c r="G26" s="23" t="inlineStr">
         <is>
-          <t>雛鳥／幼鳥／成鳥</t>
+          <t>幼年／亞成年／成年</t>
         </is>
       </c>
       <c r="H26" s="23" t="inlineStr">
         <is>
-          <t>世界最大的貓頭鷹之一、褐色斑紋、寬大耳羽、黃眼</t>
+          <t>深褐色帶斑點、耳背白斑、尾巴較粗短</t>
         </is>
       </c>
       <c r="I26" s="23" t="inlineStr">
         <is>
-          <t>溪流</t>
+          <t>南方島嶼</t>
         </is>
       </c>
       <c r="J26" s="23" t="inlineStr">
@@ -6256,17 +6296,17 @@
       </c>
       <c r="K26" s="23" t="inlineStr">
         <is>
-          <t>夜裡先亮眼睛 → 停到倒木上</t>
+          <t>從遠處走過來</t>
         </is>
       </c>
       <c r="L26" s="23" t="inlineStr">
         <is>
-          <t>國內稀少野生物種</t>
+          <t>特別天然紀念物</t>
         </is>
       </c>
       <c r="M26" s="23" t="inlineStr">
         <is>
-          <t>修好「修好山中小屋」</t>
+          <t>一開始就能找</t>
         </is>
       </c>
       <c r="N26" s="30" t="n">
@@ -6279,7 +6319,7 @@
       </c>
       <c r="P26" s="23" t="inlineStr">
         <is>
-          <t>blakiston_owl-0/1/2.png</t>
+          <t>iriomote_cat-0/1/2.png</t>
         </is>
       </c>
       <c r="Q26" s="28" t="inlineStr">
@@ -6295,12 +6335,12 @@
       </c>
       <c r="B27" s="22" t="inlineStr">
         <is>
-          <t>tsushima_cat</t>
+          <t>okinawa_woodpecker</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
         <is>
-          <t>對馬山貓</t>
+          <t>野口啄木鳥</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -6310,7 +6350,7 @@
       </c>
       <c r="E27" s="22" t="inlineStr">
         <is>
-          <t>貓科</t>
+          <t>鳥</t>
         </is>
       </c>
       <c r="F27" s="27" t="n">
@@ -6318,37 +6358,37 @@
       </c>
       <c r="G27" s="22" t="inlineStr">
         <is>
-          <t>幼獸／亞成獸／成獸</t>
+          <t>雛鳥／幼鳥／成鳥</t>
         </is>
       </c>
       <c r="H27" s="22" t="inlineStr">
         <is>
-          <t>對馬的石虎：外型近似石虎、額頭白紋，毛色略深</t>
+          <t>全身深紅褐色、頭頂紅色（雄鳥）、啄木鳥姿態</t>
         </is>
       </c>
       <c r="I27" s="22" t="inlineStr">
         <is>
-          <t>里山</t>
+          <t>南方島嶼</t>
         </is>
       </c>
       <c r="J27" s="22" t="inlineStr">
         <is>
-          <t>夜晚</t>
+          <t>白天</t>
         </is>
       </c>
       <c r="K27" s="22" t="inlineStr">
         <is>
-          <t>從遠處走過來</t>
+          <t>遠處飛 → 停到倒木上</t>
         </is>
       </c>
       <c r="L27" s="22" t="inlineStr">
         <is>
-          <t>國內稀少野生物種</t>
+          <t>特別天然紀念物</t>
         </is>
       </c>
       <c r="M27" s="22" t="inlineStr">
         <is>
-          <t>修好「疏伐過密的竹林」</t>
+          <t>一開始就能找</t>
         </is>
       </c>
       <c r="N27" s="27" t="n">
@@ -6361,7 +6401,7 @@
       </c>
       <c r="P27" s="22" t="inlineStr">
         <is>
-          <t>tsushima_cat-0/1/2.png</t>
+          <t>okinawa_woodpecker-0/1/2.png</t>
         </is>
       </c>
       <c r="Q27" s="28" t="inlineStr">
@@ -6377,12 +6417,12 @@
       </c>
       <c r="B28" s="23" t="inlineStr">
         <is>
-          <t>steller_eagle</t>
+          <t>japanese_serow</t>
         </is>
       </c>
       <c r="C28" s="23" t="inlineStr">
         <is>
-          <t>虎頭海鵰</t>
+          <t>日本鬣羚</t>
         </is>
       </c>
       <c r="D28" s="23" t="inlineStr">
@@ -6392,7 +6432,7 @@
       </c>
       <c r="E28" s="23" t="inlineStr">
         <is>
-          <t>猛禽</t>
+          <t>山羊</t>
         </is>
       </c>
       <c r="F28" s="30" t="n">
@@ -6400,37 +6440,37 @@
       </c>
       <c r="G28" s="23" t="inlineStr">
         <is>
-          <t>雛鳥／幼鳥／成鳥</t>
+          <t>幼年／亞成年／成年</t>
         </is>
       </c>
       <c r="H28" s="23" t="inlineStr">
         <is>
-          <t>巨大的橘黃色嘴、深褐色身體、白色肩羽與白尾</t>
+          <t>灰黑色、頸部有鬃毛、短角、常站在岩石上</t>
         </is>
       </c>
       <c r="I28" s="23" t="inlineStr">
         <is>
-          <t>溪流</t>
+          <t>山地森林</t>
         </is>
       </c>
       <c r="J28" s="23" t="inlineStr">
         <is>
-          <t>白天</t>
+          <t>晨昏</t>
         </is>
       </c>
       <c r="K28" s="23" t="inlineStr">
         <is>
-          <t>天空盤旋 → 降落</t>
+          <t>從遠處走過來</t>
         </is>
       </c>
       <c r="L28" s="23" t="inlineStr">
         <is>
-          <t>國內稀少野生物種</t>
+          <t>特別天然紀念物</t>
         </is>
       </c>
       <c r="M28" s="23" t="inlineStr">
         <is>
-          <t>修好「恢復清澈溪流」</t>
+          <t>修好「清出杉林小徑」</t>
         </is>
       </c>
       <c r="N28" s="30" t="n">
@@ -6443,7 +6483,7 @@
       </c>
       <c r="P28" s="23" t="inlineStr">
         <is>
-          <t>steller_eagle-0/1/2.png</t>
+          <t>japanese_serow-0/1/2.png</t>
         </is>
       </c>
       <c r="Q28" s="28" t="inlineStr">
@@ -6459,12 +6499,12 @@
       </c>
       <c r="B29" s="22" t="inlineStr">
         <is>
-          <t>moon_bear</t>
+          <t>ptarmigan</t>
         </is>
       </c>
       <c r="C29" s="22" t="inlineStr">
         <is>
-          <t>月輪熊</t>
+          <t>雷鳥</t>
         </is>
       </c>
       <c r="D29" s="22" t="inlineStr">
@@ -6474,7 +6514,7 @@
       </c>
       <c r="E29" s="22" t="inlineStr">
         <is>
-          <t>熊</t>
+          <t>雉雞</t>
         </is>
       </c>
       <c r="F29" s="27" t="n">
@@ -6482,17 +6522,17 @@
       </c>
       <c r="G29" s="22" t="inlineStr">
         <is>
-          <t>幼獸／亞成獸／成獸</t>
+          <t>雛鳥／幼鳥／成鳥</t>
         </is>
       </c>
       <c r="H29" s="22" t="inlineStr">
         <is>
-          <t>黑色毛、胸前月牙形白斑、圓耳</t>
+          <t>夏羽褐色斑駁、眼上紅色肉冠、腳有羽毛（冬羽全白可之後再做）</t>
         </is>
       </c>
       <c r="I29" s="22" t="inlineStr">
         <is>
-          <t>山地森林</t>
+          <t>高山</t>
         </is>
       </c>
       <c r="J29" s="22" t="inlineStr">
@@ -6507,12 +6547,12 @@
       </c>
       <c r="L29" s="22" t="inlineStr">
         <is>
-          <t>地區族群瀕危</t>
+          <t>特別天然紀念物</t>
         </is>
       </c>
       <c r="M29" s="22" t="inlineStr">
         <is>
-          <t>修好「設立野生動物保護站」</t>
+          <t>修好「復原里山梯田」</t>
         </is>
       </c>
       <c r="N29" s="27" t="n">
@@ -6525,7 +6565,7 @@
       </c>
       <c r="P29" s="22" t="inlineStr">
         <is>
-          <t>moon_bear-0/1/2.png</t>
+          <t>ptarmigan-0/1/2.png</t>
         </is>
       </c>
       <c r="Q29" s="28" t="inlineStr">
@@ -6541,40 +6581,40 @@
       </c>
       <c r="B30" s="23" t="inlineStr">
         <is>
-          <t>clouded_leopard</t>
+          <t>blakiston_owl</t>
         </is>
       </c>
       <c r="C30" s="23" t="inlineStr">
         <is>
-          <t>台灣雲豹</t>
+          <t>毛腿魚鴞</t>
         </is>
       </c>
       <c r="D30" s="23" t="inlineStr">
         <is>
-          <t>台灣</t>
+          <t>日本</t>
         </is>
       </c>
       <c r="E30" s="23" t="inlineStr">
         <is>
-          <t>貓科</t>
+          <t>貓頭鷹</t>
         </is>
       </c>
       <c r="F30" s="30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G30" s="23" t="inlineStr">
         <is>
-          <t>成獸（只有一種樣式）</t>
+          <t>雛鳥／幼鳥／成鳥</t>
         </is>
       </c>
       <c r="H30" s="23" t="inlineStr">
         <is>
-          <t>雲朵狀大斑塊、長尾、傳說感（可以畫得特別一點，例如淡淡的霧）</t>
+          <t>世界最大的貓頭鷹之一、褐色斑紋、寬大耳羽、黃眼</t>
         </is>
       </c>
       <c r="I30" s="23" t="inlineStr">
         <is>
-          <t>中低海拔森林</t>
+          <t>溪流</t>
         </is>
       </c>
       <c r="J30" s="23" t="inlineStr">
@@ -6584,30 +6624,30 @@
       </c>
       <c r="K30" s="23" t="inlineStr">
         <is>
-          <t>從遠處走過來</t>
+          <t>夜裡先亮眼睛 → 停到倒木上</t>
         </is>
       </c>
       <c r="L30" s="23" t="inlineStr">
         <is>
-          <t>一級・瀕臨絕種</t>
+          <t>國內稀少野生物種</t>
         </is>
       </c>
       <c r="M30" s="23" t="inlineStr">
         <is>
-          <t>Plus 會員</t>
+          <t>修好「修好山中小屋」</t>
         </is>
       </c>
       <c r="N30" s="30" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O30" s="23" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="P30" s="23" t="inlineStr">
         <is>
-          <t>clouded_leopard-2.png</t>
+          <t>blakiston_owl-0/1/2.png</t>
         </is>
       </c>
       <c r="Q30" s="28" t="inlineStr">
@@ -6623,73 +6663,73 @@
       </c>
       <c r="B31" s="22" t="inlineStr">
         <is>
-          <t>black_eagle</t>
+          <t>tsushima_cat</t>
         </is>
       </c>
       <c r="C31" s="22" t="inlineStr">
         <is>
-          <t>林鵰</t>
+          <t>對馬山貓</t>
         </is>
       </c>
       <c r="D31" s="22" t="inlineStr">
         <is>
-          <t>台灣</t>
+          <t>日本</t>
         </is>
       </c>
       <c r="E31" s="22" t="inlineStr">
         <is>
-          <t>猛禽</t>
+          <t>貓科</t>
         </is>
       </c>
       <c r="F31" s="27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G31" s="22" t="inlineStr">
         <is>
-          <t>成鳥（只有一種樣式）</t>
+          <t>幼年／亞成年／成年</t>
         </is>
       </c>
       <c r="H31" s="22" t="inlineStr">
         <is>
-          <t>全身深色的大型猛禽、黃色腳、翅膀很長</t>
+          <t>對馬的石虎：外型近似石虎、額頭白紋，毛色略深</t>
         </is>
       </c>
       <c r="I31" s="22" t="inlineStr">
         <is>
-          <t>山地森林</t>
+          <t>里山</t>
         </is>
       </c>
       <c r="J31" s="22" t="inlineStr">
         <is>
-          <t>白天</t>
+          <t>夜晚</t>
         </is>
       </c>
       <c r="K31" s="22" t="inlineStr">
         <is>
-          <t>天空盤旋 → 降落</t>
+          <t>從遠處走過來</t>
         </is>
       </c>
       <c r="L31" s="22" t="inlineStr">
         <is>
-          <t>二級・珍貴稀有</t>
+          <t>國內稀少野生物種</t>
         </is>
       </c>
       <c r="M31" s="22" t="inlineStr">
         <is>
-          <t>Plus 會員</t>
+          <t>修好「疏伐過密的竹林」</t>
         </is>
       </c>
       <c r="N31" s="27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O31" s="22" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="P31" s="22" t="inlineStr">
         <is>
-          <t>black_eagle-2.png</t>
+          <t>tsushima_cat-0/1/2.png</t>
         </is>
       </c>
       <c r="Q31" s="28" t="inlineStr">
@@ -6705,73 +6745,73 @@
       </c>
       <c r="B32" s="23" t="inlineStr">
         <is>
-          <t>lanyu_scops_owl</t>
+          <t>steller_eagle</t>
         </is>
       </c>
       <c r="C32" s="23" t="inlineStr">
         <is>
-          <t>蘭嶼角鴞</t>
+          <t>虎頭海鵰</t>
         </is>
       </c>
       <c r="D32" s="23" t="inlineStr">
         <is>
-          <t>台灣</t>
+          <t>日本</t>
         </is>
       </c>
       <c r="E32" s="23" t="inlineStr">
         <is>
-          <t>貓頭鷹</t>
+          <t>猛禽</t>
         </is>
       </c>
       <c r="F32" s="30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G32" s="23" t="inlineStr">
         <is>
-          <t>成鳥（只有一種樣式）</t>
+          <t>雛鳥／幼鳥／成鳥</t>
         </is>
       </c>
       <c r="H32" s="23" t="inlineStr">
         <is>
-          <t>小型貓頭鷹、紅褐色、耳羽較短（蘭嶼特有）</t>
+          <t>巨大的橘黃色嘴、深褐色身體、白色肩羽與白尾</t>
         </is>
       </c>
       <c r="I32" s="23" t="inlineStr">
         <is>
-          <t>南方島嶼</t>
+          <t>溪流</t>
         </is>
       </c>
       <c r="J32" s="23" t="inlineStr">
         <is>
-          <t>夜晚</t>
+          <t>白天</t>
         </is>
       </c>
       <c r="K32" s="23" t="inlineStr">
         <is>
-          <t>夜裡先亮眼睛 → 停到倒木上</t>
+          <t>天空盤旋 → 降落</t>
         </is>
       </c>
       <c r="L32" s="23" t="inlineStr">
         <is>
-          <t>二級・珍貴稀有</t>
+          <t>國內稀少野生物種</t>
         </is>
       </c>
       <c r="M32" s="23" t="inlineStr">
         <is>
-          <t>Plus 會員</t>
+          <t>修好「恢復清澈溪流」</t>
         </is>
       </c>
       <c r="N32" s="30" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O32" s="23" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="P32" s="23" t="inlineStr">
         <is>
-          <t>lanyu_scops_owl-2.png</t>
+          <t>steller_eagle-0/1/2.png</t>
         </is>
       </c>
       <c r="Q32" s="28" t="inlineStr">
@@ -6787,45 +6827,45 @@
       </c>
       <c r="B33" s="22" t="inlineStr">
         <is>
-          <t>hill_partridge</t>
+          <t>moon_bear</t>
         </is>
       </c>
       <c r="C33" s="22" t="inlineStr">
         <is>
-          <t>台灣山鷓鴣</t>
+          <t>月輪熊</t>
         </is>
       </c>
       <c r="D33" s="22" t="inlineStr">
         <is>
-          <t>台灣</t>
+          <t>日本</t>
         </is>
       </c>
       <c r="E33" s="22" t="inlineStr">
         <is>
-          <t>雉雞</t>
+          <t>熊</t>
         </is>
       </c>
       <c r="F33" s="27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G33" s="22" t="inlineStr">
         <is>
-          <t>成鳥（只有一種樣式）</t>
+          <t>幼年／亞成年／成年</t>
         </is>
       </c>
       <c r="H33" s="22" t="inlineStr">
         <is>
-          <t>圓胖的地棲鳥、褐色身體、白色喉部、紅色眼周（台灣特有）</t>
+          <t>黑色毛、胸前月牙形白斑、圓耳</t>
         </is>
       </c>
       <c r="I33" s="22" t="inlineStr">
         <is>
-          <t>中低海拔森林</t>
+          <t>山地森林</t>
         </is>
       </c>
       <c r="J33" s="22" t="inlineStr">
         <is>
-          <t>晨昏</t>
+          <t>白天</t>
         </is>
       </c>
       <c r="K33" s="22" t="inlineStr">
@@ -6835,25 +6875,25 @@
       </c>
       <c r="L33" s="22" t="inlineStr">
         <is>
-          <t>三級・其他應予保育</t>
+          <t>地區族群瀕危</t>
         </is>
       </c>
       <c r="M33" s="22" t="inlineStr">
         <is>
-          <t>Plus 會員</t>
+          <t>修好「設立野生動物保護站」</t>
         </is>
       </c>
       <c r="N33" s="27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O33" s="22" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="P33" s="22" t="inlineStr">
         <is>
-          <t>hill_partridge-2.png</t>
+          <t>moon_bear-0/1/2.png</t>
         </is>
       </c>
       <c r="Q33" s="28" t="inlineStr">
@@ -6950,7 +6990,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>飛行姿勢</t>
+          <t>額外姿勢</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -6990,17 +7030,17 @@
       </c>
       <c r="B5" s="22" t="inlineStr">
         <is>
-          <t>blue_magpie</t>
+          <t>black_bear</t>
         </is>
       </c>
       <c r="C5" s="22" t="inlineStr">
         <is>
-          <t>台灣藍鵲</t>
+          <t>台灣黑熊</t>
         </is>
       </c>
       <c r="D5" s="22" t="inlineStr">
         <is>
-          <t>鳥</t>
+          <t>熊</t>
         </is>
       </c>
       <c r="E5" s="27" t="n">
@@ -7008,17 +7048,17 @@
       </c>
       <c r="F5" s="22" t="inlineStr">
         <is>
-          <t>拿掉近側翅膀；拿掉頭；閉眼；拿掉近側腳；頭轉向鏡頭</t>
+          <t>同貓科</t>
         </is>
       </c>
       <c r="G5" s="22" t="inlineStr">
         <is>
-          <t>需要（展翅 1 張）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
-          <t>待機、跳兩步、低頭啄、理羽毛、歪頭、眨眼、拍翅；另需「飛行姿勢」1 張</t>
+          <t>待機、張望、低頭聞、坐下、走路</t>
         </is>
       </c>
       <c r="I5" s="22" t="inlineStr">
@@ -7027,7 +7067,7 @@
         </is>
       </c>
       <c r="J5" s="27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K5" s="22" t="inlineStr">
         <is>
@@ -7047,17 +7087,17 @@
       </c>
       <c r="B6" s="23" t="inlineStr">
         <is>
-          <t>scops_owl</t>
+          <t>leopard_cat</t>
         </is>
       </c>
       <c r="C6" s="23" t="inlineStr">
         <is>
-          <t>領角鴞</t>
+          <t>石虎</t>
         </is>
       </c>
       <c r="D6" s="23" t="inlineStr">
         <is>
-          <t>貓頭鷹</t>
+          <t>貓科</t>
         </is>
       </c>
       <c r="E6" s="30" t="n">
@@ -7065,7 +7105,7 @@
       </c>
       <c r="F6" s="23" t="inlineStr">
         <is>
-          <t>拿掉頭；閉眼；拿掉耳羽；頭轉向鏡頭</t>
+          <t>E1 拿掉近側兩條腿；E3 拿掉頭；E4 拿掉兩隻耳朵；E5 閉眼；E7 頭轉向鏡頭</t>
         </is>
       </c>
       <c r="G6" s="23" t="inlineStr">
@@ -7075,7 +7115,7 @@
       </c>
       <c r="H6" s="23" t="inlineStr">
         <is>
-          <t>待機、大角度轉頭、眨眼、縮成一團（發光眼睛由程式畫）</t>
+          <t>待機呼吸、張望、低頭聞、甩尾、耳朵抖、眨眼、張嘴、走路（定格每秒 8 格）</t>
         </is>
       </c>
       <c r="I6" s="23" t="inlineStr">
@@ -7091,12 +7131,16 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="L6" s="28" t="inlineStr">
-        <is>
-          <t>未開始</t>
-        </is>
-      </c>
-      <c r="M6" s="29" t="inlineStr"/>
+      <c r="L6" s="31" t="inlineStr">
+        <is>
+          <t>製作中</t>
+        </is>
+      </c>
+      <c r="M6" s="29" t="inlineStr">
+        <is>
+          <t>成年完成；目前未壓縮 460 KB 要壓到 ≤120 KB；後腿之間一小撮淺色未解；幼年、亞成年未做</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="27" t="n">
@@ -7161,12 +7205,12 @@
       </c>
       <c r="B8" s="23" t="inlineStr">
         <is>
-          <t>pitta</t>
+          <t>blue_magpie</t>
         </is>
       </c>
       <c r="C8" s="23" t="inlineStr">
         <is>
-          <t>八色鳥</t>
+          <t>台灣藍鵲</t>
         </is>
       </c>
       <c r="D8" s="23" t="inlineStr">
@@ -7184,7 +7228,7 @@
       </c>
       <c r="G8" s="23" t="inlineStr">
         <is>
-          <t>需要（展翅 1 張）</t>
+          <t>飛行姿勢 1 張</t>
         </is>
       </c>
       <c r="H8" s="23" t="inlineStr">
@@ -7218,17 +7262,17 @@
       </c>
       <c r="B9" s="22" t="inlineStr">
         <is>
-          <t>leopard_cat</t>
+          <t>pitta</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
         <is>
-          <t>石虎</t>
+          <t>八色鳥</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
         <is>
-          <t>貓科</t>
+          <t>鳥</t>
         </is>
       </c>
       <c r="E9" s="27" t="n">
@@ -7236,17 +7280,17 @@
       </c>
       <c r="F9" s="22" t="inlineStr">
         <is>
-          <t>E1 拿掉近側兩條腿；E3 拿掉頭；E4 拿掉兩隻耳朵；E5 閉眼；E7 頭轉向鏡頭</t>
+          <t>拿掉近側翅膀；拿掉頭；閉眼；拿掉近側腳；頭轉向鏡頭</t>
         </is>
       </c>
       <c r="G9" s="22" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>飛行姿勢 1 張</t>
         </is>
       </c>
       <c r="H9" s="22" t="inlineStr">
         <is>
-          <t>待機呼吸、張望、低頭聞、甩尾、耳朵抖、眨眼、張嘴、走路（定格每秒 8 格）</t>
+          <t>待機、跳兩步、低頭啄、理羽毛、歪頭、眨眼、拍翅；另需「飛行姿勢」1 張</t>
         </is>
       </c>
       <c r="I9" s="22" t="inlineStr">
@@ -7262,16 +7306,12 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="L9" s="31" t="inlineStr">
-        <is>
-          <t>製作中</t>
-        </is>
-      </c>
-      <c r="M9" s="29" t="inlineStr">
-        <is>
-          <t>成年完成；目前未壓縮 460 KB 要壓到 ≤120 KB；後腿之間一小撮淺色未解；幼年、亞成年未做</t>
-        </is>
-      </c>
+      <c r="L9" s="28" t="inlineStr">
+        <is>
+          <t>未開始</t>
+        </is>
+      </c>
+      <c r="M9" s="29" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="30" t="n">
@@ -7279,12 +7319,12 @@
       </c>
       <c r="B10" s="23" t="inlineStr">
         <is>
-          <t>swinhoe_pheasant</t>
+          <t>mikado_pheasant</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
         <is>
-          <t>藍腹鷴</t>
+          <t>帝雉</t>
         </is>
       </c>
       <c r="D10" s="23" t="inlineStr">
@@ -7293,7 +7333,7 @@
         </is>
       </c>
       <c r="E10" s="30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F10" s="23" t="inlineStr">
         <is>
@@ -7316,11 +7356,11 @@
         </is>
       </c>
       <c r="J10" s="30" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K10" s="23" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="L10" s="28" t="inlineStr">
@@ -7336,17 +7376,17 @@
       </c>
       <c r="B11" s="22" t="inlineStr">
         <is>
-          <t>crab_mongoose</t>
+          <t>swinhoe_pheasant</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
         <is>
-          <t>食蟹獴</t>
+          <t>藍腹鷴</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
         <is>
-          <t>貂、獴</t>
+          <t>雉雞</t>
         </is>
       </c>
       <c r="E11" s="27" t="n">
@@ -7354,7 +7394,7 @@
       </c>
       <c r="F11" s="22" t="inlineStr">
         <is>
-          <t>同貓科</t>
+          <t>同鳥</t>
         </is>
       </c>
       <c r="G11" s="22" t="inlineStr">
@@ -7364,7 +7404,7 @@
       </c>
       <c r="H11" s="22" t="inlineStr">
         <is>
-          <t>待機、站起來張望、低頭聞、甩尾、走路</t>
+          <t>待機、走路、低頭啄、抬頭張望、眨眼</t>
         </is>
       </c>
       <c r="I11" s="22" t="inlineStr">
@@ -7473,7 +7513,7 @@
       </c>
       <c r="G13" s="22" t="inlineStr">
         <is>
-          <t>需要（展翅 1 張）</t>
+          <t>展翅盤旋 1 張</t>
         </is>
       </c>
       <c r="H13" s="22" t="inlineStr">
@@ -7507,25 +7547,25 @@
       </c>
       <c r="B14" s="23" t="inlineStr">
         <is>
-          <t>black_bear</t>
+          <t>fish_owl</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
         <is>
-          <t>台灣黑熊</t>
+          <t>黃魚鴞</t>
         </is>
       </c>
       <c r="D14" s="23" t="inlineStr">
         <is>
-          <t>熊</t>
+          <t>貓頭鷹</t>
         </is>
       </c>
       <c r="E14" s="30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F14" s="23" t="inlineStr">
         <is>
-          <t>同貓科</t>
+          <t>拿掉頭；閉眼；拿掉耳羽；頭轉向鏡頭</t>
         </is>
       </c>
       <c r="G14" s="23" t="inlineStr">
@@ -7535,7 +7575,7 @@
       </c>
       <c r="H14" s="23" t="inlineStr">
         <is>
-          <t>待機、張望、低頭聞、坐下、走路</t>
+          <t>待機、大角度轉頭、眨眼、縮成一團（發光眼睛由程式畫）</t>
         </is>
       </c>
       <c r="I14" s="23" t="inlineStr">
@@ -7544,11 +7584,11 @@
         </is>
       </c>
       <c r="J14" s="30" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K14" s="23" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="L14" s="28" t="inlineStr">
@@ -7564,17 +7604,17 @@
       </c>
       <c r="B15" s="22" t="inlineStr">
         <is>
-          <t>civet</t>
+          <t>black_faced_spoonbill</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
         <is>
-          <t>小麝香貓</t>
+          <t>黑面琵鷺</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
         <is>
-          <t>貓科</t>
+          <t>涉禽</t>
         </is>
       </c>
       <c r="E15" s="27" t="n">
@@ -7582,17 +7622,17 @@
       </c>
       <c r="F15" s="22" t="inlineStr">
         <is>
-          <t>E1 拿掉近側兩條腿；E3 拿掉頭；E4 拿掉兩隻耳朵；E5 閉眼；E7 頭轉向鏡頭</t>
+          <t>同鳥</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>飛行姿勢 1 張（選配）</t>
         </is>
       </c>
       <c r="H15" s="22" t="inlineStr">
         <is>
-          <t>待機呼吸、張望、低頭聞、甩尾、耳朵抖、眨眼、張嘴、走路（定格每秒 8 格）</t>
+          <t>待機、涉水走、低頭左右掃嘴覓食、理羽毛</t>
         </is>
       </c>
       <c r="I15" s="22" t="inlineStr">
@@ -7601,11 +7641,11 @@
         </is>
       </c>
       <c r="J15" s="27" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K15" s="22" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="L15" s="28" t="inlineStr">
@@ -7621,17 +7661,17 @@
       </c>
       <c r="B16" s="23" t="inlineStr">
         <is>
-          <t>mikado_pheasant</t>
+          <t>yellow_tit</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
         <is>
-          <t>帝雉</t>
+          <t>黃山雀</t>
         </is>
       </c>
       <c r="D16" s="23" t="inlineStr">
         <is>
-          <t>雉雞</t>
+          <t>鳥</t>
         </is>
       </c>
       <c r="E16" s="30" t="n">
@@ -7639,17 +7679,17 @@
       </c>
       <c r="F16" s="23" t="inlineStr">
         <is>
-          <t>同鳥</t>
+          <t>拿掉近側翅膀；拿掉頭；閉眼；拿掉近側腳；頭轉向鏡頭</t>
         </is>
       </c>
       <c r="G16" s="23" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>飛行姿勢 1 張</t>
         </is>
       </c>
       <c r="H16" s="23" t="inlineStr">
         <is>
-          <t>待機、走路、低頭啄、抬頭張望、眨眼</t>
+          <t>待機、跳兩步、低頭啄、理羽毛、歪頭、眨眼、拍翅；另需「飛行姿勢」1 張</t>
         </is>
       </c>
       <c r="I16" s="23" t="inlineStr">
@@ -7678,17 +7718,17 @@
       </c>
       <c r="B17" s="22" t="inlineStr">
         <is>
-          <t>serow</t>
+          <t>hill_partridge</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
         <is>
-          <t>長鬃山羊</t>
+          <t>台灣山鷓鴣</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
         <is>
-          <t>山羊</t>
+          <t>雉雞</t>
         </is>
       </c>
       <c r="E17" s="27" t="n">
@@ -7696,7 +7736,7 @@
       </c>
       <c r="F17" s="22" t="inlineStr">
         <is>
-          <t>同貓科＋拿掉鬃毛</t>
+          <t>同鳥</t>
         </is>
       </c>
       <c r="G17" s="22" t="inlineStr">
@@ -7706,7 +7746,7 @@
       </c>
       <c r="H17" s="22" t="inlineStr">
         <is>
-          <t>待機、張望、低頭吃草、甩耳、走路</t>
+          <t>待機、走路、低頭啄、抬頭張望、眨眼</t>
         </is>
       </c>
       <c r="I17" s="22" t="inlineStr">
@@ -7715,11 +7755,11 @@
         </is>
       </c>
       <c r="J17" s="27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K17" s="22" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="L17" s="28" t="inlineStr">
@@ -7735,17 +7775,17 @@
       </c>
       <c r="B18" s="23" t="inlineStr">
         <is>
-          <t>crested_serpent_eagle</t>
+          <t>clouded_leopard</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
         <is>
-          <t>大冠鷲</t>
+          <t>台灣雲豹</t>
         </is>
       </c>
       <c r="D18" s="23" t="inlineStr">
         <is>
-          <t>猛禽</t>
+          <t>貓科</t>
         </is>
       </c>
       <c r="E18" s="30" t="n">
@@ -7753,17 +7793,17 @@
       </c>
       <c r="F18" s="23" t="inlineStr">
         <is>
-          <t>同鳥</t>
+          <t>E1 拿掉近側兩條腿；E3 拿掉頭；E4 拿掉兩隻耳朵；E5 閉眼；E7 頭轉向鏡頭</t>
         </is>
       </c>
       <c r="G18" s="23" t="inlineStr">
         <is>
-          <t>需要（展翅 1 張）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H18" s="23" t="inlineStr">
         <is>
-          <t>待機、張望、展翅；另需「飛行姿勢（展翅盤旋）」1 張</t>
+          <t>待機呼吸、張望、低頭聞、甩尾、耳朵抖、眨眼、張嘴、走路（定格每秒 8 格）</t>
         </is>
       </c>
       <c r="I18" s="23" t="inlineStr">
@@ -7772,11 +7812,11 @@
         </is>
       </c>
       <c r="J18" s="30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K18" s="23" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="L18" s="28" t="inlineStr">
@@ -7792,17 +7832,17 @@
       </c>
       <c r="B19" s="22" t="inlineStr">
         <is>
-          <t>maroon_oriole</t>
+          <t>eurasian_otter</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
         <is>
-          <t>朱鸝</t>
+          <t>歐亞水獺（金門）</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
         <is>
-          <t>鳥</t>
+          <t>水獺</t>
         </is>
       </c>
       <c r="E19" s="27" t="n">
@@ -7810,17 +7850,17 @@
       </c>
       <c r="F19" s="22" t="inlineStr">
         <is>
-          <t>拿掉近側翅膀；拿掉頭；閉眼；拿掉近側腳；頭轉向鏡頭</t>
+          <t>同貓科</t>
         </is>
       </c>
       <c r="G19" s="22" t="inlineStr">
         <is>
-          <t>需要（展翅 1 張）</t>
+          <t>游泳姿勢 1 張</t>
         </is>
       </c>
       <c r="H19" s="22" t="inlineStr">
         <is>
-          <t>待機、跳兩步、低頭啄、理羽毛、歪頭、眨眼、拍翅；另需「飛行姿勢」1 張</t>
+          <t>待機、站起來張望、走路、游泳（另畫游泳姿勢）</t>
         </is>
       </c>
       <c r="I19" s="22" t="inlineStr">
@@ -7829,11 +7869,11 @@
         </is>
       </c>
       <c r="J19" s="27" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K19" s="22" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="L19" s="28" t="inlineStr">
@@ -7849,17 +7889,17 @@
       </c>
       <c r="B20" s="23" t="inlineStr">
         <is>
-          <t>yellow_tit</t>
+          <t>formosan_salmon</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
         <is>
-          <t>黃山雀</t>
+          <t>櫻花鉤吻鮭</t>
         </is>
       </c>
       <c r="D20" s="23" t="inlineStr">
         <is>
-          <t>鳥</t>
+          <t>魚</t>
         </is>
       </c>
       <c r="E20" s="30" t="n">
@@ -7867,17 +7907,17 @@
       </c>
       <c r="F20" s="23" t="inlineStr">
         <is>
-          <t>拿掉近側翅膀；拿掉頭；閉眼；拿掉近側腳；頭轉向鏡頭</t>
+          <t>拿掉胸鰭</t>
         </is>
       </c>
       <c r="G20" s="23" t="inlineStr">
         <is>
-          <t>需要（展翅 1 張）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H20" s="23" t="inlineStr">
         <is>
-          <t>待機、跳兩步、低頭啄、理羽毛、歪頭、眨眼、拍翅；另需「飛行姿勢」1 張</t>
+          <t>游動擺尾、停在水中、轉向</t>
         </is>
       </c>
       <c r="I20" s="23" t="inlineStr">
@@ -7886,11 +7926,11 @@
         </is>
       </c>
       <c r="J20" s="30" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K20" s="23" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="L20" s="28" t="inlineStr">
@@ -7906,17 +7946,17 @@
       </c>
       <c r="B21" s="22" t="inlineStr">
         <is>
-          <t>fish_owl</t>
+          <t>green_turtle</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
         <is>
-          <t>黃魚鴞</t>
+          <t>綠蠵龜</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
         <is>
-          <t>貓頭鷹</t>
+          <t>海龜</t>
         </is>
       </c>
       <c r="E21" s="27" t="n">
@@ -7924,7 +7964,7 @@
       </c>
       <c r="F21" s="22" t="inlineStr">
         <is>
-          <t>拿掉頭；閉眼；拿掉耳羽；頭轉向鏡頭</t>
+          <t>拿掉近側前鰭</t>
         </is>
       </c>
       <c r="G21" s="22" t="inlineStr">
@@ -7934,7 +7974,7 @@
       </c>
       <c r="H21" s="22" t="inlineStr">
         <is>
-          <t>待機、大角度轉頭、眨眼、縮成一團（發光眼睛由程式畫）</t>
+          <t>划水、浮上換氣、轉頭</t>
         </is>
       </c>
       <c r="I21" s="22" t="inlineStr">
@@ -7943,11 +7983,11 @@
         </is>
       </c>
       <c r="J21" s="27" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K21" s="22" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="L21" s="28" t="inlineStr">
@@ -7963,35 +8003,35 @@
       </c>
       <c r="B22" s="23" t="inlineStr">
         <is>
-          <t>iriomote_cat</t>
+          <t>white_dolphin</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
         <is>
-          <t>西表山貓</t>
+          <t>中華白海豚</t>
         </is>
       </c>
       <c r="D22" s="23" t="inlineStr">
         <is>
-          <t>貓科</t>
+          <t>海豚</t>
         </is>
       </c>
       <c r="E22" s="30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F22" s="23" t="inlineStr">
         <is>
-          <t>E1 拿掉近側兩條腿；E3 拿掉頭；E4 拿掉兩隻耳朵；E5 閉眼；E7 頭轉向鏡頭</t>
+          <t>拿掉胸鰭</t>
         </is>
       </c>
       <c r="G22" s="23" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>躍出水面 1 張</t>
         </is>
       </c>
       <c r="H22" s="23" t="inlineStr">
         <is>
-          <t>待機呼吸、張望、低頭聞、甩尾、耳朵抖、眨眼、張嘴、走路（定格每秒 8 格）</t>
+          <t>游、躍出水面、噴氣</t>
         </is>
       </c>
       <c r="I22" s="23" t="inlineStr">
@@ -8000,11 +8040,11 @@
         </is>
       </c>
       <c r="J22" s="30" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K22" s="23" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="L22" s="28" t="inlineStr">
@@ -8020,35 +8060,35 @@
       </c>
       <c r="B23" s="22" t="inlineStr">
         <is>
-          <t>okinawa_woodpecker</t>
+          <t>broad_tailed_swallowtail</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
         <is>
-          <t>野口啄木鳥</t>
+          <t>寬尾鳳蝶</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
         <is>
-          <t>鳥</t>
+          <t>蝴蝶</t>
         </is>
       </c>
       <c r="E23" s="27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F23" s="22" t="inlineStr">
         <is>
-          <t>拿掉近側翅膀；拿掉頭；閉眼；拿掉近側腳；頭轉向鏡頭</t>
+          <t>—（另畫停棲姿勢）</t>
         </is>
       </c>
       <c r="G23" s="22" t="inlineStr">
         <is>
-          <t>需要（展翅 1 張）</t>
+          <t>停棲（翅膀合起）1 張</t>
         </is>
       </c>
       <c r="H23" s="22" t="inlineStr">
         <is>
-          <t>待機、跳兩步、低頭啄、理羽毛、歪頭、眨眼、拍翅；另需「飛行姿勢」1 張</t>
+          <t>拍翅飛舞、停在花上翅膀開合</t>
         </is>
       </c>
       <c r="I23" s="22" t="inlineStr">
@@ -8057,11 +8097,11 @@
         </is>
       </c>
       <c r="J23" s="27" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K23" s="22" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="L23" s="28" t="inlineStr">
@@ -8077,25 +8117,25 @@
       </c>
       <c r="B24" s="23" t="inlineStr">
         <is>
-          <t>japanese_serow</t>
+          <t>farmland_tree_frog</t>
         </is>
       </c>
       <c r="C24" s="23" t="inlineStr">
         <is>
-          <t>日本鬣羚</t>
+          <t>諸羅樹蛙</t>
         </is>
       </c>
       <c r="D24" s="23" t="inlineStr">
         <is>
-          <t>山羊</t>
+          <t>蛙</t>
         </is>
       </c>
       <c r="E24" s="30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F24" s="23" t="inlineStr">
         <is>
-          <t>同貓科＋拿掉鬃毛</t>
+          <t>拿掉近側後腳；閉眼</t>
         </is>
       </c>
       <c r="G24" s="23" t="inlineStr">
@@ -8105,7 +8145,7 @@
       </c>
       <c r="H24" s="23" t="inlineStr">
         <is>
-          <t>待機、張望、低頭吃草、甩耳、走路</t>
+          <t>待機、鼓鳴囊（叫）、跳、眨眼</t>
         </is>
       </c>
       <c r="I24" s="23" t="inlineStr">
@@ -8114,11 +8154,11 @@
         </is>
       </c>
       <c r="J24" s="30" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K24" s="23" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="L24" s="28" t="inlineStr">
@@ -8134,35 +8174,35 @@
       </c>
       <c r="B25" s="22" t="inlineStr">
         <is>
-          <t>ptarmigan</t>
+          <t>formosan_flying_fox</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
         <is>
-          <t>雷鳥</t>
+          <t>台灣狐蝠</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
         <is>
-          <t>雉雞</t>
+          <t>蝙蝠</t>
         </is>
       </c>
       <c r="E25" s="27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F25" s="22" t="inlineStr">
         <is>
-          <t>同鳥</t>
+          <t>—（另畫倒掛、飛行姿勢）</t>
         </is>
       </c>
       <c r="G25" s="22" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>飛行（展翼）、倒掛各 1 張</t>
         </is>
       </c>
       <c r="H25" s="22" t="inlineStr">
         <is>
-          <t>待機、走路、低頭啄、抬頭張望、眨眼</t>
+          <t>飛行拍翼、倒掛時收翼、轉頭</t>
         </is>
       </c>
       <c r="I25" s="22" t="inlineStr">
@@ -8171,11 +8211,11 @@
         </is>
       </c>
       <c r="J25" s="27" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K25" s="22" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="L25" s="28" t="inlineStr">
@@ -8191,17 +8231,17 @@
       </c>
       <c r="B26" s="23" t="inlineStr">
         <is>
-          <t>blakiston_owl</t>
+          <t>iriomote_cat</t>
         </is>
       </c>
       <c r="C26" s="23" t="inlineStr">
         <is>
-          <t>毛腿魚鴞</t>
+          <t>西表山貓</t>
         </is>
       </c>
       <c r="D26" s="23" t="inlineStr">
         <is>
-          <t>貓頭鷹</t>
+          <t>貓科</t>
         </is>
       </c>
       <c r="E26" s="30" t="n">
@@ -8209,7 +8249,7 @@
       </c>
       <c r="F26" s="23" t="inlineStr">
         <is>
-          <t>拿掉頭；閉眼；拿掉耳羽；頭轉向鏡頭</t>
+          <t>E1 拿掉近側兩條腿；E3 拿掉頭；E4 拿掉兩隻耳朵；E5 閉眼；E7 頭轉向鏡頭</t>
         </is>
       </c>
       <c r="G26" s="23" t="inlineStr">
@@ -8219,7 +8259,7 @@
       </c>
       <c r="H26" s="23" t="inlineStr">
         <is>
-          <t>待機、大角度轉頭、眨眼、縮成一團（發光眼睛由程式畫）</t>
+          <t>待機呼吸、張望、低頭聞、甩尾、耳朵抖、眨眼、張嘴、走路（定格每秒 8 格）</t>
         </is>
       </c>
       <c r="I26" s="23" t="inlineStr">
@@ -8248,17 +8288,17 @@
       </c>
       <c r="B27" s="22" t="inlineStr">
         <is>
-          <t>tsushima_cat</t>
+          <t>okinawa_woodpecker</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
         <is>
-          <t>對馬山貓</t>
+          <t>野口啄木鳥</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
         <is>
-          <t>貓科</t>
+          <t>鳥</t>
         </is>
       </c>
       <c r="E27" s="27" t="n">
@@ -8266,17 +8306,17 @@
       </c>
       <c r="F27" s="22" t="inlineStr">
         <is>
-          <t>E1 拿掉近側兩條腿；E3 拿掉頭；E4 拿掉兩隻耳朵；E5 閉眼；E7 頭轉向鏡頭</t>
+          <t>拿掉近側翅膀；拿掉頭；閉眼；拿掉近側腳；頭轉向鏡頭</t>
         </is>
       </c>
       <c r="G27" s="22" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>飛行姿勢 1 張</t>
         </is>
       </c>
       <c r="H27" s="22" t="inlineStr">
         <is>
-          <t>待機呼吸、張望、低頭聞、甩尾、耳朵抖、眨眼、張嘴、走路（定格每秒 8 格）</t>
+          <t>待機、跳兩步、低頭啄、理羽毛、歪頭、眨眼、拍翅；另需「飛行姿勢」1 張</t>
         </is>
       </c>
       <c r="I27" s="22" t="inlineStr">
@@ -8305,17 +8345,17 @@
       </c>
       <c r="B28" s="23" t="inlineStr">
         <is>
-          <t>steller_eagle</t>
+          <t>japanese_serow</t>
         </is>
       </c>
       <c r="C28" s="23" t="inlineStr">
         <is>
-          <t>虎頭海鵰</t>
+          <t>日本鬣羚</t>
         </is>
       </c>
       <c r="D28" s="23" t="inlineStr">
         <is>
-          <t>猛禽</t>
+          <t>山羊</t>
         </is>
       </c>
       <c r="E28" s="30" t="n">
@@ -8323,17 +8363,17 @@
       </c>
       <c r="F28" s="23" t="inlineStr">
         <is>
-          <t>同鳥</t>
+          <t>同貓科＋拿掉鬃毛</t>
         </is>
       </c>
       <c r="G28" s="23" t="inlineStr">
         <is>
-          <t>需要（展翅 1 張）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H28" s="23" t="inlineStr">
         <is>
-          <t>待機、張望、展翅；另需「飛行姿勢（展翅盤旋）」1 張</t>
+          <t>待機、張望、低頭吃草、甩耳、走路</t>
         </is>
       </c>
       <c r="I28" s="23" t="inlineStr">
@@ -8362,17 +8402,17 @@
       </c>
       <c r="B29" s="22" t="inlineStr">
         <is>
-          <t>moon_bear</t>
+          <t>ptarmigan</t>
         </is>
       </c>
       <c r="C29" s="22" t="inlineStr">
         <is>
-          <t>月輪熊</t>
+          <t>雷鳥</t>
         </is>
       </c>
       <c r="D29" s="22" t="inlineStr">
         <is>
-          <t>熊</t>
+          <t>雉雞</t>
         </is>
       </c>
       <c r="E29" s="27" t="n">
@@ -8380,7 +8420,7 @@
       </c>
       <c r="F29" s="22" t="inlineStr">
         <is>
-          <t>同貓科</t>
+          <t>同鳥</t>
         </is>
       </c>
       <c r="G29" s="22" t="inlineStr">
@@ -8390,7 +8430,7 @@
       </c>
       <c r="H29" s="22" t="inlineStr">
         <is>
-          <t>待機、張望、低頭聞、坐下、走路</t>
+          <t>待機、走路、低頭啄、抬頭張望、眨眼</t>
         </is>
       </c>
       <c r="I29" s="22" t="inlineStr">
@@ -8419,25 +8459,25 @@
       </c>
       <c r="B30" s="23" t="inlineStr">
         <is>
-          <t>clouded_leopard</t>
+          <t>blakiston_owl</t>
         </is>
       </c>
       <c r="C30" s="23" t="inlineStr">
         <is>
-          <t>台灣雲豹</t>
+          <t>毛腿魚鴞</t>
         </is>
       </c>
       <c r="D30" s="23" t="inlineStr">
         <is>
-          <t>貓科</t>
+          <t>貓頭鷹</t>
         </is>
       </c>
       <c r="E30" s="30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F30" s="23" t="inlineStr">
         <is>
-          <t>E1 拿掉近側兩條腿；E3 拿掉頭；E4 拿掉兩隻耳朵；E5 閉眼；E7 頭轉向鏡頭</t>
+          <t>拿掉頭；閉眼；拿掉耳羽；頭轉向鏡頭</t>
         </is>
       </c>
       <c r="G30" s="23" t="inlineStr">
@@ -8447,7 +8487,7 @@
       </c>
       <c r="H30" s="23" t="inlineStr">
         <is>
-          <t>待機呼吸、張望、低頭聞、甩尾、耳朵抖、眨眼、張嘴、走路（定格每秒 8 格）</t>
+          <t>待機、大角度轉頭、眨眼、縮成一團（發光眼睛由程式畫）</t>
         </is>
       </c>
       <c r="I30" s="23" t="inlineStr">
@@ -8456,11 +8496,11 @@
         </is>
       </c>
       <c r="J30" s="30" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K30" s="23" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="L30" s="28" t="inlineStr">
@@ -8476,35 +8516,35 @@
       </c>
       <c r="B31" s="22" t="inlineStr">
         <is>
-          <t>black_eagle</t>
+          <t>tsushima_cat</t>
         </is>
       </c>
       <c r="C31" s="22" t="inlineStr">
         <is>
-          <t>林鵰</t>
+          <t>對馬山貓</t>
         </is>
       </c>
       <c r="D31" s="22" t="inlineStr">
         <is>
-          <t>猛禽</t>
+          <t>貓科</t>
         </is>
       </c>
       <c r="E31" s="27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F31" s="22" t="inlineStr">
         <is>
-          <t>同鳥</t>
+          <t>E1 拿掉近側兩條腿；E3 拿掉頭；E4 拿掉兩隻耳朵；E5 閉眼；E7 頭轉向鏡頭</t>
         </is>
       </c>
       <c r="G31" s="22" t="inlineStr">
         <is>
-          <t>需要（展翅 1 張）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H31" s="22" t="inlineStr">
         <is>
-          <t>待機、張望、展翅；另需「飛行姿勢（展翅盤旋）」1 張</t>
+          <t>待機呼吸、張望、低頭聞、甩尾、耳朵抖、眨眼、張嘴、走路（定格每秒 8 格）</t>
         </is>
       </c>
       <c r="I31" s="22" t="inlineStr">
@@ -8513,11 +8553,11 @@
         </is>
       </c>
       <c r="J31" s="27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K31" s="22" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="L31" s="28" t="inlineStr">
@@ -8533,35 +8573,35 @@
       </c>
       <c r="B32" s="23" t="inlineStr">
         <is>
-          <t>lanyu_scops_owl</t>
+          <t>steller_eagle</t>
         </is>
       </c>
       <c r="C32" s="23" t="inlineStr">
         <is>
-          <t>蘭嶼角鴞</t>
+          <t>虎頭海鵰</t>
         </is>
       </c>
       <c r="D32" s="23" t="inlineStr">
         <is>
-          <t>貓頭鷹</t>
+          <t>猛禽</t>
         </is>
       </c>
       <c r="E32" s="30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F32" s="23" t="inlineStr">
         <is>
-          <t>拿掉頭；閉眼；拿掉耳羽；頭轉向鏡頭</t>
+          <t>同鳥</t>
         </is>
       </c>
       <c r="G32" s="23" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>展翅盤旋 1 張</t>
         </is>
       </c>
       <c r="H32" s="23" t="inlineStr">
         <is>
-          <t>待機、大角度轉頭、眨眼、縮成一團（發光眼睛由程式畫）</t>
+          <t>待機、張望、展翅；另需「飛行姿勢（展翅盤旋）」1 張</t>
         </is>
       </c>
       <c r="I32" s="23" t="inlineStr">
@@ -8570,11 +8610,11 @@
         </is>
       </c>
       <c r="J32" s="30" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K32" s="23" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="L32" s="28" t="inlineStr">
@@ -8590,25 +8630,25 @@
       </c>
       <c r="B33" s="22" t="inlineStr">
         <is>
-          <t>hill_partridge</t>
+          <t>moon_bear</t>
         </is>
       </c>
       <c r="C33" s="22" t="inlineStr">
         <is>
-          <t>台灣山鷓鴣</t>
+          <t>月輪熊</t>
         </is>
       </c>
       <c r="D33" s="22" t="inlineStr">
         <is>
-          <t>雉雞</t>
+          <t>熊</t>
         </is>
       </c>
       <c r="E33" s="27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F33" s="22" t="inlineStr">
         <is>
-          <t>同鳥</t>
+          <t>同貓科</t>
         </is>
       </c>
       <c r="G33" s="22" t="inlineStr">
@@ -8618,7 +8658,7 @@
       </c>
       <c r="H33" s="22" t="inlineStr">
         <is>
-          <t>待機、走路、低頭啄、抬頭張望、眨眼</t>
+          <t>待機、張望、低頭聞、坐下、走路</t>
         </is>
       </c>
       <c r="I33" s="22" t="inlineStr">
@@ -8627,11 +8667,11 @@
         </is>
       </c>
       <c r="J33" s="27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K33" s="22" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="L33" s="28" t="inlineStr">
@@ -8662,7 +8702,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -8744,7 +8784,7 @@
       </c>
       <c r="C5" s="22" t="inlineStr">
         <is>
-          <t>石虎、西表山貓、對馬山貓、小麝香貓、台灣雲豹</t>
+          <t>石虎、台灣雲豹、西表山貓、對馬山貓</t>
         </is>
       </c>
       <c r="D5" s="22" t="inlineStr">
@@ -8828,7 +8868,7 @@
       </c>
       <c r="C7" s="22" t="inlineStr">
         <is>
-          <t>長鬃山羊、日本鬣羚</t>
+          <t>日本鬣羚</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -8860,7 +8900,7 @@
     <row r="8">
       <c r="A8" s="23" t="inlineStr">
         <is>
-          <t>貂、獴</t>
+          <t>貂</t>
         </is>
       </c>
       <c r="B8" s="23" t="inlineStr">
@@ -8870,7 +8910,7 @@
       </c>
       <c r="C8" s="23" t="inlineStr">
         <is>
-          <t>食蟹獴、黃喉貂</t>
+          <t>黃喉貂</t>
         </is>
       </c>
       <c r="D8" s="23" t="inlineStr">
@@ -8954,7 +8994,7 @@
       </c>
       <c r="C10" s="23" t="inlineStr">
         <is>
-          <t>台灣藍鵲、八色鳥、朱鸝、黃山雀、野口啄木鳥</t>
+          <t>台灣藍鵲、八色鳥、黃山雀、野口啄木鳥</t>
         </is>
       </c>
       <c r="D10" s="23" t="inlineStr">
@@ -8996,7 +9036,7 @@
       </c>
       <c r="C11" s="22" t="inlineStr">
         <is>
-          <t>藍腹鷴、帝雉、雷鳥、台灣山鷓鴣</t>
+          <t>帝雉、藍腹鷴、台灣山鷓鴣、雷鳥</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -9038,7 +9078,7 @@
       </c>
       <c r="C12" s="23" t="inlineStr">
         <is>
-          <t>熊鷹、大冠鷲、林鵰、虎頭海鵰</t>
+          <t>熊鷹、虎頭海鵰</t>
         </is>
       </c>
       <c r="D12" s="23" t="inlineStr">
@@ -9080,7 +9120,7 @@
       </c>
       <c r="C13" s="22" t="inlineStr">
         <is>
-          <t>領角鴞、黃魚鴞、毛腿魚鴞、蘭嶼角鴞</t>
+          <t>黃魚鴞、毛腿魚鴞</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -9109,8 +9149,344 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="23" t="inlineStr">
+        <is>
+          <t>涉禽</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>wader</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>黑面琵鷺</t>
+        </is>
+      </c>
+      <c r="D14" s="23" t="inlineStr">
+        <is>
+          <t>同鳥＋長腳、長嘴</t>
+        </is>
+      </c>
+      <c r="E14" s="23" t="inlineStr">
+        <is>
+          <t>同鳥</t>
+        </is>
+      </c>
+      <c r="F14" s="23" t="inlineStr">
+        <is>
+          <t>同鳥，腳各 3 節、嘴 1 節</t>
+        </is>
+      </c>
+      <c r="G14" s="23" t="inlineStr">
+        <is>
+          <t>待機、涉水走、低頭左右掃嘴覓食、理羽毛</t>
+        </is>
+      </c>
+      <c r="H14" s="29" t="inlineStr">
+        <is>
+          <t>待第一隻實作確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="22" t="inlineStr">
+        <is>
+          <t>水獺</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>otter</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>歐亞水獺（金門）</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>同貓科；身體長、尾巴粗</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
+        <is>
+          <t>同貓科</t>
+        </is>
+      </c>
+      <c r="F15" s="22" t="inlineStr">
+        <is>
+          <t>同貓科，身體多 1 節、尾巴 3 節</t>
+        </is>
+      </c>
+      <c r="G15" s="22" t="inlineStr">
+        <is>
+          <t>待機、站起來張望、走路、游泳（另畫游泳姿勢）</t>
+        </is>
+      </c>
+      <c r="H15" s="29" t="inlineStr">
+        <is>
+          <t>待第一隻實作確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="23" t="inlineStr">
+        <is>
+          <t>魚</t>
+        </is>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>fish</t>
+        </is>
+      </c>
+      <c r="C16" s="23" t="inlineStr">
+        <is>
+          <t>櫻花鉤吻鮭</t>
+        </is>
+      </c>
+      <c r="D16" s="23" t="inlineStr">
+        <is>
+          <t>身體前段、身體後段、尾鰭、胸鰭、背鰭</t>
+        </is>
+      </c>
+      <c r="E16" s="23" t="inlineStr">
+        <is>
+          <t>拿掉胸鰭</t>
+        </is>
+      </c>
+      <c r="F16" s="23" t="inlineStr">
+        <is>
+          <t>約 5 根：身體 2 節、尾鰭、胸鰭、背鰭</t>
+        </is>
+      </c>
+      <c r="G16" s="23" t="inlineStr">
+        <is>
+          <t>游動擺尾、停在水中、轉向</t>
+        </is>
+      </c>
+      <c r="H16" s="29" t="inlineStr">
+        <is>
+          <t>待第一隻實作確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="22" t="inlineStr">
+        <is>
+          <t>海龜</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>turtle</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>綠蠵龜</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
+        <is>
+          <t>背甲、頭、前鰭（近、遠）、後鰭（近、遠）</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
+        <is>
+          <t>拿掉近側前鰭</t>
+        </is>
+      </c>
+      <c r="F17" s="22" t="inlineStr">
+        <is>
+          <t>約 6 根：甲殼、頭、四片鰭</t>
+        </is>
+      </c>
+      <c r="G17" s="22" t="inlineStr">
+        <is>
+          <t>划水、浮上換氣、轉頭</t>
+        </is>
+      </c>
+      <c r="H17" s="29" t="inlineStr">
+        <is>
+          <t>待第一隻實作確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="23" t="inlineStr">
+        <is>
+          <t>海豚</t>
+        </is>
+      </c>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>dolphin</t>
+        </is>
+      </c>
+      <c r="C18" s="23" t="inlineStr">
+        <is>
+          <t>中華白海豚</t>
+        </is>
+      </c>
+      <c r="D18" s="23" t="inlineStr">
+        <is>
+          <t>身體前段、身體後段、尾鰭、胸鰭、背鰭</t>
+        </is>
+      </c>
+      <c r="E18" s="23" t="inlineStr">
+        <is>
+          <t>拿掉胸鰭</t>
+        </is>
+      </c>
+      <c r="F18" s="23" t="inlineStr">
+        <is>
+          <t>約 5 根：身體 2 節、尾鰭、胸鰭</t>
+        </is>
+      </c>
+      <c r="G18" s="23" t="inlineStr">
+        <is>
+          <t>游、躍出水面、噴氣</t>
+        </is>
+      </c>
+      <c r="H18" s="29" t="inlineStr">
+        <is>
+          <t>待第一隻實作確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="22" t="inlineStr">
+        <is>
+          <t>蝴蝶</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>butterfly</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>寬尾鳳蝶</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>身體、前翅、後翅（左右各一）、觸角</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="inlineStr">
+        <is>
+          <t>—（另畫停棲姿勢）</t>
+        </is>
+      </c>
+      <c r="F19" s="22" t="inlineStr">
+        <is>
+          <t>約 5 根：身體、四片翅膀</t>
+        </is>
+      </c>
+      <c r="G19" s="22" t="inlineStr">
+        <is>
+          <t>拍翅飛舞、停在花上翅膀開合</t>
+        </is>
+      </c>
+      <c r="H19" s="29" t="inlineStr">
+        <is>
+          <t>待第一隻實作確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="23" t="inlineStr">
+        <is>
+          <t>蛙</t>
+        </is>
+      </c>
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>frog</t>
+        </is>
+      </c>
+      <c r="C20" s="23" t="inlineStr">
+        <is>
+          <t>諸羅樹蛙</t>
+        </is>
+      </c>
+      <c r="D20" s="23" t="inlineStr">
+        <is>
+          <t>身體、頭、前腳、後腳（近、遠）、鳴囊、張眼、閉眼</t>
+        </is>
+      </c>
+      <c r="E20" s="23" t="inlineStr">
+        <is>
+          <t>拿掉近側後腳；閉眼</t>
+        </is>
+      </c>
+      <c r="F20" s="23" t="inlineStr">
+        <is>
+          <t>約 8 根：身體、頭、四條腿、鳴囊</t>
+        </is>
+      </c>
+      <c r="G20" s="23" t="inlineStr">
+        <is>
+          <t>待機、鼓鳴囊（叫）、跳、眨眼</t>
+        </is>
+      </c>
+      <c r="H20" s="29" t="inlineStr">
+        <is>
+          <t>待第一隻實作確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="22" t="inlineStr">
+        <is>
+          <t>蝙蝠</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>bat</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>台灣狐蝠</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>身體、頭、雙翼（近、遠）、腳</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="inlineStr">
+        <is>
+          <t>—（另畫倒掛、飛行姿勢）</t>
+        </is>
+      </c>
+      <c r="F21" s="22" t="inlineStr">
+        <is>
+          <t>約 7 根：身體、頭、兩翼各 2 節、腳</t>
+        </is>
+      </c>
+      <c r="G21" s="22" t="inlineStr">
+        <is>
+          <t>飛行拍翼、倒掛時收翼、轉頭</t>
+        </is>
+      </c>
+      <c r="H21" s="29" t="inlineStr">
+        <is>
+          <t>待第一隻實作確認</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:H13"/>
+  <autoFilter ref="A4:H21"/>
   <mergeCells count="1">
     <mergeCell ref="A2:H2"/>
   </mergeCells>
@@ -9125,7 +9501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9227,7 +9603,7 @@
       </c>
       <c r="E5" s="22" t="inlineStr">
         <is>
-          <t>台灣藍鵲、八色鳥、石虎、藍腹鷴、朱鸝、台灣山鷓鴣</t>
+          <t>石虎、台灣藍鵲、八色鳥、藍腹鷴、台灣山鷓鴣</t>
         </is>
       </c>
       <c r="F5" s="22" t="inlineStr">
@@ -9275,7 +9651,7 @@
       </c>
       <c r="E6" s="23" t="inlineStr">
         <is>
-          <t>領角鴞、穿山甲、小麝香貓、台灣雲豹</t>
+          <t>穿山甲、台灣雲豹、諸羅樹蛙</t>
         </is>
       </c>
       <c r="F6" s="23" t="inlineStr">
@@ -9323,7 +9699,7 @@
       </c>
       <c r="E7" s="22" t="inlineStr">
         <is>
-          <t>食蟹獴、虎頭海鵰</t>
+          <t>虎頭海鵰</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr">
@@ -9367,7 +9743,7 @@
       </c>
       <c r="E8" s="23" t="inlineStr">
         <is>
-          <t>黃魚鴞、毛腿魚鴞</t>
+          <t>黃魚鴞、歐亞水獺（金門）、毛腿魚鴞</t>
         </is>
       </c>
       <c r="F8" s="23" t="inlineStr">
@@ -9455,7 +9831,7 @@
       </c>
       <c r="E10" s="23" t="inlineStr">
         <is>
-          <t>西表山貓、蘭嶼角鴞</t>
+          <t>台灣狐蝠、西表山貓</t>
         </is>
       </c>
       <c r="F10" s="23" t="inlineStr">
@@ -9499,7 +9875,7 @@
       </c>
       <c r="E11" s="22" t="inlineStr">
         <is>
-          <t>黃喉貂、熊鷹、台灣黑熊、帝雉、大冠鷲、黃山雀、日本鬣羚、月輪熊、林鵰</t>
+          <t>台灣黑熊、帝雉、黃喉貂、熊鷹、黃山雀、寬尾鳳蝶、日本鬣羚、月輪熊</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -9543,7 +9919,7 @@
       </c>
       <c r="E12" s="23" t="inlineStr">
         <is>
-          <t>長鬃山羊、雷鳥</t>
+          <t>雷鳥</t>
         </is>
       </c>
       <c r="F12" s="23" t="inlineStr">
@@ -9664,22 +10040,22 @@
       </c>
       <c r="B15" s="22" t="inlineStr">
         <is>
-          <t>pano-forest-low-dusk.webp</t>
+          <t>pano-wetland-day.webp</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
         <is>
-          <t>中低海拔森林</t>
+          <t>濕地河口</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
         <is>
-          <t>晨昏</t>
+          <t>白天</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
         <is>
-          <t>石虎、藍腹鷴、台灣山鷓鴣</t>
+          <t>黑面琵鷺</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -9688,21 +10064,21 @@
         </is>
       </c>
       <c r="G15" s="27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H15" s="22" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="I15" s="33" t="inlineStr">
-        <is>
-          <t>選配</t>
+      <c r="I15" s="28" t="inlineStr">
+        <is>
+          <t>未開始</t>
         </is>
       </c>
       <c r="J15" s="29" t="inlineStr">
         <is>
-          <t>先用白天版加暖色調</t>
+          <t>新增物種用（黑面琵鷺）</t>
         </is>
       </c>
     </row>
@@ -9712,22 +10088,22 @@
       </c>
       <c r="B16" s="23" t="inlineStr">
         <is>
-          <t>pano-forest-mountain-dusk.webp</t>
+          <t>pano-ocean-day.webp</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
         <is>
-          <t>山地森林（針葉林、較涼）</t>
+          <t>海洋（海面＋淺水下）</t>
         </is>
       </c>
       <c r="D16" s="23" t="inlineStr">
         <is>
-          <t>晨昏</t>
+          <t>白天</t>
         </is>
       </c>
       <c r="E16" s="23" t="inlineStr">
         <is>
-          <t>帝雉、日本鬣羚</t>
+          <t>綠蠵龜、中華白海豚</t>
         </is>
       </c>
       <c r="F16" s="23" t="inlineStr">
@@ -9736,21 +10112,21 @@
         </is>
       </c>
       <c r="G16" s="30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H16" s="23" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="I16" s="33" t="inlineStr">
-        <is>
-          <t>選配</t>
+      <c r="I16" s="28" t="inlineStr">
+        <is>
+          <t>未開始</t>
         </is>
       </c>
       <c r="J16" s="29" t="inlineStr">
         <is>
-          <t>先用白天版加暖色調</t>
+          <t>新增物種用；要看得到水下（綠蠵龜、中華白海豚）</t>
         </is>
       </c>
     </row>
@@ -9760,50 +10136,194 @@
       </c>
       <c r="B17" s="22" t="inlineStr">
         <is>
+          <t>pano-stream-under-day.webp</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>溪流水下</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
+        <is>
+          <t>白天</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
+        <is>
+          <t>櫻花鉤吻鮭</t>
+        </is>
+      </c>
+      <c r="F17" s="22" t="inlineStr">
+        <is>
+          <t>約 3000×1150</t>
+        </is>
+      </c>
+      <c r="G17" s="27" t="n">
+        <v>6</v>
+      </c>
+      <c r="H17" s="22" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I17" s="28" t="inlineStr">
+        <is>
+          <t>未開始</t>
+        </is>
+      </c>
+      <c r="J17" s="29" t="inlineStr">
+        <is>
+          <t>新增物種用（櫻花鉤吻鮭）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="30" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>pano-forest-low-dusk.webp</t>
+        </is>
+      </c>
+      <c r="C18" s="23" t="inlineStr">
+        <is>
+          <t>中低海拔森林</t>
+        </is>
+      </c>
+      <c r="D18" s="23" t="inlineStr">
+        <is>
+          <t>晨昏</t>
+        </is>
+      </c>
+      <c r="E18" s="23" t="inlineStr">
+        <is>
+          <t>石虎、藍腹鷴、台灣山鷓鴣</t>
+        </is>
+      </c>
+      <c r="F18" s="23" t="inlineStr">
+        <is>
+          <t>約 3000×1150</t>
+        </is>
+      </c>
+      <c r="G18" s="30" t="n">
+        <v>5</v>
+      </c>
+      <c r="H18" s="23" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I18" s="33" t="inlineStr">
+        <is>
+          <t>選配</t>
+        </is>
+      </c>
+      <c r="J18" s="29" t="inlineStr">
+        <is>
+          <t>先用白天版加暖色調</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="27" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>pano-forest-mountain-dusk.webp</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>山地森林（針葉林、較涼）</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>晨昏</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="inlineStr">
+        <is>
+          <t>帝雉、日本鬣羚</t>
+        </is>
+      </c>
+      <c r="F19" s="22" t="inlineStr">
+        <is>
+          <t>約 3000×1150</t>
+        </is>
+      </c>
+      <c r="G19" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="H19" s="22" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="I19" s="33" t="inlineStr">
+        <is>
+          <t>選配</t>
+        </is>
+      </c>
+      <c r="J19" s="29" t="inlineStr">
+        <is>
+          <t>先用白天版加暖色調</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="30" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="23" t="inlineStr">
+        <is>
           <t>pano-alpine-dusk.webp</t>
         </is>
       </c>
-      <c r="C17" s="22" t="inlineStr">
+      <c r="C20" s="23" t="inlineStr">
         <is>
           <t>高山（草原、岩壁）</t>
         </is>
       </c>
-      <c r="D17" s="22" t="inlineStr">
+      <c r="D20" s="23" t="inlineStr">
         <is>
           <t>晨昏</t>
         </is>
       </c>
-      <c r="E17" s="22" t="inlineStr">
-        <is>
-          <t>長鬃山羊</t>
-        </is>
-      </c>
-      <c r="F17" s="22" t="inlineStr">
+      <c r="E20" s="23" t="inlineStr">
+        <is>
+          <t>（之後新增的動物）</t>
+        </is>
+      </c>
+      <c r="F20" s="23" t="inlineStr">
         <is>
           <t>約 3000×1150</t>
         </is>
       </c>
-      <c r="G17" s="27" t="n">
+      <c r="G20" s="30" t="n">
         <v>5</v>
       </c>
-      <c r="H17" s="22" t="inlineStr">
+      <c r="H20" s="23" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="I17" s="33" t="inlineStr">
+      <c r="I20" s="33" t="inlineStr">
         <is>
           <t>選配</t>
         </is>
       </c>
-      <c r="J17" s="29" t="inlineStr">
+      <c r="J20" s="29" t="inlineStr">
         <is>
           <t>先用白天版加暖色調</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:J17"/>
+  <autoFilter ref="A4:J20"/>
   <mergeCells count="1">
     <mergeCell ref="A2:J2"/>
   </mergeCells>

--- a/docs/美術清單.xlsx
+++ b/docs/美術清單.xlsx
@@ -27,8 +27,8 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'共通規格'!$A$4:$C$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'動物尺寸'!$A$4:$E$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'A 動物主圖'!$A$4:$R$33</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'B 動物動態'!$A$4:$M$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'A 動物主圖'!$A$4:$R$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'B 動物動態'!$A$4:$M$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'B-1 體型模板'!$A$4:$H$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'C 望遠鏡全景'!$A$4:$J$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'C-1 全景規格'!$A$4:$C$13</definedName>
@@ -48,7 +48,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -82,6 +82,12 @@
       <b val="1"/>
       <color rgb="004A6A42"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <name val="Microsoft JhengHei"/>
+      <b val="1"/>
+      <color rgb="004A6A42"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Microsoft JhengHei"/>
@@ -135,6 +141,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00E8EEDB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFF4C2"/>
       </patternFill>
     </fill>
@@ -161,11 +172,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D6EBCB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E8EEDB"/>
       </patternFill>
     </fill>
     <fill>
@@ -200,42 +206,42 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -248,20 +254,20 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -270,6 +276,9 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -753,15 +762,15 @@
         </is>
       </c>
       <c r="C5" s="5">
-        <f>COUNTA('A 動物主圖'!$B$5:$B$33)</f>
+        <f>COUNTA('A 動物主圖'!$B$5:$B$35)</f>
         <v/>
       </c>
       <c r="D5" s="5">
-        <f>SUM('A 動物主圖'!$F$5:$F$33)</f>
+        <f>SUM('A 動物主圖'!$F$5:$F$35)</f>
         <v/>
       </c>
       <c r="E5" s="5">
-        <f>COUNTIF('A 動物主圖'!$Q$5:$Q$33,"已完成")</f>
+        <f>COUNTIF('A 動物主圖'!$Q$5:$Q$35,"已完成")</f>
         <v/>
       </c>
       <c r="F5" s="6">
@@ -791,15 +800,15 @@
         </is>
       </c>
       <c r="C6" s="5">
-        <f>COUNTA('B 動物動態'!$B$5:$B$33)</f>
+        <f>COUNTA('B 動物動態'!$B$5:$B$35)</f>
         <v/>
       </c>
       <c r="D6" s="5">
-        <f>SUM('B 動物動態'!$E$5:$E$33)</f>
+        <f>SUM('B 動物動態'!$E$5:$E$35)</f>
         <v/>
       </c>
       <c r="E6" s="5">
-        <f>COUNTIF('B 動物動態'!$L$5:$L$33,"已完成")</f>
+        <f>COUNTIF('B 動物動態'!$L$5:$L$35,"已完成")</f>
         <v/>
       </c>
       <c r="F6" s="6">
@@ -1431,12 +1440,12 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="F5" s="32" t="inlineStr">
+      <c r="F5" s="33" t="inlineStr">
         <is>
           <t>暫代</t>
         </is>
       </c>
-      <c r="G5" s="29" t="inlineStr">
+      <c r="G5" s="30" t="inlineStr">
         <is>
           <t>目前程式畫</t>
         </is>
@@ -1468,12 +1477,12 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="F6" s="33" t="inlineStr">
+      <c r="F6" s="34" t="inlineStr">
         <is>
           <t>選配</t>
         </is>
       </c>
-      <c r="G6" s="29" t="inlineStr"/>
+      <c r="G6" s="30" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="22" t="inlineStr">
@@ -1501,12 +1510,12 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="F7" s="33" t="inlineStr">
+      <c r="F7" s="34" t="inlineStr">
         <is>
           <t>選配</t>
         </is>
       </c>
-      <c r="G7" s="29" t="inlineStr">
+      <c r="G7" s="30" t="inlineStr">
         <is>
           <t>目前沒有用到</t>
         </is>
@@ -1538,12 +1547,12 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="F8" s="33" t="inlineStr">
+      <c r="F8" s="34" t="inlineStr">
         <is>
           <t>選配</t>
         </is>
       </c>
-      <c r="G8" s="29" t="inlineStr">
+      <c r="G8" s="30" t="inlineStr">
         <is>
           <t>每個地區 1 張</t>
         </is>
@@ -1575,12 +1584,12 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="F9" s="28" t="inlineStr">
+      <c r="F9" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="G9" s="29" t="inlineStr"/>
+      <c r="G9" s="30" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="23" t="inlineStr">
@@ -1608,12 +1617,12 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="F10" s="28" t="inlineStr">
+      <c r="F10" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="G10" s="29" t="inlineStr"/>
+      <c r="G10" s="30" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:G10"/>
@@ -1736,12 +1745,12 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="G5" s="34" t="inlineStr">
+      <c r="G5" s="35" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
       </c>
-      <c r="H5" s="29" t="inlineStr">
+      <c r="H5" s="30" t="inlineStr">
         <is>
           <t>src/assets/icons/coin.webp</t>
         </is>
@@ -1778,12 +1787,12 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="G6" s="34" t="inlineStr">
+      <c r="G6" s="35" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
       </c>
-      <c r="H6" s="29" t="inlineStr">
+      <c r="H6" s="30" t="inlineStr">
         <is>
           <t>src/assets/icons/gem.webp</t>
         </is>
@@ -1820,12 +1829,12 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="G7" s="34" t="inlineStr">
+      <c r="G7" s="35" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
       </c>
-      <c r="H7" s="29" t="inlineStr"/>
+      <c r="H7" s="30" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="23" t="inlineStr">
@@ -1858,12 +1867,12 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="G8" s="34" t="inlineStr">
+      <c r="G8" s="35" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
       </c>
-      <c r="H8" s="29" t="inlineStr"/>
+      <c r="H8" s="30" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="22" t="inlineStr">
@@ -1896,12 +1905,12 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="G9" s="34" t="inlineStr">
+      <c r="G9" s="35" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
       </c>
-      <c r="H9" s="29" t="inlineStr"/>
+      <c r="H9" s="30" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="23" t="inlineStr">
@@ -1934,12 +1943,12 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="G10" s="28" t="inlineStr">
+      <c r="G10" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="H10" s="29" t="inlineStr">
+      <c r="H10" s="30" t="inlineStr">
         <is>
           <t>使用者有提供圖，但檔案沒有傳成功，要再傳一次</t>
         </is>
@@ -1976,12 +1985,12 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="G11" s="28" t="inlineStr">
+      <c r="G11" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="H11" s="29" t="inlineStr">
+      <c r="H11" s="30" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
@@ -2018,12 +2027,12 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="G12" s="28" t="inlineStr">
+      <c r="G12" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="H12" s="29" t="inlineStr">
+      <c r="H12" s="30" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
@@ -2060,12 +2069,12 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="G13" s="28" t="inlineStr">
+      <c r="G13" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="H13" s="29" t="inlineStr">
+      <c r="H13" s="30" t="inlineStr">
         <is>
           <t>目前用文字</t>
         </is>
@@ -2102,12 +2111,12 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="G14" s="28" t="inlineStr">
+      <c r="G14" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="H14" s="29" t="inlineStr">
+      <c r="H14" s="30" t="inlineStr">
         <is>
           <t>目前用 emoji</t>
         </is>
@@ -2144,12 +2153,12 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="G15" s="28" t="inlineStr">
+      <c r="G15" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="H15" s="29" t="inlineStr">
+      <c r="H15" s="30" t="inlineStr">
         <is>
           <t>目前用 emoji</t>
         </is>
@@ -2186,12 +2195,12 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="G16" s="32" t="inlineStr">
+      <c r="G16" s="33" t="inlineStr">
         <is>
           <t>暫代</t>
         </is>
       </c>
-      <c r="H16" s="29" t="inlineStr">
+      <c r="H16" s="30" t="inlineStr">
         <is>
           <t>目前用 lucide 線條圖示，可以沿用</t>
         </is>
@@ -2228,12 +2237,12 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="G17" s="32" t="inlineStr">
+      <c r="G17" s="33" t="inlineStr">
         <is>
           <t>暫代</t>
         </is>
       </c>
-      <c r="H17" s="29" t="inlineStr">
+      <c r="H17" s="30" t="inlineStr">
         <is>
           <t>目前用 lucide 線條圖示，可以沿用</t>
         </is>
@@ -2270,12 +2279,12 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G18" s="34" t="inlineStr">
+      <c r="G18" s="35" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
       </c>
-      <c r="H18" s="29" t="inlineStr">
+      <c r="H18" s="30" t="inlineStr">
         <is>
           <t>不用畫</t>
         </is>
@@ -2376,12 +2385,12 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="E5" s="32" t="inlineStr">
+      <c r="E5" s="33" t="inlineStr">
         <is>
           <t>暫代</t>
         </is>
       </c>
-      <c r="F5" s="29" t="inlineStr">
+      <c r="F5" s="30" t="inlineStr">
         <is>
           <t>目前是舊的溫室主題小島</t>
         </is>
@@ -2408,12 +2417,12 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="E6" s="32" t="inlineStr">
+      <c r="E6" s="33" t="inlineStr">
         <is>
           <t>暫代</t>
         </is>
       </c>
-      <c r="F6" s="29" t="inlineStr"/>
+      <c r="F6" s="30" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="22" t="inlineStr">
@@ -2436,12 +2445,12 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="E7" s="32" t="inlineStr">
+      <c r="E7" s="33" t="inlineStr">
         <is>
           <t>暫代</t>
         </is>
       </c>
-      <c r="F7" s="29" t="inlineStr">
+      <c r="F7" s="30" t="inlineStr">
         <is>
           <t>目前是程式畫的望遠鏡，可以沿用</t>
         </is>
@@ -2468,12 +2477,12 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="E8" s="28" t="inlineStr">
+      <c r="E8" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="F8" s="29" t="inlineStr">
+      <c r="F8" s="30" t="inlineStr">
         <is>
           <t>上架必填</t>
         </is>
@@ -2500,12 +2509,12 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="E9" s="28" t="inlineStr">
+      <c r="E9" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="F9" s="29" t="inlineStr">
+      <c r="F9" s="30" t="inlineStr">
         <is>
           <t>建議：大廳、望遠鏡專注、遇見動物、我的小島、觀察圖鑑地圖、專注紀錄、上週回顧、時間守護</t>
         </is>
@@ -2532,12 +2541,12 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="E10" s="28" t="inlineStr">
+      <c r="E10" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="F10" s="29" t="inlineStr">
+      <c r="F10" s="30" t="inlineStr">
         <is>
           <t>可用 App 圖示</t>
         </is>
@@ -2564,12 +2573,12 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E11" s="32" t="inlineStr">
+      <c r="E11" s="33" t="inlineStr">
         <is>
           <t>暫代</t>
         </is>
       </c>
-      <c r="F11" s="29" t="inlineStr">
+      <c r="F11" s="30" t="inlineStr">
         <is>
           <t>目前用動物圖拼湊</t>
         </is>
@@ -2596,12 +2605,12 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E12" s="32" t="inlineStr">
+      <c r="E12" s="33" t="inlineStr">
         <is>
           <t>暫代</t>
         </is>
       </c>
-      <c r="F12" s="29" t="inlineStr">
+      <c r="F12" s="30" t="inlineStr">
         <is>
           <t>目前用程式畫，可以沿用</t>
         </is>
@@ -2628,12 +2637,12 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E13" s="32" t="inlineStr">
+      <c r="E13" s="33" t="inlineStr">
         <is>
           <t>暫代</t>
         </is>
       </c>
-      <c r="F13" s="29" t="inlineStr">
+      <c r="F13" s="30" t="inlineStr">
         <is>
           <t>目前用守護動物</t>
         </is>
@@ -2660,12 +2669,12 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E14" s="28" t="inlineStr">
+      <c r="E14" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="F14" s="29" t="inlineStr"/>
+      <c r="F14" s="30" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="22" t="inlineStr">
@@ -2688,12 +2697,12 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E15" s="28" t="inlineStr">
+      <c r="E15" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="F15" s="29" t="inlineStr">
+      <c r="F15" s="30" t="inlineStr">
         <is>
           <t>總時數、專注天數、最佳日、陪你最久、和前一週比、排名、總結卡</t>
         </is>
@@ -2720,12 +2729,12 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E16" s="28" t="inlineStr">
+      <c r="E16" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="F16" s="29" t="inlineStr"/>
+      <c r="F16" s="30" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="22" t="inlineStr">
@@ -2748,12 +2757,12 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E17" s="28" t="inlineStr">
+      <c r="E17" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="F17" s="29" t="inlineStr">
+      <c r="F17" s="30" t="inlineStr">
         <is>
           <t>要和金幣動物有區別</t>
         </is>
@@ -2780,12 +2789,12 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E18" s="28" t="inlineStr">
+      <c r="E18" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="F18" s="29" t="inlineStr"/>
+      <c r="F18" s="30" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:F18"/>
@@ -2882,12 +2891,12 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="E5" s="34" t="inlineStr">
+      <c r="E5" s="35" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
       </c>
-      <c r="F5" s="29" t="inlineStr">
+      <c r="F5" s="30" t="inlineStr">
         <is>
           <t>新增區域時要補標記位置</t>
         </is>
@@ -2914,12 +2923,12 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E6" s="34" t="inlineStr">
+      <c r="E6" s="35" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
       </c>
-      <c r="F6" s="29" t="inlineStr">
+      <c r="F6" s="30" t="inlineStr">
         <is>
           <t>GPT 畫，已簡化 30%</t>
         </is>
@@ -2946,12 +2955,12 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E7" s="34" t="inlineStr">
+      <c r="E7" s="35" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
       </c>
-      <c r="F7" s="29" t="inlineStr">
+      <c r="F7" s="30" t="inlineStr">
         <is>
           <t>中間只有富士山與立山連峰</t>
         </is>
@@ -2978,12 +2987,12 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E8" s="28" t="inlineStr">
+      <c r="E8" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="F8" s="29" t="inlineStr">
+      <c r="F8" s="30" t="inlineStr">
         <is>
           <t>用地形資料畫配置圖給 GPT 對位</t>
         </is>
@@ -3077,7 +3086,7 @@
           <t>160×160</t>
         </is>
       </c>
-      <c r="D5" s="27" t="n">
+      <c r="D5" s="31" t="n">
         <v>8</v>
       </c>
       <c r="E5" s="22" t="inlineStr">
@@ -3102,7 +3111,7 @@
           <t>160×160</t>
         </is>
       </c>
-      <c r="D6" s="30" t="n">
+      <c r="D6" s="28" t="n">
         <v>6</v>
       </c>
       <c r="E6" s="23" t="inlineStr">
@@ -3127,7 +3136,7 @@
           <t>512×512</t>
         </is>
       </c>
-      <c r="D7" s="27" t="n">
+      <c r="D7" s="31" t="n">
         <v>33.5</v>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -3152,7 +3161,7 @@
           <t>512×512</t>
         </is>
       </c>
-      <c r="D8" s="30" t="n">
+      <c r="D8" s="28" t="n">
         <v>38.2</v>
       </c>
       <c r="E8" s="23" t="inlineStr">
@@ -3177,7 +3186,7 @@
           <t>512×512</t>
         </is>
       </c>
-      <c r="D9" s="27" t="n">
+      <c r="D9" s="31" t="n">
         <v>49.2</v>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -3202,7 +3211,7 @@
           <t>1697×927</t>
         </is>
       </c>
-      <c r="D10" s="30" t="n">
+      <c r="D10" s="28" t="n">
         <v>145.6</v>
       </c>
       <c r="E10" s="23" t="inlineStr">
@@ -3227,7 +3236,7 @@
           <t>1167×1347</t>
         </is>
       </c>
-      <c r="D11" s="27" t="n">
+      <c r="D11" s="31" t="n">
         <v>105</v>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -3252,7 +3261,7 @@
           <t>1200×572</t>
         </is>
       </c>
-      <c r="D12" s="30" t="n">
+      <c r="D12" s="28" t="n">
         <v>89.5</v>
       </c>
       <c r="E12" s="23" t="inlineStr">
@@ -3277,7 +3286,7 @@
           <t>1024×1536</t>
         </is>
       </c>
-      <c r="D13" s="27" t="n">
+      <c r="D13" s="31" t="n">
         <v>101.4</v>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -3302,7 +3311,7 @@
           <t>1254×1254</t>
         </is>
       </c>
-      <c r="D14" s="30" t="n">
+      <c r="D14" s="28" t="n">
         <v>57</v>
       </c>
       <c r="E14" s="23" t="inlineStr">
@@ -3327,7 +3336,7 @@
           <t>512×512</t>
         </is>
       </c>
-      <c r="D15" s="27" t="n">
+      <c r="D15" s="31" t="n">
         <v>29.5</v>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -3352,7 +3361,7 @@
           <t>512×512</t>
         </is>
       </c>
-      <c r="D16" s="30" t="n">
+      <c r="D16" s="28" t="n">
         <v>11.3</v>
       </c>
       <c r="E16" s="23" t="inlineStr">
@@ -3377,7 +3386,7 @@
           <t>192×192</t>
         </is>
       </c>
-      <c r="D17" s="27" t="n">
+      <c r="D17" s="31" t="n">
         <v>3.9</v>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -3402,7 +3411,7 @@
           <t>180×180</t>
         </is>
       </c>
-      <c r="D18" s="30" t="n">
+      <c r="D18" s="28" t="n">
         <v>3.4</v>
       </c>
       <c r="E18" s="23" t="inlineStr">
@@ -3427,7 +3436,7 @@
           <t>半尺寸</t>
         </is>
       </c>
-      <c r="D19" s="27" t="n">
+      <c r="D19" s="31" t="n">
         <v>67.5</v>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -3502,7 +3511,7 @@
           <t>檔名照規則（英文小寫、底線、階段編號）</t>
         </is>
       </c>
-      <c r="C5" s="29" t="inlineStr"/>
+      <c r="C5" s="30" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="23" t="inlineStr">
@@ -3515,7 +3524,7 @@
           <t>透明背景、sRGB；深色與淺色背景上都沒有白邊、殘留色塊</t>
         </is>
       </c>
-      <c r="C6" s="29" t="inlineStr"/>
+      <c r="C6" s="30" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="22" t="inlineStr">
@@ -3528,7 +3537,7 @@
           <t>沒有文字、浮水印、地面陰影、背景物件</t>
         </is>
       </c>
-      <c r="C7" s="29" t="inlineStr"/>
+      <c r="C7" s="30" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="23" t="inlineStr">
@@ -3541,7 +3550,7 @@
           <t>用手機實際顯示的大小檢查一次（縮小後線條、斷層最容易出現）</t>
         </is>
       </c>
-      <c r="C8" s="29" t="inlineStr"/>
+      <c r="C8" s="30" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="22" t="inlineStr">
@@ -3554,7 +3563,7 @@
           <t>正側面、頭朝右；腳底貼齊 y＝472（512 畫布，離下緣 40 px），水平置中</t>
         </is>
       </c>
-      <c r="C9" s="29" t="inlineStr"/>
+      <c r="C9" s="30" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="23" t="inlineStr">
@@ -3567,7 +3576,7 @@
           <t>三個成長階段畫布一樣大，幼年約成年的 60%、亞成年約 80%，腳底在同一條線</t>
         </is>
       </c>
-      <c r="C10" s="29" t="inlineStr"/>
+      <c r="C10" s="30" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="22" t="inlineStr">
@@ -3580,7 +3589,7 @@
           <t>三個階段看得出是同一種（毛色、斑紋、臉型一致）；縮到 30 px 仍認得出</t>
         </is>
       </c>
-      <c r="C11" s="29" t="inlineStr"/>
+      <c r="C11" s="30" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="23" t="inlineStr">
@@ -3593,7 +3602,7 @@
           <t>靜止時網格圖層合成跟主圖比：平均差 ≤ 1.5、p99 ≤ 10</t>
         </is>
       </c>
-      <c r="C12" s="29" t="inlineStr"/>
+      <c r="C12" s="30" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="22" t="inlineStr">
@@ -3606,7 +3615,7 @@
           <t>走路四個時間點、張望、低頭、張嘴、眨眼、甩尾兩端、耳朵最大角度，都用半尺寸貼圖放大檢查</t>
         </is>
       </c>
-      <c r="C13" s="29" t="inlineStr"/>
+      <c r="C13" s="30" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="23" t="inlineStr">
@@ -3619,7 +3628,7 @@
           <t>在 Galaxy A8s 實機確認；每隻壓縮後 ≤ 120 KB</t>
         </is>
       </c>
-      <c r="C14" s="29" t="inlineStr"/>
+      <c r="C14" s="30" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="22" t="inlineStr">
@@ -3632,7 +3641,7 @@
           <t>3000×1150 左右；動物停下的位置（62%, 59～70%）乾淨；夜晚版與白天版構圖完全一致</t>
         </is>
       </c>
-      <c r="C15" s="29" t="inlineStr"/>
+      <c r="C15" s="30" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="23" t="inlineStr">
@@ -3645,7 +3654,7 @@
           <t>與底圖同畫布、完全對齊；6 個動物站位不被擋住</t>
         </is>
       </c>
-      <c r="C16" s="29" t="inlineStr"/>
+      <c r="C16" s="30" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="22" t="inlineStr">
@@ -3658,7 +3667,7 @@
           <t>512 px 置中、去背；縮到 24 px 仍清楚</t>
         </is>
       </c>
-      <c r="C17" s="29" t="inlineStr"/>
+      <c r="C17" s="30" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:C17"/>
@@ -4352,7 +4361,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R33"/>
+  <dimension ref="A1:R35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4481,2432 +4490,2448 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="27" t="n">
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="27" t="inlineStr">
+        <is>
+          <t>台灣（21 種）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="22" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>black_bear</t>
         </is>
       </c>
-      <c r="C5" s="22" t="inlineStr">
+      <c r="C6" s="23" t="inlineStr">
         <is>
           <t>台灣黑熊</t>
         </is>
       </c>
-      <c r="D5" s="22" t="inlineStr">
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t>台灣</t>
         </is>
       </c>
-      <c r="E5" s="22" t="inlineStr">
+      <c r="E6" s="23" t="inlineStr">
         <is>
           <t>熊</t>
         </is>
       </c>
-      <c r="F5" s="27" t="n">
+      <c r="F6" s="28" t="n">
         <v>3</v>
       </c>
-      <c r="G5" s="22" t="inlineStr">
+      <c r="G6" s="23" t="inlineStr">
         <is>
           <t>幼年／亞成年／成年</t>
         </is>
       </c>
-      <c r="H5" s="22" t="inlineStr">
+      <c r="H6" s="23" t="inlineStr">
         <is>
           <t>黑色毛、胸前白色 V 字斑、圓耳</t>
         </is>
       </c>
-      <c r="I5" s="22" t="inlineStr">
+      <c r="I6" s="23" t="inlineStr">
         <is>
           <t>山地森林</t>
         </is>
       </c>
-      <c r="J5" s="22" t="inlineStr">
+      <c r="J6" s="23" t="inlineStr">
         <is>
           <t>白天</t>
         </is>
       </c>
-      <c r="K5" s="22" t="inlineStr">
+      <c r="K6" s="23" t="inlineStr">
         <is>
           <t>從遠處走過來</t>
         </is>
       </c>
-      <c r="L5" s="22" t="inlineStr">
+      <c r="L6" s="23" t="inlineStr">
         <is>
           <t>第一級・瀕臨絕種</t>
         </is>
       </c>
-      <c r="M5" s="22" t="inlineStr">
+      <c r="M6" s="23" t="inlineStr">
         <is>
           <t>修好「設立保育救傷站」</t>
         </is>
       </c>
-      <c r="N5" s="27" t="n">
+      <c r="N6" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="O5" s="22" t="inlineStr">
+      <c r="O6" s="23" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="P5" s="22" t="inlineStr">
+      <c r="P6" s="23" t="inlineStr">
         <is>
           <t>black_bear-0/1/2.png</t>
         </is>
       </c>
-      <c r="Q5" s="28" t="inlineStr">
+      <c r="Q6" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="R5" s="29" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="30" t="n">
+      <c r="R6" s="30" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>leopard_cat</t>
         </is>
       </c>
-      <c r="C6" s="23" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>石虎</t>
         </is>
       </c>
-      <c r="D6" s="23" t="inlineStr">
+      <c r="D7" s="22" t="inlineStr">
         <is>
           <t>台灣</t>
         </is>
       </c>
-      <c r="E6" s="23" t="inlineStr">
+      <c r="E7" s="22" t="inlineStr">
         <is>
           <t>貓科</t>
         </is>
       </c>
-      <c r="F6" s="30" t="n">
+      <c r="F7" s="31" t="n">
         <v>3</v>
       </c>
-      <c r="G6" s="23" t="inlineStr">
+      <c r="G7" s="22" t="inlineStr">
         <is>
           <t>幼年／亞成年／成年</t>
         </is>
       </c>
-      <c r="H6" s="23" t="inlineStr">
+      <c r="H7" s="22" t="inlineStr">
         <is>
           <t>家貓大小、黃褐底色有黑斑、額頭兩條白紋、耳背白斑（已有主圖，作為全系列風格參考）</t>
         </is>
       </c>
-      <c r="I6" s="23" t="inlineStr">
+      <c r="I7" s="22" t="inlineStr">
         <is>
           <t>中低海拔森林</t>
         </is>
       </c>
-      <c r="J6" s="23" t="inlineStr">
+      <c r="J7" s="22" t="inlineStr">
         <is>
           <t>晨昏</t>
         </is>
       </c>
-      <c r="K6" s="23" t="inlineStr">
+      <c r="K7" s="22" t="inlineStr">
         <is>
           <t>從遠處走過來</t>
         </is>
       </c>
-      <c r="L6" s="23" t="inlineStr">
+      <c r="L7" s="22" t="inlineStr">
         <is>
           <t>第一級・瀕臨絕種</t>
         </is>
       </c>
-      <c r="M6" s="23" t="inlineStr">
+      <c r="M7" s="22" t="inlineStr">
         <is>
           <t>修好「修好森林觀察小屋」</t>
         </is>
       </c>
-      <c r="N6" s="30" t="n">
+      <c r="N7" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="O6" s="23" t="inlineStr">
+      <c r="O7" s="22" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="P6" s="23" t="inlineStr">
+      <c r="P7" s="22" t="inlineStr">
         <is>
           <t>leopard_cat-0/1/2.png</t>
         </is>
       </c>
-      <c r="Q6" s="31" t="inlineStr">
+      <c r="Q7" s="32" t="inlineStr">
         <is>
           <t>製作中</t>
         </is>
       </c>
-      <c r="R6" s="29" t="inlineStr">
+      <c r="R7" s="30" t="inlineStr">
         <is>
           <t>成年主圖、網格已完成（全系列的風格與規格參考）；幼年、亞成年未做</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="27" t="n">
+    <row r="8">
+      <c r="A8" s="28" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="22" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>pangolin</t>
         </is>
       </c>
-      <c r="C7" s="22" t="inlineStr">
+      <c r="C8" s="23" t="inlineStr">
         <is>
           <t>穿山甲</t>
         </is>
       </c>
-      <c r="D7" s="22" t="inlineStr">
+      <c r="D8" s="23" t="inlineStr">
         <is>
           <t>台灣</t>
         </is>
       </c>
-      <c r="E7" s="22" t="inlineStr">
+      <c r="E8" s="23" t="inlineStr">
         <is>
           <t>穿山甲</t>
         </is>
       </c>
-      <c r="F7" s="27" t="n">
+      <c r="F8" s="28" t="n">
         <v>3</v>
       </c>
-      <c r="G7" s="22" t="inlineStr">
+      <c r="G8" s="23" t="inlineStr">
         <is>
           <t>幼年／亞成年／成年</t>
         </is>
       </c>
-      <c r="H7" s="22" t="inlineStr">
+      <c r="H8" s="23" t="inlineStr">
         <is>
           <t>全身覆蓋褐色鱗片、尖嘴、長尾巴、短腿</t>
         </is>
       </c>
-      <c r="I7" s="22" t="inlineStr">
+      <c r="I8" s="23" t="inlineStr">
         <is>
           <t>中低海拔森林</t>
         </is>
       </c>
-      <c r="J7" s="22" t="inlineStr">
+      <c r="J8" s="23" t="inlineStr">
         <is>
           <t>夜晚</t>
         </is>
       </c>
-      <c r="K7" s="22" t="inlineStr">
+      <c r="K8" s="23" t="inlineStr">
         <is>
           <t>從遠處走過來</t>
         </is>
       </c>
-      <c r="L7" s="22" t="inlineStr">
+      <c r="L8" s="23" t="inlineStr">
         <is>
           <t>第二級・珍貴稀有</t>
         </is>
       </c>
-      <c r="M7" s="22" t="inlineStr">
+      <c r="M8" s="23" t="inlineStr">
         <is>
           <t>修好「清出林間步道」</t>
         </is>
       </c>
-      <c r="N7" s="27" t="n">
+      <c r="N8" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="O7" s="22" t="inlineStr">
+      <c r="O8" s="23" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="P7" s="22" t="inlineStr">
+      <c r="P8" s="23" t="inlineStr">
         <is>
           <t>pangolin-0/1/2.png</t>
         </is>
       </c>
-      <c r="Q7" s="28" t="inlineStr">
+      <c r="Q8" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="R7" s="29" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="30" t="n">
+      <c r="R8" s="30" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="31" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="23" t="inlineStr">
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>blue_magpie</t>
         </is>
       </c>
-      <c r="C8" s="23" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t>台灣藍鵲</t>
         </is>
       </c>
-      <c r="D8" s="23" t="inlineStr">
+      <c r="D9" s="22" t="inlineStr">
         <is>
           <t>台灣</t>
         </is>
       </c>
-      <c r="E8" s="23" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t>鳥</t>
         </is>
       </c>
-      <c r="F8" s="30" t="n">
+      <c r="F9" s="31" t="n">
         <v>3</v>
       </c>
-      <c r="G8" s="23" t="inlineStr">
+      <c r="G9" s="22" t="inlineStr">
         <is>
           <t>雛鳥／幼鳥／成鳥</t>
         </is>
       </c>
-      <c r="H8" s="23" t="inlineStr">
+      <c r="H9" s="22" t="inlineStr">
         <is>
           <t>寶藍色身體、黑頭、紅嘴紅腳、非常長的白端尾羽</t>
         </is>
       </c>
-      <c r="I8" s="23" t="inlineStr">
+      <c r="I9" s="22" t="inlineStr">
         <is>
           <t>中低海拔森林</t>
         </is>
       </c>
-      <c r="J8" s="23" t="inlineStr">
+      <c r="J9" s="22" t="inlineStr">
         <is>
           <t>白天</t>
         </is>
       </c>
-      <c r="K8" s="23" t="inlineStr">
+      <c r="K9" s="22" t="inlineStr">
         <is>
           <t>遠處飛 → 停到倒木上</t>
         </is>
       </c>
-      <c r="L8" s="23" t="inlineStr">
+      <c r="L9" s="22" t="inlineStr">
         <is>
           <t>第三級・其他應予保育</t>
         </is>
       </c>
-      <c r="M8" s="23" t="inlineStr">
+      <c r="M9" s="22" t="inlineStr">
         <is>
           <t>一開始就能找</t>
         </is>
       </c>
-      <c r="N8" s="30" t="n">
+      <c r="N9" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="O8" s="23" t="inlineStr">
+      <c r="O9" s="22" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="P8" s="23" t="inlineStr">
+      <c r="P9" s="22" t="inlineStr">
         <is>
           <t>blue_magpie-0/1/2.png</t>
         </is>
       </c>
-      <c r="Q8" s="28" t="inlineStr">
+      <c r="Q9" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="R8" s="29" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="27" t="n">
+      <c r="R9" s="30" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="28" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="22" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>pitta</t>
         </is>
       </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="C10" s="23" t="inlineStr">
         <is>
           <t>八色鳥</t>
         </is>
       </c>
-      <c r="D9" s="22" t="inlineStr">
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t>台灣</t>
         </is>
       </c>
-      <c r="E9" s="22" t="inlineStr">
+      <c r="E10" s="23" t="inlineStr">
         <is>
           <t>鳥</t>
         </is>
       </c>
-      <c r="F9" s="27" t="n">
+      <c r="F10" s="28" t="n">
         <v>3</v>
       </c>
-      <c r="G9" s="22" t="inlineStr">
+      <c r="G10" s="23" t="inlineStr">
         <is>
           <t>雛鳥／幼鳥／成鳥</t>
         </is>
       </c>
-      <c r="H9" s="22" t="inlineStr">
+      <c r="H10" s="23" t="inlineStr">
         <is>
           <t>綠背、藍色肩斑、黑色過眼線、橘黃腹部、紅色尾下覆羽，短尾</t>
         </is>
       </c>
-      <c r="I9" s="22" t="inlineStr">
+      <c r="I10" s="23" t="inlineStr">
         <is>
           <t>中低海拔森林</t>
         </is>
       </c>
-      <c r="J9" s="22" t="inlineStr">
+      <c r="J10" s="23" t="inlineStr">
         <is>
           <t>白天</t>
         </is>
       </c>
-      <c r="K9" s="22" t="inlineStr">
+      <c r="K10" s="23" t="inlineStr">
         <is>
           <t>遠處飛 → 停到倒木上</t>
         </is>
       </c>
-      <c r="L9" s="22" t="inlineStr">
+      <c r="L10" s="23" t="inlineStr">
         <is>
           <t>第二級・珍貴稀有</t>
         </is>
       </c>
-      <c r="M9" s="22" t="inlineStr">
+      <c r="M10" s="23" t="inlineStr">
         <is>
           <t>修好「種回原生樹苗」</t>
         </is>
       </c>
-      <c r="N9" s="27" t="n">
+      <c r="N10" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="O9" s="22" t="inlineStr">
+      <c r="O10" s="23" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="P9" s="22" t="inlineStr">
+      <c r="P10" s="23" t="inlineStr">
         <is>
           <t>pitta-0/1/2.png</t>
         </is>
       </c>
-      <c r="Q9" s="28" t="inlineStr">
+      <c r="Q10" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="R9" s="29" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="30" t="n">
+      <c r="R10" s="30" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="31" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="23" t="inlineStr">
+      <c r="B11" s="22" t="inlineStr">
         <is>
           <t>mikado_pheasant</t>
         </is>
       </c>
-      <c r="C10" s="23" t="inlineStr">
+      <c r="C11" s="22" t="inlineStr">
         <is>
           <t>帝雉</t>
         </is>
       </c>
-      <c r="D10" s="23" t="inlineStr">
+      <c r="D11" s="22" t="inlineStr">
         <is>
           <t>台灣</t>
         </is>
       </c>
-      <c r="E10" s="23" t="inlineStr">
+      <c r="E11" s="22" t="inlineStr">
         <is>
           <t>雉雞</t>
         </is>
       </c>
-      <c r="F10" s="30" t="n">
+      <c r="F11" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="G10" s="23" t="inlineStr">
+      <c r="G11" s="22" t="inlineStr">
         <is>
           <t>只有一種樣式</t>
         </is>
       </c>
-      <c r="H10" s="23" t="inlineStr">
+      <c r="H11" s="22" t="inlineStr">
         <is>
           <t>雄鳥深藍紫光澤羽毛、紅色臉、尾羽有白色橫帶</t>
         </is>
       </c>
-      <c r="I10" s="23" t="inlineStr">
+      <c r="I11" s="22" t="inlineStr">
         <is>
           <t>山地森林</t>
         </is>
       </c>
-      <c r="J10" s="23" t="inlineStr">
+      <c r="J11" s="22" t="inlineStr">
         <is>
           <t>晨昏</t>
         </is>
       </c>
-      <c r="K10" s="23" t="inlineStr">
+      <c r="K11" s="22" t="inlineStr">
         <is>
           <t>從遠處走過來</t>
         </is>
       </c>
-      <c r="L10" s="23" t="inlineStr">
+      <c r="L11" s="22" t="inlineStr">
         <is>
           <t>第二級・珍貴稀有</t>
         </is>
       </c>
-      <c r="M10" s="23" t="inlineStr">
+      <c r="M11" s="22" t="inlineStr">
         <is>
           <t>商店 1,200 金幣</t>
         </is>
       </c>
-      <c r="N10" s="30" t="n">
+      <c r="N11" s="31" t="n">
         <v>4</v>
       </c>
-      <c r="O10" s="23" t="inlineStr">
+      <c r="O11" s="22" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="P10" s="23" t="inlineStr">
+      <c r="P11" s="22" t="inlineStr">
         <is>
           <t>mikado_pheasant-2.png</t>
         </is>
       </c>
-      <c r="Q10" s="28" t="inlineStr">
+      <c r="Q11" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="R10" s="29" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="27" t="n">
+      <c r="R11" s="30" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="28" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="22" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>swinhoe_pheasant</t>
         </is>
       </c>
-      <c r="C11" s="22" t="inlineStr">
+      <c r="C12" s="23" t="inlineStr">
         <is>
           <t>藍腹鷴</t>
         </is>
       </c>
-      <c r="D11" s="22" t="inlineStr">
+      <c r="D12" s="23" t="inlineStr">
         <is>
           <t>台灣</t>
         </is>
       </c>
-      <c r="E11" s="22" t="inlineStr">
+      <c r="E12" s="23" t="inlineStr">
         <is>
           <t>雉雞</t>
         </is>
       </c>
-      <c r="F11" s="27" t="n">
+      <c r="F12" s="28" t="n">
         <v>3</v>
       </c>
-      <c r="G11" s="22" t="inlineStr">
+      <c r="G12" s="23" t="inlineStr">
         <is>
           <t>雛鳥／幼鳥／成鳥</t>
         </is>
       </c>
-      <c r="H11" s="22" t="inlineStr">
+      <c r="H12" s="23" t="inlineStr">
         <is>
           <t>雄鳥深藍身體、白色長尾羽、紅色臉部裸皮、白色冠羽</t>
         </is>
       </c>
-      <c r="I11" s="22" t="inlineStr">
+      <c r="I12" s="23" t="inlineStr">
         <is>
           <t>中低海拔森林</t>
         </is>
       </c>
-      <c r="J11" s="22" t="inlineStr">
+      <c r="J12" s="23" t="inlineStr">
         <is>
           <t>晨昏</t>
         </is>
       </c>
-      <c r="K11" s="22" t="inlineStr">
+      <c r="K12" s="23" t="inlineStr">
         <is>
           <t>從遠處走過來</t>
         </is>
       </c>
-      <c r="L11" s="22" t="inlineStr">
+      <c r="L12" s="23" t="inlineStr">
         <is>
           <t>第二級・珍貴稀有</t>
         </is>
       </c>
-      <c r="M11" s="22" t="inlineStr">
+      <c r="M12" s="23" t="inlineStr">
         <is>
           <t>修好「恢復林下草叢」</t>
         </is>
       </c>
-      <c r="N11" s="27" t="n">
+      <c r="N12" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="O11" s="22" t="inlineStr">
+      <c r="O12" s="23" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="P11" s="22" t="inlineStr">
+      <c r="P12" s="23" t="inlineStr">
         <is>
           <t>swinhoe_pheasant-0/1/2.png</t>
         </is>
       </c>
-      <c r="Q11" s="28" t="inlineStr">
+      <c r="Q12" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="R11" s="29" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="30" t="n">
+      <c r="R12" s="30" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="31" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="23" t="inlineStr">
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>marten</t>
         </is>
       </c>
-      <c r="C12" s="23" t="inlineStr">
+      <c r="C13" s="22" t="inlineStr">
         <is>
           <t>黃喉貂</t>
         </is>
       </c>
-      <c r="D12" s="23" t="inlineStr">
+      <c r="D13" s="22" t="inlineStr">
         <is>
           <t>台灣</t>
         </is>
       </c>
-      <c r="E12" s="23" t="inlineStr">
+      <c r="E13" s="22" t="inlineStr">
         <is>
           <t>貂、獴</t>
         </is>
       </c>
-      <c r="F12" s="30" t="n">
+      <c r="F13" s="31" t="n">
         <v>3</v>
       </c>
-      <c r="G12" s="23" t="inlineStr">
+      <c r="G13" s="22" t="inlineStr">
         <is>
           <t>幼年／亞成年／成年</t>
         </is>
       </c>
-      <c r="H12" s="23" t="inlineStr">
+      <c r="H13" s="22" t="inlineStr">
         <is>
           <t>深褐近黑的細長身體、亮黃色喉嚨、長尾</t>
         </is>
       </c>
-      <c r="I12" s="23" t="inlineStr">
+      <c r="I13" s="22" t="inlineStr">
         <is>
           <t>山地森林</t>
         </is>
       </c>
-      <c r="J12" s="23" t="inlineStr">
+      <c r="J13" s="22" t="inlineStr">
         <is>
           <t>白天</t>
         </is>
       </c>
-      <c r="K12" s="23" t="inlineStr">
+      <c r="K13" s="22" t="inlineStr">
         <is>
           <t>從遠處走過來</t>
         </is>
       </c>
-      <c r="L12" s="23" t="inlineStr">
+      <c r="L13" s="22" t="inlineStr">
         <is>
           <t>第三級・其他應予保育</t>
         </is>
       </c>
-      <c r="M12" s="23" t="inlineStr">
+      <c r="M13" s="22" t="inlineStr">
         <is>
           <t>修好「整理森林水源地」</t>
         </is>
       </c>
-      <c r="N12" s="30" t="n">
+      <c r="N13" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="O12" s="23" t="inlineStr">
+      <c r="O13" s="22" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="P12" s="23" t="inlineStr">
+      <c r="P13" s="22" t="inlineStr">
         <is>
           <t>marten-0/1/2.png</t>
         </is>
       </c>
-      <c r="Q12" s="28" t="inlineStr">
+      <c r="Q13" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="R12" s="29" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="27" t="n">
+      <c r="R13" s="30" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="28" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="22" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t>hawk_eagle</t>
         </is>
       </c>
-      <c r="C13" s="22" t="inlineStr">
+      <c r="C14" s="23" t="inlineStr">
         <is>
           <t>熊鷹</t>
         </is>
       </c>
-      <c r="D13" s="22" t="inlineStr">
+      <c r="D14" s="23" t="inlineStr">
         <is>
           <t>台灣</t>
         </is>
       </c>
-      <c r="E13" s="22" t="inlineStr">
+      <c r="E14" s="23" t="inlineStr">
         <is>
           <t>猛禽</t>
         </is>
       </c>
-      <c r="F13" s="27" t="n">
+      <c r="F14" s="28" t="n">
         <v>3</v>
       </c>
-      <c r="G13" s="22" t="inlineStr">
+      <c r="G14" s="23" t="inlineStr">
         <is>
           <t>雛鳥／幼鳥／成鳥</t>
         </is>
       </c>
-      <c r="H13" s="22" t="inlineStr">
+      <c r="H14" s="23" t="inlineStr">
         <is>
           <t>大型猛禽、褐色身體、胸腹有橫斑、頭後短冠羽、寬大的翅膀</t>
         </is>
       </c>
-      <c r="I13" s="22" t="inlineStr">
+      <c r="I14" s="23" t="inlineStr">
         <is>
           <t>山地森林</t>
         </is>
       </c>
-      <c r="J13" s="22" t="inlineStr">
+      <c r="J14" s="23" t="inlineStr">
         <is>
           <t>白天</t>
         </is>
       </c>
-      <c r="K13" s="22" t="inlineStr">
+      <c r="K14" s="23" t="inlineStr">
         <is>
           <t>天空盤旋 → 降落</t>
         </is>
       </c>
-      <c r="L13" s="22" t="inlineStr">
+      <c r="L14" s="23" t="inlineStr">
         <is>
           <t>第一級・瀕臨絕種</t>
         </is>
       </c>
-      <c r="M13" s="22" t="inlineStr">
+      <c r="M14" s="23" t="inlineStr">
         <is>
           <t>修好「搭建樹冠步道」</t>
         </is>
       </c>
-      <c r="N13" s="27" t="n">
+      <c r="N14" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="O13" s="22" t="inlineStr">
+      <c r="O14" s="23" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="P13" s="22" t="inlineStr">
+      <c r="P14" s="23" t="inlineStr">
         <is>
           <t>hawk_eagle-0/1/2.png</t>
         </is>
       </c>
-      <c r="Q13" s="28" t="inlineStr">
+      <c r="Q14" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="R13" s="29" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="30" t="n">
+      <c r="R14" s="30" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="31" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="23" t="inlineStr">
+      <c r="B15" s="22" t="inlineStr">
         <is>
           <t>fish_owl</t>
         </is>
       </c>
-      <c r="C14" s="23" t="inlineStr">
+      <c r="C15" s="22" t="inlineStr">
         <is>
           <t>黃魚鴞</t>
         </is>
       </c>
-      <c r="D14" s="23" t="inlineStr">
+      <c r="D15" s="22" t="inlineStr">
         <is>
           <t>台灣</t>
         </is>
       </c>
-      <c r="E14" s="23" t="inlineStr">
+      <c r="E15" s="22" t="inlineStr">
         <is>
           <t>貓頭鷹</t>
         </is>
       </c>
-      <c r="F14" s="30" t="n">
+      <c r="F15" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="G14" s="23" t="inlineStr">
+      <c r="G15" s="22" t="inlineStr">
         <is>
           <t>只有一種樣式</t>
         </is>
       </c>
-      <c r="H14" s="23" t="inlineStr">
+      <c r="H15" s="22" t="inlineStr">
         <is>
           <t>大型貓頭鷹、橘黃褐色、明顯耳羽、黃色眼睛、腳上沒有羽毛</t>
         </is>
       </c>
-      <c r="I14" s="23" t="inlineStr">
+      <c r="I15" s="22" t="inlineStr">
         <is>
           <t>溪流</t>
         </is>
       </c>
-      <c r="J14" s="23" t="inlineStr">
+      <c r="J15" s="22" t="inlineStr">
         <is>
           <t>夜晚</t>
         </is>
       </c>
-      <c r="K14" s="23" t="inlineStr">
+      <c r="K15" s="22" t="inlineStr">
         <is>
           <t>夜裡先亮眼睛 → 停到倒木上</t>
         </is>
       </c>
-      <c r="L14" s="23" t="inlineStr">
+      <c r="L15" s="22" t="inlineStr">
         <is>
           <t>第二級・珍貴稀有</t>
         </is>
       </c>
-      <c r="M14" s="23" t="inlineStr">
+      <c r="M15" s="22" t="inlineStr">
         <is>
           <t>商店 90 寶石</t>
         </is>
       </c>
-      <c r="N14" s="30" t="n">
+      <c r="N15" s="31" t="n">
         <v>4</v>
       </c>
-      <c r="O14" s="23" t="inlineStr">
+      <c r="O15" s="22" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="P14" s="23" t="inlineStr">
+      <c r="P15" s="22" t="inlineStr">
         <is>
           <t>fish_owl-2.png</t>
         </is>
       </c>
-      <c r="Q14" s="28" t="inlineStr">
+      <c r="Q15" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="R14" s="29" t="inlineStr">
+      <c r="R15" s="30" t="inlineStr">
         <is>
           <t>程式原本寫第一級，已改成第二級</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="27" t="n">
+    <row r="16">
+      <c r="A16" s="28" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="22" t="inlineStr">
+      <c r="B16" s="23" t="inlineStr">
         <is>
           <t>black_faced_spoonbill</t>
         </is>
       </c>
-      <c r="C15" s="22" t="inlineStr">
+      <c r="C16" s="23" t="inlineStr">
         <is>
           <t>黑面琵鷺</t>
         </is>
       </c>
-      <c r="D15" s="22" t="inlineStr">
+      <c r="D16" s="23" t="inlineStr">
         <is>
           <t>台灣</t>
         </is>
       </c>
-      <c r="E15" s="22" t="inlineStr">
+      <c r="E16" s="23" t="inlineStr">
         <is>
           <t>涉禽</t>
         </is>
       </c>
-      <c r="F15" s="27" t="n">
+      <c r="F16" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="G15" s="22" t="inlineStr">
+      <c r="G16" s="23" t="inlineStr">
         <is>
           <t>只有一種樣式</t>
         </is>
       </c>
-      <c r="H15" s="22" t="inlineStr">
+      <c r="H16" s="23" t="inlineStr">
         <is>
           <t>白色羽毛、黑色的臉、黑色湯匙狀長嘴、長腳（冬候鳥，曾文溪口）</t>
         </is>
       </c>
-      <c r="I15" s="22" t="inlineStr">
+      <c r="I16" s="23" t="inlineStr">
         <is>
           <t>濕地河口</t>
         </is>
       </c>
-      <c r="J15" s="22" t="inlineStr">
+      <c r="J16" s="23" t="inlineStr">
         <is>
           <t>白天</t>
         </is>
       </c>
-      <c r="K15" s="22" t="inlineStr">
+      <c r="K16" s="23" t="inlineStr">
         <is>
           <t>從遠處涉水走過來</t>
         </is>
       </c>
-      <c r="L15" s="22" t="inlineStr">
+      <c r="L16" s="23" t="inlineStr">
         <is>
           <t>第一級・瀕臨絕種</t>
         </is>
       </c>
-      <c r="M15" s="22" t="inlineStr">
+      <c r="M16" s="23" t="inlineStr">
         <is>
           <t>待定（新物種）</t>
         </is>
       </c>
-      <c r="N15" s="27" t="n">
+      <c r="N16" s="28" t="n">
         <v>6</v>
       </c>
-      <c r="O15" s="22" t="inlineStr">
+      <c r="O16" s="23" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="P15" s="22" t="inlineStr">
+      <c r="P16" s="23" t="inlineStr">
         <is>
           <t>black_faced_spoonbill-2.png</t>
         </is>
       </c>
-      <c r="Q15" s="28" t="inlineStr">
+      <c r="Q16" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="R15" s="29" t="inlineStr">
+      <c r="R16" s="30" t="inlineStr">
         <is>
           <t>新增</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="30" t="n">
+    <row r="17">
+      <c r="A17" s="31" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="23" t="inlineStr">
+      <c r="B17" s="22" t="inlineStr">
         <is>
           <t>yellow_tit</t>
         </is>
       </c>
-      <c r="C16" s="23" t="inlineStr">
+      <c r="C17" s="22" t="inlineStr">
         <is>
           <t>黃山雀</t>
         </is>
       </c>
-      <c r="D16" s="23" t="inlineStr">
+      <c r="D17" s="22" t="inlineStr">
         <is>
           <t>台灣</t>
         </is>
       </c>
-      <c r="E16" s="23" t="inlineStr">
+      <c r="E17" s="22" t="inlineStr">
         <is>
           <t>鳥</t>
         </is>
       </c>
-      <c r="F16" s="30" t="n">
+      <c r="F17" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="G16" s="23" t="inlineStr">
+      <c r="G17" s="22" t="inlineStr">
         <is>
           <t>只有一種樣式</t>
         </is>
       </c>
-      <c r="H16" s="23" t="inlineStr">
+      <c r="H17" s="22" t="inlineStr">
         <is>
           <t>黃色身體、黑色冠羽、黑色喉部、灰藍翅膀（台灣特有種）</t>
         </is>
       </c>
-      <c r="I16" s="23" t="inlineStr">
+      <c r="I17" s="22" t="inlineStr">
         <is>
           <t>山地森林</t>
         </is>
       </c>
-      <c r="J16" s="23" t="inlineStr">
+      <c r="J17" s="22" t="inlineStr">
         <is>
           <t>白天</t>
         </is>
       </c>
-      <c r="K16" s="23" t="inlineStr">
+      <c r="K17" s="22" t="inlineStr">
         <is>
           <t>遠處飛 → 停到倒木上</t>
         </is>
       </c>
-      <c r="L16" s="23" t="inlineStr">
+      <c r="L17" s="22" t="inlineStr">
         <is>
           <t>第二級・珍貴稀有</t>
         </is>
       </c>
-      <c r="M16" s="23" t="inlineStr">
+      <c r="M17" s="22" t="inlineStr">
         <is>
           <t>商店 70 寶石</t>
         </is>
       </c>
-      <c r="N16" s="30" t="n">
+      <c r="N17" s="31" t="n">
         <v>4</v>
       </c>
-      <c r="O16" s="23" t="inlineStr">
+      <c r="O17" s="22" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="P16" s="23" t="inlineStr">
+      <c r="P17" s="22" t="inlineStr">
         <is>
           <t>yellow_tit-2.png</t>
         </is>
       </c>
-      <c r="Q16" s="28" t="inlineStr">
+      <c r="Q17" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="R16" s="29" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="27" t="n">
+      <c r="R17" s="30" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="28" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="22" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>hill_partridge</t>
         </is>
       </c>
-      <c r="C17" s="22" t="inlineStr">
+      <c r="C18" s="23" t="inlineStr">
         <is>
           <t>台灣山鷓鴣</t>
         </is>
       </c>
-      <c r="D17" s="22" t="inlineStr">
+      <c r="D18" s="23" t="inlineStr">
         <is>
           <t>台灣</t>
         </is>
       </c>
-      <c r="E17" s="22" t="inlineStr">
+      <c r="E18" s="23" t="inlineStr">
         <is>
           <t>雉雞</t>
         </is>
       </c>
-      <c r="F17" s="27" t="n">
+      <c r="F18" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="G17" s="22" t="inlineStr">
+      <c r="G18" s="23" t="inlineStr">
         <is>
           <t>只有一種樣式</t>
         </is>
       </c>
-      <c r="H17" s="22" t="inlineStr">
+      <c r="H18" s="23" t="inlineStr">
         <is>
           <t>圓胖的地棲鳥、褐色身體、白色喉部、紅色眼周（台灣特有）</t>
         </is>
       </c>
-      <c r="I17" s="22" t="inlineStr">
+      <c r="I18" s="23" t="inlineStr">
         <is>
           <t>中低海拔森林</t>
         </is>
       </c>
-      <c r="J17" s="22" t="inlineStr">
+      <c r="J18" s="23" t="inlineStr">
         <is>
           <t>晨昏</t>
         </is>
       </c>
-      <c r="K17" s="22" t="inlineStr">
+      <c r="K18" s="23" t="inlineStr">
         <is>
           <t>從遠處走過來</t>
         </is>
       </c>
-      <c r="L17" s="22" t="inlineStr">
+      <c r="L18" s="23" t="inlineStr">
         <is>
           <t>第三級・其他應予保育</t>
         </is>
       </c>
-      <c r="M17" s="22" t="inlineStr">
+      <c r="M18" s="23" t="inlineStr">
         <is>
           <t>Plus 會員</t>
         </is>
       </c>
-      <c r="N17" s="27" t="n">
+      <c r="N18" s="28" t="n">
         <v>5</v>
       </c>
-      <c r="O17" s="22" t="inlineStr">
+      <c r="O18" s="23" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="P17" s="22" t="inlineStr">
+      <c r="P18" s="23" t="inlineStr">
         <is>
           <t>hill_partridge-2.png</t>
         </is>
       </c>
-      <c r="Q17" s="28" t="inlineStr">
+      <c r="Q18" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="R17" s="29" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="30" t="n">
+      <c r="R18" s="30" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="31" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="23" t="inlineStr">
+      <c r="B19" s="22" t="inlineStr">
         <is>
           <t>clouded_leopard</t>
         </is>
       </c>
-      <c r="C18" s="23" t="inlineStr">
+      <c r="C19" s="22" t="inlineStr">
         <is>
           <t>台灣雲豹</t>
         </is>
       </c>
-      <c r="D18" s="23" t="inlineStr">
+      <c r="D19" s="22" t="inlineStr">
         <is>
           <t>台灣</t>
         </is>
       </c>
-      <c r="E18" s="23" t="inlineStr">
+      <c r="E19" s="22" t="inlineStr">
         <is>
           <t>貓科</t>
         </is>
       </c>
-      <c r="F18" s="30" t="n">
+      <c r="F19" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="G18" s="23" t="inlineStr">
+      <c r="G19" s="22" t="inlineStr">
         <is>
           <t>只有一種樣式</t>
         </is>
       </c>
-      <c r="H18" s="23" t="inlineStr">
+      <c r="H19" s="22" t="inlineStr">
         <is>
           <t>雲朵狀大斑塊、長尾、傳說感（可以畫得特別一點，例如淡淡的霧）</t>
         </is>
       </c>
-      <c r="I18" s="23" t="inlineStr">
+      <c r="I19" s="22" t="inlineStr">
         <is>
           <t>中低海拔森林</t>
         </is>
       </c>
-      <c r="J18" s="23" t="inlineStr">
+      <c r="J19" s="22" t="inlineStr">
         <is>
           <t>夜晚</t>
         </is>
       </c>
-      <c r="K18" s="23" t="inlineStr">
+      <c r="K19" s="22" t="inlineStr">
         <is>
           <t>從遠處走過來</t>
         </is>
       </c>
-      <c r="L18" s="23" t="inlineStr">
+      <c r="L19" s="22" t="inlineStr">
         <is>
           <t>第一級・瀕臨絕種</t>
         </is>
       </c>
-      <c r="M18" s="23" t="inlineStr">
+      <c r="M19" s="22" t="inlineStr">
         <is>
           <t>Plus 會員</t>
         </is>
       </c>
-      <c r="N18" s="30" t="n">
+      <c r="N19" s="31" t="n">
         <v>5</v>
       </c>
-      <c r="O18" s="23" t="inlineStr">
+      <c r="O19" s="22" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="P18" s="23" t="inlineStr">
+      <c r="P19" s="22" t="inlineStr">
         <is>
           <t>clouded_leopard-2.png</t>
         </is>
       </c>
-      <c r="Q18" s="28" t="inlineStr">
+      <c r="Q19" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="R18" s="29" t="inlineStr">
+      <c r="R19" s="30" t="inlineStr">
         <is>
           <t>名錄列第一級；野外可能已滅絕（傳說）</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="27" t="n">
+    <row r="20">
+      <c r="A20" s="28" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="22" t="inlineStr">
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>eurasian_otter</t>
         </is>
       </c>
-      <c r="C19" s="22" t="inlineStr">
+      <c r="C20" s="23" t="inlineStr">
         <is>
           <t>歐亞水獺（金門）</t>
         </is>
       </c>
-      <c r="D19" s="22" t="inlineStr">
+      <c r="D20" s="23" t="inlineStr">
         <is>
           <t>台灣</t>
         </is>
       </c>
-      <c r="E19" s="22" t="inlineStr">
+      <c r="E20" s="23" t="inlineStr">
         <is>
           <t>水獺</t>
         </is>
       </c>
-      <c r="F19" s="27" t="n">
+      <c r="F20" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="G19" s="22" t="inlineStr">
+      <c r="G20" s="23" t="inlineStr">
         <is>
           <t>只有一種樣式</t>
         </is>
       </c>
-      <c r="H19" s="22" t="inlineStr">
+      <c r="H20" s="23" t="inlineStr">
         <is>
           <t>深褐色流線身體、扁頭、粗長的尾巴、蹼足、濕亮的毛（金門）</t>
         </is>
       </c>
-      <c r="I19" s="22" t="inlineStr">
+      <c r="I20" s="23" t="inlineStr">
         <is>
           <t>溪流</t>
         </is>
       </c>
-      <c r="J19" s="22" t="inlineStr">
+      <c r="J20" s="23" t="inlineStr">
         <is>
           <t>夜晚</t>
         </is>
       </c>
-      <c r="K19" s="22" t="inlineStr">
+      <c r="K20" s="23" t="inlineStr">
         <is>
           <t>從遠處走過來（溪邊、湖邊）</t>
         </is>
       </c>
-      <c r="L19" s="22" t="inlineStr">
+      <c r="L20" s="23" t="inlineStr">
         <is>
           <t>第一級・瀕臨絕種</t>
         </is>
       </c>
-      <c r="M19" s="22" t="inlineStr">
+      <c r="M20" s="23" t="inlineStr">
         <is>
           <t>待定（新物種）</t>
         </is>
       </c>
-      <c r="N19" s="27" t="n">
+      <c r="N20" s="28" t="n">
         <v>6</v>
       </c>
-      <c r="O19" s="22" t="inlineStr">
+      <c r="O20" s="23" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="P19" s="22" t="inlineStr">
+      <c r="P20" s="23" t="inlineStr">
         <is>
           <t>eurasian_otter-2.png</t>
         </is>
       </c>
-      <c r="Q19" s="28" t="inlineStr">
+      <c r="Q20" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="R19" s="29" t="inlineStr">
+      <c r="R20" s="30" t="inlineStr">
         <is>
           <t>新增</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="30" t="n">
+    <row r="21">
+      <c r="A21" s="31" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="23" t="inlineStr">
+      <c r="B21" s="22" t="inlineStr">
         <is>
           <t>formosan_salmon</t>
         </is>
       </c>
-      <c r="C20" s="23" t="inlineStr">
+      <c r="C21" s="22" t="inlineStr">
         <is>
           <t>櫻花鉤吻鮭</t>
         </is>
       </c>
-      <c r="D20" s="23" t="inlineStr">
+      <c r="D21" s="22" t="inlineStr">
         <is>
           <t>台灣</t>
         </is>
       </c>
-      <c r="E20" s="23" t="inlineStr">
+      <c r="E21" s="22" t="inlineStr">
         <is>
           <t>魚</t>
         </is>
       </c>
-      <c r="F20" s="30" t="n">
+      <c r="F21" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="G20" s="23" t="inlineStr">
+      <c r="G21" s="22" t="inlineStr">
         <is>
           <t>只有一種樣式</t>
         </is>
       </c>
-      <c r="H20" s="23" t="inlineStr">
+      <c r="H21" s="22" t="inlineStr">
         <is>
           <t>銀綠色身體、體側橢圓形雲斑，繁殖期帶粉紅色（七家灣溪）</t>
         </is>
       </c>
-      <c r="I20" s="23" t="inlineStr">
+      <c r="I21" s="22" t="inlineStr">
         <is>
           <t>溪流水下</t>
         </is>
       </c>
-      <c r="J20" s="23" t="inlineStr">
+      <c r="J21" s="22" t="inlineStr">
         <is>
           <t>白天</t>
         </is>
       </c>
-      <c r="K20" s="23" t="inlineStr">
+      <c r="K21" s="22" t="inlineStr">
         <is>
           <t>水裡由遠游近（新出現方式，程式待做）</t>
         </is>
       </c>
-      <c r="L20" s="23" t="inlineStr">
+      <c r="L21" s="22" t="inlineStr">
         <is>
           <t>第一級・瀕臨絕種</t>
         </is>
       </c>
-      <c r="M20" s="23" t="inlineStr">
+      <c r="M21" s="22" t="inlineStr">
         <is>
           <t>待定（新物種）</t>
         </is>
       </c>
-      <c r="N20" s="30" t="n">
+      <c r="N21" s="31" t="n">
         <v>6</v>
       </c>
-      <c r="O20" s="23" t="inlineStr">
+      <c r="O21" s="22" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="P20" s="23" t="inlineStr">
+      <c r="P21" s="22" t="inlineStr">
         <is>
           <t>formosan_salmon-2.png</t>
         </is>
       </c>
-      <c r="Q20" s="28" t="inlineStr">
+      <c r="Q21" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="R20" s="29" t="inlineStr">
+      <c r="R21" s="30" t="inlineStr">
         <is>
           <t>新增（台灣特有亞種）</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="27" t="n">
+    <row r="22">
+      <c r="A22" s="28" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="22" t="inlineStr">
+      <c r="B22" s="23" t="inlineStr">
         <is>
           <t>green_turtle</t>
         </is>
       </c>
-      <c r="C21" s="22" t="inlineStr">
+      <c r="C22" s="23" t="inlineStr">
         <is>
           <t>綠蠵龜</t>
         </is>
       </c>
-      <c r="D21" s="22" t="inlineStr">
+      <c r="D22" s="23" t="inlineStr">
         <is>
           <t>台灣</t>
         </is>
       </c>
-      <c r="E21" s="22" t="inlineStr">
+      <c r="E22" s="23" t="inlineStr">
         <is>
           <t>海龜</t>
         </is>
       </c>
-      <c r="F21" s="27" t="n">
+      <c r="F22" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="G21" s="22" t="inlineStr">
+      <c r="G22" s="23" t="inlineStr">
         <is>
           <t>只有一種樣式</t>
         </is>
       </c>
-      <c r="H21" s="22" t="inlineStr">
+      <c r="H22" s="23" t="inlineStr">
         <is>
           <t>橢圓形背甲（橄欖綠帶褐色放射紋）、鰭狀前肢、小頭</t>
         </is>
       </c>
-      <c r="I21" s="22" t="inlineStr">
+      <c r="I22" s="23" t="inlineStr">
         <is>
           <t>海洋</t>
         </is>
       </c>
-      <c r="J21" s="22" t="inlineStr">
+      <c r="J22" s="23" t="inlineStr">
         <is>
           <t>白天</t>
         </is>
       </c>
-      <c r="K21" s="22" t="inlineStr">
+      <c r="K22" s="23" t="inlineStr">
         <is>
           <t>浮出海面換氣，越游越近（新，程式待做）</t>
         </is>
       </c>
-      <c r="L21" s="22" t="inlineStr">
+      <c r="L22" s="23" t="inlineStr">
         <is>
           <t>第一級・瀕臨絕種</t>
         </is>
       </c>
-      <c r="M21" s="22" t="inlineStr">
+      <c r="M22" s="23" t="inlineStr">
         <is>
           <t>待定（新物種）</t>
         </is>
       </c>
-      <c r="N21" s="27" t="n">
+      <c r="N22" s="28" t="n">
         <v>6</v>
       </c>
-      <c r="O21" s="22" t="inlineStr">
+      <c r="O22" s="23" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="P21" s="22" t="inlineStr">
+      <c r="P22" s="23" t="inlineStr">
         <is>
           <t>green_turtle-2.png</t>
         </is>
       </c>
-      <c r="Q21" s="28" t="inlineStr">
+      <c r="Q22" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="R21" s="29" t="inlineStr">
+      <c r="R22" s="30" t="inlineStr">
         <is>
           <t>新增（海洋保育類）</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="30" t="n">
+    <row r="23">
+      <c r="A23" s="31" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="23" t="inlineStr">
+      <c r="B23" s="22" t="inlineStr">
         <is>
           <t>white_dolphin</t>
         </is>
       </c>
-      <c r="C22" s="23" t="inlineStr">
+      <c r="C23" s="22" t="inlineStr">
         <is>
           <t>中華白海豚</t>
         </is>
       </c>
-      <c r="D22" s="23" t="inlineStr">
+      <c r="D23" s="22" t="inlineStr">
         <is>
           <t>台灣</t>
         </is>
       </c>
-      <c r="E22" s="23" t="inlineStr">
+      <c r="E23" s="22" t="inlineStr">
         <is>
           <t>海豚</t>
         </is>
       </c>
-      <c r="F22" s="30" t="n">
+      <c r="F23" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="G22" s="23" t="inlineStr">
+      <c r="G23" s="22" t="inlineStr">
         <is>
           <t>只有一種樣式</t>
         </is>
       </c>
-      <c r="H22" s="23" t="inlineStr">
+      <c r="H23" s="22" t="inlineStr">
         <is>
           <t>粉紅帶灰白斑點的身體、細長的嘴、三角形背鰭（台灣西部沿岸）</t>
         </is>
       </c>
-      <c r="I22" s="23" t="inlineStr">
+      <c r="I23" s="22" t="inlineStr">
         <is>
           <t>海洋</t>
         </is>
       </c>
-      <c r="J22" s="23" t="inlineStr">
+      <c r="J23" s="22" t="inlineStr">
         <is>
           <t>白天</t>
         </is>
       </c>
-      <c r="K22" s="23" t="inlineStr">
+      <c r="K23" s="22" t="inlineStr">
         <is>
           <t>遠方躍出海面，越來越近（新，程式待做）</t>
         </is>
       </c>
-      <c r="L22" s="23" t="inlineStr">
+      <c r="L23" s="22" t="inlineStr">
         <is>
           <t>第一級・瀕臨絕種</t>
         </is>
       </c>
-      <c r="M22" s="23" t="inlineStr">
+      <c r="M23" s="22" t="inlineStr">
         <is>
           <t>待定（新物種）</t>
         </is>
       </c>
-      <c r="N22" s="30" t="n">
+      <c r="N23" s="31" t="n">
         <v>6</v>
       </c>
-      <c r="O22" s="23" t="inlineStr">
+      <c r="O23" s="22" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="P22" s="23" t="inlineStr">
+      <c r="P23" s="22" t="inlineStr">
         <is>
           <t>white_dolphin-2.png</t>
         </is>
       </c>
-      <c r="Q22" s="28" t="inlineStr">
+      <c r="Q23" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="R22" s="29" t="inlineStr">
+      <c r="R23" s="30" t="inlineStr">
         <is>
           <t>新增（海洋保育類，台灣亞種）</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="27" t="n">
+    <row r="24">
+      <c r="A24" s="28" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="22" t="inlineStr">
+      <c r="B24" s="23" t="inlineStr">
         <is>
           <t>broad_tailed_swallowtail</t>
         </is>
       </c>
-      <c r="C23" s="22" t="inlineStr">
+      <c r="C24" s="23" t="inlineStr">
         <is>
           <t>寬尾鳳蝶</t>
         </is>
       </c>
-      <c r="D23" s="22" t="inlineStr">
+      <c r="D24" s="23" t="inlineStr">
         <is>
           <t>台灣</t>
         </is>
       </c>
-      <c r="E23" s="22" t="inlineStr">
+      <c r="E24" s="23" t="inlineStr">
         <is>
           <t>蝴蝶</t>
         </is>
       </c>
-      <c r="F23" s="27" t="n">
+      <c r="F24" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="G23" s="22" t="inlineStr">
+      <c r="G24" s="23" t="inlineStr">
         <is>
           <t>只有一種樣式</t>
         </is>
       </c>
-      <c r="H23" s="22" t="inlineStr">
+      <c r="H24" s="23" t="inlineStr">
         <is>
           <t>黑色翅膀、後翅有寬大的尾突與紅色斑紋（台灣特有種）</t>
         </is>
       </c>
-      <c r="I23" s="22" t="inlineStr">
+      <c r="I24" s="23" t="inlineStr">
         <is>
           <t>山地森林</t>
         </is>
       </c>
-      <c r="J23" s="22" t="inlineStr">
+      <c r="J24" s="23" t="inlineStr">
         <is>
           <t>白天</t>
         </is>
       </c>
-      <c r="K23" s="22" t="inlineStr">
+      <c r="K24" s="23" t="inlineStr">
         <is>
           <t>飛舞，最後停到花上（新，程式待做）</t>
         </is>
       </c>
-      <c r="L23" s="22" t="inlineStr">
+      <c r="L24" s="23" t="inlineStr">
         <is>
           <t>第一級・瀕臨絕種</t>
         </is>
       </c>
-      <c r="M23" s="22" t="inlineStr">
+      <c r="M24" s="23" t="inlineStr">
         <is>
           <t>待定（新物種）</t>
         </is>
       </c>
-      <c r="N23" s="27" t="n">
+      <c r="N24" s="28" t="n">
         <v>6</v>
       </c>
-      <c r="O23" s="22" t="inlineStr">
+      <c r="O24" s="23" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="P23" s="22" t="inlineStr">
+      <c r="P24" s="23" t="inlineStr">
         <is>
           <t>broad_tailed_swallowtail-2.png</t>
         </is>
       </c>
-      <c r="Q23" s="28" t="inlineStr">
+      <c r="Q24" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="R23" s="29" t="inlineStr">
+      <c r="R24" s="30" t="inlineStr">
         <is>
           <t>新增（台灣特有種）</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="30" t="n">
+    <row r="25">
+      <c r="A25" s="31" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="23" t="inlineStr">
+      <c r="B25" s="22" t="inlineStr">
         <is>
           <t>farmland_tree_frog</t>
         </is>
       </c>
-      <c r="C24" s="23" t="inlineStr">
+      <c r="C25" s="22" t="inlineStr">
         <is>
           <t>諸羅樹蛙</t>
         </is>
       </c>
-      <c r="D24" s="23" t="inlineStr">
+      <c r="D25" s="22" t="inlineStr">
         <is>
           <t>台灣</t>
         </is>
       </c>
-      <c r="E24" s="23" t="inlineStr">
+      <c r="E25" s="22" t="inlineStr">
         <is>
           <t>蛙</t>
         </is>
       </c>
-      <c r="F24" s="30" t="n">
+      <c r="F25" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="G24" s="23" t="inlineStr">
+      <c r="G25" s="22" t="inlineStr">
         <is>
           <t>只有一種樣式</t>
         </is>
       </c>
-      <c r="H24" s="23" t="inlineStr">
+      <c r="H25" s="22" t="inlineStr">
         <is>
           <t>翠綠色背部、白色腹部、體側白線、指端吸盤（台灣特有種，雲嘉南平地）</t>
         </is>
       </c>
-      <c r="I24" s="23" t="inlineStr">
+      <c r="I25" s="22" t="inlineStr">
         <is>
           <t>中低海拔森林</t>
         </is>
       </c>
-      <c r="J24" s="23" t="inlineStr">
+      <c r="J25" s="22" t="inlineStr">
         <is>
           <t>夜晚</t>
         </is>
       </c>
-      <c r="K24" s="23" t="inlineStr">
+      <c r="K25" s="22" t="inlineStr">
         <is>
           <t>夜裡先聽到叫聲、看到眼睛（同貓頭鷹）</t>
         </is>
       </c>
-      <c r="L24" s="23" t="inlineStr">
+      <c r="L25" s="22" t="inlineStr">
         <is>
           <t>第二級・珍貴稀有</t>
         </is>
       </c>
-      <c r="M24" s="23" t="inlineStr">
+      <c r="M25" s="22" t="inlineStr">
         <is>
           <t>待定（新物種）</t>
         </is>
       </c>
-      <c r="N24" s="30" t="n">
+      <c r="N25" s="31" t="n">
         <v>6</v>
       </c>
-      <c r="O24" s="23" t="inlineStr">
+      <c r="O25" s="22" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="P24" s="23" t="inlineStr">
+      <c r="P25" s="22" t="inlineStr">
         <is>
           <t>farmland_tree_frog-2.png</t>
         </is>
       </c>
-      <c r="Q24" s="28" t="inlineStr">
+      <c r="Q25" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="R24" s="29" t="inlineStr">
+      <c r="R25" s="30" t="inlineStr">
         <is>
           <t>新增（台灣特有種）</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="27" t="n">
+    <row r="26">
+      <c r="A26" s="28" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="22" t="inlineStr">
+      <c r="B26" s="23" t="inlineStr">
         <is>
           <t>formosan_flying_fox</t>
         </is>
       </c>
-      <c r="C25" s="22" t="inlineStr">
+      <c r="C26" s="23" t="inlineStr">
         <is>
           <t>台灣狐蝠</t>
         </is>
       </c>
-      <c r="D25" s="22" t="inlineStr">
+      <c r="D26" s="23" t="inlineStr">
         <is>
           <t>台灣</t>
         </is>
       </c>
-      <c r="E25" s="22" t="inlineStr">
+      <c r="E26" s="23" t="inlineStr">
         <is>
           <t>蝙蝠</t>
         </is>
       </c>
-      <c r="F25" s="27" t="n">
+      <c r="F26" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="G25" s="22" t="inlineStr">
+      <c r="G26" s="23" t="inlineStr">
         <is>
           <t>只有一種樣式</t>
         </is>
       </c>
-      <c r="H25" s="22" t="inlineStr">
+      <c r="H26" s="23" t="inlineStr">
         <is>
           <t>大型蝙蝠、狐狸臉、金褐色頸毛、黑色膜翼（綠島、龜山島）</t>
         </is>
       </c>
-      <c r="I25" s="22" t="inlineStr">
+      <c r="I26" s="23" t="inlineStr">
         <is>
           <t>南方島嶼</t>
         </is>
       </c>
-      <c r="J25" s="22" t="inlineStr">
+      <c r="J26" s="23" t="inlineStr">
         <is>
           <t>夜晚</t>
         </is>
       </c>
-      <c r="K25" s="22" t="inlineStr">
+      <c r="K26" s="23" t="inlineStr">
         <is>
           <t>夜空中飛，最後倒掛在樹枝上（同猛禽盤旋）</t>
         </is>
       </c>
-      <c r="L25" s="22" t="inlineStr">
+      <c r="L26" s="23" t="inlineStr">
         <is>
           <t>第一級・瀕臨絕種</t>
         </is>
       </c>
-      <c r="M25" s="22" t="inlineStr">
+      <c r="M26" s="23" t="inlineStr">
         <is>
           <t>待定（新物種）</t>
         </is>
       </c>
-      <c r="N25" s="27" t="n">
+      <c r="N26" s="28" t="n">
         <v>6</v>
       </c>
-      <c r="O25" s="22" t="inlineStr">
+      <c r="O26" s="23" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="P25" s="22" t="inlineStr">
+      <c r="P26" s="23" t="inlineStr">
         <is>
           <t>formosan_flying_fox-2.png</t>
         </is>
       </c>
-      <c r="Q25" s="28" t="inlineStr">
+      <c r="Q26" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="R25" s="29" t="inlineStr">
+      <c r="R26" s="30" t="inlineStr">
         <is>
           <t>新增</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="30" t="n">
-        <v>22</v>
-      </c>
-      <c r="B26" s="23" t="inlineStr">
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="27" t="inlineStr">
+        <is>
+          <t>日本（8 種）</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="B28" s="23" t="inlineStr">
         <is>
           <t>iriomote_cat</t>
         </is>
       </c>
-      <c r="C26" s="23" t="inlineStr">
+      <c r="C28" s="23" t="inlineStr">
         <is>
           <t>西表山貓</t>
         </is>
       </c>
-      <c r="D26" s="23" t="inlineStr">
+      <c r="D28" s="23" t="inlineStr">
         <is>
           <t>日本</t>
         </is>
       </c>
-      <c r="E26" s="23" t="inlineStr">
+      <c r="E28" s="23" t="inlineStr">
         <is>
           <t>貓科</t>
         </is>
       </c>
-      <c r="F26" s="30" t="n">
+      <c r="F28" s="28" t="n">
         <v>3</v>
       </c>
-      <c r="G26" s="23" t="inlineStr">
+      <c r="G28" s="23" t="inlineStr">
         <is>
           <t>幼年／亞成年／成年</t>
         </is>
       </c>
-      <c r="H26" s="23" t="inlineStr">
+      <c r="H28" s="23" t="inlineStr">
         <is>
           <t>深褐色帶斑點、耳背白斑、尾巴較粗短</t>
         </is>
       </c>
-      <c r="I26" s="23" t="inlineStr">
+      <c r="I28" s="23" t="inlineStr">
         <is>
           <t>南方島嶼</t>
         </is>
       </c>
-      <c r="J26" s="23" t="inlineStr">
+      <c r="J28" s="23" t="inlineStr">
         <is>
           <t>夜晚</t>
         </is>
       </c>
-      <c r="K26" s="23" t="inlineStr">
+      <c r="K28" s="23" t="inlineStr">
         <is>
           <t>從遠處走過來</t>
         </is>
       </c>
-      <c r="L26" s="23" t="inlineStr">
+      <c r="L28" s="23" t="inlineStr">
         <is>
           <t>特別天然紀念物</t>
         </is>
       </c>
-      <c r="M26" s="23" t="inlineStr">
+      <c r="M28" s="23" t="inlineStr">
         <is>
           <t>一開始就能找</t>
         </is>
       </c>
-      <c r="N26" s="30" t="n">
+      <c r="N28" s="28" t="n">
         <v>3</v>
       </c>
-      <c r="O26" s="23" t="inlineStr">
+      <c r="O28" s="23" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="P26" s="23" t="inlineStr">
+      <c r="P28" s="23" t="inlineStr">
         <is>
           <t>iriomote_cat-0/1/2.png</t>
         </is>
       </c>
-      <c r="Q26" s="28" t="inlineStr">
+      <c r="Q28" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="R26" s="29" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="27" t="n">
-        <v>23</v>
-      </c>
-      <c r="B27" s="22" t="inlineStr">
+      <c r="R28" s="30" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="B29" s="22" t="inlineStr">
         <is>
           <t>okinawa_woodpecker</t>
         </is>
       </c>
-      <c r="C27" s="22" t="inlineStr">
+      <c r="C29" s="22" t="inlineStr">
         <is>
           <t>野口啄木鳥</t>
         </is>
       </c>
-      <c r="D27" s="22" t="inlineStr">
+      <c r="D29" s="22" t="inlineStr">
         <is>
           <t>日本</t>
         </is>
       </c>
-      <c r="E27" s="22" t="inlineStr">
+      <c r="E29" s="22" t="inlineStr">
         <is>
           <t>鳥</t>
         </is>
       </c>
-      <c r="F27" s="27" t="n">
+      <c r="F29" s="31" t="n">
         <v>3</v>
       </c>
-      <c r="G27" s="22" t="inlineStr">
+      <c r="G29" s="22" t="inlineStr">
         <is>
           <t>雛鳥／幼鳥／成鳥</t>
         </is>
       </c>
-      <c r="H27" s="22" t="inlineStr">
+      <c r="H29" s="22" t="inlineStr">
         <is>
           <t>全身深紅褐色、頭頂紅色（雄鳥）、啄木鳥姿態</t>
         </is>
       </c>
-      <c r="I27" s="22" t="inlineStr">
+      <c r="I29" s="22" t="inlineStr">
         <is>
           <t>南方島嶼</t>
         </is>
       </c>
-      <c r="J27" s="22" t="inlineStr">
+      <c r="J29" s="22" t="inlineStr">
         <is>
           <t>白天</t>
         </is>
       </c>
-      <c r="K27" s="22" t="inlineStr">
+      <c r="K29" s="22" t="inlineStr">
         <is>
           <t>遠處飛 → 停到倒木上</t>
         </is>
       </c>
-      <c r="L27" s="22" t="inlineStr">
+      <c r="L29" s="22" t="inlineStr">
         <is>
           <t>特別天然紀念物</t>
         </is>
       </c>
-      <c r="M27" s="22" t="inlineStr">
+      <c r="M29" s="22" t="inlineStr">
         <is>
           <t>一開始就能找</t>
         </is>
       </c>
-      <c r="N27" s="27" t="n">
+      <c r="N29" s="31" t="n">
         <v>3</v>
       </c>
-      <c r="O27" s="22" t="inlineStr">
+      <c r="O29" s="22" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="P27" s="22" t="inlineStr">
+      <c r="P29" s="22" t="inlineStr">
         <is>
           <t>okinawa_woodpecker-0/1/2.png</t>
         </is>
       </c>
-      <c r="Q27" s="28" t="inlineStr">
+      <c r="Q29" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="R27" s="29" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="30" t="n">
-        <v>24</v>
-      </c>
-      <c r="B28" s="23" t="inlineStr">
+      <c r="R29" s="30" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="B30" s="23" t="inlineStr">
         <is>
           <t>japanese_serow</t>
         </is>
       </c>
-      <c r="C28" s="23" t="inlineStr">
+      <c r="C30" s="23" t="inlineStr">
         <is>
           <t>日本鬣羚</t>
         </is>
       </c>
-      <c r="D28" s="23" t="inlineStr">
+      <c r="D30" s="23" t="inlineStr">
         <is>
           <t>日本</t>
         </is>
       </c>
-      <c r="E28" s="23" t="inlineStr">
+      <c r="E30" s="23" t="inlineStr">
         <is>
           <t>山羊</t>
         </is>
       </c>
-      <c r="F28" s="30" t="n">
+      <c r="F30" s="28" t="n">
         <v>3</v>
       </c>
-      <c r="G28" s="23" t="inlineStr">
+      <c r="G30" s="23" t="inlineStr">
         <is>
           <t>幼年／亞成年／成年</t>
         </is>
       </c>
-      <c r="H28" s="23" t="inlineStr">
+      <c r="H30" s="23" t="inlineStr">
         <is>
           <t>灰黑色、頸部有鬃毛、短角、常站在岩石上</t>
         </is>
       </c>
-      <c r="I28" s="23" t="inlineStr">
+      <c r="I30" s="23" t="inlineStr">
         <is>
           <t>山地森林</t>
         </is>
       </c>
-      <c r="J28" s="23" t="inlineStr">
+      <c r="J30" s="23" t="inlineStr">
         <is>
           <t>晨昏</t>
         </is>
       </c>
-      <c r="K28" s="23" t="inlineStr">
+      <c r="K30" s="23" t="inlineStr">
         <is>
           <t>從遠處走過來</t>
         </is>
       </c>
-      <c r="L28" s="23" t="inlineStr">
+      <c r="L30" s="23" t="inlineStr">
         <is>
           <t>特別天然紀念物</t>
         </is>
       </c>
-      <c r="M28" s="23" t="inlineStr">
+      <c r="M30" s="23" t="inlineStr">
         <is>
           <t>修好「清出杉林小徑」</t>
         </is>
       </c>
-      <c r="N28" s="30" t="n">
+      <c r="N30" s="28" t="n">
         <v>3</v>
       </c>
-      <c r="O28" s="23" t="inlineStr">
+      <c r="O30" s="23" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="P28" s="23" t="inlineStr">
+      <c r="P30" s="23" t="inlineStr">
         <is>
           <t>japanese_serow-0/1/2.png</t>
         </is>
       </c>
-      <c r="Q28" s="28" t="inlineStr">
+      <c r="Q30" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="R28" s="29" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="27" t="n">
-        <v>25</v>
-      </c>
-      <c r="B29" s="22" t="inlineStr">
+      <c r="R30" s="30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="B31" s="22" t="inlineStr">
         <is>
           <t>ptarmigan</t>
         </is>
       </c>
-      <c r="C29" s="22" t="inlineStr">
+      <c r="C31" s="22" t="inlineStr">
         <is>
           <t>雷鳥</t>
         </is>
       </c>
-      <c r="D29" s="22" t="inlineStr">
+      <c r="D31" s="22" t="inlineStr">
         <is>
           <t>日本</t>
         </is>
       </c>
-      <c r="E29" s="22" t="inlineStr">
+      <c r="E31" s="22" t="inlineStr">
         <is>
           <t>雉雞</t>
         </is>
       </c>
-      <c r="F29" s="27" t="n">
+      <c r="F31" s="31" t="n">
         <v>3</v>
       </c>
-      <c r="G29" s="22" t="inlineStr">
+      <c r="G31" s="22" t="inlineStr">
         <is>
           <t>雛鳥／幼鳥／成鳥</t>
         </is>
       </c>
-      <c r="H29" s="22" t="inlineStr">
+      <c r="H31" s="22" t="inlineStr">
         <is>
           <t>夏羽褐色斑駁、眼上紅色肉冠、腳有羽毛（冬羽全白可之後再做）</t>
         </is>
       </c>
-      <c r="I29" s="22" t="inlineStr">
+      <c r="I31" s="22" t="inlineStr">
         <is>
           <t>高山</t>
         </is>
       </c>
-      <c r="J29" s="22" t="inlineStr">
+      <c r="J31" s="22" t="inlineStr">
         <is>
           <t>白天</t>
         </is>
       </c>
-      <c r="K29" s="22" t="inlineStr">
+      <c r="K31" s="22" t="inlineStr">
         <is>
           <t>從遠處走過來</t>
         </is>
       </c>
-      <c r="L29" s="22" t="inlineStr">
+      <c r="L31" s="22" t="inlineStr">
         <is>
           <t>特別天然紀念物</t>
         </is>
       </c>
-      <c r="M29" s="22" t="inlineStr">
+      <c r="M31" s="22" t="inlineStr">
         <is>
           <t>修好「復原里山梯田」</t>
         </is>
       </c>
-      <c r="N29" s="27" t="n">
+      <c r="N31" s="31" t="n">
         <v>3</v>
       </c>
-      <c r="O29" s="22" t="inlineStr">
+      <c r="O31" s="22" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="P29" s="22" t="inlineStr">
+      <c r="P31" s="22" t="inlineStr">
         <is>
           <t>ptarmigan-0/1/2.png</t>
         </is>
       </c>
-      <c r="Q29" s="28" t="inlineStr">
+      <c r="Q31" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="R29" s="29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="30" t="n">
-        <v>26</v>
-      </c>
-      <c r="B30" s="23" t="inlineStr">
+      <c r="R31" s="30" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="28" t="n">
+        <v>5</v>
+      </c>
+      <c r="B32" s="23" t="inlineStr">
         <is>
           <t>blakiston_owl</t>
         </is>
       </c>
-      <c r="C30" s="23" t="inlineStr">
+      <c r="C32" s="23" t="inlineStr">
         <is>
           <t>毛腿魚鴞</t>
         </is>
       </c>
-      <c r="D30" s="23" t="inlineStr">
+      <c r="D32" s="23" t="inlineStr">
         <is>
           <t>日本</t>
         </is>
       </c>
-      <c r="E30" s="23" t="inlineStr">
+      <c r="E32" s="23" t="inlineStr">
         <is>
           <t>貓頭鷹</t>
         </is>
       </c>
-      <c r="F30" s="30" t="n">
+      <c r="F32" s="28" t="n">
         <v>3</v>
       </c>
-      <c r="G30" s="23" t="inlineStr">
+      <c r="G32" s="23" t="inlineStr">
         <is>
           <t>雛鳥／幼鳥／成鳥</t>
         </is>
       </c>
-      <c r="H30" s="23" t="inlineStr">
+      <c r="H32" s="23" t="inlineStr">
         <is>
           <t>世界最大的貓頭鷹之一、褐色斑紋、寬大耳羽、黃眼</t>
         </is>
       </c>
-      <c r="I30" s="23" t="inlineStr">
+      <c r="I32" s="23" t="inlineStr">
         <is>
           <t>溪流</t>
         </is>
       </c>
-      <c r="J30" s="23" t="inlineStr">
+      <c r="J32" s="23" t="inlineStr">
         <is>
           <t>夜晚</t>
         </is>
       </c>
-      <c r="K30" s="23" t="inlineStr">
+      <c r="K32" s="23" t="inlineStr">
         <is>
           <t>夜裡先亮眼睛 → 停到倒木上</t>
         </is>
       </c>
-      <c r="L30" s="23" t="inlineStr">
+      <c r="L32" s="23" t="inlineStr">
         <is>
           <t>國內稀少野生物種</t>
         </is>
       </c>
-      <c r="M30" s="23" t="inlineStr">
+      <c r="M32" s="23" t="inlineStr">
         <is>
           <t>修好「修好山中小屋」</t>
         </is>
       </c>
-      <c r="N30" s="30" t="n">
+      <c r="N32" s="28" t="n">
         <v>3</v>
       </c>
-      <c r="O30" s="23" t="inlineStr">
+      <c r="O32" s="23" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="P30" s="23" t="inlineStr">
+      <c r="P32" s="23" t="inlineStr">
         <is>
           <t>blakiston_owl-0/1/2.png</t>
         </is>
       </c>
-      <c r="Q30" s="28" t="inlineStr">
+      <c r="Q32" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="R30" s="29" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="27" t="n">
-        <v>27</v>
-      </c>
-      <c r="B31" s="22" t="inlineStr">
+      <c r="R32" s="30" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="31" t="n">
+        <v>6</v>
+      </c>
+      <c r="B33" s="22" t="inlineStr">
         <is>
           <t>tsushima_cat</t>
         </is>
       </c>
-      <c r="C31" s="22" t="inlineStr">
+      <c r="C33" s="22" t="inlineStr">
         <is>
           <t>對馬山貓</t>
         </is>
       </c>
-      <c r="D31" s="22" t="inlineStr">
+      <c r="D33" s="22" t="inlineStr">
         <is>
           <t>日本</t>
         </is>
       </c>
-      <c r="E31" s="22" t="inlineStr">
+      <c r="E33" s="22" t="inlineStr">
         <is>
           <t>貓科</t>
         </is>
       </c>
-      <c r="F31" s="27" t="n">
+      <c r="F33" s="31" t="n">
         <v>3</v>
       </c>
-      <c r="G31" s="22" t="inlineStr">
+      <c r="G33" s="22" t="inlineStr">
         <is>
           <t>幼年／亞成年／成年</t>
         </is>
       </c>
-      <c r="H31" s="22" t="inlineStr">
+      <c r="H33" s="22" t="inlineStr">
         <is>
           <t>對馬的石虎：外型近似石虎、額頭白紋，毛色略深</t>
         </is>
       </c>
-      <c r="I31" s="22" t="inlineStr">
+      <c r="I33" s="22" t="inlineStr">
         <is>
           <t>里山</t>
         </is>
       </c>
-      <c r="J31" s="22" t="inlineStr">
+      <c r="J33" s="22" t="inlineStr">
         <is>
           <t>夜晚</t>
         </is>
       </c>
-      <c r="K31" s="22" t="inlineStr">
+      <c r="K33" s="22" t="inlineStr">
         <is>
           <t>從遠處走過來</t>
         </is>
       </c>
-      <c r="L31" s="22" t="inlineStr">
+      <c r="L33" s="22" t="inlineStr">
         <is>
           <t>國內稀少野生物種</t>
         </is>
       </c>
-      <c r="M31" s="22" t="inlineStr">
+      <c r="M33" s="22" t="inlineStr">
         <is>
           <t>修好「疏伐過密的竹林」</t>
         </is>
       </c>
-      <c r="N31" s="27" t="n">
+      <c r="N33" s="31" t="n">
         <v>3</v>
       </c>
-      <c r="O31" s="22" t="inlineStr">
+      <c r="O33" s="22" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="P31" s="22" t="inlineStr">
+      <c r="P33" s="22" t="inlineStr">
         <is>
           <t>tsushima_cat-0/1/2.png</t>
         </is>
       </c>
-      <c r="Q31" s="28" t="inlineStr">
+      <c r="Q33" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="R31" s="29" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="30" t="n">
-        <v>28</v>
-      </c>
-      <c r="B32" s="23" t="inlineStr">
+      <c r="R33" s="30" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="28" t="n">
+        <v>7</v>
+      </c>
+      <c r="B34" s="23" t="inlineStr">
         <is>
           <t>steller_eagle</t>
         </is>
       </c>
-      <c r="C32" s="23" t="inlineStr">
+      <c r="C34" s="23" t="inlineStr">
         <is>
           <t>虎頭海鵰</t>
         </is>
       </c>
-      <c r="D32" s="23" t="inlineStr">
+      <c r="D34" s="23" t="inlineStr">
         <is>
           <t>日本</t>
         </is>
       </c>
-      <c r="E32" s="23" t="inlineStr">
+      <c r="E34" s="23" t="inlineStr">
         <is>
           <t>猛禽</t>
         </is>
       </c>
-      <c r="F32" s="30" t="n">
+      <c r="F34" s="28" t="n">
         <v>3</v>
       </c>
-      <c r="G32" s="23" t="inlineStr">
+      <c r="G34" s="23" t="inlineStr">
         <is>
           <t>雛鳥／幼鳥／成鳥</t>
         </is>
       </c>
-      <c r="H32" s="23" t="inlineStr">
+      <c r="H34" s="23" t="inlineStr">
         <is>
           <t>巨大的橘黃色嘴、深褐色身體、白色肩羽與白尾</t>
         </is>
       </c>
-      <c r="I32" s="23" t="inlineStr">
+      <c r="I34" s="23" t="inlineStr">
         <is>
           <t>溪流</t>
         </is>
       </c>
-      <c r="J32" s="23" t="inlineStr">
+      <c r="J34" s="23" t="inlineStr">
         <is>
           <t>白天</t>
         </is>
       </c>
-      <c r="K32" s="23" t="inlineStr">
+      <c r="K34" s="23" t="inlineStr">
         <is>
           <t>天空盤旋 → 降落</t>
         </is>
       </c>
-      <c r="L32" s="23" t="inlineStr">
+      <c r="L34" s="23" t="inlineStr">
         <is>
           <t>國內稀少野生物種</t>
         </is>
       </c>
-      <c r="M32" s="23" t="inlineStr">
+      <c r="M34" s="23" t="inlineStr">
         <is>
           <t>修好「恢復清澈溪流」</t>
         </is>
       </c>
-      <c r="N32" s="30" t="n">
+      <c r="N34" s="28" t="n">
         <v>3</v>
       </c>
-      <c r="O32" s="23" t="inlineStr">
+      <c r="O34" s="23" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="P32" s="23" t="inlineStr">
+      <c r="P34" s="23" t="inlineStr">
         <is>
           <t>steller_eagle-0/1/2.png</t>
         </is>
       </c>
-      <c r="Q32" s="28" t="inlineStr">
+      <c r="Q34" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="R32" s="29" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="27" t="n">
-        <v>29</v>
-      </c>
-      <c r="B33" s="22" t="inlineStr">
+      <c r="R34" s="30" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="B35" s="22" t="inlineStr">
         <is>
           <t>moon_bear</t>
         </is>
       </c>
-      <c r="C33" s="22" t="inlineStr">
+      <c r="C35" s="22" t="inlineStr">
         <is>
           <t>月輪熊</t>
         </is>
       </c>
-      <c r="D33" s="22" t="inlineStr">
+      <c r="D35" s="22" t="inlineStr">
         <is>
           <t>日本</t>
         </is>
       </c>
-      <c r="E33" s="22" t="inlineStr">
+      <c r="E35" s="22" t="inlineStr">
         <is>
           <t>熊</t>
         </is>
       </c>
-      <c r="F33" s="27" t="n">
+      <c r="F35" s="31" t="n">
         <v>3</v>
       </c>
-      <c r="G33" s="22" t="inlineStr">
+      <c r="G35" s="22" t="inlineStr">
         <is>
           <t>幼年／亞成年／成年</t>
         </is>
       </c>
-      <c r="H33" s="22" t="inlineStr">
+      <c r="H35" s="22" t="inlineStr">
         <is>
           <t>黑色毛、胸前月牙形白斑、圓耳</t>
         </is>
       </c>
-      <c r="I33" s="22" t="inlineStr">
+      <c r="I35" s="22" t="inlineStr">
         <is>
           <t>山地森林</t>
         </is>
       </c>
-      <c r="J33" s="22" t="inlineStr">
+      <c r="J35" s="22" t="inlineStr">
         <is>
           <t>白天</t>
         </is>
       </c>
-      <c r="K33" s="22" t="inlineStr">
+      <c r="K35" s="22" t="inlineStr">
         <is>
           <t>從遠處走過來</t>
         </is>
       </c>
-      <c r="L33" s="22" t="inlineStr">
+      <c r="L35" s="22" t="inlineStr">
         <is>
           <t>地區族群瀕危</t>
         </is>
       </c>
-      <c r="M33" s="22" t="inlineStr">
+      <c r="M35" s="22" t="inlineStr">
         <is>
           <t>修好「設立野生動物保護站」</t>
         </is>
       </c>
-      <c r="N33" s="27" t="n">
+      <c r="N35" s="31" t="n">
         <v>3</v>
       </c>
-      <c r="O33" s="22" t="inlineStr">
+      <c r="O35" s="22" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="P33" s="22" t="inlineStr">
+      <c r="P35" s="22" t="inlineStr">
         <is>
           <t>moon_bear-0/1/2.png</t>
         </is>
       </c>
-      <c r="Q33" s="28" t="inlineStr">
+      <c r="Q35" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="R33" s="29" t="inlineStr"/>
+      <c r="R35" s="30" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:R33"/>
-  <mergeCells count="1">
+  <autoFilter ref="A4:R35"/>
+  <mergeCells count="3">
+    <mergeCell ref="A27:R27"/>
     <mergeCell ref="A2:R2"/>
+    <mergeCell ref="A5:R5"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="Q5:Q304" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="狀態" error="請從清單選一個狀態" type="list">
@@ -6925,7 +6950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:M35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -7024,1667 +7049,1683 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="27" t="n">
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="27" t="inlineStr">
+        <is>
+          <t>台灣（21 種）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="22" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>black_bear</t>
         </is>
       </c>
-      <c r="C5" s="22" t="inlineStr">
+      <c r="C6" s="23" t="inlineStr">
         <is>
           <t>台灣黑熊</t>
         </is>
       </c>
-      <c r="D5" s="22" t="inlineStr">
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t>熊</t>
         </is>
       </c>
-      <c r="E5" s="27" t="n">
+      <c r="E6" s="28" t="n">
         <v>3</v>
       </c>
-      <c r="F5" s="22" t="inlineStr">
+      <c r="F6" s="23" t="inlineStr">
         <is>
           <t>同貓科</t>
         </is>
       </c>
-      <c r="G5" s="22" t="inlineStr">
+      <c r="G6" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H5" s="22" t="inlineStr">
+      <c r="H6" s="23" t="inlineStr">
         <is>
           <t>待機、張望、低頭聞、坐下、走路</t>
         </is>
       </c>
-      <c r="I5" s="22" t="inlineStr">
+      <c r="I6" s="23" t="inlineStr">
         <is>
           <t>≤ 120 KB</t>
         </is>
       </c>
-      <c r="J5" s="27" t="n">
+      <c r="J6" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="K5" s="22" t="inlineStr">
+      <c r="K6" s="23" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="L5" s="28" t="inlineStr">
+      <c r="L6" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="M5" s="29" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="30" t="n">
+      <c r="M6" s="30" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>leopard_cat</t>
         </is>
       </c>
-      <c r="C6" s="23" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>石虎</t>
         </is>
       </c>
-      <c r="D6" s="23" t="inlineStr">
+      <c r="D7" s="22" t="inlineStr">
         <is>
           <t>貓科</t>
         </is>
       </c>
-      <c r="E6" s="30" t="n">
+      <c r="E7" s="31" t="n">
         <v>3</v>
       </c>
-      <c r="F6" s="23" t="inlineStr">
+      <c r="F7" s="22" t="inlineStr">
         <is>
           <t>E1 拿掉近側兩條腿；E3 拿掉頭；E4 拿掉兩隻耳朵；E5 閉眼；E7 頭轉向鏡頭</t>
         </is>
       </c>
-      <c r="G6" s="23" t="inlineStr">
+      <c r="G7" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H6" s="23" t="inlineStr">
+      <c r="H7" s="22" t="inlineStr">
         <is>
           <t>待機呼吸、張望、低頭聞、甩尾、耳朵抖、眨眼、張嘴、走路（定格每秒 8 格）</t>
         </is>
       </c>
-      <c r="I6" s="23" t="inlineStr">
+      <c r="I7" s="22" t="inlineStr">
         <is>
           <t>≤ 120 KB</t>
         </is>
       </c>
-      <c r="J6" s="30" t="n">
+      <c r="J7" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="K6" s="23" t="inlineStr">
+      <c r="K7" s="22" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="L6" s="31" t="inlineStr">
+      <c r="L7" s="32" t="inlineStr">
         <is>
           <t>製作中</t>
         </is>
       </c>
-      <c r="M6" s="29" t="inlineStr">
+      <c r="M7" s="30" t="inlineStr">
         <is>
           <t>成年完成；目前未壓縮 460 KB 要壓到 ≤120 KB；後腿之間一小撮淺色未解；幼年、亞成年未做</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="27" t="n">
+    <row r="8">
+      <c r="A8" s="28" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="22" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>pangolin</t>
         </is>
       </c>
-      <c r="C7" s="22" t="inlineStr">
+      <c r="C8" s="23" t="inlineStr">
         <is>
           <t>穿山甲</t>
         </is>
       </c>
-      <c r="D7" s="22" t="inlineStr">
+      <c r="D8" s="23" t="inlineStr">
         <is>
           <t>穿山甲</t>
         </is>
       </c>
-      <c r="E7" s="27" t="n">
+      <c r="E8" s="28" t="n">
         <v>3</v>
       </c>
-      <c r="F7" s="22" t="inlineStr">
+      <c r="F8" s="23" t="inlineStr">
         <is>
           <t>同貓科</t>
         </is>
       </c>
-      <c r="G7" s="22" t="inlineStr">
+      <c r="G8" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H7" s="22" t="inlineStr">
+      <c r="H8" s="23" t="inlineStr">
         <is>
           <t>待機、低頭聞、甩尾、走路（選配：捲成球）</t>
         </is>
       </c>
-      <c r="I7" s="22" t="inlineStr">
+      <c r="I8" s="23" t="inlineStr">
         <is>
           <t>≤ 120 KB</t>
         </is>
       </c>
-      <c r="J7" s="27" t="n">
+      <c r="J8" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="K7" s="22" t="inlineStr">
+      <c r="K8" s="23" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="L7" s="28" t="inlineStr">
+      <c r="L8" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="M7" s="29" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="30" t="n">
+      <c r="M8" s="30" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="31" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="23" t="inlineStr">
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>blue_magpie</t>
         </is>
       </c>
-      <c r="C8" s="23" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t>台灣藍鵲</t>
         </is>
       </c>
-      <c r="D8" s="23" t="inlineStr">
+      <c r="D9" s="22" t="inlineStr">
         <is>
           <t>鳥</t>
         </is>
       </c>
-      <c r="E8" s="30" t="n">
+      <c r="E9" s="31" t="n">
         <v>3</v>
       </c>
-      <c r="F8" s="23" t="inlineStr">
+      <c r="F9" s="22" t="inlineStr">
         <is>
           <t>拿掉近側翅膀；拿掉頭；閉眼；拿掉近側腳；頭轉向鏡頭</t>
         </is>
       </c>
-      <c r="G8" s="23" t="inlineStr">
+      <c r="G9" s="22" t="inlineStr">
         <is>
           <t>飛行姿勢 1 張</t>
         </is>
       </c>
-      <c r="H8" s="23" t="inlineStr">
+      <c r="H9" s="22" t="inlineStr">
         <is>
           <t>待機、跳兩步、低頭啄、理羽毛、歪頭、眨眼、拍翅；另需「飛行姿勢」1 張</t>
         </is>
       </c>
-      <c r="I8" s="23" t="inlineStr">
+      <c r="I9" s="22" t="inlineStr">
         <is>
           <t>≤ 120 KB</t>
         </is>
       </c>
-      <c r="J8" s="30" t="n">
+      <c r="J9" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="K8" s="23" t="inlineStr">
+      <c r="K9" s="22" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="L8" s="28" t="inlineStr">
+      <c r="L9" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="M8" s="29" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="27" t="n">
+      <c r="M9" s="30" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="28" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="22" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>pitta</t>
         </is>
       </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="C10" s="23" t="inlineStr">
         <is>
           <t>八色鳥</t>
         </is>
       </c>
-      <c r="D9" s="22" t="inlineStr">
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t>鳥</t>
         </is>
       </c>
-      <c r="E9" s="27" t="n">
+      <c r="E10" s="28" t="n">
         <v>3</v>
       </c>
-      <c r="F9" s="22" t="inlineStr">
+      <c r="F10" s="23" t="inlineStr">
         <is>
           <t>拿掉近側翅膀；拿掉頭；閉眼；拿掉近側腳；頭轉向鏡頭</t>
         </is>
       </c>
-      <c r="G9" s="22" t="inlineStr">
+      <c r="G10" s="23" t="inlineStr">
         <is>
           <t>飛行姿勢 1 張</t>
         </is>
       </c>
-      <c r="H9" s="22" t="inlineStr">
+      <c r="H10" s="23" t="inlineStr">
         <is>
           <t>待機、跳兩步、低頭啄、理羽毛、歪頭、眨眼、拍翅；另需「飛行姿勢」1 張</t>
         </is>
       </c>
-      <c r="I9" s="22" t="inlineStr">
+      <c r="I10" s="23" t="inlineStr">
         <is>
           <t>≤ 120 KB</t>
         </is>
       </c>
-      <c r="J9" s="27" t="n">
+      <c r="J10" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="K9" s="22" t="inlineStr">
+      <c r="K10" s="23" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="L9" s="28" t="inlineStr">
+      <c r="L10" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="M9" s="29" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="30" t="n">
+      <c r="M10" s="30" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="31" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="23" t="inlineStr">
+      <c r="B11" s="22" t="inlineStr">
         <is>
           <t>mikado_pheasant</t>
         </is>
       </c>
-      <c r="C10" s="23" t="inlineStr">
+      <c r="C11" s="22" t="inlineStr">
         <is>
           <t>帝雉</t>
         </is>
       </c>
-      <c r="D10" s="23" t="inlineStr">
+      <c r="D11" s="22" t="inlineStr">
         <is>
           <t>雉雞</t>
         </is>
       </c>
-      <c r="E10" s="30" t="n">
+      <c r="E11" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="F10" s="23" t="inlineStr">
+      <c r="F11" s="22" t="inlineStr">
         <is>
           <t>同鳥</t>
         </is>
       </c>
-      <c r="G10" s="23" t="inlineStr">
+      <c r="G11" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H10" s="23" t="inlineStr">
+      <c r="H11" s="22" t="inlineStr">
         <is>
           <t>待機、走路、低頭啄、抬頭張望、眨眼</t>
         </is>
       </c>
-      <c r="I10" s="23" t="inlineStr">
+      <c r="I11" s="22" t="inlineStr">
         <is>
           <t>≤ 120 KB</t>
         </is>
       </c>
-      <c r="J10" s="30" t="n">
+      <c r="J11" s="31" t="n">
         <v>4</v>
       </c>
-      <c r="K10" s="23" t="inlineStr">
+      <c r="K11" s="22" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="L10" s="28" t="inlineStr">
+      <c r="L11" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="M10" s="29" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="27" t="n">
+      <c r="M11" s="30" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="28" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="22" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>swinhoe_pheasant</t>
         </is>
       </c>
-      <c r="C11" s="22" t="inlineStr">
+      <c r="C12" s="23" t="inlineStr">
         <is>
           <t>藍腹鷴</t>
         </is>
       </c>
-      <c r="D11" s="22" t="inlineStr">
+      <c r="D12" s="23" t="inlineStr">
         <is>
           <t>雉雞</t>
         </is>
       </c>
-      <c r="E11" s="27" t="n">
+      <c r="E12" s="28" t="n">
         <v>3</v>
       </c>
-      <c r="F11" s="22" t="inlineStr">
+      <c r="F12" s="23" t="inlineStr">
         <is>
           <t>同鳥</t>
         </is>
       </c>
-      <c r="G11" s="22" t="inlineStr">
+      <c r="G12" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H11" s="22" t="inlineStr">
+      <c r="H12" s="23" t="inlineStr">
         <is>
           <t>待機、走路、低頭啄、抬頭張望、眨眼</t>
         </is>
       </c>
-      <c r="I11" s="22" t="inlineStr">
+      <c r="I12" s="23" t="inlineStr">
         <is>
           <t>≤ 120 KB</t>
         </is>
       </c>
-      <c r="J11" s="27" t="n">
+      <c r="J12" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="K11" s="22" t="inlineStr">
+      <c r="K12" s="23" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="L11" s="28" t="inlineStr">
+      <c r="L12" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="M11" s="29" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="30" t="n">
+      <c r="M12" s="30" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="31" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="23" t="inlineStr">
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>marten</t>
         </is>
       </c>
-      <c r="C12" s="23" t="inlineStr">
+      <c r="C13" s="22" t="inlineStr">
         <is>
           <t>黃喉貂</t>
         </is>
       </c>
-      <c r="D12" s="23" t="inlineStr">
+      <c r="D13" s="22" t="inlineStr">
         <is>
           <t>貂、獴</t>
         </is>
       </c>
-      <c r="E12" s="30" t="n">
+      <c r="E13" s="31" t="n">
         <v>3</v>
       </c>
-      <c r="F12" s="23" t="inlineStr">
+      <c r="F13" s="22" t="inlineStr">
         <is>
           <t>同貓科</t>
         </is>
       </c>
-      <c r="G12" s="23" t="inlineStr">
+      <c r="G13" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H12" s="23" t="inlineStr">
+      <c r="H13" s="22" t="inlineStr">
         <is>
           <t>待機、站起來張望、低頭聞、甩尾、走路</t>
         </is>
       </c>
-      <c r="I12" s="23" t="inlineStr">
+      <c r="I13" s="22" t="inlineStr">
         <is>
           <t>≤ 120 KB</t>
         </is>
       </c>
-      <c r="J12" s="30" t="n">
+      <c r="J13" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="K12" s="23" t="inlineStr">
+      <c r="K13" s="22" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="L12" s="28" t="inlineStr">
+      <c r="L13" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="M12" s="29" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="27" t="n">
+      <c r="M13" s="30" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="28" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="22" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t>hawk_eagle</t>
         </is>
       </c>
-      <c r="C13" s="22" t="inlineStr">
+      <c r="C14" s="23" t="inlineStr">
         <is>
           <t>熊鷹</t>
         </is>
       </c>
-      <c r="D13" s="22" t="inlineStr">
+      <c r="D14" s="23" t="inlineStr">
         <is>
           <t>猛禽</t>
         </is>
       </c>
-      <c r="E13" s="27" t="n">
+      <c r="E14" s="28" t="n">
         <v>3</v>
       </c>
-      <c r="F13" s="22" t="inlineStr">
+      <c r="F14" s="23" t="inlineStr">
         <is>
           <t>同鳥</t>
         </is>
       </c>
-      <c r="G13" s="22" t="inlineStr">
+      <c r="G14" s="23" t="inlineStr">
         <is>
           <t>展翅盤旋 1 張</t>
         </is>
       </c>
-      <c r="H13" s="22" t="inlineStr">
+      <c r="H14" s="23" t="inlineStr">
         <is>
           <t>待機、張望、展翅；另需「飛行姿勢（展翅盤旋）」1 張</t>
         </is>
       </c>
-      <c r="I13" s="22" t="inlineStr">
+      <c r="I14" s="23" t="inlineStr">
         <is>
           <t>≤ 120 KB</t>
         </is>
       </c>
-      <c r="J13" s="27" t="n">
+      <c r="J14" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="K13" s="22" t="inlineStr">
+      <c r="K14" s="23" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="L13" s="28" t="inlineStr">
+      <c r="L14" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="M13" s="29" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="30" t="n">
+      <c r="M14" s="30" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="31" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="23" t="inlineStr">
+      <c r="B15" s="22" t="inlineStr">
         <is>
           <t>fish_owl</t>
         </is>
       </c>
-      <c r="C14" s="23" t="inlineStr">
+      <c r="C15" s="22" t="inlineStr">
         <is>
           <t>黃魚鴞</t>
         </is>
       </c>
-      <c r="D14" s="23" t="inlineStr">
+      <c r="D15" s="22" t="inlineStr">
         <is>
           <t>貓頭鷹</t>
         </is>
       </c>
-      <c r="E14" s="30" t="n">
+      <c r="E15" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="F14" s="23" t="inlineStr">
+      <c r="F15" s="22" t="inlineStr">
         <is>
           <t>拿掉頭；閉眼；拿掉耳羽；頭轉向鏡頭</t>
         </is>
       </c>
-      <c r="G14" s="23" t="inlineStr">
+      <c r="G15" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H14" s="23" t="inlineStr">
+      <c r="H15" s="22" t="inlineStr">
         <is>
           <t>待機、大角度轉頭、眨眼、縮成一團（發光眼睛由程式畫）</t>
         </is>
       </c>
-      <c r="I14" s="23" t="inlineStr">
+      <c r="I15" s="22" t="inlineStr">
         <is>
           <t>≤ 120 KB</t>
         </is>
       </c>
-      <c r="J14" s="30" t="n">
+      <c r="J15" s="31" t="n">
         <v>4</v>
       </c>
-      <c r="K14" s="23" t="inlineStr">
+      <c r="K15" s="22" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="L14" s="28" t="inlineStr">
+      <c r="L15" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="M14" s="29" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="27" t="n">
+      <c r="M15" s="30" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="28" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="22" t="inlineStr">
+      <c r="B16" s="23" t="inlineStr">
         <is>
           <t>black_faced_spoonbill</t>
         </is>
       </c>
-      <c r="C15" s="22" t="inlineStr">
+      <c r="C16" s="23" t="inlineStr">
         <is>
           <t>黑面琵鷺</t>
         </is>
       </c>
-      <c r="D15" s="22" t="inlineStr">
+      <c r="D16" s="23" t="inlineStr">
         <is>
           <t>涉禽</t>
         </is>
       </c>
-      <c r="E15" s="27" t="n">
+      <c r="E16" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="F15" s="22" t="inlineStr">
+      <c r="F16" s="23" t="inlineStr">
         <is>
           <t>同鳥</t>
         </is>
       </c>
-      <c r="G15" s="22" t="inlineStr">
+      <c r="G16" s="23" t="inlineStr">
         <is>
           <t>飛行姿勢 1 張（選配）</t>
         </is>
       </c>
-      <c r="H15" s="22" t="inlineStr">
+      <c r="H16" s="23" t="inlineStr">
         <is>
           <t>待機、涉水走、低頭左右掃嘴覓食、理羽毛</t>
         </is>
       </c>
-      <c r="I15" s="22" t="inlineStr">
+      <c r="I16" s="23" t="inlineStr">
         <is>
           <t>≤ 120 KB</t>
         </is>
       </c>
-      <c r="J15" s="27" t="n">
+      <c r="J16" s="28" t="n">
         <v>6</v>
       </c>
-      <c r="K15" s="22" t="inlineStr">
+      <c r="K16" s="23" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="L15" s="28" t="inlineStr">
+      <c r="L16" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="M15" s="29" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="30" t="n">
+      <c r="M16" s="30" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="31" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="23" t="inlineStr">
+      <c r="B17" s="22" t="inlineStr">
         <is>
           <t>yellow_tit</t>
         </is>
       </c>
-      <c r="C16" s="23" t="inlineStr">
+      <c r="C17" s="22" t="inlineStr">
         <is>
           <t>黃山雀</t>
         </is>
       </c>
-      <c r="D16" s="23" t="inlineStr">
+      <c r="D17" s="22" t="inlineStr">
         <is>
           <t>鳥</t>
         </is>
       </c>
-      <c r="E16" s="30" t="n">
+      <c r="E17" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="F16" s="23" t="inlineStr">
+      <c r="F17" s="22" t="inlineStr">
         <is>
           <t>拿掉近側翅膀；拿掉頭；閉眼；拿掉近側腳；頭轉向鏡頭</t>
         </is>
       </c>
-      <c r="G16" s="23" t="inlineStr">
+      <c r="G17" s="22" t="inlineStr">
         <is>
           <t>飛行姿勢 1 張</t>
         </is>
       </c>
-      <c r="H16" s="23" t="inlineStr">
+      <c r="H17" s="22" t="inlineStr">
         <is>
           <t>待機、跳兩步、低頭啄、理羽毛、歪頭、眨眼、拍翅；另需「飛行姿勢」1 張</t>
         </is>
       </c>
-      <c r="I16" s="23" t="inlineStr">
+      <c r="I17" s="22" t="inlineStr">
         <is>
           <t>≤ 120 KB</t>
         </is>
       </c>
-      <c r="J16" s="30" t="n">
+      <c r="J17" s="31" t="n">
         <v>4</v>
       </c>
-      <c r="K16" s="23" t="inlineStr">
+      <c r="K17" s="22" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="L16" s="28" t="inlineStr">
+      <c r="L17" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="M16" s="29" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="27" t="n">
+      <c r="M17" s="30" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="28" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="22" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>hill_partridge</t>
         </is>
       </c>
-      <c r="C17" s="22" t="inlineStr">
+      <c r="C18" s="23" t="inlineStr">
         <is>
           <t>台灣山鷓鴣</t>
         </is>
       </c>
-      <c r="D17" s="22" t="inlineStr">
+      <c r="D18" s="23" t="inlineStr">
         <is>
           <t>雉雞</t>
         </is>
       </c>
-      <c r="E17" s="27" t="n">
+      <c r="E18" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="F17" s="22" t="inlineStr">
+      <c r="F18" s="23" t="inlineStr">
         <is>
           <t>同鳥</t>
         </is>
       </c>
-      <c r="G17" s="22" t="inlineStr">
+      <c r="G18" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H17" s="22" t="inlineStr">
+      <c r="H18" s="23" t="inlineStr">
         <is>
           <t>待機、走路、低頭啄、抬頭張望、眨眼</t>
         </is>
       </c>
-      <c r="I17" s="22" t="inlineStr">
+      <c r="I18" s="23" t="inlineStr">
         <is>
           <t>≤ 120 KB</t>
         </is>
       </c>
-      <c r="J17" s="27" t="n">
+      <c r="J18" s="28" t="n">
         <v>5</v>
       </c>
-      <c r="K17" s="22" t="inlineStr">
+      <c r="K18" s="23" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="L17" s="28" t="inlineStr">
+      <c r="L18" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="M17" s="29" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="30" t="n">
+      <c r="M18" s="30" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="31" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="23" t="inlineStr">
+      <c r="B19" s="22" t="inlineStr">
         <is>
           <t>clouded_leopard</t>
         </is>
       </c>
-      <c r="C18" s="23" t="inlineStr">
+      <c r="C19" s="22" t="inlineStr">
         <is>
           <t>台灣雲豹</t>
         </is>
       </c>
-      <c r="D18" s="23" t="inlineStr">
+      <c r="D19" s="22" t="inlineStr">
         <is>
           <t>貓科</t>
         </is>
       </c>
-      <c r="E18" s="30" t="n">
+      <c r="E19" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="F18" s="23" t="inlineStr">
+      <c r="F19" s="22" t="inlineStr">
         <is>
           <t>E1 拿掉近側兩條腿；E3 拿掉頭；E4 拿掉兩隻耳朵；E5 閉眼；E7 頭轉向鏡頭</t>
         </is>
       </c>
-      <c r="G18" s="23" t="inlineStr">
+      <c r="G19" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H18" s="23" t="inlineStr">
+      <c r="H19" s="22" t="inlineStr">
         <is>
           <t>待機呼吸、張望、低頭聞、甩尾、耳朵抖、眨眼、張嘴、走路（定格每秒 8 格）</t>
         </is>
       </c>
-      <c r="I18" s="23" t="inlineStr">
+      <c r="I19" s="22" t="inlineStr">
         <is>
           <t>≤ 120 KB</t>
         </is>
       </c>
-      <c r="J18" s="30" t="n">
+      <c r="J19" s="31" t="n">
         <v>5</v>
       </c>
-      <c r="K18" s="23" t="inlineStr">
+      <c r="K19" s="22" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="L18" s="28" t="inlineStr">
+      <c r="L19" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="M18" s="29" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="27" t="n">
+      <c r="M19" s="30" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="28" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="22" t="inlineStr">
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>eurasian_otter</t>
         </is>
       </c>
-      <c r="C19" s="22" t="inlineStr">
+      <c r="C20" s="23" t="inlineStr">
         <is>
           <t>歐亞水獺（金門）</t>
         </is>
       </c>
-      <c r="D19" s="22" t="inlineStr">
+      <c r="D20" s="23" t="inlineStr">
         <is>
           <t>水獺</t>
         </is>
       </c>
-      <c r="E19" s="27" t="n">
+      <c r="E20" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="F19" s="22" t="inlineStr">
+      <c r="F20" s="23" t="inlineStr">
         <is>
           <t>同貓科</t>
         </is>
       </c>
-      <c r="G19" s="22" t="inlineStr">
+      <c r="G20" s="23" t="inlineStr">
         <is>
           <t>游泳姿勢 1 張</t>
         </is>
       </c>
-      <c r="H19" s="22" t="inlineStr">
+      <c r="H20" s="23" t="inlineStr">
         <is>
           <t>待機、站起來張望、走路、游泳（另畫游泳姿勢）</t>
         </is>
       </c>
-      <c r="I19" s="22" t="inlineStr">
+      <c r="I20" s="23" t="inlineStr">
         <is>
           <t>≤ 120 KB</t>
         </is>
       </c>
-      <c r="J19" s="27" t="n">
+      <c r="J20" s="28" t="n">
         <v>6</v>
       </c>
-      <c r="K19" s="22" t="inlineStr">
+      <c r="K20" s="23" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="L19" s="28" t="inlineStr">
+      <c r="L20" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="M19" s="29" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="30" t="n">
+      <c r="M20" s="30" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="31" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="23" t="inlineStr">
+      <c r="B21" s="22" t="inlineStr">
         <is>
           <t>formosan_salmon</t>
         </is>
       </c>
-      <c r="C20" s="23" t="inlineStr">
+      <c r="C21" s="22" t="inlineStr">
         <is>
           <t>櫻花鉤吻鮭</t>
         </is>
       </c>
-      <c r="D20" s="23" t="inlineStr">
+      <c r="D21" s="22" t="inlineStr">
         <is>
           <t>魚</t>
         </is>
       </c>
-      <c r="E20" s="30" t="n">
+      <c r="E21" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="F20" s="23" t="inlineStr">
+      <c r="F21" s="22" t="inlineStr">
         <is>
           <t>拿掉胸鰭</t>
         </is>
       </c>
-      <c r="G20" s="23" t="inlineStr">
+      <c r="G21" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H20" s="23" t="inlineStr">
+      <c r="H21" s="22" t="inlineStr">
         <is>
           <t>游動擺尾、停在水中、轉向</t>
         </is>
       </c>
-      <c r="I20" s="23" t="inlineStr">
+      <c r="I21" s="22" t="inlineStr">
         <is>
           <t>≤ 120 KB</t>
         </is>
       </c>
-      <c r="J20" s="30" t="n">
+      <c r="J21" s="31" t="n">
         <v>6</v>
       </c>
-      <c r="K20" s="23" t="inlineStr">
+      <c r="K21" s="22" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="L20" s="28" t="inlineStr">
+      <c r="L21" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="M20" s="29" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="27" t="n">
+      <c r="M21" s="30" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="28" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="22" t="inlineStr">
+      <c r="B22" s="23" t="inlineStr">
         <is>
           <t>green_turtle</t>
         </is>
       </c>
-      <c r="C21" s="22" t="inlineStr">
+      <c r="C22" s="23" t="inlineStr">
         <is>
           <t>綠蠵龜</t>
         </is>
       </c>
-      <c r="D21" s="22" t="inlineStr">
+      <c r="D22" s="23" t="inlineStr">
         <is>
           <t>海龜</t>
         </is>
       </c>
-      <c r="E21" s="27" t="n">
+      <c r="E22" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="F21" s="22" t="inlineStr">
+      <c r="F22" s="23" t="inlineStr">
         <is>
           <t>拿掉近側前鰭</t>
         </is>
       </c>
-      <c r="G21" s="22" t="inlineStr">
+      <c r="G22" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H21" s="22" t="inlineStr">
+      <c r="H22" s="23" t="inlineStr">
         <is>
           <t>划水、浮上換氣、轉頭</t>
         </is>
       </c>
-      <c r="I21" s="22" t="inlineStr">
+      <c r="I22" s="23" t="inlineStr">
         <is>
           <t>≤ 120 KB</t>
         </is>
       </c>
-      <c r="J21" s="27" t="n">
+      <c r="J22" s="28" t="n">
         <v>6</v>
       </c>
-      <c r="K21" s="22" t="inlineStr">
+      <c r="K22" s="23" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="L21" s="28" t="inlineStr">
+      <c r="L22" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="M21" s="29" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="30" t="n">
+      <c r="M22" s="30" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="31" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="23" t="inlineStr">
+      <c r="B23" s="22" t="inlineStr">
         <is>
           <t>white_dolphin</t>
         </is>
       </c>
-      <c r="C22" s="23" t="inlineStr">
+      <c r="C23" s="22" t="inlineStr">
         <is>
           <t>中華白海豚</t>
         </is>
       </c>
-      <c r="D22" s="23" t="inlineStr">
+      <c r="D23" s="22" t="inlineStr">
         <is>
           <t>海豚</t>
         </is>
       </c>
-      <c r="E22" s="30" t="n">
+      <c r="E23" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="F22" s="23" t="inlineStr">
+      <c r="F23" s="22" t="inlineStr">
         <is>
           <t>拿掉胸鰭</t>
         </is>
       </c>
-      <c r="G22" s="23" t="inlineStr">
+      <c r="G23" s="22" t="inlineStr">
         <is>
           <t>躍出水面 1 張</t>
         </is>
       </c>
-      <c r="H22" s="23" t="inlineStr">
+      <c r="H23" s="22" t="inlineStr">
         <is>
           <t>游、躍出水面、噴氣</t>
         </is>
       </c>
-      <c r="I22" s="23" t="inlineStr">
+      <c r="I23" s="22" t="inlineStr">
         <is>
           <t>≤ 120 KB</t>
         </is>
       </c>
-      <c r="J22" s="30" t="n">
+      <c r="J23" s="31" t="n">
         <v>6</v>
       </c>
-      <c r="K22" s="23" t="inlineStr">
+      <c r="K23" s="22" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="L22" s="28" t="inlineStr">
+      <c r="L23" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="M22" s="29" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="27" t="n">
+      <c r="M23" s="30" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="28" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="22" t="inlineStr">
+      <c r="B24" s="23" t="inlineStr">
         <is>
           <t>broad_tailed_swallowtail</t>
         </is>
       </c>
-      <c r="C23" s="22" t="inlineStr">
+      <c r="C24" s="23" t="inlineStr">
         <is>
           <t>寬尾鳳蝶</t>
         </is>
       </c>
-      <c r="D23" s="22" t="inlineStr">
+      <c r="D24" s="23" t="inlineStr">
         <is>
           <t>蝴蝶</t>
         </is>
       </c>
-      <c r="E23" s="27" t="n">
+      <c r="E24" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="F23" s="22" t="inlineStr">
+      <c r="F24" s="23" t="inlineStr">
         <is>
           <t>—（另畫停棲姿勢）</t>
         </is>
       </c>
-      <c r="G23" s="22" t="inlineStr">
+      <c r="G24" s="23" t="inlineStr">
         <is>
           <t>停棲（翅膀合起）1 張</t>
         </is>
       </c>
-      <c r="H23" s="22" t="inlineStr">
+      <c r="H24" s="23" t="inlineStr">
         <is>
           <t>拍翅飛舞、停在花上翅膀開合</t>
         </is>
       </c>
-      <c r="I23" s="22" t="inlineStr">
+      <c r="I24" s="23" t="inlineStr">
         <is>
           <t>≤ 120 KB</t>
         </is>
       </c>
-      <c r="J23" s="27" t="n">
+      <c r="J24" s="28" t="n">
         <v>6</v>
       </c>
-      <c r="K23" s="22" t="inlineStr">
+      <c r="K24" s="23" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="L23" s="28" t="inlineStr">
+      <c r="L24" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="M23" s="29" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="30" t="n">
+      <c r="M24" s="30" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="31" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="23" t="inlineStr">
+      <c r="B25" s="22" t="inlineStr">
         <is>
           <t>farmland_tree_frog</t>
         </is>
       </c>
-      <c r="C24" s="23" t="inlineStr">
+      <c r="C25" s="22" t="inlineStr">
         <is>
           <t>諸羅樹蛙</t>
         </is>
       </c>
-      <c r="D24" s="23" t="inlineStr">
+      <c r="D25" s="22" t="inlineStr">
         <is>
           <t>蛙</t>
         </is>
       </c>
-      <c r="E24" s="30" t="n">
+      <c r="E25" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="F24" s="23" t="inlineStr">
+      <c r="F25" s="22" t="inlineStr">
         <is>
           <t>拿掉近側後腳；閉眼</t>
         </is>
       </c>
-      <c r="G24" s="23" t="inlineStr">
+      <c r="G25" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H24" s="23" t="inlineStr">
+      <c r="H25" s="22" t="inlineStr">
         <is>
           <t>待機、鼓鳴囊（叫）、跳、眨眼</t>
         </is>
       </c>
-      <c r="I24" s="23" t="inlineStr">
+      <c r="I25" s="22" t="inlineStr">
         <is>
           <t>≤ 120 KB</t>
         </is>
       </c>
-      <c r="J24" s="30" t="n">
+      <c r="J25" s="31" t="n">
         <v>6</v>
       </c>
-      <c r="K24" s="23" t="inlineStr">
+      <c r="K25" s="22" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="L24" s="28" t="inlineStr">
+      <c r="L25" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="M24" s="29" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="27" t="n">
+      <c r="M25" s="30" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="28" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="22" t="inlineStr">
+      <c r="B26" s="23" t="inlineStr">
         <is>
           <t>formosan_flying_fox</t>
         </is>
       </c>
-      <c r="C25" s="22" t="inlineStr">
+      <c r="C26" s="23" t="inlineStr">
         <is>
           <t>台灣狐蝠</t>
         </is>
       </c>
-      <c r="D25" s="22" t="inlineStr">
+      <c r="D26" s="23" t="inlineStr">
         <is>
           <t>蝙蝠</t>
         </is>
       </c>
-      <c r="E25" s="27" t="n">
+      <c r="E26" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="F25" s="22" t="inlineStr">
+      <c r="F26" s="23" t="inlineStr">
         <is>
           <t>—（另畫倒掛、飛行姿勢）</t>
         </is>
       </c>
-      <c r="G25" s="22" t="inlineStr">
+      <c r="G26" s="23" t="inlineStr">
         <is>
           <t>飛行（展翼）、倒掛各 1 張</t>
         </is>
       </c>
-      <c r="H25" s="22" t="inlineStr">
+      <c r="H26" s="23" t="inlineStr">
         <is>
           <t>飛行拍翼、倒掛時收翼、轉頭</t>
         </is>
       </c>
-      <c r="I25" s="22" t="inlineStr">
+      <c r="I26" s="23" t="inlineStr">
         <is>
           <t>≤ 120 KB</t>
         </is>
       </c>
-      <c r="J25" s="27" t="n">
+      <c r="J26" s="28" t="n">
         <v>6</v>
       </c>
-      <c r="K25" s="22" t="inlineStr">
+      <c r="K26" s="23" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="L25" s="28" t="inlineStr">
+      <c r="L26" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="M25" s="29" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="30" t="n">
-        <v>22</v>
-      </c>
-      <c r="B26" s="23" t="inlineStr">
+      <c r="M26" s="30" t="inlineStr"/>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="27" t="inlineStr">
+        <is>
+          <t>日本（8 種）</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="B28" s="23" t="inlineStr">
         <is>
           <t>iriomote_cat</t>
         </is>
       </c>
-      <c r="C26" s="23" t="inlineStr">
+      <c r="C28" s="23" t="inlineStr">
         <is>
           <t>西表山貓</t>
         </is>
       </c>
-      <c r="D26" s="23" t="inlineStr">
+      <c r="D28" s="23" t="inlineStr">
         <is>
           <t>貓科</t>
         </is>
       </c>
-      <c r="E26" s="30" t="n">
+      <c r="E28" s="28" t="n">
         <v>3</v>
       </c>
-      <c r="F26" s="23" t="inlineStr">
+      <c r="F28" s="23" t="inlineStr">
         <is>
           <t>E1 拿掉近側兩條腿；E3 拿掉頭；E4 拿掉兩隻耳朵；E5 閉眼；E7 頭轉向鏡頭</t>
         </is>
       </c>
-      <c r="G26" s="23" t="inlineStr">
+      <c r="G28" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H26" s="23" t="inlineStr">
+      <c r="H28" s="23" t="inlineStr">
         <is>
           <t>待機呼吸、張望、低頭聞、甩尾、耳朵抖、眨眼、張嘴、走路（定格每秒 8 格）</t>
         </is>
       </c>
-      <c r="I26" s="23" t="inlineStr">
+      <c r="I28" s="23" t="inlineStr">
         <is>
           <t>≤ 120 KB</t>
         </is>
       </c>
-      <c r="J26" s="30" t="n">
+      <c r="J28" s="28" t="n">
         <v>3</v>
       </c>
-      <c r="K26" s="23" t="inlineStr">
+      <c r="K28" s="23" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="L26" s="28" t="inlineStr">
+      <c r="L28" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="M26" s="29" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="27" t="n">
-        <v>23</v>
-      </c>
-      <c r="B27" s="22" t="inlineStr">
+      <c r="M28" s="30" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="B29" s="22" t="inlineStr">
         <is>
           <t>okinawa_woodpecker</t>
         </is>
       </c>
-      <c r="C27" s="22" t="inlineStr">
+      <c r="C29" s="22" t="inlineStr">
         <is>
           <t>野口啄木鳥</t>
         </is>
       </c>
-      <c r="D27" s="22" t="inlineStr">
+      <c r="D29" s="22" t="inlineStr">
         <is>
           <t>鳥</t>
         </is>
       </c>
-      <c r="E27" s="27" t="n">
+      <c r="E29" s="31" t="n">
         <v>3</v>
       </c>
-      <c r="F27" s="22" t="inlineStr">
+      <c r="F29" s="22" t="inlineStr">
         <is>
           <t>拿掉近側翅膀；拿掉頭；閉眼；拿掉近側腳；頭轉向鏡頭</t>
         </is>
       </c>
-      <c r="G27" s="22" t="inlineStr">
+      <c r="G29" s="22" t="inlineStr">
         <is>
           <t>飛行姿勢 1 張</t>
         </is>
       </c>
-      <c r="H27" s="22" t="inlineStr">
+      <c r="H29" s="22" t="inlineStr">
         <is>
           <t>待機、跳兩步、低頭啄、理羽毛、歪頭、眨眼、拍翅；另需「飛行姿勢」1 張</t>
         </is>
       </c>
-      <c r="I27" s="22" t="inlineStr">
+      <c r="I29" s="22" t="inlineStr">
         <is>
           <t>≤ 120 KB</t>
         </is>
       </c>
-      <c r="J27" s="27" t="n">
+      <c r="J29" s="31" t="n">
         <v>3</v>
       </c>
-      <c r="K27" s="22" t="inlineStr">
+      <c r="K29" s="22" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="L27" s="28" t="inlineStr">
+      <c r="L29" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="M27" s="29" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="30" t="n">
-        <v>24</v>
-      </c>
-      <c r="B28" s="23" t="inlineStr">
+      <c r="M29" s="30" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="B30" s="23" t="inlineStr">
         <is>
           <t>japanese_serow</t>
         </is>
       </c>
-      <c r="C28" s="23" t="inlineStr">
+      <c r="C30" s="23" t="inlineStr">
         <is>
           <t>日本鬣羚</t>
         </is>
       </c>
-      <c r="D28" s="23" t="inlineStr">
+      <c r="D30" s="23" t="inlineStr">
         <is>
           <t>山羊</t>
         </is>
       </c>
-      <c r="E28" s="30" t="n">
+      <c r="E30" s="28" t="n">
         <v>3</v>
       </c>
-      <c r="F28" s="23" t="inlineStr">
+      <c r="F30" s="23" t="inlineStr">
         <is>
           <t>同貓科＋拿掉鬃毛</t>
         </is>
       </c>
-      <c r="G28" s="23" t="inlineStr">
+      <c r="G30" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H28" s="23" t="inlineStr">
+      <c r="H30" s="23" t="inlineStr">
         <is>
           <t>待機、張望、低頭吃草、甩耳、走路</t>
         </is>
       </c>
-      <c r="I28" s="23" t="inlineStr">
+      <c r="I30" s="23" t="inlineStr">
         <is>
           <t>≤ 120 KB</t>
         </is>
       </c>
-      <c r="J28" s="30" t="n">
+      <c r="J30" s="28" t="n">
         <v>3</v>
       </c>
-      <c r="K28" s="23" t="inlineStr">
+      <c r="K30" s="23" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="L28" s="28" t="inlineStr">
+      <c r="L30" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="M28" s="29" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="27" t="n">
-        <v>25</v>
-      </c>
-      <c r="B29" s="22" t="inlineStr">
+      <c r="M30" s="30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="B31" s="22" t="inlineStr">
         <is>
           <t>ptarmigan</t>
         </is>
       </c>
-      <c r="C29" s="22" t="inlineStr">
+      <c r="C31" s="22" t="inlineStr">
         <is>
           <t>雷鳥</t>
         </is>
       </c>
-      <c r="D29" s="22" t="inlineStr">
+      <c r="D31" s="22" t="inlineStr">
         <is>
           <t>雉雞</t>
         </is>
       </c>
-      <c r="E29" s="27" t="n">
+      <c r="E31" s="31" t="n">
         <v>3</v>
       </c>
-      <c r="F29" s="22" t="inlineStr">
+      <c r="F31" s="22" t="inlineStr">
         <is>
           <t>同鳥</t>
         </is>
       </c>
-      <c r="G29" s="22" t="inlineStr">
+      <c r="G31" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H29" s="22" t="inlineStr">
+      <c r="H31" s="22" t="inlineStr">
         <is>
           <t>待機、走路、低頭啄、抬頭張望、眨眼</t>
         </is>
       </c>
-      <c r="I29" s="22" t="inlineStr">
+      <c r="I31" s="22" t="inlineStr">
         <is>
           <t>≤ 120 KB</t>
         </is>
       </c>
-      <c r="J29" s="27" t="n">
+      <c r="J31" s="31" t="n">
         <v>3</v>
       </c>
-      <c r="K29" s="22" t="inlineStr">
+      <c r="K31" s="22" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="L29" s="28" t="inlineStr">
+      <c r="L31" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="M29" s="29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="30" t="n">
-        <v>26</v>
-      </c>
-      <c r="B30" s="23" t="inlineStr">
+      <c r="M31" s="30" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="28" t="n">
+        <v>5</v>
+      </c>
+      <c r="B32" s="23" t="inlineStr">
         <is>
           <t>blakiston_owl</t>
         </is>
       </c>
-      <c r="C30" s="23" t="inlineStr">
+      <c r="C32" s="23" t="inlineStr">
         <is>
           <t>毛腿魚鴞</t>
         </is>
       </c>
-      <c r="D30" s="23" t="inlineStr">
+      <c r="D32" s="23" t="inlineStr">
         <is>
           <t>貓頭鷹</t>
         </is>
       </c>
-      <c r="E30" s="30" t="n">
+      <c r="E32" s="28" t="n">
         <v>3</v>
       </c>
-      <c r="F30" s="23" t="inlineStr">
+      <c r="F32" s="23" t="inlineStr">
         <is>
           <t>拿掉頭；閉眼；拿掉耳羽；頭轉向鏡頭</t>
         </is>
       </c>
-      <c r="G30" s="23" t="inlineStr">
+      <c r="G32" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H30" s="23" t="inlineStr">
+      <c r="H32" s="23" t="inlineStr">
         <is>
           <t>待機、大角度轉頭、眨眼、縮成一團（發光眼睛由程式畫）</t>
         </is>
       </c>
-      <c r="I30" s="23" t="inlineStr">
+      <c r="I32" s="23" t="inlineStr">
         <is>
           <t>≤ 120 KB</t>
         </is>
       </c>
-      <c r="J30" s="30" t="n">
+      <c r="J32" s="28" t="n">
         <v>3</v>
       </c>
-      <c r="K30" s="23" t="inlineStr">
+      <c r="K32" s="23" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="L30" s="28" t="inlineStr">
+      <c r="L32" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="M30" s="29" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="27" t="n">
-        <v>27</v>
-      </c>
-      <c r="B31" s="22" t="inlineStr">
+      <c r="M32" s="30" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="31" t="n">
+        <v>6</v>
+      </c>
+      <c r="B33" s="22" t="inlineStr">
         <is>
           <t>tsushima_cat</t>
         </is>
       </c>
-      <c r="C31" s="22" t="inlineStr">
+      <c r="C33" s="22" t="inlineStr">
         <is>
           <t>對馬山貓</t>
         </is>
       </c>
-      <c r="D31" s="22" t="inlineStr">
+      <c r="D33" s="22" t="inlineStr">
         <is>
           <t>貓科</t>
         </is>
       </c>
-      <c r="E31" s="27" t="n">
+      <c r="E33" s="31" t="n">
         <v>3</v>
       </c>
-      <c r="F31" s="22" t="inlineStr">
+      <c r="F33" s="22" t="inlineStr">
         <is>
           <t>E1 拿掉近側兩條腿；E3 拿掉頭；E4 拿掉兩隻耳朵；E5 閉眼；E7 頭轉向鏡頭</t>
         </is>
       </c>
-      <c r="G31" s="22" t="inlineStr">
+      <c r="G33" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H31" s="22" t="inlineStr">
+      <c r="H33" s="22" t="inlineStr">
         <is>
           <t>待機呼吸、張望、低頭聞、甩尾、耳朵抖、眨眼、張嘴、走路（定格每秒 8 格）</t>
         </is>
       </c>
-      <c r="I31" s="22" t="inlineStr">
+      <c r="I33" s="22" t="inlineStr">
         <is>
           <t>≤ 120 KB</t>
         </is>
       </c>
-      <c r="J31" s="27" t="n">
+      <c r="J33" s="31" t="n">
         <v>3</v>
       </c>
-      <c r="K31" s="22" t="inlineStr">
+      <c r="K33" s="22" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="L31" s="28" t="inlineStr">
+      <c r="L33" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="M31" s="29" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="30" t="n">
-        <v>28</v>
-      </c>
-      <c r="B32" s="23" t="inlineStr">
+      <c r="M33" s="30" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="28" t="n">
+        <v>7</v>
+      </c>
+      <c r="B34" s="23" t="inlineStr">
         <is>
           <t>steller_eagle</t>
         </is>
       </c>
-      <c r="C32" s="23" t="inlineStr">
+      <c r="C34" s="23" t="inlineStr">
         <is>
           <t>虎頭海鵰</t>
         </is>
       </c>
-      <c r="D32" s="23" t="inlineStr">
+      <c r="D34" s="23" t="inlineStr">
         <is>
           <t>猛禽</t>
         </is>
       </c>
-      <c r="E32" s="30" t="n">
+      <c r="E34" s="28" t="n">
         <v>3</v>
       </c>
-      <c r="F32" s="23" t="inlineStr">
+      <c r="F34" s="23" t="inlineStr">
         <is>
           <t>同鳥</t>
         </is>
       </c>
-      <c r="G32" s="23" t="inlineStr">
+      <c r="G34" s="23" t="inlineStr">
         <is>
           <t>展翅盤旋 1 張</t>
         </is>
       </c>
-      <c r="H32" s="23" t="inlineStr">
+      <c r="H34" s="23" t="inlineStr">
         <is>
           <t>待機、張望、展翅；另需「飛行姿勢（展翅盤旋）」1 張</t>
         </is>
       </c>
-      <c r="I32" s="23" t="inlineStr">
+      <c r="I34" s="23" t="inlineStr">
         <is>
           <t>≤ 120 KB</t>
         </is>
       </c>
-      <c r="J32" s="30" t="n">
+      <c r="J34" s="28" t="n">
         <v>3</v>
       </c>
-      <c r="K32" s="23" t="inlineStr">
+      <c r="K34" s="23" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="L32" s="28" t="inlineStr">
+      <c r="L34" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="M32" s="29" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="27" t="n">
-        <v>29</v>
-      </c>
-      <c r="B33" s="22" t="inlineStr">
+      <c r="M34" s="30" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="B35" s="22" t="inlineStr">
         <is>
           <t>moon_bear</t>
         </is>
       </c>
-      <c r="C33" s="22" t="inlineStr">
+      <c r="C35" s="22" t="inlineStr">
         <is>
           <t>月輪熊</t>
         </is>
       </c>
-      <c r="D33" s="22" t="inlineStr">
+      <c r="D35" s="22" t="inlineStr">
         <is>
           <t>熊</t>
         </is>
       </c>
-      <c r="E33" s="27" t="n">
+      <c r="E35" s="31" t="n">
         <v>3</v>
       </c>
-      <c r="F33" s="22" t="inlineStr">
+      <c r="F35" s="22" t="inlineStr">
         <is>
           <t>同貓科</t>
         </is>
       </c>
-      <c r="G33" s="22" t="inlineStr">
+      <c r="G35" s="22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H33" s="22" t="inlineStr">
+      <c r="H35" s="22" t="inlineStr">
         <is>
           <t>待機、張望、低頭聞、坐下、走路</t>
         </is>
       </c>
-      <c r="I33" s="22" t="inlineStr">
+      <c r="I35" s="22" t="inlineStr">
         <is>
           <t>≤ 120 KB</t>
         </is>
       </c>
-      <c r="J33" s="27" t="n">
+      <c r="J35" s="31" t="n">
         <v>3</v>
       </c>
-      <c r="K33" s="22" t="inlineStr">
+      <c r="K35" s="22" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="L33" s="28" t="inlineStr">
+      <c r="L35" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="M33" s="29" t="inlineStr"/>
+      <c r="M35" s="30" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:M33"/>
-  <mergeCells count="1">
+  <autoFilter ref="A4:M35"/>
+  <mergeCells count="3">
+    <mergeCell ref="A27:M27"/>
     <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A5:M5"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="L5:L304" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="狀態" error="請從清單選一個狀態" type="list">
@@ -8807,7 +8848,7 @@
           <t>待機呼吸、張望、低頭聞、甩尾、耳朵抖、眨眼、張嘴、走路（定格每秒 8 格）</t>
         </is>
       </c>
-      <c r="H5" s="29" t="inlineStr">
+      <c r="H5" s="30" t="inlineStr">
         <is>
           <t>已驗證（石虎）</t>
         </is>
@@ -8849,7 +8890,7 @@
           <t>待機、張望、低頭聞、坐下、走路</t>
         </is>
       </c>
-      <c r="H6" s="29" t="inlineStr">
+      <c r="H6" s="30" t="inlineStr">
         <is>
           <t>待第一隻實作確認</t>
         </is>
@@ -8891,7 +8932,7 @@
           <t>待機、張望、低頭吃草、甩耳、走路</t>
         </is>
       </c>
-      <c r="H7" s="29" t="inlineStr">
+      <c r="H7" s="30" t="inlineStr">
         <is>
           <t>待第一隻實作確認</t>
         </is>
@@ -8933,7 +8974,7 @@
           <t>待機、站起來張望、低頭聞、甩尾、走路</t>
         </is>
       </c>
-      <c r="H8" s="29" t="inlineStr">
+      <c r="H8" s="30" t="inlineStr">
         <is>
           <t>待第一隻實作確認</t>
         </is>
@@ -8975,7 +9016,7 @@
           <t>待機、低頭聞、甩尾、走路（選配：捲成球）</t>
         </is>
       </c>
-      <c r="H9" s="29" t="inlineStr">
+      <c r="H9" s="30" t="inlineStr">
         <is>
           <t>待第一隻實作確認</t>
         </is>
@@ -9017,7 +9058,7 @@
           <t>待機、跳兩步、低頭啄、理羽毛、歪頭、眨眼、拍翅；另需「飛行姿勢」1 張</t>
         </is>
       </c>
-      <c r="H10" s="29" t="inlineStr">
+      <c r="H10" s="30" t="inlineStr">
         <is>
           <t>待第一隻實作確認</t>
         </is>
@@ -9059,7 +9100,7 @@
           <t>待機、走路、低頭啄、抬頭張望、眨眼</t>
         </is>
       </c>
-      <c r="H11" s="29" t="inlineStr">
+      <c r="H11" s="30" t="inlineStr">
         <is>
           <t>待第一隻實作確認</t>
         </is>
@@ -9101,7 +9142,7 @@
           <t>待機、張望、展翅；另需「飛行姿勢（展翅盤旋）」1 張</t>
         </is>
       </c>
-      <c r="H12" s="29" t="inlineStr">
+      <c r="H12" s="30" t="inlineStr">
         <is>
           <t>待第一隻實作確認</t>
         </is>
@@ -9143,7 +9184,7 @@
           <t>待機、大角度轉頭、眨眼、縮成一團（發光眼睛由程式畫）</t>
         </is>
       </c>
-      <c r="H13" s="29" t="inlineStr">
+      <c r="H13" s="30" t="inlineStr">
         <is>
           <t>待第一隻實作確認</t>
         </is>
@@ -9185,7 +9226,7 @@
           <t>待機、涉水走、低頭左右掃嘴覓食、理羽毛</t>
         </is>
       </c>
-      <c r="H14" s="29" t="inlineStr">
+      <c r="H14" s="30" t="inlineStr">
         <is>
           <t>待第一隻實作確認</t>
         </is>
@@ -9227,7 +9268,7 @@
           <t>待機、站起來張望、走路、游泳（另畫游泳姿勢）</t>
         </is>
       </c>
-      <c r="H15" s="29" t="inlineStr">
+      <c r="H15" s="30" t="inlineStr">
         <is>
           <t>待第一隻實作確認</t>
         </is>
@@ -9269,7 +9310,7 @@
           <t>游動擺尾、停在水中、轉向</t>
         </is>
       </c>
-      <c r="H16" s="29" t="inlineStr">
+      <c r="H16" s="30" t="inlineStr">
         <is>
           <t>待第一隻實作確認</t>
         </is>
@@ -9311,7 +9352,7 @@
           <t>划水、浮上換氣、轉頭</t>
         </is>
       </c>
-      <c r="H17" s="29" t="inlineStr">
+      <c r="H17" s="30" t="inlineStr">
         <is>
           <t>待第一隻實作確認</t>
         </is>
@@ -9353,7 +9394,7 @@
           <t>游、躍出水面、噴氣</t>
         </is>
       </c>
-      <c r="H18" s="29" t="inlineStr">
+      <c r="H18" s="30" t="inlineStr">
         <is>
           <t>待第一隻實作確認</t>
         </is>
@@ -9395,7 +9436,7 @@
           <t>拍翅飛舞、停在花上翅膀開合</t>
         </is>
       </c>
-      <c r="H19" s="29" t="inlineStr">
+      <c r="H19" s="30" t="inlineStr">
         <is>
           <t>待第一隻實作確認</t>
         </is>
@@ -9437,7 +9478,7 @@
           <t>待機、鼓鳴囊（叫）、跳、眨眼</t>
         </is>
       </c>
-      <c r="H20" s="29" t="inlineStr">
+      <c r="H20" s="30" t="inlineStr">
         <is>
           <t>待第一隻實作確認</t>
         </is>
@@ -9479,7 +9520,7 @@
           <t>飛行拍翼、倒掛時收翼、轉頭</t>
         </is>
       </c>
-      <c r="H21" s="29" t="inlineStr">
+      <c r="H21" s="30" t="inlineStr">
         <is>
           <t>待第一隻實作確認</t>
         </is>
@@ -9583,7 +9624,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="27" t="n">
+      <c r="A5" s="31" t="n">
         <v>1</v>
       </c>
       <c r="B5" s="22" t="inlineStr">
@@ -9611,7 +9652,7 @@
           <t>約 3000×1150</t>
         </is>
       </c>
-      <c r="G5" s="27" t="n">
+      <c r="G5" s="31" t="n">
         <v>1</v>
       </c>
       <c r="H5" s="22" t="inlineStr">
@@ -9619,19 +9660,19 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="I5" s="32" t="inlineStr">
+      <c r="I5" s="33" t="inlineStr">
         <is>
           <t>暫代</t>
         </is>
       </c>
-      <c r="J5" s="29" t="inlineStr">
+      <c r="J5" s="30" t="inlineStr">
         <is>
           <t>原型暫時用 focus-done.webp（白天山景）</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="30" t="n">
+      <c r="A6" s="28" t="n">
         <v>2</v>
       </c>
       <c r="B6" s="23" t="inlineStr">
@@ -9659,7 +9700,7 @@
           <t>約 3000×1150</t>
         </is>
       </c>
-      <c r="G6" s="30" t="n">
+      <c r="G6" s="28" t="n">
         <v>1</v>
       </c>
       <c r="H6" s="23" t="inlineStr">
@@ -9667,19 +9708,19 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="I6" s="32" t="inlineStr">
+      <c r="I6" s="33" t="inlineStr">
         <is>
           <t>暫代</t>
         </is>
       </c>
-      <c r="J6" s="29" t="inlineStr">
+      <c r="J6" s="30" t="inlineStr">
         <is>
           <t>原型暫時把白天全景壓暗</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="27" t="n">
+      <c r="A7" s="31" t="n">
         <v>3</v>
       </c>
       <c r="B7" s="22" t="inlineStr">
@@ -9707,7 +9748,7 @@
           <t>約 3000×1150</t>
         </is>
       </c>
-      <c r="G7" s="27" t="n">
+      <c r="G7" s="31" t="n">
         <v>2</v>
       </c>
       <c r="H7" s="22" t="inlineStr">
@@ -9715,15 +9756,15 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I7" s="28" t="inlineStr">
+      <c r="I7" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="J7" s="29" t="inlineStr"/>
+      <c r="J7" s="30" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="30" t="n">
+      <c r="A8" s="28" t="n">
         <v>4</v>
       </c>
       <c r="B8" s="23" t="inlineStr">
@@ -9751,7 +9792,7 @@
           <t>約 3000×1150</t>
         </is>
       </c>
-      <c r="G8" s="30" t="n">
+      <c r="G8" s="28" t="n">
         <v>2</v>
       </c>
       <c r="H8" s="23" t="inlineStr">
@@ -9759,15 +9800,15 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I8" s="28" t="inlineStr">
+      <c r="I8" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="J8" s="29" t="inlineStr"/>
+      <c r="J8" s="30" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="27" t="n">
+      <c r="A9" s="31" t="n">
         <v>5</v>
       </c>
       <c r="B9" s="22" t="inlineStr">
@@ -9795,7 +9836,7 @@
           <t>約 3000×1150</t>
         </is>
       </c>
-      <c r="G9" s="27" t="n">
+      <c r="G9" s="31" t="n">
         <v>3</v>
       </c>
       <c r="H9" s="22" t="inlineStr">
@@ -9803,15 +9844,15 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I9" s="28" t="inlineStr">
+      <c r="I9" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="J9" s="29" t="inlineStr"/>
+      <c r="J9" s="30" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="30" t="n">
+      <c r="A10" s="28" t="n">
         <v>6</v>
       </c>
       <c r="B10" s="23" t="inlineStr">
@@ -9839,7 +9880,7 @@
           <t>約 3000×1150</t>
         </is>
       </c>
-      <c r="G10" s="30" t="n">
+      <c r="G10" s="28" t="n">
         <v>3</v>
       </c>
       <c r="H10" s="23" t="inlineStr">
@@ -9847,15 +9888,15 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I10" s="28" t="inlineStr">
+      <c r="I10" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="J10" s="29" t="inlineStr"/>
+      <c r="J10" s="30" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="27" t="n">
+      <c r="A11" s="31" t="n">
         <v>7</v>
       </c>
       <c r="B11" s="22" t="inlineStr">
@@ -9883,7 +9924,7 @@
           <t>約 3000×1150</t>
         </is>
       </c>
-      <c r="G11" s="27" t="n">
+      <c r="G11" s="31" t="n">
         <v>4</v>
       </c>
       <c r="H11" s="22" t="inlineStr">
@@ -9891,15 +9932,15 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I11" s="28" t="inlineStr">
+      <c r="I11" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="J11" s="29" t="inlineStr"/>
+      <c r="J11" s="30" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="30" t="n">
+      <c r="A12" s="28" t="n">
         <v>8</v>
       </c>
       <c r="B12" s="23" t="inlineStr">
@@ -9927,7 +9968,7 @@
           <t>約 3000×1150</t>
         </is>
       </c>
-      <c r="G12" s="30" t="n">
+      <c r="G12" s="28" t="n">
         <v>4</v>
       </c>
       <c r="H12" s="23" t="inlineStr">
@@ -9935,15 +9976,15 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I12" s="28" t="inlineStr">
+      <c r="I12" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="J12" s="29" t="inlineStr"/>
+      <c r="J12" s="30" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="27" t="n">
+      <c r="A13" s="31" t="n">
         <v>9</v>
       </c>
       <c r="B13" s="22" t="inlineStr">
@@ -9971,7 +10012,7 @@
           <t>約 3000×1150</t>
         </is>
       </c>
-      <c r="G13" s="27" t="n">
+      <c r="G13" s="31" t="n">
         <v>4</v>
       </c>
       <c r="H13" s="22" t="inlineStr">
@@ -9979,15 +10020,15 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I13" s="28" t="inlineStr">
+      <c r="I13" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="J13" s="29" t="inlineStr"/>
+      <c r="J13" s="30" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="30" t="n">
+      <c r="A14" s="28" t="n">
         <v>10</v>
       </c>
       <c r="B14" s="23" t="inlineStr">
@@ -10015,7 +10056,7 @@
           <t>約 3000×1150</t>
         </is>
       </c>
-      <c r="G14" s="30" t="n">
+      <c r="G14" s="28" t="n">
         <v>5</v>
       </c>
       <c r="H14" s="23" t="inlineStr">
@@ -10023,19 +10064,19 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="I14" s="33" t="inlineStr">
+      <c r="I14" s="34" t="inlineStr">
         <is>
           <t>選配</t>
         </is>
       </c>
-      <c r="J14" s="29" t="inlineStr">
+      <c r="J14" s="30" t="inlineStr">
         <is>
           <t>之後新增日本白天活動的動物時再畫</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="27" t="n">
+      <c r="A15" s="31" t="n">
         <v>11</v>
       </c>
       <c r="B15" s="22" t="inlineStr">
@@ -10063,7 +10104,7 @@
           <t>約 3000×1150</t>
         </is>
       </c>
-      <c r="G15" s="27" t="n">
+      <c r="G15" s="31" t="n">
         <v>6</v>
       </c>
       <c r="H15" s="22" t="inlineStr">
@@ -10071,19 +10112,19 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="I15" s="28" t="inlineStr">
+      <c r="I15" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="J15" s="29" t="inlineStr">
+      <c r="J15" s="30" t="inlineStr">
         <is>
           <t>新增物種用（黑面琵鷺）</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="30" t="n">
+      <c r="A16" s="28" t="n">
         <v>12</v>
       </c>
       <c r="B16" s="23" t="inlineStr">
@@ -10111,7 +10152,7 @@
           <t>約 3000×1150</t>
         </is>
       </c>
-      <c r="G16" s="30" t="n">
+      <c r="G16" s="28" t="n">
         <v>6</v>
       </c>
       <c r="H16" s="23" t="inlineStr">
@@ -10119,19 +10160,19 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="I16" s="28" t="inlineStr">
+      <c r="I16" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="J16" s="29" t="inlineStr">
+      <c r="J16" s="30" t="inlineStr">
         <is>
           <t>新增物種用；要看得到水下（綠蠵龜、中華白海豚）</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="27" t="n">
+      <c r="A17" s="31" t="n">
         <v>13</v>
       </c>
       <c r="B17" s="22" t="inlineStr">
@@ -10159,7 +10200,7 @@
           <t>約 3000×1150</t>
         </is>
       </c>
-      <c r="G17" s="27" t="n">
+      <c r="G17" s="31" t="n">
         <v>6</v>
       </c>
       <c r="H17" s="22" t="inlineStr">
@@ -10167,19 +10208,19 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="I17" s="28" t="inlineStr">
+      <c r="I17" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="J17" s="29" t="inlineStr">
+      <c r="J17" s="30" t="inlineStr">
         <is>
           <t>新增物種用（櫻花鉤吻鮭）</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="30" t="n">
+      <c r="A18" s="28" t="n">
         <v>14</v>
       </c>
       <c r="B18" s="23" t="inlineStr">
@@ -10207,7 +10248,7 @@
           <t>約 3000×1150</t>
         </is>
       </c>
-      <c r="G18" s="30" t="n">
+      <c r="G18" s="28" t="n">
         <v>5</v>
       </c>
       <c r="H18" s="23" t="inlineStr">
@@ -10215,19 +10256,19 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="I18" s="33" t="inlineStr">
+      <c r="I18" s="34" t="inlineStr">
         <is>
           <t>選配</t>
         </is>
       </c>
-      <c r="J18" s="29" t="inlineStr">
+      <c r="J18" s="30" t="inlineStr">
         <is>
           <t>先用白天版加暖色調</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="27" t="n">
+      <c r="A19" s="31" t="n">
         <v>15</v>
       </c>
       <c r="B19" s="22" t="inlineStr">
@@ -10255,7 +10296,7 @@
           <t>約 3000×1150</t>
         </is>
       </c>
-      <c r="G19" s="27" t="n">
+      <c r="G19" s="31" t="n">
         <v>5</v>
       </c>
       <c r="H19" s="22" t="inlineStr">
@@ -10263,19 +10304,19 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="I19" s="33" t="inlineStr">
+      <c r="I19" s="34" t="inlineStr">
         <is>
           <t>選配</t>
         </is>
       </c>
-      <c r="J19" s="29" t="inlineStr">
+      <c r="J19" s="30" t="inlineStr">
         <is>
           <t>先用白天版加暖色調</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="30" t="n">
+      <c r="A20" s="28" t="n">
         <v>16</v>
       </c>
       <c r="B20" s="23" t="inlineStr">
@@ -10303,7 +10344,7 @@
           <t>約 3000×1150</t>
         </is>
       </c>
-      <c r="G20" s="30" t="n">
+      <c r="G20" s="28" t="n">
         <v>5</v>
       </c>
       <c r="H20" s="23" t="inlineStr">
@@ -10311,12 +10352,12 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="I20" s="33" t="inlineStr">
+      <c r="I20" s="34" t="inlineStr">
         <is>
           <t>選配</t>
         </is>
       </c>
-      <c r="J20" s="29" t="inlineStr">
+      <c r="J20" s="30" t="inlineStr">
         <is>
           <t>先用白天版加暖色調</t>
         </is>
@@ -10634,7 +10675,7 @@
           <t>台灣・棲光森林</t>
         </is>
       </c>
-      <c r="B5" s="27" t="n">
+      <c r="B5" s="31" t="n">
         <v>0</v>
       </c>
       <c r="C5" s="22" t="inlineStr">
@@ -10663,12 +10704,12 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="I5" s="32" t="inlineStr">
+      <c r="I5" s="33" t="inlineStr">
         <is>
           <t>暫代</t>
         </is>
       </c>
-      <c r="J5" s="29" t="inlineStr">
+      <c r="J5" s="30" t="inlineStr">
         <is>
           <t>目前用 forest.webp（1167×1347，GPT 畫的完成狀態）</t>
         </is>
@@ -10680,7 +10721,7 @@
           <t>台灣・棲光森林</t>
         </is>
       </c>
-      <c r="B6" s="30" t="n">
+      <c r="B6" s="28" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="23" t="inlineStr">
@@ -10693,7 +10734,7 @@
           <t>清出林間步道</t>
         </is>
       </c>
-      <c r="E6" s="30" t="n">
+      <c r="E6" s="28" t="n">
         <v>10</v>
       </c>
       <c r="F6" s="23" t="inlineStr">
@@ -10711,12 +10752,12 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="I6" s="28" t="inlineStr">
+      <c r="I6" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="J6" s="29" t="inlineStr"/>
+      <c r="J6" s="30" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="22" t="inlineStr">
@@ -10724,7 +10765,7 @@
           <t>台灣・棲光森林</t>
         </is>
       </c>
-      <c r="B7" s="27" t="n">
+      <c r="B7" s="31" t="n">
         <v>2</v>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -10737,7 +10778,7 @@
           <t>種回原生樹苗</t>
         </is>
       </c>
-      <c r="E7" s="27" t="n">
+      <c r="E7" s="31" t="n">
         <v>430</v>
       </c>
       <c r="F7" s="22" t="inlineStr">
@@ -10755,12 +10796,12 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="I7" s="28" t="inlineStr">
+      <c r="I7" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="J7" s="29" t="inlineStr"/>
+      <c r="J7" s="30" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="23" t="inlineStr">
@@ -10768,7 +10809,7 @@
           <t>台灣・棲光森林</t>
         </is>
       </c>
-      <c r="B8" s="30" t="n">
+      <c r="B8" s="28" t="n">
         <v>3</v>
       </c>
       <c r="C8" s="23" t="inlineStr">
@@ -10781,7 +10822,7 @@
           <t>修好森林觀察小屋</t>
         </is>
       </c>
-      <c r="E8" s="30" t="n">
+      <c r="E8" s="28" t="n">
         <v>1300</v>
       </c>
       <c r="F8" s="23" t="inlineStr">
@@ -10799,12 +10840,12 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="I8" s="28" t="inlineStr">
+      <c r="I8" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="J8" s="29" t="inlineStr"/>
+      <c r="J8" s="30" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="22" t="inlineStr">
@@ -10812,7 +10853,7 @@
           <t>台灣・棲光森林</t>
         </is>
       </c>
-      <c r="B9" s="27" t="n">
+      <c r="B9" s="31" t="n">
         <v>4</v>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -10825,7 +10866,7 @@
           <t>恢復林下草叢</t>
         </is>
       </c>
-      <c r="E9" s="27" t="n">
+      <c r="E9" s="31" t="n">
         <v>1850</v>
       </c>
       <c r="F9" s="22" t="inlineStr">
@@ -10843,12 +10884,12 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="I9" s="28" t="inlineStr">
+      <c r="I9" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="J9" s="29" t="inlineStr"/>
+      <c r="J9" s="30" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="23" t="inlineStr">
@@ -10856,7 +10897,7 @@
           <t>台灣・棲光森林</t>
         </is>
       </c>
-      <c r="B10" s="30" t="n">
+      <c r="B10" s="28" t="n">
         <v>5</v>
       </c>
       <c r="C10" s="23" t="inlineStr">
@@ -10869,7 +10910,7 @@
           <t>架設生態廊道</t>
         </is>
       </c>
-      <c r="E10" s="30" t="n">
+      <c r="E10" s="28" t="n">
         <v>2150</v>
       </c>
       <c r="F10" s="23" t="inlineStr">
@@ -10887,12 +10928,12 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="I10" s="28" t="inlineStr">
+      <c r="I10" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="J10" s="29" t="inlineStr"/>
+      <c r="J10" s="30" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="22" t="inlineStr">
@@ -10900,7 +10941,7 @@
           <t>台灣・棲光森林</t>
         </is>
       </c>
-      <c r="B11" s="27" t="n">
+      <c r="B11" s="31" t="n">
         <v>6</v>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -10913,7 +10954,7 @@
           <t>整理森林水源地</t>
         </is>
       </c>
-      <c r="E11" s="27" t="n">
+      <c r="E11" s="31" t="n">
         <v>2450</v>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -10931,12 +10972,12 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="I11" s="28" t="inlineStr">
+      <c r="I11" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="J11" s="29" t="inlineStr"/>
+      <c r="J11" s="30" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="23" t="inlineStr">
@@ -10944,7 +10985,7 @@
           <t>台灣・棲光森林</t>
         </is>
       </c>
-      <c r="B12" s="30" t="n">
+      <c r="B12" s="28" t="n">
         <v>7</v>
       </c>
       <c r="C12" s="23" t="inlineStr">
@@ -10957,7 +10998,7 @@
           <t>搭建樹冠步道</t>
         </is>
       </c>
-      <c r="E12" s="30" t="n">
+      <c r="E12" s="28" t="n">
         <v>2600</v>
       </c>
       <c r="F12" s="23" t="inlineStr">
@@ -10975,12 +11016,12 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="I12" s="28" t="inlineStr">
+      <c r="I12" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="J12" s="29" t="inlineStr"/>
+      <c r="J12" s="30" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="22" t="inlineStr">
@@ -10988,7 +11029,7 @@
           <t>台灣・棲光森林</t>
         </is>
       </c>
-      <c r="B13" s="27" t="n">
+      <c r="B13" s="31" t="n">
         <v>8</v>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -11001,7 +11042,7 @@
           <t>設立保育救傷站</t>
         </is>
       </c>
-      <c r="E13" s="27" t="n">
+      <c r="E13" s="31" t="n">
         <v>2700</v>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -11019,12 +11060,12 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="I13" s="28" t="inlineStr">
+      <c r="I13" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="J13" s="29" t="inlineStr"/>
+      <c r="J13" s="30" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="23" t="inlineStr">
@@ -11032,7 +11073,7 @@
           <t>日本・里山</t>
         </is>
       </c>
-      <c r="B14" s="30" t="n">
+      <c r="B14" s="28" t="n">
         <v>0</v>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -11061,12 +11102,12 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I14" s="28" t="inlineStr">
+      <c r="I14" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="J14" s="29" t="inlineStr"/>
+      <c r="J14" s="30" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="22" t="inlineStr">
@@ -11074,7 +11115,7 @@
           <t>日本・里山</t>
         </is>
       </c>
-      <c r="B15" s="27" t="n">
+      <c r="B15" s="31" t="n">
         <v>1</v>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -11087,7 +11128,7 @@
           <t>清出杉林小徑</t>
         </is>
       </c>
-      <c r="E15" s="27" t="n">
+      <c r="E15" s="31" t="n">
         <v>300</v>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -11105,12 +11146,12 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I15" s="28" t="inlineStr">
+      <c r="I15" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="J15" s="29" t="inlineStr"/>
+      <c r="J15" s="30" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="23" t="inlineStr">
@@ -11118,7 +11159,7 @@
           <t>日本・里山</t>
         </is>
       </c>
-      <c r="B16" s="30" t="n">
+      <c r="B16" s="28" t="n">
         <v>2</v>
       </c>
       <c r="C16" s="23" t="inlineStr">
@@ -11131,7 +11172,7 @@
           <t>復原里山梯田</t>
         </is>
       </c>
-      <c r="E16" s="30" t="n">
+      <c r="E16" s="28" t="n">
         <v>800</v>
       </c>
       <c r="F16" s="23" t="inlineStr">
@@ -11149,12 +11190,12 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I16" s="28" t="inlineStr">
+      <c r="I16" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="J16" s="29" t="inlineStr"/>
+      <c r="J16" s="30" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="22" t="inlineStr">
@@ -11162,7 +11203,7 @@
           <t>日本・里山</t>
         </is>
       </c>
-      <c r="B17" s="27" t="n">
+      <c r="B17" s="31" t="n">
         <v>3</v>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -11175,7 +11216,7 @@
           <t>修好山中小屋</t>
         </is>
       </c>
-      <c r="E17" s="27" t="n">
+      <c r="E17" s="31" t="n">
         <v>1100</v>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -11193,12 +11234,12 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I17" s="28" t="inlineStr">
+      <c r="I17" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="J17" s="29" t="inlineStr"/>
+      <c r="J17" s="30" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="23" t="inlineStr">
@@ -11206,7 +11247,7 @@
           <t>日本・里山</t>
         </is>
       </c>
-      <c r="B18" s="30" t="n">
+      <c r="B18" s="28" t="n">
         <v>4</v>
       </c>
       <c r="C18" s="23" t="inlineStr">
@@ -11219,7 +11260,7 @@
           <t>疏伐過密的竹林</t>
         </is>
       </c>
-      <c r="E18" s="30" t="n">
+      <c r="E18" s="28" t="n">
         <v>1300</v>
       </c>
       <c r="F18" s="23" t="inlineStr">
@@ -11237,12 +11278,12 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I18" s="28" t="inlineStr">
+      <c r="I18" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="J18" s="29" t="inlineStr"/>
+      <c r="J18" s="30" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="22" t="inlineStr">
@@ -11250,7 +11291,7 @@
           <t>日本・里山</t>
         </is>
       </c>
-      <c r="B19" s="27" t="n">
+      <c r="B19" s="31" t="n">
         <v>5</v>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -11263,7 +11304,7 @@
           <t>恢復清澈溪流</t>
         </is>
       </c>
-      <c r="E19" s="27" t="n">
+      <c r="E19" s="31" t="n">
         <v>1500</v>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -11281,12 +11322,12 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I19" s="28" t="inlineStr">
+      <c r="I19" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="J19" s="29" t="inlineStr"/>
+      <c r="J19" s="30" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="23" t="inlineStr">
@@ -11294,7 +11335,7 @@
           <t>日本・里山</t>
         </is>
       </c>
-      <c r="B20" s="30" t="n">
+      <c r="B20" s="28" t="n">
         <v>6</v>
       </c>
       <c r="C20" s="23" t="inlineStr">
@@ -11307,7 +11348,7 @@
           <t>設立野生動物保護站</t>
         </is>
       </c>
-      <c r="E20" s="30" t="n">
+      <c r="E20" s="28" t="n">
         <v>1600</v>
       </c>
       <c r="F20" s="23" t="inlineStr">
@@ -11325,12 +11366,12 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I20" s="28" t="inlineStr">
+      <c r="I20" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="J20" s="29" t="inlineStr"/>
+      <c r="J20" s="30" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:J20"/>

--- a/docs/美術清單.xlsx
+++ b/docs/美術清單.xlsx
@@ -7996,7 +7996,7 @@
       </c>
       <c r="F22" s="23" t="inlineStr">
         <is>
-          <t>拿掉近側前鰭</t>
+          <t>拿掉近側前鰭；頭轉向鏡頭</t>
         </is>
       </c>
       <c r="G22" s="23" t="inlineStr">
@@ -8053,7 +8053,7 @@
       </c>
       <c r="F23" s="22" t="inlineStr">
         <is>
-          <t>拿掉胸鰭</t>
+          <t>拿掉胸鰭；頭轉向鏡頭</t>
         </is>
       </c>
       <c r="G23" s="22" t="inlineStr">
@@ -8167,7 +8167,7 @@
       </c>
       <c r="F25" s="22" t="inlineStr">
         <is>
-          <t>拿掉近側後腳；閉眼</t>
+          <t>拿掉近側後腳；閉眼；頭轉向鏡頭</t>
         </is>
       </c>
       <c r="G25" s="22" t="inlineStr">
@@ -8224,7 +8224,7 @@
       </c>
       <c r="F26" s="23" t="inlineStr">
         <is>
-          <t>—（另畫倒掛、飛行姿勢）</t>
+          <t>頭轉向鏡頭（另畫倒掛、飛行姿勢）</t>
         </is>
       </c>
       <c r="G26" s="23" t="inlineStr">
@@ -9339,7 +9339,7 @@
       </c>
       <c r="E17" s="22" t="inlineStr">
         <is>
-          <t>拿掉近側前鰭</t>
+          <t>拿掉近側前鰭；頭轉向鏡頭</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -9381,7 +9381,7 @@
       </c>
       <c r="E18" s="23" t="inlineStr">
         <is>
-          <t>拿掉胸鰭</t>
+          <t>拿掉胸鰭；頭轉向鏡頭</t>
         </is>
       </c>
       <c r="F18" s="23" t="inlineStr">
@@ -9465,7 +9465,7 @@
       </c>
       <c r="E20" s="23" t="inlineStr">
         <is>
-          <t>拿掉近側後腳；閉眼</t>
+          <t>拿掉近側後腳；閉眼；頭轉向鏡頭</t>
         </is>
       </c>
       <c r="F20" s="23" t="inlineStr">
@@ -9507,7 +9507,7 @@
       </c>
       <c r="E21" s="22" t="inlineStr">
         <is>
-          <t>—（另畫倒掛、飛行姿勢）</t>
+          <t>頭轉向鏡頭（另畫倒掛、飛行姿勢）</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">

--- a/docs/美術清單.xlsx
+++ b/docs/美術清單.xlsx
@@ -27,9 +27,9 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'共通規格'!$A$4:$C$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'動物尺寸'!$A$4:$E$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'A 動物主圖'!$A$4:$R$35</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'B 動物動態'!$A$4:$M$35</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'B-1 體型模板'!$A$4:$H$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'A 動物主圖'!$A$4:$R$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'B 動物動態'!$A$4:$M$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'B-1 體型模板'!$A$4:$H$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'C 望遠鏡全景'!$A$4:$J$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'C-1 全景規格'!$A$4:$C$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'D 小島場景'!$A$4:$J$20</definedName>
@@ -758,19 +758,19 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>29 種動物（台灣 21、日本 8），每個成長階段 1 張（正側面）</t>
+          <t>40 種動物（台灣 21、日本 19），每個成長階段 1 張（正側面）</t>
         </is>
       </c>
       <c r="C5" s="5">
-        <f>COUNTA('A 動物主圖'!$B$5:$B$35)</f>
+        <f>COUNTA('A 動物主圖'!$B$5:$B$46)</f>
         <v/>
       </c>
       <c r="D5" s="5">
-        <f>SUM('A 動物主圖'!$F$5:$F$35)</f>
+        <f>SUM('A 動物主圖'!$F$5:$F$46)</f>
         <v/>
       </c>
       <c r="E5" s="5">
-        <f>COUNTIF('A 動物主圖'!$Q$5:$Q$35,"已完成")</f>
+        <f>COUNTIF('A 動物主圖'!$Q$5:$Q$46,"已完成")</f>
         <v/>
       </c>
       <c r="F5" s="6">
@@ -800,15 +800,15 @@
         </is>
       </c>
       <c r="C6" s="5">
-        <f>COUNTA('B 動物動態'!$B$5:$B$35)</f>
+        <f>COUNTA('B 動物動態'!$B$5:$B$46)</f>
         <v/>
       </c>
       <c r="D6" s="5">
-        <f>SUM('B 動物動態'!$E$5:$E$35)</f>
+        <f>SUM('B 動物動態'!$E$5:$E$46)</f>
         <v/>
       </c>
       <c r="E6" s="5">
-        <f>COUNTIF('B 動物動態'!$L$5:$L$35,"已完成")</f>
+        <f>COUNTIF('B 動物動態'!$L$5:$L$46,"已完成")</f>
         <v/>
       </c>
       <c r="F6" s="6">
@@ -4324,7 +4324,7 @@
       </c>
       <c r="C17" s="26" t="inlineStr">
         <is>
-          <t>旗艦機推近也清楚；每隻容量約多 1.5～2 倍，29 隻約多 3～4 MB。主圖是 1024，可以直接重新輸出，不用重畫。</t>
+          <t>旗艦機推近也清楚；每隻容量約多 1.5～2 倍，40 隻約多 4～6 MB。主圖是 1024，可以直接重新輸出，不用重畫。</t>
         </is>
       </c>
     </row>
@@ -4361,7 +4361,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R35"/>
+  <dimension ref="A1:R46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -6266,7 +6266,7 @@
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="27" t="inlineStr">
         <is>
-          <t>日本（8 種）</t>
+          <t>日本（19 種）</t>
         </is>
       </c>
     </row>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="L28" s="23" t="inlineStr">
         <is>
-          <t>特別天然紀念物</t>
+          <t>絕滅危懼 IA 類（CR）｜特別天然紀念物・國內稀少種</t>
         </is>
       </c>
       <c r="M28" s="23" t="inlineStr">
@@ -6350,7 +6350,11 @@
           <t>未開始</t>
         </is>
       </c>
-      <c r="R28" s="30" t="inlineStr"/>
+      <c r="R28" s="30" t="inlineStr">
+        <is>
+          <t>紅色名錄 2020</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="31" t="n">
@@ -6358,12 +6362,12 @@
       </c>
       <c r="B29" s="22" t="inlineStr">
         <is>
-          <t>okinawa_woodpecker</t>
+          <t>tsushima_cat</t>
         </is>
       </c>
       <c r="C29" s="22" t="inlineStr">
         <is>
-          <t>野口啄木鳥</t>
+          <t>對馬山貓</t>
         </is>
       </c>
       <c r="D29" s="22" t="inlineStr">
@@ -6373,7 +6377,7 @@
       </c>
       <c r="E29" s="22" t="inlineStr">
         <is>
-          <t>鳥</t>
+          <t>貓科</t>
         </is>
       </c>
       <c r="F29" s="31" t="n">
@@ -6381,37 +6385,37 @@
       </c>
       <c r="G29" s="22" t="inlineStr">
         <is>
-          <t>雛鳥／幼鳥／成鳥</t>
+          <t>幼年／亞成年／成年</t>
         </is>
       </c>
       <c r="H29" s="22" t="inlineStr">
         <is>
-          <t>全身深紅褐色、頭頂紅色（雄鳥）、啄木鳥姿態</t>
+          <t>對馬的石虎：外型近似石虎、額頭白紋，毛色略深</t>
         </is>
       </c>
       <c r="I29" s="22" t="inlineStr">
         <is>
-          <t>南方島嶼</t>
+          <t>里山</t>
         </is>
       </c>
       <c r="J29" s="22" t="inlineStr">
         <is>
-          <t>白天</t>
+          <t>夜晚</t>
         </is>
       </c>
       <c r="K29" s="22" t="inlineStr">
         <is>
-          <t>遠處飛 → 停到倒木上</t>
+          <t>從遠處走過來</t>
         </is>
       </c>
       <c r="L29" s="22" t="inlineStr">
         <is>
-          <t>特別天然紀念物</t>
+          <t>絕滅危懼 IA 類（CR）｜天然紀念物・國內稀少種</t>
         </is>
       </c>
       <c r="M29" s="22" t="inlineStr">
         <is>
-          <t>一開始就能找</t>
+          <t>修好「疏伐過密的竹林」</t>
         </is>
       </c>
       <c r="N29" s="31" t="n">
@@ -6424,7 +6428,7 @@
       </c>
       <c r="P29" s="22" t="inlineStr">
         <is>
-          <t>okinawa_woodpecker-0/1/2.png</t>
+          <t>tsushima_cat-0/1/2.png</t>
         </is>
       </c>
       <c r="Q29" s="29" t="inlineStr">
@@ -6432,7 +6436,11 @@
           <t>未開始</t>
         </is>
       </c>
-      <c r="R29" s="30" t="inlineStr"/>
+      <c r="R29" s="30" t="inlineStr">
+        <is>
+          <t>紅色名錄 2020</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="28" t="n">
@@ -6440,12 +6448,12 @@
       </c>
       <c r="B30" s="23" t="inlineStr">
         <is>
-          <t>japanese_serow</t>
+          <t>amami_rabbit</t>
         </is>
       </c>
       <c r="C30" s="23" t="inlineStr">
         <is>
-          <t>日本鬣羚</t>
+          <t>奄美黑兔</t>
         </is>
       </c>
       <c r="D30" s="23" t="inlineStr">
@@ -6455,58 +6463,58 @@
       </c>
       <c r="E30" s="23" t="inlineStr">
         <is>
-          <t>山羊</t>
+          <t>兔</t>
         </is>
       </c>
       <c r="F30" s="28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G30" s="23" t="inlineStr">
         <is>
-          <t>幼年／亞成年／成年</t>
+          <t>只有一種樣式</t>
         </is>
       </c>
       <c r="H30" s="23" t="inlineStr">
         <is>
-          <t>灰黑色、頸部有鬃毛、短角、常站在岩石上</t>
+          <t>深褐色短毛、耳朵和腳都很短、圓胖身體（奄美大島、德之島特有）</t>
         </is>
       </c>
       <c r="I30" s="23" t="inlineStr">
         <is>
-          <t>山地森林</t>
+          <t>南方島嶼</t>
         </is>
       </c>
       <c r="J30" s="23" t="inlineStr">
         <is>
-          <t>晨昏</t>
+          <t>夜晚</t>
         </is>
       </c>
       <c r="K30" s="23" t="inlineStr">
         <is>
-          <t>從遠處走過來</t>
+          <t>夜裡從遠處跳過來</t>
         </is>
       </c>
       <c r="L30" s="23" t="inlineStr">
         <is>
-          <t>特別天然紀念物</t>
+          <t>絕滅危懼 IB 類（EN）｜特別天然紀念物・國內稀少種</t>
         </is>
       </c>
       <c r="M30" s="23" t="inlineStr">
         <is>
-          <t>修好「清出杉林小徑」</t>
+          <t>待定（新物種）</t>
         </is>
       </c>
       <c r="N30" s="28" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O30" s="23" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="P30" s="23" t="inlineStr">
         <is>
-          <t>japanese_serow-0/1/2.png</t>
+          <t>amami_rabbit-2.png</t>
         </is>
       </c>
       <c r="Q30" s="29" t="inlineStr">
@@ -6514,7 +6522,11 @@
           <t>未開始</t>
         </is>
       </c>
-      <c r="R30" s="30" t="inlineStr"/>
+      <c r="R30" s="30" t="inlineStr">
+        <is>
+          <t>新增；紅色名錄 2020</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="31" t="n">
@@ -6522,12 +6534,12 @@
       </c>
       <c r="B31" s="22" t="inlineStr">
         <is>
-          <t>ptarmigan</t>
+          <t>japanese_serow</t>
         </is>
       </c>
       <c r="C31" s="22" t="inlineStr">
         <is>
-          <t>雷鳥</t>
+          <t>日本鬣羚</t>
         </is>
       </c>
       <c r="D31" s="22" t="inlineStr">
@@ -6537,7 +6549,7 @@
       </c>
       <c r="E31" s="22" t="inlineStr">
         <is>
-          <t>雉雞</t>
+          <t>山羊</t>
         </is>
       </c>
       <c r="F31" s="31" t="n">
@@ -6545,22 +6557,22 @@
       </c>
       <c r="G31" s="22" t="inlineStr">
         <is>
-          <t>雛鳥／幼鳥／成鳥</t>
+          <t>幼年／亞成年／成年</t>
         </is>
       </c>
       <c r="H31" s="22" t="inlineStr">
         <is>
-          <t>夏羽褐色斑駁、眼上紅色肉冠、腳有羽毛（冬羽全白可之後再做）</t>
+          <t>灰黑色、頸部有鬃毛、短角、常站在岩石上</t>
         </is>
       </c>
       <c r="I31" s="22" t="inlineStr">
         <is>
-          <t>高山</t>
+          <t>山地森林</t>
         </is>
       </c>
       <c r="J31" s="22" t="inlineStr">
         <is>
-          <t>白天</t>
+          <t>晨昏</t>
         </is>
       </c>
       <c r="K31" s="22" t="inlineStr">
@@ -6570,12 +6582,12 @@
       </c>
       <c r="L31" s="22" t="inlineStr">
         <is>
-          <t>特別天然紀念物</t>
+          <t>紅色名錄未列｜特別天然紀念物</t>
         </is>
       </c>
       <c r="M31" s="22" t="inlineStr">
         <is>
-          <t>修好「復原里山梯田」</t>
+          <t>修好「清出杉林小徑」</t>
         </is>
       </c>
       <c r="N31" s="31" t="n">
@@ -6588,7 +6600,7 @@
       </c>
       <c r="P31" s="22" t="inlineStr">
         <is>
-          <t>ptarmigan-0/1/2.png</t>
+          <t>japanese_serow-0/1/2.png</t>
         </is>
       </c>
       <c r="Q31" s="29" t="inlineStr">
@@ -6596,7 +6608,11 @@
           <t>未開始</t>
         </is>
       </c>
-      <c r="R31" s="30" t="inlineStr"/>
+      <c r="R31" s="30" t="inlineStr">
+        <is>
+          <t>全國未列入紅色名錄，但是代表性的特別天然紀念物</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="28" t="n">
@@ -6604,12 +6620,12 @@
       </c>
       <c r="B32" s="23" t="inlineStr">
         <is>
-          <t>blakiston_owl</t>
+          <t>bonin_flying_fox</t>
         </is>
       </c>
       <c r="C32" s="23" t="inlineStr">
         <is>
-          <t>毛腿魚鴞</t>
+          <t>小笠原狐蝠</t>
         </is>
       </c>
       <c r="D32" s="23" t="inlineStr">
@@ -6619,25 +6635,25 @@
       </c>
       <c r="E32" s="23" t="inlineStr">
         <is>
-          <t>貓頭鷹</t>
+          <t>蝙蝠</t>
         </is>
       </c>
       <c r="F32" s="28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G32" s="23" t="inlineStr">
         <is>
-          <t>雛鳥／幼鳥／成鳥</t>
+          <t>只有一種樣式</t>
         </is>
       </c>
       <c r="H32" s="23" t="inlineStr">
         <is>
-          <t>世界最大的貓頭鷹之一、褐色斑紋、寬大耳羽、黃眼</t>
+          <t>大型蝙蝠、全身深褐、頸部帶銀灰色毛、黑色膜翼（小笠原特有）</t>
         </is>
       </c>
       <c r="I32" s="23" t="inlineStr">
         <is>
-          <t>溪流</t>
+          <t>南方島嶼</t>
         </is>
       </c>
       <c r="J32" s="23" t="inlineStr">
@@ -6647,30 +6663,30 @@
       </c>
       <c r="K32" s="23" t="inlineStr">
         <is>
-          <t>夜裡先亮眼睛 → 停到倒木上</t>
+          <t>夜空中飛，最後倒掛在樹枝上（同猛禽盤旋）</t>
         </is>
       </c>
       <c r="L32" s="23" t="inlineStr">
         <is>
-          <t>國內稀少野生物種</t>
+          <t>絕滅危懼 IA 類（CR）｜天然紀念物・國內稀少種</t>
         </is>
       </c>
       <c r="M32" s="23" t="inlineStr">
         <is>
-          <t>修好「修好山中小屋」</t>
+          <t>待定（新物種）</t>
         </is>
       </c>
       <c r="N32" s="28" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O32" s="23" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="P32" s="23" t="inlineStr">
         <is>
-          <t>blakiston_owl-0/1/2.png</t>
+          <t>bonin_flying_fox-2.png</t>
         </is>
       </c>
       <c r="Q32" s="29" t="inlineStr">
@@ -6678,7 +6694,11 @@
           <t>未開始</t>
         </is>
       </c>
-      <c r="R32" s="30" t="inlineStr"/>
+      <c r="R32" s="30" t="inlineStr">
+        <is>
+          <t>新增；紅色名錄 2020</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="31" t="n">
@@ -6686,12 +6706,12 @@
       </c>
       <c r="B33" s="22" t="inlineStr">
         <is>
-          <t>tsushima_cat</t>
+          <t>toki</t>
         </is>
       </c>
       <c r="C33" s="22" t="inlineStr">
         <is>
-          <t>對馬山貓</t>
+          <t>朱鷺</t>
         </is>
       </c>
       <c r="D33" s="22" t="inlineStr">
@@ -6701,20 +6721,20 @@
       </c>
       <c r="E33" s="22" t="inlineStr">
         <is>
-          <t>貓科</t>
+          <t>涉禽</t>
         </is>
       </c>
       <c r="F33" s="31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G33" s="22" t="inlineStr">
         <is>
-          <t>幼年／亞成年／成年</t>
+          <t>只有一種樣式</t>
         </is>
       </c>
       <c r="H33" s="22" t="inlineStr">
         <is>
-          <t>對馬的石虎：外型近似石虎、額頭白紋，毛色略深</t>
+          <t>白中帶淡粉紅（朱鷺色）的羽毛、紅色臉部裸皮、黑色下彎長嘴、後腦冠羽</t>
         </is>
       </c>
       <c r="I33" s="22" t="inlineStr">
@@ -6724,35 +6744,35 @@
       </c>
       <c r="J33" s="22" t="inlineStr">
         <is>
-          <t>夜晚</t>
+          <t>白天</t>
         </is>
       </c>
       <c r="K33" s="22" t="inlineStr">
         <is>
-          <t>從遠處走過來</t>
+          <t>從遠處涉水走過來</t>
         </is>
       </c>
       <c r="L33" s="22" t="inlineStr">
         <is>
-          <t>國內稀少野生物種</t>
+          <t>絕滅危懼 IB 類（EN）｜特別天然紀念物・國內稀少種</t>
         </is>
       </c>
       <c r="M33" s="22" t="inlineStr">
         <is>
-          <t>修好「疏伐過密的竹林」</t>
+          <t>待定（新物種）</t>
         </is>
       </c>
       <c r="N33" s="31" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O33" s="22" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="P33" s="22" t="inlineStr">
         <is>
-          <t>tsushima_cat-0/1/2.png</t>
+          <t>toki-2.png</t>
         </is>
       </c>
       <c r="Q33" s="29" t="inlineStr">
@@ -6760,7 +6780,11 @@
           <t>未開始</t>
         </is>
       </c>
-      <c r="R33" s="30" t="inlineStr"/>
+      <c r="R33" s="30" t="inlineStr">
+        <is>
+          <t>新增；第 5 次從 CR 降為 EN（佐渡野生約 576 隻）</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="28" t="n">
@@ -6768,12 +6792,12 @@
       </c>
       <c r="B34" s="23" t="inlineStr">
         <is>
-          <t>steller_eagle</t>
+          <t>red_crowned_crane</t>
         </is>
       </c>
       <c r="C34" s="23" t="inlineStr">
         <is>
-          <t>虎頭海鵰</t>
+          <t>丹頂鶴</t>
         </is>
       </c>
       <c r="D34" s="23" t="inlineStr">
@@ -6783,25 +6807,25 @@
       </c>
       <c r="E34" s="23" t="inlineStr">
         <is>
-          <t>猛禽</t>
+          <t>涉禽</t>
         </is>
       </c>
       <c r="F34" s="28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G34" s="23" t="inlineStr">
         <is>
-          <t>雛鳥／幼鳥／成鳥</t>
+          <t>只有一種樣式</t>
         </is>
       </c>
       <c r="H34" s="23" t="inlineStr">
         <is>
-          <t>巨大的橘黃色嘴、深褐色身體、白色肩羽與白尾</t>
+          <t>白色身體、頭頂紅色、黑色頸部與次級飛羽、長腳（北海道釧路濕原）</t>
         </is>
       </c>
       <c r="I34" s="23" t="inlineStr">
         <is>
-          <t>溪流</t>
+          <t>濕地河口</t>
         </is>
       </c>
       <c r="J34" s="23" t="inlineStr">
@@ -6811,30 +6835,30 @@
       </c>
       <c r="K34" s="23" t="inlineStr">
         <is>
-          <t>天空盤旋 → 降落</t>
+          <t>從遠處涉水走過來</t>
         </is>
       </c>
       <c r="L34" s="23" t="inlineStr">
         <is>
-          <t>國內稀少野生物種</t>
+          <t>準絕滅危懼（NT）｜特別天然紀念物・國內稀少種</t>
         </is>
       </c>
       <c r="M34" s="23" t="inlineStr">
         <is>
-          <t>修好「恢復清澈溪流」</t>
+          <t>待定（新物種）</t>
         </is>
       </c>
       <c r="N34" s="28" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O34" s="23" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="P34" s="23" t="inlineStr">
         <is>
-          <t>steller_eagle-0/1/2.png</t>
+          <t>red_crowned_crane-2.png</t>
         </is>
       </c>
       <c r="Q34" s="29" t="inlineStr">
@@ -6842,7 +6866,11 @@
           <t>未開始</t>
         </is>
       </c>
-      <c r="R34" s="30" t="inlineStr"/>
+      <c r="R34" s="30" t="inlineStr">
+        <is>
+          <t>新增；第 5 次從 VU 降為 NT（已不算瀕危）</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="31" t="n">
@@ -6850,12 +6878,12 @@
       </c>
       <c r="B35" s="22" t="inlineStr">
         <is>
-          <t>moon_bear</t>
+          <t>oriental_stork</t>
         </is>
       </c>
       <c r="C35" s="22" t="inlineStr">
         <is>
-          <t>月輪熊</t>
+          <t>東方白鸛</t>
         </is>
       </c>
       <c r="D35" s="22" t="inlineStr">
@@ -6865,69 +6893,1011 @@
       </c>
       <c r="E35" s="22" t="inlineStr">
         <is>
-          <t>熊</t>
+          <t>涉禽</t>
         </is>
       </c>
       <c r="F35" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="22" t="inlineStr">
+        <is>
+          <t>只有一種樣式</t>
+        </is>
+      </c>
+      <c r="H35" s="22" t="inlineStr">
+        <is>
+          <t>白色身體、黑色飛羽、粗長的黑嘴、紅色眼周與腳（兵庫豐岡）</t>
+        </is>
+      </c>
+      <c r="I35" s="22" t="inlineStr">
+        <is>
+          <t>里山</t>
+        </is>
+      </c>
+      <c r="J35" s="22" t="inlineStr">
+        <is>
+          <t>白天</t>
+        </is>
+      </c>
+      <c r="K35" s="22" t="inlineStr">
+        <is>
+          <t>從遠處涉水走過來</t>
+        </is>
+      </c>
+      <c r="L35" s="22" t="inlineStr">
+        <is>
+          <t>絕滅危懼 IB 類（EN）｜特別天然紀念物・國內稀少種</t>
+        </is>
+      </c>
+      <c r="M35" s="22" t="inlineStr">
+        <is>
+          <t>待定（新物種）</t>
+        </is>
+      </c>
+      <c r="N35" s="31" t="n">
+        <v>6</v>
+      </c>
+      <c r="O35" s="22" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="P35" s="22" t="inlineStr">
+        <is>
+          <t>oriental_stork-2.png</t>
+        </is>
+      </c>
+      <c r="Q35" s="29" t="inlineStr">
+        <is>
+          <t>未開始</t>
+        </is>
+      </c>
+      <c r="R35" s="30" t="inlineStr">
+        <is>
+          <t>新增；第 5 次從 CR 降為 EN</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="28" t="n">
+        <v>9</v>
+      </c>
+      <c r="B36" s="23" t="inlineStr">
+        <is>
+          <t>okinawa_rail</t>
+        </is>
+      </c>
+      <c r="C36" s="23" t="inlineStr">
+        <is>
+          <t>山原秧雞</t>
+        </is>
+      </c>
+      <c r="D36" s="23" t="inlineStr">
+        <is>
+          <t>日本</t>
+        </is>
+      </c>
+      <c r="E36" s="23" t="inlineStr">
+        <is>
+          <t>雉雞</t>
+        </is>
+      </c>
+      <c r="F36" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" s="23" t="inlineStr">
+        <is>
+          <t>只有一種樣式</t>
+        </is>
+      </c>
+      <c r="H36" s="23" t="inlineStr">
+        <is>
+          <t>橄欖褐色背部、黑白橫紋的腹部、紅色的嘴和腳、不會飛</t>
+        </is>
+      </c>
+      <c r="I36" s="23" t="inlineStr">
+        <is>
+          <t>南方島嶼</t>
+        </is>
+      </c>
+      <c r="J36" s="23" t="inlineStr">
+        <is>
+          <t>晨昏</t>
+        </is>
+      </c>
+      <c r="K36" s="23" t="inlineStr">
+        <is>
+          <t>從遠處走過來</t>
+        </is>
+      </c>
+      <c r="L36" s="23" t="inlineStr">
+        <is>
+          <t>絕滅危懼 IA 類（CR）｜天然紀念物・國內稀少種</t>
+        </is>
+      </c>
+      <c r="M36" s="23" t="inlineStr">
+        <is>
+          <t>待定（新物種）</t>
+        </is>
+      </c>
+      <c r="N36" s="28" t="n">
+        <v>6</v>
+      </c>
+      <c r="O36" s="23" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="P36" s="23" t="inlineStr">
+        <is>
+          <t>okinawa_rail-2.png</t>
+        </is>
+      </c>
+      <c r="Q36" s="29" t="inlineStr">
+        <is>
+          <t>未開始</t>
+        </is>
+      </c>
+      <c r="R36" s="30" t="inlineStr">
+        <is>
+          <t>新增；沖繩北部特有、不會飛</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="31" t="n">
+        <v>10</v>
+      </c>
+      <c r="B37" s="22" t="inlineStr">
+        <is>
+          <t>okinawa_woodpecker</t>
+        </is>
+      </c>
+      <c r="C37" s="22" t="inlineStr">
+        <is>
+          <t>野口啄木鳥</t>
+        </is>
+      </c>
+      <c r="D37" s="22" t="inlineStr">
+        <is>
+          <t>日本</t>
+        </is>
+      </c>
+      <c r="E37" s="22" t="inlineStr">
+        <is>
+          <t>鳥</t>
+        </is>
+      </c>
+      <c r="F37" s="31" t="n">
         <v>3</v>
       </c>
-      <c r="G35" s="22" t="inlineStr">
-        <is>
-          <t>幼年／亞成年／成年</t>
-        </is>
-      </c>
-      <c r="H35" s="22" t="inlineStr">
-        <is>
-          <t>黑色毛、胸前月牙形白斑、圓耳</t>
-        </is>
-      </c>
-      <c r="I35" s="22" t="inlineStr">
-        <is>
-          <t>山地森林</t>
-        </is>
-      </c>
-      <c r="J35" s="22" t="inlineStr">
+      <c r="G37" s="22" t="inlineStr">
+        <is>
+          <t>雛鳥／幼鳥／成鳥</t>
+        </is>
+      </c>
+      <c r="H37" s="22" t="inlineStr">
+        <is>
+          <t>全身深紅褐色、頭頂紅色（雄鳥）、啄木鳥姿態</t>
+        </is>
+      </c>
+      <c r="I37" s="22" t="inlineStr">
+        <is>
+          <t>南方島嶼</t>
+        </is>
+      </c>
+      <c r="J37" s="22" t="inlineStr">
         <is>
           <t>白天</t>
         </is>
       </c>
-      <c r="K35" s="22" t="inlineStr">
+      <c r="K37" s="22" t="inlineStr">
+        <is>
+          <t>遠處飛 → 停到倒木上</t>
+        </is>
+      </c>
+      <c r="L37" s="22" t="inlineStr">
+        <is>
+          <t>絕滅危懼 IB 類（EN）｜特別天然紀念物・國內稀少種</t>
+        </is>
+      </c>
+      <c r="M37" s="22" t="inlineStr">
+        <is>
+          <t>一開始就能找</t>
+        </is>
+      </c>
+      <c r="N37" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="O37" s="22" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="P37" s="22" t="inlineStr">
+        <is>
+          <t>okinawa_woodpecker-0/1/2.png</t>
+        </is>
+      </c>
+      <c r="Q37" s="29" t="inlineStr">
+        <is>
+          <t>未開始</t>
+        </is>
+      </c>
+      <c r="R37" s="30" t="inlineStr">
+        <is>
+          <t>第 5 次從 CR 降為 EN</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="28" t="n">
+        <v>11</v>
+      </c>
+      <c r="B38" s="23" t="inlineStr">
+        <is>
+          <t>ptarmigan</t>
+        </is>
+      </c>
+      <c r="C38" s="23" t="inlineStr">
+        <is>
+          <t>雷鳥</t>
+        </is>
+      </c>
+      <c r="D38" s="23" t="inlineStr">
+        <is>
+          <t>日本</t>
+        </is>
+      </c>
+      <c r="E38" s="23" t="inlineStr">
+        <is>
+          <t>雉雞</t>
+        </is>
+      </c>
+      <c r="F38" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="G38" s="23" t="inlineStr">
+        <is>
+          <t>雛鳥／幼鳥／成鳥</t>
+        </is>
+      </c>
+      <c r="H38" s="23" t="inlineStr">
+        <is>
+          <t>夏羽褐色斑駁、眼上紅色肉冠、腳有羽毛（冬羽全白可之後再做）</t>
+        </is>
+      </c>
+      <c r="I38" s="23" t="inlineStr">
+        <is>
+          <t>高山</t>
+        </is>
+      </c>
+      <c r="J38" s="23" t="inlineStr">
+        <is>
+          <t>白天</t>
+        </is>
+      </c>
+      <c r="K38" s="23" t="inlineStr">
         <is>
           <t>從遠處走過來</t>
         </is>
       </c>
-      <c r="L35" s="22" t="inlineStr">
-        <is>
-          <t>地區族群瀕危</t>
-        </is>
-      </c>
-      <c r="M35" s="22" t="inlineStr">
-        <is>
-          <t>修好「設立野生動物保護站」</t>
-        </is>
-      </c>
-      <c r="N35" s="31" t="n">
+      <c r="L38" s="23" t="inlineStr">
+        <is>
+          <t>絕滅危懼 IB 類（EN）｜特別天然紀念物・國內稀少種</t>
+        </is>
+      </c>
+      <c r="M38" s="23" t="inlineStr">
+        <is>
+          <t>修好「復原里山梯田」</t>
+        </is>
+      </c>
+      <c r="N38" s="28" t="n">
         <v>3</v>
       </c>
-      <c r="O35" s="22" t="inlineStr">
+      <c r="O38" s="23" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="P35" s="22" t="inlineStr">
-        <is>
-          <t>moon_bear-0/1/2.png</t>
-        </is>
-      </c>
-      <c r="Q35" s="29" t="inlineStr">
+      <c r="P38" s="23" t="inlineStr">
+        <is>
+          <t>ptarmigan-0/1/2.png</t>
+        </is>
+      </c>
+      <c r="Q38" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="R35" s="30" t="inlineStr"/>
+      <c r="R38" s="30" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="31" t="n">
+        <v>12</v>
+      </c>
+      <c r="B39" s="22" t="inlineStr">
+        <is>
+          <t>blakiston_owl</t>
+        </is>
+      </c>
+      <c r="C39" s="22" t="inlineStr">
+        <is>
+          <t>毛腿魚鴞</t>
+        </is>
+      </c>
+      <c r="D39" s="22" t="inlineStr">
+        <is>
+          <t>日本</t>
+        </is>
+      </c>
+      <c r="E39" s="22" t="inlineStr">
+        <is>
+          <t>貓頭鷹</t>
+        </is>
+      </c>
+      <c r="F39" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="G39" s="22" t="inlineStr">
+        <is>
+          <t>雛鳥／幼鳥／成鳥</t>
+        </is>
+      </c>
+      <c r="H39" s="22" t="inlineStr">
+        <is>
+          <t>世界最大的貓頭鷹之一、褐色斑紋、寬大耳羽、黃眼</t>
+        </is>
+      </c>
+      <c r="I39" s="22" t="inlineStr">
+        <is>
+          <t>溪流</t>
+        </is>
+      </c>
+      <c r="J39" s="22" t="inlineStr">
+        <is>
+          <t>夜晚</t>
+        </is>
+      </c>
+      <c r="K39" s="22" t="inlineStr">
+        <is>
+          <t>夜裡先亮眼睛 → 停到倒木上</t>
+        </is>
+      </c>
+      <c r="L39" s="22" t="inlineStr">
+        <is>
+          <t>絕滅危懼 IB 類（EN）｜天然紀念物・國內稀少種</t>
+        </is>
+      </c>
+      <c r="M39" s="22" t="inlineStr">
+        <is>
+          <t>修好「修好山中小屋」</t>
+        </is>
+      </c>
+      <c r="N39" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="O39" s="22" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="P39" s="22" t="inlineStr">
+        <is>
+          <t>blakiston_owl-0/1/2.png</t>
+        </is>
+      </c>
+      <c r="Q39" s="29" t="inlineStr">
+        <is>
+          <t>未開始</t>
+        </is>
+      </c>
+      <c r="R39" s="30" t="inlineStr">
+        <is>
+          <t>第 5 次從 CR 降為 EN</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="28" t="n">
+        <v>13</v>
+      </c>
+      <c r="B40" s="23" t="inlineStr">
+        <is>
+          <t>steller_eagle</t>
+        </is>
+      </c>
+      <c r="C40" s="23" t="inlineStr">
+        <is>
+          <t>虎頭海鵰</t>
+        </is>
+      </c>
+      <c r="D40" s="23" t="inlineStr">
+        <is>
+          <t>日本</t>
+        </is>
+      </c>
+      <c r="E40" s="23" t="inlineStr">
+        <is>
+          <t>猛禽</t>
+        </is>
+      </c>
+      <c r="F40" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="G40" s="23" t="inlineStr">
+        <is>
+          <t>雛鳥／幼鳥／成鳥</t>
+        </is>
+      </c>
+      <c r="H40" s="23" t="inlineStr">
+        <is>
+          <t>巨大的橘黃色嘴、深褐色身體、白色肩羽與白尾</t>
+        </is>
+      </c>
+      <c r="I40" s="23" t="inlineStr">
+        <is>
+          <t>溪流</t>
+        </is>
+      </c>
+      <c r="J40" s="23" t="inlineStr">
+        <is>
+          <t>白天</t>
+        </is>
+      </c>
+      <c r="K40" s="23" t="inlineStr">
+        <is>
+          <t>天空盤旋 → 降落</t>
+        </is>
+      </c>
+      <c r="L40" s="23" t="inlineStr">
+        <is>
+          <t>絕滅危懼 II 類（VU）｜天然紀念物・國內稀少種</t>
+        </is>
+      </c>
+      <c r="M40" s="23" t="inlineStr">
+        <is>
+          <t>修好「恢復清澈溪流」</t>
+        </is>
+      </c>
+      <c r="N40" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="O40" s="23" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="P40" s="23" t="inlineStr">
+        <is>
+          <t>steller_eagle-0/1/2.png</t>
+        </is>
+      </c>
+      <c r="Q40" s="29" t="inlineStr">
+        <is>
+          <t>未開始</t>
+        </is>
+      </c>
+      <c r="R40" s="30" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="31" t="n">
+        <v>14</v>
+      </c>
+      <c r="B41" s="22" t="inlineStr">
+        <is>
+          <t>golden_eagle</t>
+        </is>
+      </c>
+      <c r="C41" s="22" t="inlineStr">
+        <is>
+          <t>金鵰</t>
+        </is>
+      </c>
+      <c r="D41" s="22" t="inlineStr">
+        <is>
+          <t>日本</t>
+        </is>
+      </c>
+      <c r="E41" s="22" t="inlineStr">
+        <is>
+          <t>猛禽</t>
+        </is>
+      </c>
+      <c r="F41" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" s="22" t="inlineStr">
+        <is>
+          <t>只有一種樣式</t>
+        </is>
+      </c>
+      <c r="H41" s="22" t="inlineStr">
+        <is>
+          <t>大型深褐色猛禽、後頸金黃色、腳有羽毛</t>
+        </is>
+      </c>
+      <c r="I41" s="22" t="inlineStr">
+        <is>
+          <t>高山</t>
+        </is>
+      </c>
+      <c r="J41" s="22" t="inlineStr">
+        <is>
+          <t>白天</t>
+        </is>
+      </c>
+      <c r="K41" s="22" t="inlineStr">
+        <is>
+          <t>天空盤旋 → 降落</t>
+        </is>
+      </c>
+      <c r="L41" s="22" t="inlineStr">
+        <is>
+          <t>絕滅危懼 IB 類（EN）｜天然紀念物・國內稀少種</t>
+        </is>
+      </c>
+      <c r="M41" s="22" t="inlineStr">
+        <is>
+          <t>待定（新物種）</t>
+        </is>
+      </c>
+      <c r="N41" s="31" t="n">
+        <v>6</v>
+      </c>
+      <c r="O41" s="22" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="P41" s="22" t="inlineStr">
+        <is>
+          <t>golden_eagle-2.png</t>
+        </is>
+      </c>
+      <c r="Q41" s="29" t="inlineStr">
+        <is>
+          <t>未開始</t>
+        </is>
+      </c>
+      <c r="R41" s="30" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="28" t="n">
+        <v>15</v>
+      </c>
+      <c r="B42" s="23" t="inlineStr">
+        <is>
+          <t>short_tailed_albatross</t>
+        </is>
+      </c>
+      <c r="C42" s="23" t="inlineStr">
+        <is>
+          <t>短尾信天翁</t>
+        </is>
+      </c>
+      <c r="D42" s="23" t="inlineStr">
+        <is>
+          <t>日本</t>
+        </is>
+      </c>
+      <c r="E42" s="23" t="inlineStr">
+        <is>
+          <t>海鳥</t>
+        </is>
+      </c>
+      <c r="F42" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="23" t="inlineStr">
+        <is>
+          <t>只有一種樣式</t>
+        </is>
+      </c>
+      <c r="H42" s="23" t="inlineStr">
+        <is>
+          <t>白色身體、頭頸黃色、粉紅色大嘴、長而窄的翅膀</t>
+        </is>
+      </c>
+      <c r="I42" s="23" t="inlineStr">
+        <is>
+          <t>海洋</t>
+        </is>
+      </c>
+      <c r="J42" s="23" t="inlineStr">
+        <is>
+          <t>白天</t>
+        </is>
+      </c>
+      <c r="K42" s="23" t="inlineStr">
+        <is>
+          <t>海面上空滑翔 → 降落（同猛禽盤旋）</t>
+        </is>
+      </c>
+      <c r="L42" s="23" t="inlineStr">
+        <is>
+          <t>絕滅危懼 II 類（VU）｜特別天然紀念物・國內稀少種</t>
+        </is>
+      </c>
+      <c r="M42" s="23" t="inlineStr">
+        <is>
+          <t>待定（新物種）</t>
+        </is>
+      </c>
+      <c r="N42" s="28" t="n">
+        <v>6</v>
+      </c>
+      <c r="O42" s="23" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="P42" s="23" t="inlineStr">
+        <is>
+          <t>short_tailed_albatross-2.png</t>
+        </is>
+      </c>
+      <c r="Q42" s="29" t="inlineStr">
+        <is>
+          <t>未開始</t>
+        </is>
+      </c>
+      <c r="R42" s="30" t="inlineStr">
+        <is>
+          <t>新增；鳥島、尖閣繁殖</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="31" t="n">
+        <v>16</v>
+      </c>
+      <c r="B43" s="22" t="inlineStr">
+        <is>
+          <t>giant_salamander</t>
+        </is>
+      </c>
+      <c r="C43" s="22" t="inlineStr">
+        <is>
+          <t>日本大山椒魚</t>
+        </is>
+      </c>
+      <c r="D43" s="22" t="inlineStr">
+        <is>
+          <t>日本</t>
+        </is>
+      </c>
+      <c r="E43" s="22" t="inlineStr">
+        <is>
+          <t>山椒魚</t>
+        </is>
+      </c>
+      <c r="F43" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" s="22" t="inlineStr">
+        <is>
+          <t>只有一種樣式</t>
+        </is>
+      </c>
+      <c r="H43" s="22" t="inlineStr">
+        <is>
+          <t>扁平的頭、小眼睛、褐色帶深色斑的皺褶皮膚、粗短四肢（可長到 1 公尺以上）</t>
+        </is>
+      </c>
+      <c r="I43" s="22" t="inlineStr">
+        <is>
+          <t>溪流</t>
+        </is>
+      </c>
+      <c r="J43" s="22" t="inlineStr">
+        <is>
+          <t>夜晚</t>
+        </is>
+      </c>
+      <c r="K43" s="22" t="inlineStr">
+        <is>
+          <t>夜裡在溪底慢慢爬近（新，程式待做）</t>
+        </is>
+      </c>
+      <c r="L43" s="22" t="inlineStr">
+        <is>
+          <t>絕滅危懼 II 類（VU）｜特別天然紀念物</t>
+        </is>
+      </c>
+      <c r="M43" s="22" t="inlineStr">
+        <is>
+          <t>待定（新物種）</t>
+        </is>
+      </c>
+      <c r="N43" s="31" t="n">
+        <v>6</v>
+      </c>
+      <c r="O43" s="22" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="P43" s="22" t="inlineStr">
+        <is>
+          <t>giant_salamander-2.png</t>
+        </is>
+      </c>
+      <c r="Q43" s="29" t="inlineStr">
+        <is>
+          <t>未開始</t>
+        </is>
+      </c>
+      <c r="R43" s="30" t="inlineStr">
+        <is>
+          <t>新增；世界最大的兩生類之一</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="28" t="n">
+        <v>17</v>
+      </c>
+      <c r="B44" s="23" t="inlineStr">
+        <is>
+          <t>ishikawa_frog</t>
+        </is>
+      </c>
+      <c r="C44" s="23" t="inlineStr">
+        <is>
+          <t>沖繩石川蛙</t>
+        </is>
+      </c>
+      <c r="D44" s="23" t="inlineStr">
+        <is>
+          <t>日本</t>
+        </is>
+      </c>
+      <c r="E44" s="23" t="inlineStr">
+        <is>
+          <t>蛙</t>
+        </is>
+      </c>
+      <c r="F44" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" s="23" t="inlineStr">
+        <is>
+          <t>只有一種樣式</t>
+        </is>
+      </c>
+      <c r="H44" s="23" t="inlineStr">
+        <is>
+          <t>綠底帶金色與黑色斑點的背部、指端吸盤（沖繩北部溪流）</t>
+        </is>
+      </c>
+      <c r="I44" s="23" t="inlineStr">
+        <is>
+          <t>南方島嶼</t>
+        </is>
+      </c>
+      <c r="J44" s="23" t="inlineStr">
+        <is>
+          <t>夜晚</t>
+        </is>
+      </c>
+      <c r="K44" s="23" t="inlineStr">
+        <is>
+          <t>夜裡先聽到叫聲、看到眼睛（同貓頭鷹）</t>
+        </is>
+      </c>
+      <c r="L44" s="23" t="inlineStr">
+        <is>
+          <t>絕滅危懼 IB 類（EN）｜國內稀少種（沖繩縣天然紀念物）</t>
+        </is>
+      </c>
+      <c r="M44" s="23" t="inlineStr">
+        <is>
+          <t>待定（新物種）</t>
+        </is>
+      </c>
+      <c r="N44" s="28" t="n">
+        <v>6</v>
+      </c>
+      <c r="O44" s="23" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="P44" s="23" t="inlineStr">
+        <is>
+          <t>ishikawa_frog-2.png</t>
+        </is>
+      </c>
+      <c r="Q44" s="29" t="inlineStr">
+        <is>
+          <t>未開始</t>
+        </is>
+      </c>
+      <c r="R44" s="30" t="inlineStr">
+        <is>
+          <t>新增；被稱為日本最美的蛙</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="31" t="n">
+        <v>18</v>
+      </c>
+      <c r="B45" s="22" t="inlineStr">
+        <is>
+          <t>loggerhead</t>
+        </is>
+      </c>
+      <c r="C45" s="22" t="inlineStr">
+        <is>
+          <t>赤蠵龜</t>
+        </is>
+      </c>
+      <c r="D45" s="22" t="inlineStr">
+        <is>
+          <t>日本</t>
+        </is>
+      </c>
+      <c r="E45" s="22" t="inlineStr">
+        <is>
+          <t>海龜</t>
+        </is>
+      </c>
+      <c r="F45" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" s="22" t="inlineStr">
+        <is>
+          <t>只有一種樣式</t>
+        </is>
+      </c>
+      <c r="H45" s="22" t="inlineStr">
+        <is>
+          <t>紅褐色心形背甲、大頭、鰭狀前肢</t>
+        </is>
+      </c>
+      <c r="I45" s="22" t="inlineStr">
+        <is>
+          <t>海洋</t>
+        </is>
+      </c>
+      <c r="J45" s="22" t="inlineStr">
+        <is>
+          <t>白天</t>
+        </is>
+      </c>
+      <c r="K45" s="22" t="inlineStr">
+        <is>
+          <t>浮出海面換氣，越游越近（新，程式待做）</t>
+        </is>
+      </c>
+      <c r="L45" s="22" t="inlineStr">
+        <is>
+          <t>絕滅危懼 IB 類（EN）</t>
+        </is>
+      </c>
+      <c r="M45" s="22" t="inlineStr">
+        <is>
+          <t>待定（新物種）</t>
+        </is>
+      </c>
+      <c r="N45" s="31" t="n">
+        <v>6</v>
+      </c>
+      <c r="O45" s="22" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="P45" s="22" t="inlineStr">
+        <is>
+          <t>loggerhead-2.png</t>
+        </is>
+      </c>
+      <c r="Q45" s="29" t="inlineStr">
+        <is>
+          <t>未開始</t>
+        </is>
+      </c>
+      <c r="R45" s="30" t="inlineStr">
+        <is>
+          <t>新增；日本是北太平洋主要產卵地</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="28" t="n">
+        <v>19</v>
+      </c>
+      <c r="B46" s="23" t="inlineStr">
+        <is>
+          <t>sakhalin_taimen</t>
+        </is>
+      </c>
+      <c r="C46" s="23" t="inlineStr">
+        <is>
+          <t>哲羅魚（伊富魚）</t>
+        </is>
+      </c>
+      <c r="D46" s="23" t="inlineStr">
+        <is>
+          <t>日本</t>
+        </is>
+      </c>
+      <c r="E46" s="23" t="inlineStr">
+        <is>
+          <t>魚</t>
+        </is>
+      </c>
+      <c r="F46" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" s="23" t="inlineStr">
+        <is>
+          <t>只有一種樣式</t>
+        </is>
+      </c>
+      <c r="H46" s="23" t="inlineStr">
+        <is>
+          <t>細長的銀褐色身體、扁平的大頭、體側小黑點，繁殖期偏紅</t>
+        </is>
+      </c>
+      <c r="I46" s="23" t="inlineStr">
+        <is>
+          <t>溪流水下</t>
+        </is>
+      </c>
+      <c r="J46" s="23" t="inlineStr">
+        <is>
+          <t>白天</t>
+        </is>
+      </c>
+      <c r="K46" s="23" t="inlineStr">
+        <is>
+          <t>水裡由遠游近（新出現方式，程式待做）</t>
+        </is>
+      </c>
+      <c r="L46" s="23" t="inlineStr">
+        <is>
+          <t>絕滅危懼 IB 類（EN）</t>
+        </is>
+      </c>
+      <c r="M46" s="23" t="inlineStr">
+        <is>
+          <t>待定（新物種）</t>
+        </is>
+      </c>
+      <c r="N46" s="28" t="n">
+        <v>6</v>
+      </c>
+      <c r="O46" s="23" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="P46" s="23" t="inlineStr">
+        <is>
+          <t>sakhalin_taimen-2.png</t>
+        </is>
+      </c>
+      <c r="Q46" s="29" t="inlineStr">
+        <is>
+          <t>未開始</t>
+        </is>
+      </c>
+      <c r="R46" s="30" t="inlineStr">
+        <is>
+          <t>新增；北海道「夢幻之魚」；紅色名錄 2020</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:R35"/>
+  <autoFilter ref="A4:R46"/>
   <mergeCells count="3">
     <mergeCell ref="A27:R27"/>
     <mergeCell ref="A2:R2"/>
@@ -6950,7 +7920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M35"/>
+  <dimension ref="A1:M46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -8260,7 +9230,7 @@
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="27" t="inlineStr">
         <is>
-          <t>日本（8 種）</t>
+          <t>日本（19 種）</t>
         </is>
       </c>
     </row>
@@ -8327,17 +9297,17 @@
       </c>
       <c r="B29" s="22" t="inlineStr">
         <is>
-          <t>okinawa_woodpecker</t>
+          <t>tsushima_cat</t>
         </is>
       </c>
       <c r="C29" s="22" t="inlineStr">
         <is>
-          <t>野口啄木鳥</t>
+          <t>對馬山貓</t>
         </is>
       </c>
       <c r="D29" s="22" t="inlineStr">
         <is>
-          <t>鳥</t>
+          <t>貓科</t>
         </is>
       </c>
       <c r="E29" s="31" t="n">
@@ -8345,17 +9315,17 @@
       </c>
       <c r="F29" s="22" t="inlineStr">
         <is>
-          <t>拿掉近側翅膀；拿掉頭；閉眼；拿掉近側腳；頭轉向鏡頭</t>
+          <t>E1 拿掉近側兩條腿；E3 拿掉頭；E4 拿掉兩隻耳朵；E5 閉眼；E7 頭轉向鏡頭</t>
         </is>
       </c>
       <c r="G29" s="22" t="inlineStr">
         <is>
-          <t>飛行姿勢 1 張</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H29" s="22" t="inlineStr">
         <is>
-          <t>待機、跳兩步、低頭啄、理羽毛、歪頭、眨眼、拍翅；另需「飛行姿勢」1 張</t>
+          <t>待機呼吸、張望、低頭聞、甩尾、耳朵抖、眨眼、張嘴、走路（定格每秒 8 格）</t>
         </is>
       </c>
       <c r="I29" s="22" t="inlineStr">
@@ -8384,25 +9354,25 @@
       </c>
       <c r="B30" s="23" t="inlineStr">
         <is>
-          <t>japanese_serow</t>
+          <t>amami_rabbit</t>
         </is>
       </c>
       <c r="C30" s="23" t="inlineStr">
         <is>
-          <t>日本鬣羚</t>
+          <t>奄美黑兔</t>
         </is>
       </c>
       <c r="D30" s="23" t="inlineStr">
         <is>
-          <t>山羊</t>
+          <t>兔</t>
         </is>
       </c>
       <c r="E30" s="28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F30" s="23" t="inlineStr">
         <is>
-          <t>同貓科＋拿掉鬃毛</t>
+          <t>同貓科</t>
         </is>
       </c>
       <c r="G30" s="23" t="inlineStr">
@@ -8412,7 +9382,7 @@
       </c>
       <c r="H30" s="23" t="inlineStr">
         <is>
-          <t>待機、張望、低頭吃草、甩耳、走路</t>
+          <t>待機、鼻子抽動、跳、低頭吃草、坐起張望</t>
         </is>
       </c>
       <c r="I30" s="23" t="inlineStr">
@@ -8421,11 +9391,11 @@
         </is>
       </c>
       <c r="J30" s="28" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K30" s="23" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="L30" s="29" t="inlineStr">
@@ -8441,17 +9411,17 @@
       </c>
       <c r="B31" s="22" t="inlineStr">
         <is>
-          <t>ptarmigan</t>
+          <t>japanese_serow</t>
         </is>
       </c>
       <c r="C31" s="22" t="inlineStr">
         <is>
-          <t>雷鳥</t>
+          <t>日本鬣羚</t>
         </is>
       </c>
       <c r="D31" s="22" t="inlineStr">
         <is>
-          <t>雉雞</t>
+          <t>山羊</t>
         </is>
       </c>
       <c r="E31" s="31" t="n">
@@ -8459,7 +9429,7 @@
       </c>
       <c r="F31" s="22" t="inlineStr">
         <is>
-          <t>同鳥</t>
+          <t>同貓科＋拿掉鬃毛</t>
         </is>
       </c>
       <c r="G31" s="22" t="inlineStr">
@@ -8469,7 +9439,7 @@
       </c>
       <c r="H31" s="22" t="inlineStr">
         <is>
-          <t>待機、走路、低頭啄、抬頭張望、眨眼</t>
+          <t>待機、張望、低頭吃草、甩耳、走路</t>
         </is>
       </c>
       <c r="I31" s="22" t="inlineStr">
@@ -8498,35 +9468,35 @@
       </c>
       <c r="B32" s="23" t="inlineStr">
         <is>
-          <t>blakiston_owl</t>
+          <t>bonin_flying_fox</t>
         </is>
       </c>
       <c r="C32" s="23" t="inlineStr">
         <is>
-          <t>毛腿魚鴞</t>
+          <t>小笠原狐蝠</t>
         </is>
       </c>
       <c r="D32" s="23" t="inlineStr">
         <is>
-          <t>貓頭鷹</t>
+          <t>蝙蝠</t>
         </is>
       </c>
       <c r="E32" s="28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F32" s="23" t="inlineStr">
         <is>
-          <t>拿掉頭；閉眼；拿掉耳羽；頭轉向鏡頭</t>
+          <t>頭轉向鏡頭（另畫倒掛、飛行姿勢）</t>
         </is>
       </c>
       <c r="G32" s="23" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>飛行（展翼）、倒掛各 1 張</t>
         </is>
       </c>
       <c r="H32" s="23" t="inlineStr">
         <is>
-          <t>待機、大角度轉頭、眨眼、縮成一團（發光眼睛由程式畫）</t>
+          <t>飛行拍翼、倒掛時收翼、轉頭</t>
         </is>
       </c>
       <c r="I32" s="23" t="inlineStr">
@@ -8535,11 +9505,11 @@
         </is>
       </c>
       <c r="J32" s="28" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K32" s="23" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="L32" s="29" t="inlineStr">
@@ -8555,35 +9525,35 @@
       </c>
       <c r="B33" s="22" t="inlineStr">
         <is>
-          <t>tsushima_cat</t>
+          <t>toki</t>
         </is>
       </c>
       <c r="C33" s="22" t="inlineStr">
         <is>
-          <t>對馬山貓</t>
+          <t>朱鷺</t>
         </is>
       </c>
       <c r="D33" s="22" t="inlineStr">
         <is>
-          <t>貓科</t>
+          <t>涉禽</t>
         </is>
       </c>
       <c r="E33" s="31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F33" s="22" t="inlineStr">
         <is>
-          <t>E1 拿掉近側兩條腿；E3 拿掉頭；E4 拿掉兩隻耳朵；E5 閉眼；E7 頭轉向鏡頭</t>
+          <t>同鳥</t>
         </is>
       </c>
       <c r="G33" s="22" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>飛行姿勢 1 張（選配）</t>
         </is>
       </c>
       <c r="H33" s="22" t="inlineStr">
         <is>
-          <t>待機呼吸、張望、低頭聞、甩尾、耳朵抖、眨眼、張嘴、走路（定格每秒 8 格）</t>
+          <t>待機、涉水走、低頭左右掃嘴覓食、理羽毛</t>
         </is>
       </c>
       <c r="I33" s="22" t="inlineStr">
@@ -8592,11 +9562,11 @@
         </is>
       </c>
       <c r="J33" s="31" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K33" s="22" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="L33" s="29" t="inlineStr">
@@ -8612,21 +9582,21 @@
       </c>
       <c r="B34" s="23" t="inlineStr">
         <is>
-          <t>steller_eagle</t>
+          <t>red_crowned_crane</t>
         </is>
       </c>
       <c r="C34" s="23" t="inlineStr">
         <is>
-          <t>虎頭海鵰</t>
+          <t>丹頂鶴</t>
         </is>
       </c>
       <c r="D34" s="23" t="inlineStr">
         <is>
-          <t>猛禽</t>
+          <t>涉禽</t>
         </is>
       </c>
       <c r="E34" s="28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F34" s="23" t="inlineStr">
         <is>
@@ -8635,12 +9605,12 @@
       </c>
       <c r="G34" s="23" t="inlineStr">
         <is>
-          <t>展翅盤旋 1 張</t>
+          <t>飛行姿勢 1 張（選配）</t>
         </is>
       </c>
       <c r="H34" s="23" t="inlineStr">
         <is>
-          <t>待機、張望、展翅；另需「飛行姿勢（展翅盤旋）」1 張</t>
+          <t>待機、涉水走、低頭左右掃嘴覓食、理羽毛</t>
         </is>
       </c>
       <c r="I34" s="23" t="inlineStr">
@@ -8649,11 +9619,11 @@
         </is>
       </c>
       <c r="J34" s="28" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K34" s="23" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="L34" s="29" t="inlineStr">
@@ -8669,59 +9639,686 @@
       </c>
       <c r="B35" s="22" t="inlineStr">
         <is>
-          <t>moon_bear</t>
+          <t>oriental_stork</t>
         </is>
       </c>
       <c r="C35" s="22" t="inlineStr">
         <is>
-          <t>月輪熊</t>
+          <t>東方白鸛</t>
         </is>
       </c>
       <c r="D35" s="22" t="inlineStr">
         <is>
-          <t>熊</t>
+          <t>涉禽</t>
         </is>
       </c>
       <c r="E35" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" s="22" t="inlineStr">
+        <is>
+          <t>同鳥</t>
+        </is>
+      </c>
+      <c r="G35" s="22" t="inlineStr">
+        <is>
+          <t>飛行姿勢 1 張（選配）</t>
+        </is>
+      </c>
+      <c r="H35" s="22" t="inlineStr">
+        <is>
+          <t>待機、涉水走、低頭左右掃嘴覓食、理羽毛</t>
+        </is>
+      </c>
+      <c r="I35" s="22" t="inlineStr">
+        <is>
+          <t>≤ 120 KB</t>
+        </is>
+      </c>
+      <c r="J35" s="31" t="n">
+        <v>6</v>
+      </c>
+      <c r="K35" s="22" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L35" s="29" t="inlineStr">
+        <is>
+          <t>未開始</t>
+        </is>
+      </c>
+      <c r="M35" s="30" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="28" t="n">
+        <v>9</v>
+      </c>
+      <c r="B36" s="23" t="inlineStr">
+        <is>
+          <t>okinawa_rail</t>
+        </is>
+      </c>
+      <c r="C36" s="23" t="inlineStr">
+        <is>
+          <t>山原秧雞</t>
+        </is>
+      </c>
+      <c r="D36" s="23" t="inlineStr">
+        <is>
+          <t>雉雞</t>
+        </is>
+      </c>
+      <c r="E36" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" s="23" t="inlineStr">
+        <is>
+          <t>同鳥</t>
+        </is>
+      </c>
+      <c r="G36" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H36" s="23" t="inlineStr">
+        <is>
+          <t>待機、走路、低頭啄、抬頭張望、眨眼</t>
+        </is>
+      </c>
+      <c r="I36" s="23" t="inlineStr">
+        <is>
+          <t>≤ 120 KB</t>
+        </is>
+      </c>
+      <c r="J36" s="28" t="n">
+        <v>6</v>
+      </c>
+      <c r="K36" s="23" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L36" s="29" t="inlineStr">
+        <is>
+          <t>未開始</t>
+        </is>
+      </c>
+      <c r="M36" s="30" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="31" t="n">
+        <v>10</v>
+      </c>
+      <c r="B37" s="22" t="inlineStr">
+        <is>
+          <t>okinawa_woodpecker</t>
+        </is>
+      </c>
+      <c r="C37" s="22" t="inlineStr">
+        <is>
+          <t>野口啄木鳥</t>
+        </is>
+      </c>
+      <c r="D37" s="22" t="inlineStr">
+        <is>
+          <t>鳥</t>
+        </is>
+      </c>
+      <c r="E37" s="31" t="n">
         <v>3</v>
       </c>
-      <c r="F35" s="22" t="inlineStr">
-        <is>
-          <t>同貓科</t>
-        </is>
-      </c>
-      <c r="G35" s="22" t="inlineStr">
+      <c r="F37" s="22" t="inlineStr">
+        <is>
+          <t>拿掉近側翅膀；拿掉頭；閉眼；拿掉近側腳；頭轉向鏡頭</t>
+        </is>
+      </c>
+      <c r="G37" s="22" t="inlineStr">
+        <is>
+          <t>飛行姿勢 1 張</t>
+        </is>
+      </c>
+      <c r="H37" s="22" t="inlineStr">
+        <is>
+          <t>待機、跳兩步、低頭啄、理羽毛、歪頭、眨眼、拍翅；另需「飛行姿勢」1 張</t>
+        </is>
+      </c>
+      <c r="I37" s="22" t="inlineStr">
+        <is>
+          <t>≤ 120 KB</t>
+        </is>
+      </c>
+      <c r="J37" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="K37" s="22" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="L37" s="29" t="inlineStr">
+        <is>
+          <t>未開始</t>
+        </is>
+      </c>
+      <c r="M37" s="30" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="28" t="n">
+        <v>11</v>
+      </c>
+      <c r="B38" s="23" t="inlineStr">
+        <is>
+          <t>ptarmigan</t>
+        </is>
+      </c>
+      <c r="C38" s="23" t="inlineStr">
+        <is>
+          <t>雷鳥</t>
+        </is>
+      </c>
+      <c r="D38" s="23" t="inlineStr">
+        <is>
+          <t>雉雞</t>
+        </is>
+      </c>
+      <c r="E38" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="F38" s="23" t="inlineStr">
+        <is>
+          <t>同鳥</t>
+        </is>
+      </c>
+      <c r="G38" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H35" s="22" t="inlineStr">
-        <is>
-          <t>待機、張望、低頭聞、坐下、走路</t>
-        </is>
-      </c>
-      <c r="I35" s="22" t="inlineStr">
+      <c r="H38" s="23" t="inlineStr">
+        <is>
+          <t>待機、走路、低頭啄、抬頭張望、眨眼</t>
+        </is>
+      </c>
+      <c r="I38" s="23" t="inlineStr">
         <is>
           <t>≤ 120 KB</t>
         </is>
       </c>
-      <c r="J35" s="31" t="n">
+      <c r="J38" s="28" t="n">
         <v>3</v>
       </c>
-      <c r="K35" s="22" t="inlineStr">
+      <c r="K38" s="23" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="L35" s="29" t="inlineStr">
+      <c r="L38" s="29" t="inlineStr">
         <is>
           <t>未開始</t>
         </is>
       </c>
-      <c r="M35" s="30" t="inlineStr"/>
+      <c r="M38" s="30" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="31" t="n">
+        <v>12</v>
+      </c>
+      <c r="B39" s="22" t="inlineStr">
+        <is>
+          <t>blakiston_owl</t>
+        </is>
+      </c>
+      <c r="C39" s="22" t="inlineStr">
+        <is>
+          <t>毛腿魚鴞</t>
+        </is>
+      </c>
+      <c r="D39" s="22" t="inlineStr">
+        <is>
+          <t>貓頭鷹</t>
+        </is>
+      </c>
+      <c r="E39" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="F39" s="22" t="inlineStr">
+        <is>
+          <t>拿掉頭；閉眼；拿掉耳羽；頭轉向鏡頭</t>
+        </is>
+      </c>
+      <c r="G39" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H39" s="22" t="inlineStr">
+        <is>
+          <t>待機、大角度轉頭、眨眼、縮成一團（發光眼睛由程式畫）</t>
+        </is>
+      </c>
+      <c r="I39" s="22" t="inlineStr">
+        <is>
+          <t>≤ 120 KB</t>
+        </is>
+      </c>
+      <c r="J39" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="K39" s="22" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="L39" s="29" t="inlineStr">
+        <is>
+          <t>未開始</t>
+        </is>
+      </c>
+      <c r="M39" s="30" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="28" t="n">
+        <v>13</v>
+      </c>
+      <c r="B40" s="23" t="inlineStr">
+        <is>
+          <t>steller_eagle</t>
+        </is>
+      </c>
+      <c r="C40" s="23" t="inlineStr">
+        <is>
+          <t>虎頭海鵰</t>
+        </is>
+      </c>
+      <c r="D40" s="23" t="inlineStr">
+        <is>
+          <t>猛禽</t>
+        </is>
+      </c>
+      <c r="E40" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="F40" s="23" t="inlineStr">
+        <is>
+          <t>同鳥</t>
+        </is>
+      </c>
+      <c r="G40" s="23" t="inlineStr">
+        <is>
+          <t>展翅盤旋 1 張</t>
+        </is>
+      </c>
+      <c r="H40" s="23" t="inlineStr">
+        <is>
+          <t>待機、張望、展翅；另需「飛行姿勢（展翅盤旋）」1 張</t>
+        </is>
+      </c>
+      <c r="I40" s="23" t="inlineStr">
+        <is>
+          <t>≤ 120 KB</t>
+        </is>
+      </c>
+      <c r="J40" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="K40" s="23" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="L40" s="29" t="inlineStr">
+        <is>
+          <t>未開始</t>
+        </is>
+      </c>
+      <c r="M40" s="30" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="31" t="n">
+        <v>14</v>
+      </c>
+      <c r="B41" s="22" t="inlineStr">
+        <is>
+          <t>golden_eagle</t>
+        </is>
+      </c>
+      <c r="C41" s="22" t="inlineStr">
+        <is>
+          <t>金鵰</t>
+        </is>
+      </c>
+      <c r="D41" s="22" t="inlineStr">
+        <is>
+          <t>猛禽</t>
+        </is>
+      </c>
+      <c r="E41" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" s="22" t="inlineStr">
+        <is>
+          <t>同鳥</t>
+        </is>
+      </c>
+      <c r="G41" s="22" t="inlineStr">
+        <is>
+          <t>展翅盤旋 1 張</t>
+        </is>
+      </c>
+      <c r="H41" s="22" t="inlineStr">
+        <is>
+          <t>待機、張望、展翅；另需「飛行姿勢（展翅盤旋）」1 張</t>
+        </is>
+      </c>
+      <c r="I41" s="22" t="inlineStr">
+        <is>
+          <t>≤ 120 KB</t>
+        </is>
+      </c>
+      <c r="J41" s="31" t="n">
+        <v>6</v>
+      </c>
+      <c r="K41" s="22" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L41" s="29" t="inlineStr">
+        <is>
+          <t>未開始</t>
+        </is>
+      </c>
+      <c r="M41" s="30" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="28" t="n">
+        <v>15</v>
+      </c>
+      <c r="B42" s="23" t="inlineStr">
+        <is>
+          <t>short_tailed_albatross</t>
+        </is>
+      </c>
+      <c r="C42" s="23" t="inlineStr">
+        <is>
+          <t>短尾信天翁</t>
+        </is>
+      </c>
+      <c r="D42" s="23" t="inlineStr">
+        <is>
+          <t>海鳥</t>
+        </is>
+      </c>
+      <c r="E42" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" s="23" t="inlineStr">
+        <is>
+          <t>同鳥</t>
+        </is>
+      </c>
+      <c r="G42" s="23" t="inlineStr">
+        <is>
+          <t>展翅滑翔 1 張</t>
+        </is>
+      </c>
+      <c r="H42" s="23" t="inlineStr">
+        <is>
+          <t>待機、張望、滑翔、互相碰嘴；另需「展翅滑翔」1 張</t>
+        </is>
+      </c>
+      <c r="I42" s="23" t="inlineStr">
+        <is>
+          <t>≤ 120 KB</t>
+        </is>
+      </c>
+      <c r="J42" s="28" t="n">
+        <v>6</v>
+      </c>
+      <c r="K42" s="23" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L42" s="29" t="inlineStr">
+        <is>
+          <t>未開始</t>
+        </is>
+      </c>
+      <c r="M42" s="30" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="31" t="n">
+        <v>16</v>
+      </c>
+      <c r="B43" s="22" t="inlineStr">
+        <is>
+          <t>giant_salamander</t>
+        </is>
+      </c>
+      <c r="C43" s="22" t="inlineStr">
+        <is>
+          <t>日本大山椒魚</t>
+        </is>
+      </c>
+      <c r="D43" s="22" t="inlineStr">
+        <is>
+          <t>山椒魚</t>
+        </is>
+      </c>
+      <c r="E43" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" s="22" t="inlineStr">
+        <is>
+          <t>拿掉近側兩條腿</t>
+        </is>
+      </c>
+      <c r="G43" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H43" s="22" t="inlineStr">
+        <is>
+          <t>待機、慢慢爬、張大嘴、尾巴擺動</t>
+        </is>
+      </c>
+      <c r="I43" s="22" t="inlineStr">
+        <is>
+          <t>≤ 120 KB</t>
+        </is>
+      </c>
+      <c r="J43" s="31" t="n">
+        <v>6</v>
+      </c>
+      <c r="K43" s="22" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L43" s="29" t="inlineStr">
+        <is>
+          <t>未開始</t>
+        </is>
+      </c>
+      <c r="M43" s="30" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="28" t="n">
+        <v>17</v>
+      </c>
+      <c r="B44" s="23" t="inlineStr">
+        <is>
+          <t>ishikawa_frog</t>
+        </is>
+      </c>
+      <c r="C44" s="23" t="inlineStr">
+        <is>
+          <t>沖繩石川蛙</t>
+        </is>
+      </c>
+      <c r="D44" s="23" t="inlineStr">
+        <is>
+          <t>蛙</t>
+        </is>
+      </c>
+      <c r="E44" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" s="23" t="inlineStr">
+        <is>
+          <t>拿掉近側後腳；閉眼；頭轉向鏡頭</t>
+        </is>
+      </c>
+      <c r="G44" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H44" s="23" t="inlineStr">
+        <is>
+          <t>待機、鼓鳴囊（叫）、跳、眨眼</t>
+        </is>
+      </c>
+      <c r="I44" s="23" t="inlineStr">
+        <is>
+          <t>≤ 120 KB</t>
+        </is>
+      </c>
+      <c r="J44" s="28" t="n">
+        <v>6</v>
+      </c>
+      <c r="K44" s="23" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L44" s="29" t="inlineStr">
+        <is>
+          <t>未開始</t>
+        </is>
+      </c>
+      <c r="M44" s="30" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="31" t="n">
+        <v>18</v>
+      </c>
+      <c r="B45" s="22" t="inlineStr">
+        <is>
+          <t>loggerhead</t>
+        </is>
+      </c>
+      <c r="C45" s="22" t="inlineStr">
+        <is>
+          <t>赤蠵龜</t>
+        </is>
+      </c>
+      <c r="D45" s="22" t="inlineStr">
+        <is>
+          <t>海龜</t>
+        </is>
+      </c>
+      <c r="E45" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" s="22" t="inlineStr">
+        <is>
+          <t>拿掉近側前鰭；頭轉向鏡頭</t>
+        </is>
+      </c>
+      <c r="G45" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H45" s="22" t="inlineStr">
+        <is>
+          <t>划水、浮上換氣、轉頭</t>
+        </is>
+      </c>
+      <c r="I45" s="22" t="inlineStr">
+        <is>
+          <t>≤ 120 KB</t>
+        </is>
+      </c>
+      <c r="J45" s="31" t="n">
+        <v>6</v>
+      </c>
+      <c r="K45" s="22" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L45" s="29" t="inlineStr">
+        <is>
+          <t>未開始</t>
+        </is>
+      </c>
+      <c r="M45" s="30" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="28" t="n">
+        <v>19</v>
+      </c>
+      <c r="B46" s="23" t="inlineStr">
+        <is>
+          <t>sakhalin_taimen</t>
+        </is>
+      </c>
+      <c r="C46" s="23" t="inlineStr">
+        <is>
+          <t>哲羅魚（伊富魚）</t>
+        </is>
+      </c>
+      <c r="D46" s="23" t="inlineStr">
+        <is>
+          <t>魚</t>
+        </is>
+      </c>
+      <c r="E46" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" s="23" t="inlineStr">
+        <is>
+          <t>拿掉胸鰭</t>
+        </is>
+      </c>
+      <c r="G46" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H46" s="23" t="inlineStr">
+        <is>
+          <t>游動擺尾、停在水中、轉向</t>
+        </is>
+      </c>
+      <c r="I46" s="23" t="inlineStr">
+        <is>
+          <t>≤ 120 KB</t>
+        </is>
+      </c>
+      <c r="J46" s="28" t="n">
+        <v>6</v>
+      </c>
+      <c r="K46" s="23" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="L46" s="29" t="inlineStr">
+        <is>
+          <t>未開始</t>
+        </is>
+      </c>
+      <c r="M46" s="30" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:M35"/>
+  <autoFilter ref="A4:M46"/>
   <mergeCells count="3">
     <mergeCell ref="A27:M27"/>
     <mergeCell ref="A2:M2"/>
@@ -8743,7 +10340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -8766,7 +10363,7 @@
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>29 隻動物只有 9 種體型，每種體型做 1 套骨架、權重規則與動作。貓科已用石虎驗證；其他體型以第一隻實作確認後再定案。</t>
+          <t>40 隻動物只有 20 種體型，每種體型做 1 套骨架、權重規則與動作。貓科已用石虎驗證；其他體型以第一隻實作確認後再定案。</t>
         </is>
       </c>
     </row>
@@ -8867,7 +10464,7 @@
       </c>
       <c r="C6" s="23" t="inlineStr">
         <is>
-          <t>台灣黑熊、月輪熊</t>
+          <t>台灣黑熊</t>
         </is>
       </c>
       <c r="D6" s="23" t="inlineStr">
@@ -9077,7 +10674,7 @@
       </c>
       <c r="C11" s="22" t="inlineStr">
         <is>
-          <t>帝雉、藍腹鷴、台灣山鷓鴣、雷鳥</t>
+          <t>帝雉、藍腹鷴、台灣山鷓鴣、雷鳥、山原秧雞</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -9119,7 +10716,7 @@
       </c>
       <c r="C12" s="23" t="inlineStr">
         <is>
-          <t>熊鷹、虎頭海鵰</t>
+          <t>熊鷹、虎頭海鵰、金鵰</t>
         </is>
       </c>
       <c r="D12" s="23" t="inlineStr">
@@ -9203,7 +10800,7 @@
       </c>
       <c r="C14" s="23" t="inlineStr">
         <is>
-          <t>黑面琵鷺</t>
+          <t>黑面琵鷺、朱鷺、丹頂鶴、東方白鸛</t>
         </is>
       </c>
       <c r="D14" s="23" t="inlineStr">
@@ -9287,7 +10884,7 @@
       </c>
       <c r="C16" s="23" t="inlineStr">
         <is>
-          <t>櫻花鉤吻鮭</t>
+          <t>櫻花鉤吻鮭、哲羅魚</t>
         </is>
       </c>
       <c r="D16" s="23" t="inlineStr">
@@ -9329,7 +10926,7 @@
       </c>
       <c r="C17" s="22" t="inlineStr">
         <is>
-          <t>綠蠵龜</t>
+          <t>綠蠵龜、赤蠵龜</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -9455,7 +11052,7 @@
       </c>
       <c r="C20" s="23" t="inlineStr">
         <is>
-          <t>諸羅樹蛙</t>
+          <t>諸羅樹蛙、沖繩石川蛙</t>
         </is>
       </c>
       <c r="D20" s="23" t="inlineStr">
@@ -9497,7 +11094,7 @@
       </c>
       <c r="C21" s="22" t="inlineStr">
         <is>
-          <t>台灣狐蝠</t>
+          <t>台灣狐蝠、小笠原狐蝠</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -9526,8 +11123,134 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="23" t="inlineStr">
+        <is>
+          <t>兔</t>
+        </is>
+      </c>
+      <c r="B22" s="23" t="inlineStr">
+        <is>
+          <t>rabbit</t>
+        </is>
+      </c>
+      <c r="C22" s="23" t="inlineStr">
+        <is>
+          <t>奄美黑兔</t>
+        </is>
+      </c>
+      <c r="D22" s="23" t="inlineStr">
+        <is>
+          <t>同貓科；耳朵短、後腳大</t>
+        </is>
+      </c>
+      <c r="E22" s="23" t="inlineStr">
+        <is>
+          <t>同貓科</t>
+        </is>
+      </c>
+      <c r="F22" s="23" t="inlineStr">
+        <is>
+          <t>同貓科，尾巴 1 根</t>
+        </is>
+      </c>
+      <c r="G22" s="23" t="inlineStr">
+        <is>
+          <t>待機、鼻子抽動、跳、低頭吃草、坐起張望</t>
+        </is>
+      </c>
+      <c r="H22" s="30" t="inlineStr">
+        <is>
+          <t>待第一隻實作確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="22" t="inlineStr">
+        <is>
+          <t>山椒魚</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>salamander</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>日本大山椒魚</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="inlineStr">
+        <is>
+          <t>頭、身體前段、身體後段、尾巴 2 節、四條腿</t>
+        </is>
+      </c>
+      <c r="E23" s="22" t="inlineStr">
+        <is>
+          <t>拿掉近側兩條腿</t>
+        </is>
+      </c>
+      <c r="F23" s="22" t="inlineStr">
+        <is>
+          <t>約 9 根：頭、身體 2 節、尾巴 2 節、四條腿</t>
+        </is>
+      </c>
+      <c r="G23" s="22" t="inlineStr">
+        <is>
+          <t>待機、慢慢爬、張大嘴、尾巴擺動</t>
+        </is>
+      </c>
+      <c r="H23" s="30" t="inlineStr">
+        <is>
+          <t>待第一隻實作確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="23" t="inlineStr">
+        <is>
+          <t>海鳥</t>
+        </is>
+      </c>
+      <c r="B24" s="23" t="inlineStr">
+        <is>
+          <t>seabird</t>
+        </is>
+      </c>
+      <c r="C24" s="23" t="inlineStr">
+        <is>
+          <t>短尾信天翁</t>
+        </is>
+      </c>
+      <c r="D24" s="23" t="inlineStr">
+        <is>
+          <t>同鳥；翅膀很長</t>
+        </is>
+      </c>
+      <c r="E24" s="23" t="inlineStr">
+        <is>
+          <t>同鳥</t>
+        </is>
+      </c>
+      <c r="F24" s="23" t="inlineStr">
+        <is>
+          <t>同鳥</t>
+        </is>
+      </c>
+      <c r="G24" s="23" t="inlineStr">
+        <is>
+          <t>待機、張望、滑翔、互相碰嘴；另需「展翅滑翔」1 張</t>
+        </is>
+      </c>
+      <c r="H24" s="30" t="inlineStr">
+        <is>
+          <t>待第一隻實作確認</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:H21"/>
+  <autoFilter ref="A4:H24"/>
   <mergeCells count="1">
     <mergeCell ref="A2:H2"/>
   </mergeCells>
@@ -9784,7 +11507,7 @@
       </c>
       <c r="E8" s="23" t="inlineStr">
         <is>
-          <t>黃魚鴞、歐亞水獺（金門）、毛腿魚鴞</t>
+          <t>黃魚鴞、歐亞水獺（金門）、毛腿魚鴞、日本大山椒魚</t>
         </is>
       </c>
       <c r="F8" s="23" t="inlineStr">
@@ -9828,7 +11551,7 @@
       </c>
       <c r="E9" s="22" t="inlineStr">
         <is>
-          <t>野口啄木鳥</t>
+          <t>山原秧雞、野口啄木鳥</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
@@ -9872,7 +11595,7 @@
       </c>
       <c r="E10" s="23" t="inlineStr">
         <is>
-          <t>台灣狐蝠、西表山貓</t>
+          <t>台灣狐蝠、西表山貓、奄美黑兔、小笠原狐蝠、沖繩石川蛙</t>
         </is>
       </c>
       <c r="F10" s="23" t="inlineStr">
@@ -9916,7 +11639,7 @@
       </c>
       <c r="E11" s="22" t="inlineStr">
         <is>
-          <t>台灣黑熊、帝雉、黃喉貂、熊鷹、黃山雀、寬尾鳳蝶、日本鬣羚、月輪熊</t>
+          <t>台灣黑熊、帝雉、黃喉貂、熊鷹、黃山雀、寬尾鳳蝶、日本鬣羚</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -9960,7 +11683,7 @@
       </c>
       <c r="E12" s="23" t="inlineStr">
         <is>
-          <t>雷鳥</t>
+          <t>雷鳥、金鵰</t>
         </is>
       </c>
       <c r="F12" s="23" t="inlineStr">
@@ -10048,7 +11771,7 @@
       </c>
       <c r="E14" s="23" t="inlineStr">
         <is>
-          <t>（之後新增的動物）</t>
+          <t>朱鷺、東方白鸛</t>
         </is>
       </c>
       <c r="F14" s="23" t="inlineStr">
@@ -10057,21 +11780,21 @@
         </is>
       </c>
       <c r="G14" s="28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H14" s="23" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="I14" s="34" t="inlineStr">
-        <is>
-          <t>選配</t>
+      <c r="I14" s="29" t="inlineStr">
+        <is>
+          <t>未開始</t>
         </is>
       </c>
       <c r="J14" s="30" t="inlineStr">
         <is>
-          <t>之後新增日本白天活動的動物時再畫</t>
+          <t>日本新增物種用（朱鷺、東方白鸛：水田、溪邊）</t>
         </is>
       </c>
     </row>
@@ -10096,7 +11819,7 @@
       </c>
       <c r="E15" s="22" t="inlineStr">
         <is>
-          <t>黑面琵鷺</t>
+          <t>黑面琵鷺、丹頂鶴</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -10119,7 +11842,7 @@
       </c>
       <c r="J15" s="30" t="inlineStr">
         <is>
-          <t>新增物種用（黑面琵鷺）</t>
+          <t>新增物種用（黑面琵鷺、丹頂鶴；丹頂鶴可加雪地版）</t>
         </is>
       </c>
     </row>
@@ -10144,7 +11867,7 @@
       </c>
       <c r="E16" s="23" t="inlineStr">
         <is>
-          <t>綠蠵龜、中華白海豚</t>
+          <t>綠蠵龜、中華白海豚、短尾信天翁、赤蠵龜</t>
         </is>
       </c>
       <c r="F16" s="23" t="inlineStr">
@@ -10167,7 +11890,7 @@
       </c>
       <c r="J16" s="30" t="inlineStr">
         <is>
-          <t>新增物種用；要看得到水下（綠蠵龜、中華白海豚）</t>
+          <t>新增物種用；要看得到水下（綠蠵龜、中華白海豚、赤蠵龜、短尾信天翁）</t>
         </is>
       </c>
     </row>
@@ -10192,7 +11915,7 @@
       </c>
       <c r="E17" s="22" t="inlineStr">
         <is>
-          <t>櫻花鉤吻鮭</t>
+          <t>櫻花鉤吻鮭、哲羅魚（伊富魚）</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -10215,7 +11938,7 @@
       </c>
       <c r="J17" s="30" t="inlineStr">
         <is>
-          <t>新增物種用（櫻花鉤吻鮭）</t>
+          <t>新增物種用（櫻花鉤吻鮭、哲羅魚）</t>
         </is>
       </c>
     </row>

--- a/docs/美術清單.xlsx
+++ b/docs/美術清單.xlsx
@@ -6324,7 +6324,7 @@
       </c>
       <c r="L28" s="23" t="inlineStr">
         <is>
-          <t>絕滅危懼 IA 類（CR）｜特別天然紀念物・國內稀少種</t>
+          <t>第一級・瀕臨絕種</t>
         </is>
       </c>
       <c r="M28" s="23" t="inlineStr">
@@ -6352,7 +6352,7 @@
       </c>
       <c r="R28" s="30" t="inlineStr">
         <is>
-          <t>紅色名錄 2020</t>
+          <t>絕滅危懼 IA 類（CR）｜特別天然紀念物・國內稀少種；紅色名錄 2020</t>
         </is>
       </c>
     </row>
@@ -6410,7 +6410,7 @@
       </c>
       <c r="L29" s="22" t="inlineStr">
         <is>
-          <t>絕滅危懼 IA 類（CR）｜天然紀念物・國內稀少種</t>
+          <t>第一級・瀕臨絕種</t>
         </is>
       </c>
       <c r="M29" s="22" t="inlineStr">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="R29" s="30" t="inlineStr">
         <is>
-          <t>紅色名錄 2020</t>
+          <t>絕滅危懼 IA 類（CR）｜天然紀念物・國內稀少種；紅色名錄 2020</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
       </c>
       <c r="L30" s="23" t="inlineStr">
         <is>
-          <t>絕滅危懼 IB 類（EN）｜特別天然紀念物・國內稀少種</t>
+          <t>第二級・珍貴稀有</t>
         </is>
       </c>
       <c r="M30" s="23" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="R30" s="30" t="inlineStr">
         <is>
-          <t>新增；紅色名錄 2020</t>
+          <t>絕滅危懼 IB 類（EN）｜特別天然紀念物・國內稀少種；新增；紅色名錄 2020</t>
         </is>
       </c>
     </row>
@@ -6582,7 +6582,7 @@
       </c>
       <c r="L31" s="22" t="inlineStr">
         <is>
-          <t>紅色名錄未列｜特別天然紀念物</t>
+          <t>第三級・其他應予保育</t>
         </is>
       </c>
       <c r="M31" s="22" t="inlineStr">
@@ -6610,7 +6610,7 @@
       </c>
       <c r="R31" s="30" t="inlineStr">
         <is>
-          <t>全國未列入紅色名錄，但是代表性的特別天然紀念物</t>
+          <t>紅色名錄未列｜特別天然紀念物；全國未列入紅色名錄，但是代表性的特別天然紀念物</t>
         </is>
       </c>
     </row>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="L32" s="23" t="inlineStr">
         <is>
-          <t>絕滅危懼 IA 類（CR）｜天然紀念物・國內稀少種</t>
+          <t>第一級・瀕臨絕種</t>
         </is>
       </c>
       <c r="M32" s="23" t="inlineStr">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="R32" s="30" t="inlineStr">
         <is>
-          <t>新增；紅色名錄 2020</t>
+          <t>絕滅危懼 IA 類（CR）｜天然紀念物・國內稀少種；新增；紅色名錄 2020</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="L33" s="22" t="inlineStr">
         <is>
-          <t>絕滅危懼 IB 類（EN）｜特別天然紀念物・國內稀少種</t>
+          <t>第二級・珍貴稀有</t>
         </is>
       </c>
       <c r="M33" s="22" t="inlineStr">
@@ -6782,7 +6782,7 @@
       </c>
       <c r="R33" s="30" t="inlineStr">
         <is>
-          <t>新增；第 5 次從 CR 降為 EN（佐渡野生約 576 隻）</t>
+          <t>絕滅危懼 IB 類（EN）｜特別天然紀念物・國內稀少種；新增；第 5 次從 CR 降為 EN（佐渡野生約 576 隻）</t>
         </is>
       </c>
     </row>
@@ -6840,7 +6840,7 @@
       </c>
       <c r="L34" s="23" t="inlineStr">
         <is>
-          <t>準絕滅危懼（NT）｜特別天然紀念物・國內稀少種</t>
+          <t>第三級・其他應予保育</t>
         </is>
       </c>
       <c r="M34" s="23" t="inlineStr">
@@ -6868,7 +6868,7 @@
       </c>
       <c r="R34" s="30" t="inlineStr">
         <is>
-          <t>新增；第 5 次從 VU 降為 NT（已不算瀕危）</t>
+          <t>準絕滅危懼（NT）｜特別天然紀念物・國內稀少種；新增；第 5 次從 VU 降為 NT（已不算瀕危）</t>
         </is>
       </c>
     </row>
@@ -6926,7 +6926,7 @@
       </c>
       <c r="L35" s="22" t="inlineStr">
         <is>
-          <t>絕滅危懼 IB 類（EN）｜特別天然紀念物・國內稀少種</t>
+          <t>第二級・珍貴稀有</t>
         </is>
       </c>
       <c r="M35" s="22" t="inlineStr">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="R35" s="30" t="inlineStr">
         <is>
-          <t>新增；第 5 次從 CR 降為 EN</t>
+          <t>絕滅危懼 IB 類（EN）｜特別天然紀念物・國內稀少種；新增；第 5 次從 CR 降為 EN</t>
         </is>
       </c>
     </row>
@@ -7012,7 +7012,7 @@
       </c>
       <c r="L36" s="23" t="inlineStr">
         <is>
-          <t>絕滅危懼 IA 類（CR）｜天然紀念物・國內稀少種</t>
+          <t>第一級・瀕臨絕種</t>
         </is>
       </c>
       <c r="M36" s="23" t="inlineStr">
@@ -7040,7 +7040,7 @@
       </c>
       <c r="R36" s="30" t="inlineStr">
         <is>
-          <t>新增；沖繩北部特有、不會飛</t>
+          <t>絕滅危懼 IA 類（CR）｜天然紀念物・國內稀少種；新增；沖繩北部特有、不會飛</t>
         </is>
       </c>
     </row>
@@ -7098,7 +7098,7 @@
       </c>
       <c r="L37" s="22" t="inlineStr">
         <is>
-          <t>絕滅危懼 IB 類（EN）｜特別天然紀念物・國內稀少種</t>
+          <t>第二級・珍貴稀有</t>
         </is>
       </c>
       <c r="M37" s="22" t="inlineStr">
@@ -7126,7 +7126,7 @@
       </c>
       <c r="R37" s="30" t="inlineStr">
         <is>
-          <t>第 5 次從 CR 降為 EN</t>
+          <t>絕滅危懼 IB 類（EN）｜特別天然紀念物・國內稀少種；第 5 次從 CR 降為 EN</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
       </c>
       <c r="L38" s="23" t="inlineStr">
         <is>
-          <t>絕滅危懼 IB 類（EN）｜特別天然紀念物・國內稀少種</t>
+          <t>第二級・珍貴稀有</t>
         </is>
       </c>
       <c r="M38" s="23" t="inlineStr">
@@ -7210,7 +7210,11 @@
           <t>未開始</t>
         </is>
       </c>
-      <c r="R38" s="30" t="inlineStr"/>
+      <c r="R38" s="30" t="inlineStr">
+        <is>
+          <t>絕滅危懼 IB 類（EN）｜特別天然紀念物・國內稀少種</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="31" t="n">
@@ -7266,7 +7270,7 @@
       </c>
       <c r="L39" s="22" t="inlineStr">
         <is>
-          <t>絕滅危懼 IB 類（EN）｜天然紀念物・國內稀少種</t>
+          <t>第二級・珍貴稀有</t>
         </is>
       </c>
       <c r="M39" s="22" t="inlineStr">
@@ -7294,7 +7298,7 @@
       </c>
       <c r="R39" s="30" t="inlineStr">
         <is>
-          <t>第 5 次從 CR 降為 EN</t>
+          <t>絕滅危懼 IB 類（EN）｜天然紀念物・國內稀少種；第 5 次從 CR 降為 EN</t>
         </is>
       </c>
     </row>
@@ -7352,7 +7356,7 @@
       </c>
       <c r="L40" s="23" t="inlineStr">
         <is>
-          <t>絕滅危懼 II 類（VU）｜天然紀念物・國內稀少種</t>
+          <t>第三級・其他應予保育</t>
         </is>
       </c>
       <c r="M40" s="23" t="inlineStr">
@@ -7378,7 +7382,11 @@
           <t>未開始</t>
         </is>
       </c>
-      <c r="R40" s="30" t="inlineStr"/>
+      <c r="R40" s="30" t="inlineStr">
+        <is>
+          <t>絕滅危懼 II 類（VU）｜天然紀念物・國內稀少種</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="31" t="n">
@@ -7434,7 +7442,7 @@
       </c>
       <c r="L41" s="22" t="inlineStr">
         <is>
-          <t>絕滅危懼 IB 類（EN）｜天然紀念物・國內稀少種</t>
+          <t>第二級・珍貴稀有</t>
         </is>
       </c>
       <c r="M41" s="22" t="inlineStr">
@@ -7462,7 +7470,7 @@
       </c>
       <c r="R41" s="30" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>絕滅危懼 IB 類（EN）｜天然紀念物・國內稀少種；新增</t>
         </is>
       </c>
     </row>
@@ -7520,7 +7528,7 @@
       </c>
       <c r="L42" s="23" t="inlineStr">
         <is>
-          <t>絕滅危懼 II 類（VU）｜特別天然紀念物・國內稀少種</t>
+          <t>第三級・其他應予保育</t>
         </is>
       </c>
       <c r="M42" s="23" t="inlineStr">
@@ -7548,7 +7556,7 @@
       </c>
       <c r="R42" s="30" t="inlineStr">
         <is>
-          <t>新增；鳥島、尖閣繁殖</t>
+          <t>絕滅危懼 II 類（VU）｜特別天然紀念物・國內稀少種；新增；鳥島、尖閣繁殖</t>
         </is>
       </c>
     </row>
@@ -7606,7 +7614,7 @@
       </c>
       <c r="L43" s="22" t="inlineStr">
         <is>
-          <t>絕滅危懼 II 類（VU）｜特別天然紀念物</t>
+          <t>第三級・其他應予保育</t>
         </is>
       </c>
       <c r="M43" s="22" t="inlineStr">
@@ -7634,7 +7642,7 @@
       </c>
       <c r="R43" s="30" t="inlineStr">
         <is>
-          <t>新增；世界最大的兩生類之一</t>
+          <t>絕滅危懼 II 類（VU）｜特別天然紀念物；新增；世界最大的兩生類之一</t>
         </is>
       </c>
     </row>
@@ -7692,7 +7700,7 @@
       </c>
       <c r="L44" s="23" t="inlineStr">
         <is>
-          <t>絕滅危懼 IB 類（EN）｜國內稀少種（沖繩縣天然紀念物）</t>
+          <t>第二級・珍貴稀有</t>
         </is>
       </c>
       <c r="M44" s="23" t="inlineStr">
@@ -7720,7 +7728,7 @@
       </c>
       <c r="R44" s="30" t="inlineStr">
         <is>
-          <t>新增；被稱為日本最美的蛙</t>
+          <t>絕滅危懼 IB 類（EN）｜國內稀少種（沖繩縣天然紀念物）；新增；被稱為日本最美的蛙</t>
         </is>
       </c>
     </row>
@@ -7778,7 +7786,7 @@
       </c>
       <c r="L45" s="22" t="inlineStr">
         <is>
-          <t>絕滅危懼 IB 類（EN）</t>
+          <t>第二級・珍貴稀有</t>
         </is>
       </c>
       <c r="M45" s="22" t="inlineStr">
@@ -7806,7 +7814,7 @@
       </c>
       <c r="R45" s="30" t="inlineStr">
         <is>
-          <t>新增；日本是北太平洋主要產卵地</t>
+          <t>絕滅危懼 IB 類（EN）；新增；日本是北太平洋主要產卵地</t>
         </is>
       </c>
     </row>
@@ -7864,7 +7872,7 @@
       </c>
       <c r="L46" s="23" t="inlineStr">
         <is>
-          <t>絕滅危懼 IB 類（EN）</t>
+          <t>第二級・珍貴稀有</t>
         </is>
       </c>
       <c r="M46" s="23" t="inlineStr">
@@ -7892,7 +7900,7 @@
       </c>
       <c r="R46" s="30" t="inlineStr">
         <is>
-          <t>新增；北海道「夢幻之魚」；紅色名錄 2020</t>
+          <t>絕滅危懼 IB 類（EN）；新增；北海道「夢幻之魚」；紅色名錄 2020</t>
         </is>
       </c>
     </row>
